--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Scenario summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Scenario summary (LNG)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Scenario summary (PRODUCT)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Pair trades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Scenario summary (DRY_BULK)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pair trades" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -525,28 +526,28 @@
         <v>44</v>
       </c>
       <c r="E2" t="n">
-        <v>81.38</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>66.98</v>
+        <v>61.65</v>
       </c>
       <c r="G2" t="n">
-        <v>43.32</v>
+        <v>38.67</v>
       </c>
       <c r="H2" t="n">
-        <v>38.1</v>
+        <v>34.68</v>
       </c>
       <c r="I2" t="n">
-        <v>49.37</v>
+        <v>57.61</v>
       </c>
       <c r="J2" t="n">
-        <v>85</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>-13.4</v>
+        <v>-21.2</v>
       </c>
       <c r="L2" t="n">
-        <v>12.2</v>
+        <v>30.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -574,28 +575,28 @@
         <v>70.8</v>
       </c>
       <c r="E3" t="n">
-        <v>92.19</v>
+        <v>85.73</v>
       </c>
       <c r="F3" t="n">
-        <v>81.22</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>64.97</v>
+        <v>61.24</v>
       </c>
       <c r="H3" t="n">
-        <v>61.68</v>
+        <v>59.6</v>
       </c>
       <c r="I3" t="n">
-        <v>69.31</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>30.2</v>
+        <v>21.1</v>
       </c>
       <c r="K3" t="n">
-        <v>-12.9</v>
+        <v>-15.8</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.1</v>
+        <v>4.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -623,28 +624,28 @@
         <v>16.4</v>
       </c>
       <c r="E4" t="n">
-        <v>22.36</v>
+        <v>19.63</v>
       </c>
       <c r="F4" t="n">
-        <v>18.35</v>
+        <v>16.23</v>
       </c>
       <c r="G4" t="n">
-        <v>11.51</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>10.37</v>
+        <v>9.07</v>
       </c>
       <c r="I4" t="n">
-        <v>13.34</v>
+        <v>15.08</v>
       </c>
       <c r="J4" t="n">
-        <v>36.3</v>
+        <v>19.7</v>
       </c>
       <c r="K4" t="n">
-        <v>-36.7</v>
+        <v>-44.7</v>
       </c>
       <c r="L4" t="n">
-        <v>-18.7</v>
+        <v>-8.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -672,28 +673,28 @@
         <v>34.5</v>
       </c>
       <c r="E5" t="n">
-        <v>46.11</v>
+        <v>40.77</v>
       </c>
       <c r="F5" t="n">
-        <v>36.64</v>
+        <v>32.42</v>
       </c>
       <c r="G5" t="n">
-        <v>19.29</v>
+        <v>16.09</v>
       </c>
       <c r="H5" t="n">
-        <v>16.48</v>
+        <v>13.98</v>
       </c>
       <c r="I5" t="n">
-        <v>23.87</v>
+        <v>29.36</v>
       </c>
       <c r="J5" t="n">
-        <v>33.7</v>
+        <v>18.2</v>
       </c>
       <c r="K5" t="n">
-        <v>-52.2</v>
+        <v>-59.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-30.8</v>
+        <v>-14.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -721,28 +722,28 @@
         <v>47.7</v>
       </c>
       <c r="E6" t="n">
-        <v>61.59</v>
+        <v>54.21</v>
       </c>
       <c r="F6" t="n">
-        <v>49.1</v>
+        <v>43.17</v>
       </c>
       <c r="G6" t="n">
-        <v>26.56</v>
+        <v>22.15</v>
       </c>
       <c r="H6" t="n">
-        <v>22.9</v>
+        <v>19.62</v>
       </c>
       <c r="I6" t="n">
-        <v>32.53</v>
+        <v>39.32</v>
       </c>
       <c r="J6" t="n">
-        <v>29.1</v>
+        <v>13.6</v>
       </c>
       <c r="K6" t="n">
-        <v>-52</v>
+        <v>-58.9</v>
       </c>
       <c r="L6" t="n">
-        <v>-31.8</v>
+        <v>-17.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -770,28 +771,28 @@
         <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>80.33</v>
+        <v>74.14</v>
       </c>
       <c r="F7" t="n">
-        <v>69.11</v>
+        <v>64</v>
       </c>
       <c r="G7" t="n">
-        <v>46.7</v>
+        <v>42.12</v>
       </c>
       <c r="H7" t="n">
-        <v>41.31</v>
+        <v>38.18</v>
       </c>
       <c r="I7" t="n">
-        <v>52.08</v>
+        <v>59.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="K7" t="n">
-        <v>-47</v>
+        <v>-51.1</v>
       </c>
       <c r="L7" t="n">
-        <v>-33.2</v>
+        <v>-23.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -819,28 +820,28 @@
         <v>5.2</v>
       </c>
       <c r="E8" t="n">
-        <v>4.79</v>
+        <v>4.18</v>
       </c>
       <c r="F8" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="H8" t="n">
-        <v>1.54</v>
+        <v>1.2</v>
       </c>
       <c r="I8" t="n">
-        <v>2.28</v>
+        <v>2.87</v>
       </c>
       <c r="J8" t="n">
-        <v>-8</v>
+        <v>-19.6</v>
       </c>
       <c r="K8" t="n">
-        <v>-70.40000000000001</v>
+        <v>-77</v>
       </c>
       <c r="L8" t="n">
-        <v>-56.1</v>
+        <v>-44.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -994,19 +995,19 @@
         <v>9.59</v>
       </c>
       <c r="I2" t="n">
-        <v>1.05</v>
+        <v>-0.45</v>
       </c>
       <c r="J2" t="n">
-        <v>26.45</v>
+        <v>29.63</v>
       </c>
       <c r="K2" t="n">
         <v>121.5</v>
       </c>
       <c r="L2" t="n">
-        <v>-95.2</v>
+        <v>-102.1</v>
       </c>
       <c r="M2" t="n">
-        <v>20.8</v>
+        <v>35.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1014,7 +1015,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>47.47</v>
+        <v>48.97</v>
       </c>
       <c r="P2" t="n">
         <v>1.95</v>
@@ -1052,27 +1053,27 @@
         <v>19.03</v>
       </c>
       <c r="I3" t="n">
-        <v>14.58</v>
+        <v>13.81</v>
       </c>
       <c r="J3" t="n">
-        <v>28.04</v>
+        <v>29.73</v>
       </c>
       <c r="K3" t="n">
         <v>33.9</v>
       </c>
       <c r="L3" t="n">
-        <v>-50.9</v>
+        <v>-53.5</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.6</v>
+        <v>0.1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>25.18</v>
+        <v>25.95</v>
       </c>
       <c r="P3" t="n">
         <v>1.04</v>
@@ -1200,31 +1201,31 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>94.90000000000001</v>
+        <v>90.78</v>
       </c>
       <c r="F2" t="n">
-        <v>89.52</v>
+        <v>85.52</v>
       </c>
       <c r="G2" t="n">
-        <v>63.42</v>
+        <v>56.57</v>
       </c>
       <c r="H2" t="n">
-        <v>54.95</v>
+        <v>52.04</v>
       </c>
       <c r="I2" t="n">
-        <v>49.93</v>
+        <v>47.88</v>
       </c>
       <c r="J2" t="n">
-        <v>73.40000000000001</v>
+        <v>73.13</v>
       </c>
       <c r="K2" t="n">
-        <v>25.5</v>
+        <v>20.1</v>
       </c>
       <c r="L2" t="n">
-        <v>-34</v>
+        <v>-36.7</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9</v>
+        <v>-3.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1252,31 +1253,31 @@
         <v>28.2</v>
       </c>
       <c r="E3" t="n">
-        <v>40.58</v>
+        <v>39.1</v>
       </c>
       <c r="F3" t="n">
-        <v>34.18</v>
+        <v>32.74</v>
       </c>
       <c r="G3" t="n">
-        <v>19.33</v>
+        <v>16.68</v>
       </c>
       <c r="H3" t="n">
-        <v>15.07</v>
+        <v>13.84</v>
       </c>
       <c r="I3" t="n">
-        <v>11.69</v>
+        <v>10.86</v>
       </c>
       <c r="J3" t="n">
-        <v>25.59</v>
+        <v>26.68</v>
       </c>
       <c r="K3" t="n">
-        <v>43.9</v>
+        <v>38.7</v>
       </c>
       <c r="L3" t="n">
-        <v>-58.5</v>
+        <v>-61.5</v>
       </c>
       <c r="M3" t="n">
-        <v>-9.300000000000001</v>
+        <v>-5.4</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1304,31 +1305,31 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>18.08</v>
+        <v>18.05</v>
       </c>
       <c r="F4" t="n">
-        <v>15.94</v>
+        <v>15.92</v>
       </c>
       <c r="G4" t="n">
-        <v>13.57</v>
+        <v>13.54</v>
       </c>
       <c r="H4" t="n">
-        <v>11.33</v>
+        <v>11.31</v>
       </c>
       <c r="I4" t="n">
-        <v>9.43</v>
+        <v>9.41</v>
       </c>
       <c r="J4" t="n">
-        <v>14.5</v>
+        <v>15.05</v>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="L4" t="n">
-        <v>-41.1</v>
+        <v>-41.2</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.4</v>
+        <v>-5.9</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1356,31 +1357,31 @@
         <v>7.7</v>
       </c>
       <c r="E5" t="n">
-        <v>8.41</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>7.01</v>
+        <v>6.88</v>
       </c>
       <c r="G5" t="n">
-        <v>4.18</v>
+        <v>3.81</v>
       </c>
       <c r="H5" t="n">
-        <v>3.42</v>
+        <v>3.26</v>
       </c>
       <c r="I5" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="J5" t="n">
-        <v>5.41</v>
+        <v>5.77</v>
       </c>
       <c r="K5" t="n">
-        <v>9.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-64.40000000000001</v>
+        <v>-65.59999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-29.7</v>
+        <v>-25.1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1399,7 +1400,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>current_price</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>china_acceleration_FV</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>moderate_growth_FV</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>china_property_drag_FV</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>coordinated_slowdown_FV</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>probability_weighted_FV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>upside_pct</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>downside_pct</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>expected_value_pct</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>position_recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>dry_bulk</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="H2" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="I2" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-29.2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1454,13 +1600,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.8</v>
+        <v>35.3</v>
       </c>
       <c r="D2" t="n">
-        <v>-56.1</v>
+        <v>-44.8</v>
       </c>
       <c r="E2" t="n">
-        <v>76.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1480,13 +1626,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12.2</v>
+        <v>30.9</v>
       </c>
       <c r="D3" t="n">
-        <v>-56.1</v>
+        <v>-44.8</v>
       </c>
       <c r="E3" t="n">
-        <v>68.3</v>
+        <v>75.7</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1497,26 +1643,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-2.1</v>
+        <v>35.3</v>
       </c>
       <c r="D4" t="n">
-        <v>-56.1</v>
+        <v>-25.1</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>60.4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -1532,13 +1678,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.8</v>
+        <v>35.3</v>
       </c>
       <c r="D5" t="n">
-        <v>-33.2</v>
+        <v>-23.7</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1549,52 +1695,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-2.9</v>
+        <v>30.9</v>
       </c>
       <c r="D6" t="n">
-        <v>-56.1</v>
+        <v>-25.1</v>
       </c>
       <c r="E6" t="n">
-        <v>53.2</v>
+        <v>56.1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.8</v>
+        <v>30.9</v>
       </c>
       <c r="D7" t="n">
-        <v>-31.8</v>
+        <v>-23.7</v>
       </c>
       <c r="E7" t="n">
-        <v>52.6</v>
+        <v>54.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1606,17 +1752,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.8</v>
+        <v>35.3</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.8</v>
+        <v>-17.6</v>
       </c>
       <c r="E8" t="n">
-        <v>51.6</v>
+        <v>52.9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1627,22 +1773,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-5.6</v>
+        <v>35.3</v>
       </c>
       <c r="D9" t="n">
-        <v>-56.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E9" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1653,182 +1799,182 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.8</v>
+        <v>4.1</v>
       </c>
       <c r="D10" t="n">
-        <v>-29.7</v>
+        <v>-44.8</v>
       </c>
       <c r="E10" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-9.300000000000001</v>
+        <v>30.9</v>
       </c>
       <c r="D11" t="n">
-        <v>-56.1</v>
+        <v>-17.6</v>
       </c>
       <c r="E11" t="n">
-        <v>46.9</v>
+        <v>48.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-9.4</v>
+        <v>30.9</v>
       </c>
       <c r="D12" t="n">
-        <v>-56.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E12" t="n">
-        <v>46.8</v>
+        <v>45.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12.2</v>
+        <v>0.1</v>
       </c>
       <c r="D13" t="n">
-        <v>-33.2</v>
+        <v>-44.8</v>
       </c>
       <c r="E13" t="n">
-        <v>45.4</v>
+        <v>44.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12.2</v>
+        <v>35.3</v>
       </c>
       <c r="D14" t="n">
-        <v>-31.8</v>
+        <v>-8.1</v>
       </c>
       <c r="E14" t="n">
-        <v>44</v>
+        <v>43.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12.2</v>
+        <v>-3.3</v>
       </c>
       <c r="D15" t="n">
-        <v>-30.8</v>
+        <v>-44.8</v>
       </c>
       <c r="E15" t="n">
-        <v>43</v>
+        <v>41.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12.2</v>
+        <v>35.3</v>
       </c>
       <c r="D16" t="n">
-        <v>-29.7</v>
+        <v>-5.9</v>
       </c>
       <c r="E16" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -1840,151 +1986,151 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.8</v>
+        <v>35.3</v>
       </c>
       <c r="D17" t="n">
-        <v>-18.7</v>
+        <v>-5.7</v>
       </c>
       <c r="E17" t="n">
-        <v>39.5</v>
+        <v>41</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-18.7</v>
+        <v>35.3</v>
       </c>
       <c r="D18" t="n">
-        <v>-56.1</v>
+        <v>-5.4</v>
       </c>
       <c r="E18" t="n">
-        <v>37.4</v>
+        <v>40.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-2.1</v>
+        <v>-5.4</v>
       </c>
       <c r="D19" t="n">
-        <v>-33.2</v>
+        <v>-44.8</v>
       </c>
       <c r="E19" t="n">
-        <v>31.1</v>
+        <v>39.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12.2</v>
+        <v>-5.7</v>
       </c>
       <c r="D20" t="n">
-        <v>-18.7</v>
+        <v>-44.8</v>
       </c>
       <c r="E20" t="n">
-        <v>30.9</v>
+        <v>39.1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-2.9</v>
+        <v>30.9</v>
       </c>
       <c r="D21" t="n">
-        <v>-33.2</v>
+        <v>-8.1</v>
       </c>
       <c r="E21" t="n">
-        <v>30.3</v>
+        <v>39</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20.8</v>
+        <v>-5.9</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.4</v>
+        <v>-44.8</v>
       </c>
       <c r="E22" t="n">
-        <v>30.1</v>
+        <v>38.9</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -1996,17 +2142,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>20.8</v>
+        <v>35.3</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.300000000000001</v>
+        <v>-3.3</v>
       </c>
       <c r="E23" t="n">
-        <v>30</v>
+        <v>38.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2017,189 +2163,189 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-2.1</v>
+        <v>30.9</v>
       </c>
       <c r="D24" t="n">
-        <v>-31.8</v>
+        <v>-5.9</v>
       </c>
       <c r="E24" t="n">
-        <v>29.7</v>
+        <v>36.9</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-2.9</v>
+        <v>-8.1</v>
       </c>
       <c r="D25" t="n">
-        <v>-31.8</v>
+        <v>-44.8</v>
       </c>
       <c r="E25" t="n">
-        <v>28.9</v>
+        <v>36.8</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-2.1</v>
+        <v>30.9</v>
       </c>
       <c r="D26" t="n">
-        <v>-30.8</v>
+        <v>-5.7</v>
       </c>
       <c r="E26" t="n">
-        <v>28.7</v>
+        <v>36.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-2.9</v>
+        <v>30.9</v>
       </c>
       <c r="D27" t="n">
-        <v>-30.8</v>
+        <v>-5.4</v>
       </c>
       <c r="E27" t="n">
-        <v>27.9</v>
+        <v>36.3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>INSW (WHOLE-CO)</t>
-        </is>
-      </c>
       <c r="C28" t="n">
-        <v>-5.6</v>
+        <v>35.3</v>
       </c>
       <c r="D28" t="n">
-        <v>-33.2</v>
+        <v>0.1</v>
       </c>
       <c r="E28" t="n">
-        <v>27.7</v>
+        <v>35.2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-2.1</v>
+        <v>30.9</v>
       </c>
       <c r="D29" t="n">
-        <v>-29.7</v>
+        <v>-3.3</v>
       </c>
       <c r="E29" t="n">
-        <v>27.6</v>
+        <v>34.2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-2.9</v>
+        <v>35.3</v>
       </c>
       <c r="D30" t="n">
-        <v>-29.7</v>
+        <v>4.1</v>
       </c>
       <c r="E30" t="n">
-        <v>26.8</v>
+        <v>31.1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2208,24 +2354,24 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>20.8</v>
+        <v>30.9</v>
       </c>
       <c r="D31" t="n">
-        <v>-5.6</v>
+        <v>0.1</v>
       </c>
       <c r="E31" t="n">
-        <v>26.4</v>
+        <v>30.8</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2234,121 +2380,121 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-29.7</v>
+        <v>-14.9</v>
       </c>
       <c r="D32" t="n">
-        <v>-56.1</v>
+        <v>-44.8</v>
       </c>
       <c r="E32" t="n">
-        <v>26.4</v>
+        <v>29.9</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-5.6</v>
+        <v>4.1</v>
       </c>
       <c r="D33" t="n">
-        <v>-31.8</v>
+        <v>-25.1</v>
       </c>
       <c r="E33" t="n">
-        <v>26.2</v>
+        <v>29.3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-30.8</v>
+        <v>4.1</v>
       </c>
       <c r="D34" t="n">
-        <v>-56.1</v>
+        <v>-23.7</v>
       </c>
       <c r="E34" t="n">
-        <v>25.3</v>
+        <v>27.9</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-5.6</v>
+        <v>-17.6</v>
       </c>
       <c r="D35" t="n">
-        <v>-30.8</v>
+        <v>-44.8</v>
       </c>
       <c r="E35" t="n">
-        <v>25.2</v>
+        <v>27.2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-31.8</v>
+        <v>30.9</v>
       </c>
       <c r="D36" t="n">
-        <v>-56.1</v>
+        <v>4.1</v>
       </c>
       <c r="E36" t="n">
-        <v>24.3</v>
+        <v>26.8</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2364,13 +2510,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-5.6</v>
+        <v>0.1</v>
       </c>
       <c r="D37" t="n">
-        <v>-29.7</v>
+        <v>-25.1</v>
       </c>
       <c r="E37" t="n">
-        <v>24.2</v>
+        <v>25.2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2381,7 +2527,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2390,69 +2536,69 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-9.300000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="D38" t="n">
-        <v>-33.2</v>
+        <v>-23.7</v>
       </c>
       <c r="E38" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-9.4</v>
+        <v>-3.3</v>
       </c>
       <c r="D39" t="n">
-        <v>-33.2</v>
+        <v>-25.1</v>
       </c>
       <c r="E39" t="n">
-        <v>23.9</v>
+        <v>21.9</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>20.8</v>
+        <v>4.1</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.9</v>
+        <v>-17.6</v>
       </c>
       <c r="E40" t="n">
-        <v>23.7</v>
+        <v>21.7</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2468,13 +2614,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-33.2</v>
+        <v>-23.7</v>
       </c>
       <c r="D41" t="n">
-        <v>-56.1</v>
+        <v>-44.8</v>
       </c>
       <c r="E41" t="n">
-        <v>22.9</v>
+        <v>21.1</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2485,48 +2631,48 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>20.8</v>
+        <v>-3.3</v>
       </c>
       <c r="D42" t="n">
-        <v>-2.1</v>
+        <v>-23.7</v>
       </c>
       <c r="E42" t="n">
-        <v>22.9</v>
+        <v>20.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-9.300000000000001</v>
+        <v>-25.1</v>
       </c>
       <c r="D43" t="n">
-        <v>-31.8</v>
+        <v>-44.8</v>
       </c>
       <c r="E43" t="n">
-        <v>22.5</v>
+        <v>19.7</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2537,156 +2683,156 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-9.4</v>
+        <v>-5.4</v>
       </c>
       <c r="D44" t="n">
-        <v>-31.8</v>
+        <v>-25.1</v>
       </c>
       <c r="E44" t="n">
-        <v>22.4</v>
+        <v>19.7</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>12.2</v>
+        <v>-5.7</v>
       </c>
       <c r="D45" t="n">
-        <v>-9.4</v>
+        <v>-25.1</v>
       </c>
       <c r="E45" t="n">
-        <v>21.6</v>
+        <v>19.4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-9.300000000000001</v>
+        <v>-5.9</v>
       </c>
       <c r="D46" t="n">
-        <v>-30.8</v>
+        <v>-25.1</v>
       </c>
       <c r="E46" t="n">
-        <v>21.5</v>
+        <v>19.2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>12.2</v>
+        <v>4.1</v>
       </c>
       <c r="D47" t="n">
-        <v>-9.300000000000001</v>
+        <v>-14.9</v>
       </c>
       <c r="E47" t="n">
-        <v>21.5</v>
+        <v>19.1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-9.4</v>
+        <v>-5.4</v>
       </c>
       <c r="D48" t="n">
-        <v>-30.8</v>
+        <v>-23.7</v>
       </c>
       <c r="E48" t="n">
-        <v>21.4</v>
+        <v>18.3</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-9.300000000000001</v>
+        <v>-5.7</v>
       </c>
       <c r="D49" t="n">
-        <v>-29.7</v>
+        <v>-23.7</v>
       </c>
       <c r="E49" t="n">
-        <v>20.5</v>
+        <v>18</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2698,184 +2844,184 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-9.4</v>
+        <v>-5.9</v>
       </c>
       <c r="D50" t="n">
-        <v>-29.7</v>
+        <v>-23.7</v>
       </c>
       <c r="E50" t="n">
-        <v>20.4</v>
+        <v>17.8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>12.2</v>
+        <v>0.1</v>
       </c>
       <c r="D51" t="n">
-        <v>-5.6</v>
+        <v>-17.6</v>
       </c>
       <c r="E51" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-2.1</v>
+        <v>-8.1</v>
       </c>
       <c r="D52" t="n">
-        <v>-18.7</v>
+        <v>-25.1</v>
       </c>
       <c r="E52" t="n">
-        <v>16.6</v>
+        <v>17.1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-2.9</v>
+        <v>-8.1</v>
       </c>
       <c r="D53" t="n">
-        <v>-18.7</v>
+        <v>-23.7</v>
       </c>
       <c r="E53" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>12.2</v>
+        <v>0.1</v>
       </c>
       <c r="D54" t="n">
-        <v>-2.9</v>
+        <v>-14.9</v>
       </c>
       <c r="E54" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-18.7</v>
+        <v>-3.3</v>
       </c>
       <c r="D55" t="n">
-        <v>-33.2</v>
+        <v>-17.6</v>
       </c>
       <c r="E55" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C56" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E56" t="n">
         <v>12.2</v>
       </c>
-      <c r="D56" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="E56" t="n">
-        <v>14.3</v>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2884,50 +3030,50 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-18.7</v>
+        <v>-5.4</v>
       </c>
       <c r="D57" t="n">
-        <v>-31.8</v>
+        <v>-17.6</v>
       </c>
       <c r="E57" t="n">
-        <v>13.1</v>
+        <v>12.2</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-5.6</v>
+        <v>-5.7</v>
       </c>
       <c r="D58" t="n">
-        <v>-18.7</v>
+        <v>-17.6</v>
       </c>
       <c r="E58" t="n">
-        <v>13.1</v>
+        <v>11.8</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2936,121 +3082,121 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-18.7</v>
+        <v>-3.3</v>
       </c>
       <c r="D59" t="n">
-        <v>-30.8</v>
+        <v>-14.9</v>
       </c>
       <c r="E59" t="n">
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-18.7</v>
+        <v>-5.9</v>
       </c>
       <c r="D60" t="n">
-        <v>-29.7</v>
+        <v>-17.6</v>
       </c>
       <c r="E60" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-9.300000000000001</v>
+        <v>-14.9</v>
       </c>
       <c r="D61" t="n">
-        <v>-18.7</v>
+        <v>-25.1</v>
       </c>
       <c r="E61" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>ASC</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>DHT</t>
-        </is>
-      </c>
       <c r="C62" t="n">
-        <v>-9.4</v>
+        <v>4.1</v>
       </c>
       <c r="D62" t="n">
-        <v>-18.7</v>
+        <v>-5.9</v>
       </c>
       <c r="E62" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>20.8</v>
+        <v>4.1</v>
       </c>
       <c r="D63" t="n">
-        <v>12.2</v>
+        <v>-5.7</v>
       </c>
       <c r="E63" t="n">
-        <v>8.6</v>
+        <v>9.9</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -3062,17 +3208,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-2.1</v>
+        <v>4.1</v>
       </c>
       <c r="D64" t="n">
-        <v>-9.4</v>
+        <v>-5.4</v>
       </c>
       <c r="E64" t="n">
-        <v>7.3</v>
+        <v>9.6</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3083,390 +3229,728 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-2.1</v>
+        <v>-8.1</v>
       </c>
       <c r="D65" t="n">
-        <v>-9.300000000000001</v>
+        <v>-17.6</v>
       </c>
       <c r="E65" t="n">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-2.9</v>
+        <v>-5.4</v>
       </c>
       <c r="D66" t="n">
-        <v>-9.4</v>
+        <v>-14.9</v>
       </c>
       <c r="E66" t="n">
-        <v>6.4</v>
+        <v>9.5</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-2.9</v>
+        <v>-5.7</v>
       </c>
       <c r="D67" t="n">
-        <v>-9.300000000000001</v>
+        <v>-14.9</v>
       </c>
       <c r="E67" t="n">
-        <v>6.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-5.6</v>
+        <v>-5.9</v>
       </c>
       <c r="D68" t="n">
-        <v>-9.4</v>
+        <v>-14.9</v>
       </c>
       <c r="E68" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-5.6</v>
+        <v>-14.9</v>
       </c>
       <c r="D69" t="n">
-        <v>-9.300000000000001</v>
+        <v>-23.7</v>
       </c>
       <c r="E69" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-2.1</v>
+        <v>0.1</v>
       </c>
       <c r="D70" t="n">
-        <v>-5.6</v>
+        <v>-8.1</v>
       </c>
       <c r="E70" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>HAFN</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>INSW (WHOLE-CO)</t>
-        </is>
-      </c>
       <c r="C71" t="n">
-        <v>-29.7</v>
+        <v>-17.6</v>
       </c>
       <c r="D71" t="n">
-        <v>-33.2</v>
+        <v>-25.1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>STNG</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>FLNG</t>
-        </is>
-      </c>
       <c r="C72" t="n">
-        <v>-2.9</v>
+        <v>4.1</v>
       </c>
       <c r="D72" t="n">
-        <v>-5.6</v>
+        <v>-3.3</v>
       </c>
       <c r="E72" t="n">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs lng)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>FRO</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>INSW (WHOLE-CO)</t>
-        </is>
-      </c>
       <c r="C73" t="n">
-        <v>-30.8</v>
+        <v>-8.1</v>
       </c>
       <c r="D73" t="n">
-        <v>-33.2</v>
+        <v>-14.9</v>
       </c>
       <c r="E73" t="n">
-        <v>2.4</v>
+        <v>6.9</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-29.7</v>
+        <v>-17.6</v>
       </c>
       <c r="D74" t="n">
-        <v>-31.8</v>
+        <v>-23.7</v>
       </c>
       <c r="E74" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-31.8</v>
+        <v>0.1</v>
       </c>
       <c r="D75" t="n">
-        <v>-33.2</v>
+        <v>-5.9</v>
       </c>
       <c r="E75" t="n">
-        <v>1.4</v>
+        <v>6.1</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-29.7</v>
+        <v>0.1</v>
       </c>
       <c r="D76" t="n">
-        <v>-30.8</v>
+        <v>-5.7</v>
       </c>
       <c r="E76" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-30.8</v>
+        <v>0.1</v>
       </c>
       <c r="D77" t="n">
-        <v>-31.8</v>
+        <v>-5.4</v>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-2.1</v>
+        <v>-3.3</v>
       </c>
       <c r="D78" t="n">
-        <v>-2.9</v>
+        <v>-8.1</v>
       </c>
       <c r="E78" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TEN (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="D79" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E79" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>4</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs lng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="E81" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-17.6</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>TRMD</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>ASC</t>
         </is>
       </c>
-      <c r="C79" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="D79" t="n">
-        <v>-9.4</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F79" t="inlineStr">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>-23.7</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -1400,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1488,47 +1488,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>dry_bulk</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="H2" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="I2" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="J2" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-19</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>whole-company</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>dry_bulk</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>27.2</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>32.63</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>26.27</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>22.86</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H3" t="n">
         <v>19.27</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I3" t="n">
         <v>25.64</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J3" t="n">
         <v>20</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K3" t="n">
         <v>-29.2</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L3" t="n">
         <v>-5.7</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
@@ -1545,7 +1594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1773,78 +1822,78 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35.3</v>
+        <v>6.9</v>
       </c>
       <c r="D9" t="n">
-        <v>-14.9</v>
+        <v>-44.8</v>
       </c>
       <c r="E9" t="n">
-        <v>50.2</v>
+        <v>51.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.1</v>
+        <v>35.3</v>
       </c>
       <c r="D10" t="n">
-        <v>-44.8</v>
+        <v>-14.9</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>50.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30.9</v>
+        <v>4.1</v>
       </c>
       <c r="D11" t="n">
-        <v>-17.6</v>
+        <v>-44.8</v>
       </c>
       <c r="E11" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1856,17 +1905,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>30.9</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.9</v>
+        <v>-17.6</v>
       </c>
       <c r="E12" t="n">
-        <v>45.8</v>
+        <v>48.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1877,48 +1926,48 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1</v>
+        <v>30.9</v>
       </c>
       <c r="D13" t="n">
-        <v>-44.8</v>
+        <v>-14.9</v>
       </c>
       <c r="E13" t="n">
-        <v>44.9</v>
+        <v>45.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>35.3</v>
+        <v>0.1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.1</v>
+        <v>-44.8</v>
       </c>
       <c r="E14" t="n">
-        <v>43.4</v>
+        <v>44.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1929,52 +1978,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-3.3</v>
+        <v>35.3</v>
       </c>
       <c r="D15" t="n">
-        <v>-44.8</v>
+        <v>-8.1</v>
       </c>
       <c r="E15" t="n">
-        <v>41.5</v>
+        <v>43.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>35.3</v>
+        <v>-3.3</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.9</v>
+        <v>-44.8</v>
       </c>
       <c r="E16" t="n">
-        <v>41.2</v>
+        <v>41.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -1986,21 +2035,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>35.3</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.7</v>
+        <v>-5.9</v>
       </c>
       <c r="E17" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -2012,54 +2061,54 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>35.3</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.4</v>
+        <v>-5.7</v>
       </c>
       <c r="E18" t="n">
-        <v>40.7</v>
+        <v>41</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>TRMD</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C19" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="D19" t="n">
         <v>-5.4</v>
       </c>
-      <c r="D19" t="n">
-        <v>-44.8</v>
-      </c>
       <c r="E19" t="n">
-        <v>39.4</v>
+        <v>40.7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2068,173 +2117,173 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="D20" t="n">
         <v>-44.8</v>
       </c>
       <c r="E20" t="n">
-        <v>39.1</v>
+        <v>39.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.9</v>
+        <v>-5.7</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.1</v>
+        <v>-44.8</v>
       </c>
       <c r="E21" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-5.9</v>
+        <v>30.9</v>
       </c>
       <c r="D22" t="n">
-        <v>-44.8</v>
+        <v>-8.1</v>
       </c>
       <c r="E22" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35.3</v>
+        <v>-5.9</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3</v>
+        <v>-44.8</v>
       </c>
       <c r="E23" t="n">
-        <v>38.6</v>
+        <v>38.9</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>30.9</v>
+        <v>35.3</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9</v>
+        <v>-3.3</v>
       </c>
       <c r="E24" t="n">
-        <v>36.9</v>
+        <v>38.6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-8.1</v>
+        <v>30.9</v>
       </c>
       <c r="D25" t="n">
-        <v>-44.8</v>
+        <v>-5.9</v>
       </c>
       <c r="E25" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>30.9</v>
+        <v>-8.1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.7</v>
+        <v>-44.8</v>
       </c>
       <c r="E26" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2246,184 +2295,184 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>30.9</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.4</v>
+        <v>-5.7</v>
       </c>
       <c r="E27" t="n">
-        <v>36.3</v>
+        <v>36.7</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>35.3</v>
+        <v>30.9</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1</v>
+        <v>-5.4</v>
       </c>
       <c r="E28" t="n">
-        <v>35.2</v>
+        <v>36.3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>30.9</v>
+        <v>35.3</v>
       </c>
       <c r="D29" t="n">
-        <v>-3.3</v>
+        <v>0.1</v>
       </c>
       <c r="E29" t="n">
-        <v>34.2</v>
+        <v>35.2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>35.3</v>
+        <v>30.9</v>
       </c>
       <c r="D30" t="n">
-        <v>4.1</v>
+        <v>-3.3</v>
       </c>
       <c r="E30" t="n">
-        <v>31.1</v>
+        <v>34.2</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30.9</v>
+        <v>6.9</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1</v>
+        <v>-25.1</v>
       </c>
       <c r="E31" t="n">
-        <v>30.8</v>
+        <v>32</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-14.9</v>
+        <v>35.3</v>
       </c>
       <c r="D32" t="n">
-        <v>-44.8</v>
+        <v>4.1</v>
       </c>
       <c r="E32" t="n">
-        <v>29.9</v>
+        <v>31.1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4.1</v>
+        <v>30.9</v>
       </c>
       <c r="D33" t="n">
-        <v>-25.1</v>
+        <v>0.1</v>
       </c>
       <c r="E33" t="n">
-        <v>29.3</v>
+        <v>30.8</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2432,24 +2481,24 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
       <c r="D34" t="n">
         <v>-23.7</v>
       </c>
       <c r="E34" t="n">
-        <v>27.9</v>
+        <v>30.6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2458,13 +2507,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-17.6</v>
+        <v>-14.9</v>
       </c>
       <c r="D35" t="n">
         <v>-44.8</v>
       </c>
       <c r="E35" t="n">
-        <v>27.2</v>
+        <v>29.9</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2475,59 +2524,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>30.9</v>
+        <v>4.1</v>
       </c>
       <c r="D36" t="n">
-        <v>4.1</v>
+        <v>-25.1</v>
       </c>
       <c r="E36" t="n">
-        <v>26.8</v>
+        <v>29.3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.1</v>
+        <v>35.3</v>
       </c>
       <c r="D37" t="n">
-        <v>-25.1</v>
+        <v>6.9</v>
       </c>
       <c r="E37" t="n">
-        <v>25.2</v>
+        <v>28.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2536,39 +2585,39 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="D38" t="n">
         <v>-23.7</v>
       </c>
       <c r="E38" t="n">
-        <v>23.8</v>
+        <v>27.9</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-3.3</v>
+        <v>-17.6</v>
       </c>
       <c r="D39" t="n">
-        <v>-25.1</v>
+        <v>-44.8</v>
       </c>
       <c r="E39" t="n">
-        <v>21.9</v>
+        <v>27.2</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2579,137 +2628,137 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>TEN (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>TNK</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ECO</t>
-        </is>
-      </c>
       <c r="C40" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="D40" t="n">
         <v>4.1</v>
       </c>
-      <c r="D40" t="n">
-        <v>-17.6</v>
-      </c>
       <c r="E40" t="n">
-        <v>21.7</v>
+        <v>26.8</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-23.7</v>
+        <v>0.1</v>
       </c>
       <c r="D41" t="n">
-        <v>-44.8</v>
+        <v>-25.1</v>
       </c>
       <c r="E41" t="n">
-        <v>21.1</v>
+        <v>25.2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-3.3</v>
+        <v>6.9</v>
       </c>
       <c r="D42" t="n">
-        <v>-23.7</v>
+        <v>-17.6</v>
       </c>
       <c r="E42" t="n">
-        <v>20.5</v>
+        <v>24.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-25.1</v>
+        <v>30.9</v>
       </c>
       <c r="D43" t="n">
-        <v>-44.8</v>
+        <v>6.9</v>
       </c>
       <c r="E43" t="n">
-        <v>19.7</v>
+        <v>24</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-5.4</v>
+        <v>0.1</v>
       </c>
       <c r="D44" t="n">
-        <v>-25.1</v>
+        <v>-23.7</v>
       </c>
       <c r="E44" t="n">
-        <v>19.7</v>
+        <v>23.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2718,43 +2767,43 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-5.7</v>
+        <v>-3.3</v>
       </c>
       <c r="D45" t="n">
         <v>-25.1</v>
       </c>
       <c r="E45" t="n">
-        <v>19.4</v>
+        <v>21.9</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-5.9</v>
+        <v>6.9</v>
       </c>
       <c r="D46" t="n">
-        <v>-25.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E46" t="n">
-        <v>19.2</v>
+        <v>21.8</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -2766,17 +2815,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>4.1</v>
       </c>
       <c r="D47" t="n">
-        <v>-14.9</v>
+        <v>-17.6</v>
       </c>
       <c r="E47" t="n">
-        <v>19.1</v>
+        <v>21.7</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2787,33 +2836,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-5.4</v>
+        <v>-23.7</v>
       </c>
       <c r="D48" t="n">
-        <v>-23.7</v>
+        <v>-44.8</v>
       </c>
       <c r="E48" t="n">
-        <v>18.3</v>
+        <v>21.1</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2822,76 +2871,76 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-5.7</v>
+        <v>-3.3</v>
       </c>
       <c r="D49" t="n">
         <v>-23.7</v>
       </c>
       <c r="E49" t="n">
-        <v>18</v>
+        <v>20.5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-5.9</v>
+        <v>-25.1</v>
       </c>
       <c r="D50" t="n">
-        <v>-23.7</v>
+        <v>-44.8</v>
       </c>
       <c r="E50" t="n">
-        <v>17.8</v>
+        <v>19.7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.1</v>
+        <v>-5.4</v>
       </c>
       <c r="D51" t="n">
-        <v>-17.6</v>
+        <v>-25.1</v>
       </c>
       <c r="E51" t="n">
-        <v>17.7</v>
+        <v>19.7</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2900,50 +2949,50 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-8.1</v>
+        <v>-5.7</v>
       </c>
       <c r="D52" t="n">
         <v>-25.1</v>
       </c>
       <c r="E52" t="n">
-        <v>17.1</v>
+        <v>19.4</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-8.1</v>
+        <v>-5.9</v>
       </c>
       <c r="D53" t="n">
-        <v>-23.7</v>
+        <v>-25.1</v>
       </c>
       <c r="E53" t="n">
-        <v>15.7</v>
+        <v>19.2</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2952,102 +3001,102 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="D54" t="n">
         <v>-14.9</v>
       </c>
       <c r="E54" t="n">
-        <v>15</v>
+        <v>19.1</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-3.3</v>
+        <v>-5.4</v>
       </c>
       <c r="D55" t="n">
-        <v>-17.6</v>
+        <v>-23.7</v>
       </c>
       <c r="E55" t="n">
-        <v>14.3</v>
+        <v>18.3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4.1</v>
+        <v>-5.7</v>
       </c>
       <c r="D56" t="n">
-        <v>-8.1</v>
+        <v>-23.7</v>
       </c>
       <c r="E56" t="n">
-        <v>12.2</v>
+        <v>18</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-5.4</v>
+        <v>-5.9</v>
       </c>
       <c r="D57" t="n">
-        <v>-17.6</v>
+        <v>-23.7</v>
       </c>
       <c r="E57" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3056,195 +3105,195 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-5.7</v>
+        <v>0.1</v>
       </c>
       <c r="D58" t="n">
         <v>-17.6</v>
       </c>
       <c r="E58" t="n">
-        <v>11.8</v>
+        <v>17.7</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-3.3</v>
+        <v>-8.1</v>
       </c>
       <c r="D59" t="n">
-        <v>-14.9</v>
+        <v>-25.1</v>
       </c>
       <c r="E59" t="n">
-        <v>11.6</v>
+        <v>17.1</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-5.9</v>
+        <v>-8.1</v>
       </c>
       <c r="D60" t="n">
-        <v>-17.6</v>
+        <v>-23.7</v>
       </c>
       <c r="E60" t="n">
-        <v>11.6</v>
+        <v>15.7</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>FRO</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>HAFN</t>
-        </is>
-      </c>
       <c r="C61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D61" t="n">
         <v>-14.9</v>
       </c>
-      <c r="D61" t="n">
-        <v>-25.1</v>
-      </c>
       <c r="E61" t="n">
-        <v>10.2</v>
+        <v>15</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
       <c r="D62" t="n">
-        <v>-5.9</v>
+        <v>-8.1</v>
       </c>
       <c r="E62" t="n">
-        <v>10.1</v>
+        <v>15</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4.1</v>
+        <v>-3.3</v>
       </c>
       <c r="D63" t="n">
-        <v>-5.7</v>
+        <v>-17.6</v>
       </c>
       <c r="E63" t="n">
-        <v>9.9</v>
+        <v>14.3</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
       <c r="D64" t="n">
-        <v>-5.4</v>
+        <v>-5.9</v>
       </c>
       <c r="E64" t="n">
-        <v>9.6</v>
+        <v>12.8</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-8.1</v>
+        <v>6.9</v>
       </c>
       <c r="D65" t="n">
-        <v>-17.6</v>
+        <v>-5.7</v>
       </c>
       <c r="E65" t="n">
-        <v>9.5</v>
+        <v>12.6</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3255,74 +3304,74 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>TRMD</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>FRO</t>
-        </is>
-      </c>
       <c r="C66" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D66" t="n">
         <v>-5.4</v>
       </c>
-      <c r="D66" t="n">
-        <v>-14.9</v>
-      </c>
       <c r="E66" t="n">
-        <v>9.5</v>
+        <v>12.3</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-5.7</v>
+        <v>4.1</v>
       </c>
       <c r="D67" t="n">
-        <v>-14.9</v>
+        <v>-8.1</v>
       </c>
       <c r="E67" t="n">
-        <v>9.199999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-5.9</v>
+        <v>-5.4</v>
       </c>
       <c r="D68" t="n">
-        <v>-14.9</v>
+        <v>-17.6</v>
       </c>
       <c r="E68" t="n">
-        <v>9</v>
+        <v>12.2</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3333,100 +3382,100 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-14.9</v>
+        <v>-5.7</v>
       </c>
       <c r="D69" t="n">
-        <v>-23.7</v>
+        <v>-17.6</v>
       </c>
       <c r="E69" t="n">
-        <v>8.800000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.1</v>
+        <v>-3.3</v>
       </c>
       <c r="D70" t="n">
-        <v>-8.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E70" t="n">
-        <v>8.199999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>ECO</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>HAFN</t>
-        </is>
-      </c>
       <c r="C71" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="D71" t="n">
         <v>-17.6</v>
       </c>
-      <c r="D71" t="n">
-        <v>-25.1</v>
-      </c>
       <c r="E71" t="n">
-        <v>7.6</v>
+        <v>11.6</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4.1</v>
+        <v>-14.9</v>
       </c>
       <c r="D72" t="n">
-        <v>-3.3</v>
+        <v>-25.1</v>
       </c>
       <c r="E72" t="n">
-        <v>7.4</v>
+        <v>10.2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3437,152 +3486,152 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-8.1</v>
+        <v>6.9</v>
       </c>
       <c r="D73" t="n">
-        <v>-14.9</v>
+        <v>-3.3</v>
       </c>
       <c r="E73" t="n">
-        <v>6.9</v>
+        <v>10.2</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-17.6</v>
+        <v>4.1</v>
       </c>
       <c r="D74" t="n">
-        <v>-23.7</v>
+        <v>-5.9</v>
       </c>
       <c r="E74" t="n">
-        <v>6.2</v>
+        <v>10.1</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="D75" t="n">
-        <v>-5.9</v>
+        <v>-5.7</v>
       </c>
       <c r="E75" t="n">
-        <v>6.1</v>
+        <v>9.9</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="D76" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="E76" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.1</v>
+        <v>-8.1</v>
       </c>
       <c r="D77" t="n">
-        <v>-5.4</v>
+        <v>-17.6</v>
       </c>
       <c r="E77" t="n">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-3.3</v>
+        <v>-5.4</v>
       </c>
       <c r="D78" t="n">
-        <v>-8.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E78" t="n">
-        <v>4.8</v>
+        <v>9.5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3593,362 +3642,726 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>35.3</v>
+        <v>-5.7</v>
       </c>
       <c r="D79" t="n">
-        <v>30.9</v>
+        <v>-14.9</v>
       </c>
       <c r="E79" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4.1</v>
+        <v>-5.9</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E80" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.1</v>
+        <v>-14.9</v>
       </c>
       <c r="D81" t="n">
-        <v>-3.3</v>
+        <v>-23.7</v>
       </c>
       <c r="E81" t="n">
-        <v>3.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-14.9</v>
+        <v>0.1</v>
       </c>
       <c r="D82" t="n">
-        <v>-17.6</v>
+        <v>-8.1</v>
       </c>
       <c r="E82" t="n">
-        <v>2.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-3.3</v>
+        <v>-17.6</v>
       </c>
       <c r="D83" t="n">
-        <v>-5.9</v>
+        <v>-25.1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-5.4</v>
+        <v>4.1</v>
       </c>
       <c r="D84" t="n">
-        <v>-8.1</v>
+        <v>-3.3</v>
       </c>
       <c r="E84" t="n">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-3.3</v>
+        <v>-8.1</v>
       </c>
       <c r="D85" t="n">
-        <v>-5.7</v>
+        <v>-14.9</v>
       </c>
       <c r="E85" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-5.7</v>
+        <v>6.9</v>
       </c>
       <c r="D86" t="n">
-        <v>-8.1</v>
+        <v>0.1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-3.3</v>
+        <v>-17.6</v>
       </c>
       <c r="D87" t="n">
-        <v>-5.4</v>
+        <v>-23.7</v>
       </c>
       <c r="E87" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>ASC</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>DHT</t>
-        </is>
-      </c>
       <c r="C88" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D88" t="n">
         <v>-5.9</v>
       </c>
-      <c r="D88" t="n">
-        <v>-8.1</v>
-      </c>
       <c r="E88" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-23.7</v>
+        <v>0.1</v>
       </c>
       <c r="D89" t="n">
-        <v>-25.1</v>
+        <v>-5.7</v>
       </c>
       <c r="E89" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>TRMD</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>ASC</t>
-        </is>
-      </c>
       <c r="C90" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D90" t="n">
         <v>-5.4</v>
       </c>
-      <c r="D90" t="n">
-        <v>-5.9</v>
-      </c>
       <c r="E90" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-5.4</v>
+        <v>-3.3</v>
       </c>
       <c r="D91" t="n">
-        <v>-5.7</v>
+        <v>-8.1</v>
       </c>
       <c r="E91" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>TEN (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="D92" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E92" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>4</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs lng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-17.6</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D98" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="C99" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="E99" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>ASC</t>
         </is>
       </c>
-      <c r="C92" t="n">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>-23.7</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="D105" t="n">
         <v>-5.7</v>
       </c>
-      <c r="D92" t="n">
+      <c r="E105" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="D106" t="n">
         <v>-5.9</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E106" t="n">
         <v>0.2</v>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -526,7 +526,7 @@
         <v>44</v>
       </c>
       <c r="E2" t="n">
-        <v>74.98999999999999</v>
+        <v>75</v>
       </c>
       <c r="F2" t="n">
         <v>61.65</v>
@@ -575,25 +575,25 @@
         <v>70.8</v>
       </c>
       <c r="E3" t="n">
-        <v>85.73</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>75.84999999999999</v>
+        <v>75.81</v>
       </c>
       <c r="G3" t="n">
-        <v>61.24</v>
+        <v>61.21</v>
       </c>
       <c r="H3" t="n">
-        <v>59.6</v>
+        <v>59.57</v>
       </c>
       <c r="I3" t="n">
-        <v>73.73999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="J3" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.8</v>
+        <v>-15.9</v>
       </c>
       <c r="L3" t="n">
         <v>4.1</v>
@@ -673,13 +673,13 @@
         <v>34.5</v>
       </c>
       <c r="E5" t="n">
-        <v>40.77</v>
+        <v>40.78</v>
       </c>
       <c r="F5" t="n">
         <v>32.42</v>
       </c>
       <c r="G5" t="n">
-        <v>16.09</v>
+        <v>16.1</v>
       </c>
       <c r="H5" t="n">
         <v>13.98</v>
@@ -722,28 +722,28 @@
         <v>47.7</v>
       </c>
       <c r="E6" t="n">
-        <v>54.21</v>
+        <v>54.22</v>
       </c>
       <c r="F6" t="n">
-        <v>43.17</v>
+        <v>43.18</v>
       </c>
       <c r="G6" t="n">
-        <v>22.15</v>
+        <v>22.16</v>
       </c>
       <c r="H6" t="n">
-        <v>19.62</v>
+        <v>19.63</v>
       </c>
       <c r="I6" t="n">
-        <v>39.32</v>
+        <v>39.33</v>
       </c>
       <c r="J6" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="K6" t="n">
         <v>-58.9</v>
       </c>
       <c r="L6" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>74.14</v>
+        <v>74.11</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>63.97</v>
       </c>
       <c r="G7" t="n">
-        <v>42.12</v>
+        <v>42.1</v>
       </c>
       <c r="H7" t="n">
-        <v>38.18</v>
+        <v>38.16</v>
       </c>
       <c r="I7" t="n">
-        <v>59.5</v>
+        <v>59.47</v>
       </c>
       <c r="J7" t="n">
         <v>-5</v>
@@ -792,7 +792,7 @@
         <v>-51.1</v>
       </c>
       <c r="L7" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -820,28 +820,28 @@
         <v>5.2</v>
       </c>
       <c r="E8" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="G8" t="n">
         <v>1.34</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="I8" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="J8" t="n">
-        <v>-19.6</v>
+        <v>-19.8</v>
       </c>
       <c r="K8" t="n">
-        <v>-77</v>
+        <v>-77.09999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1652,10 +1652,10 @@
         <v>35.3</v>
       </c>
       <c r="D2" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E2" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         <v>30.9</v>
       </c>
       <c r="D3" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E3" t="n">
-        <v>75.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>35.3</v>
       </c>
       <c r="D5" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="E5" t="n">
         <v>59</v>
@@ -1782,7 +1782,7 @@
         <v>30.9</v>
       </c>
       <c r="D7" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="E7" t="n">
         <v>54.7</v>
@@ -1808,10 +1808,10 @@
         <v>35.3</v>
       </c>
       <c r="D8" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="E8" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1834,10 +1834,10 @@
         <v>6.9</v>
       </c>
       <c r="D9" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E9" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>4.1</v>
       </c>
       <c r="D11" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E11" t="n">
         <v>49</v>
@@ -1912,7 +1912,7 @@
         <v>30.9</v>
       </c>
       <c r="D12" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="E12" t="n">
         <v>48.5</v>
@@ -1964,10 +1964,10 @@
         <v>0.1</v>
       </c>
       <c r="D14" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E14" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
         <v>-3.3</v>
       </c>
       <c r="D16" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E16" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2120,10 +2120,10 @@
         <v>-5.4</v>
       </c>
       <c r="D20" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E20" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2146,10 +2146,10 @@
         <v>-5.7</v>
       </c>
       <c r="D21" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E21" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2160,52 +2160,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>30.9</v>
+        <v>-5.9</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.1</v>
+        <v>-44.9</v>
       </c>
       <c r="E22" t="n">
         <v>39</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-5.9</v>
+        <v>30.9</v>
       </c>
       <c r="D23" t="n">
-        <v>-44.8</v>
+        <v>-8.1</v>
       </c>
       <c r="E23" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2238,52 +2238,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>30.9</v>
+        <v>-8.1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.9</v>
+        <v>-44.9</v>
       </c>
       <c r="E25" t="n">
         <v>36.9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-8.1</v>
+        <v>30.9</v>
       </c>
       <c r="D26" t="n">
-        <v>-44.8</v>
+        <v>-5.9</v>
       </c>
       <c r="E26" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
         <v>4.1</v>
       </c>
       <c r="E32" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>6.9</v>
       </c>
       <c r="D34" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="E34" t="n">
         <v>30.6</v>
@@ -2510,10 +2510,10 @@
         <v>-14.9</v>
       </c>
       <c r="D35" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E35" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>-25.1</v>
       </c>
       <c r="E36" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>4.1</v>
       </c>
       <c r="D38" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="E38" t="n">
         <v>27.9</v>
@@ -2611,13 +2611,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="D39" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E39" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2692,10 +2692,10 @@
         <v>6.9</v>
       </c>
       <c r="D42" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="E42" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         <v>0.1</v>
       </c>
       <c r="D44" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="E44" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2822,10 +2822,10 @@
         <v>4.1</v>
       </c>
       <c r="D47" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="E47" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2845,13 +2845,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="D48" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E48" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>-3.3</v>
       </c>
       <c r="D49" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="E49" t="n">
         <v>20.5</v>
@@ -2900,10 +2900,10 @@
         <v>-25.1</v>
       </c>
       <c r="D50" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E50" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>-14.9</v>
       </c>
       <c r="E54" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>-5.4</v>
       </c>
       <c r="D55" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="E55" t="n">
         <v>18.3</v>
@@ -3056,7 +3056,7 @@
         <v>-5.7</v>
       </c>
       <c r="D56" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="E56" t="n">
         <v>18</v>
@@ -3082,7 +3082,7 @@
         <v>-5.9</v>
       </c>
       <c r="D57" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="E57" t="n">
         <v>17.8</v>
@@ -3108,10 +3108,10 @@
         <v>0.1</v>
       </c>
       <c r="D58" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="E58" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>-8.1</v>
       </c>
       <c r="D60" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="E60" t="n">
         <v>15.7</v>
@@ -3238,7 +3238,7 @@
         <v>-3.3</v>
       </c>
       <c r="D63" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="E63" t="n">
         <v>14.3</v>
@@ -3368,10 +3368,10 @@
         <v>-5.4</v>
       </c>
       <c r="D68" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="E68" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>-5.7</v>
       </c>
       <c r="D69" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="E69" t="n">
         <v>11.8</v>
@@ -3446,7 +3446,7 @@
         <v>-5.9</v>
       </c>
       <c r="D71" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="E71" t="n">
         <v>11.6</v>
@@ -3527,7 +3527,7 @@
         <v>-5.9</v>
       </c>
       <c r="E74" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>-5.7</v>
       </c>
       <c r="E75" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3564,52 +3564,52 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="D76" t="n">
-        <v>-5.4</v>
+        <v>-17.5</v>
       </c>
       <c r="E76" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-8.1</v>
+        <v>4.1</v>
       </c>
       <c r="D77" t="n">
-        <v>-17.6</v>
+        <v>-5.4</v>
       </c>
       <c r="E77" t="n">
         <v>9.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
         <v>-14.9</v>
       </c>
       <c r="D81" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="E81" t="n">
         <v>8.800000000000001</v>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="D83" t="n">
         <v>-25.1</v>
@@ -3813,7 +3813,7 @@
         <v>-14.9</v>
       </c>
       <c r="E85" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="D87" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="E87" t="n">
         <v>6.2</v>
@@ -4058,26 +4058,26 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-14.9</v>
+        <v>6.9</v>
       </c>
       <c r="D95" t="n">
-        <v>-17.6</v>
+        <v>4.1</v>
       </c>
       <c r="E95" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -4136,26 +4136,26 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6.9</v>
+        <v>-14.9</v>
       </c>
       <c r="D98" t="n">
-        <v>4.1</v>
+        <v>-17.5</v>
       </c>
       <c r="E98" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="D103" t="n">
         <v>-25.1</v>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -1505,28 +1505,28 @@
         <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>32.82</v>
+        <v>32.91</v>
       </c>
       <c r="F2" t="n">
-        <v>26.46</v>
+        <v>26.54</v>
       </c>
       <c r="G2" t="n">
-        <v>22.36</v>
+        <v>22.44</v>
       </c>
       <c r="H2" t="n">
-        <v>19.43</v>
+        <v>19.5</v>
       </c>
       <c r="I2" t="n">
-        <v>25.65</v>
+        <v>25.73</v>
       </c>
       <c r="J2" t="n">
-        <v>36.7</v>
+        <v>37.1</v>
       </c>
       <c r="K2" t="n">
-        <v>-19</v>
+        <v>-18.8</v>
       </c>
       <c r="L2" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1554,28 +1554,28 @@
         <v>27.2</v>
       </c>
       <c r="E3" t="n">
-        <v>32.63</v>
+        <v>32.72</v>
       </c>
       <c r="F3" t="n">
-        <v>26.27</v>
+        <v>26.35</v>
       </c>
       <c r="G3" t="n">
-        <v>22.86</v>
+        <v>22.94</v>
       </c>
       <c r="H3" t="n">
-        <v>19.27</v>
+        <v>19.34</v>
       </c>
       <c r="I3" t="n">
-        <v>25.64</v>
+        <v>25.72</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="K3" t="n">
-        <v>-29.2</v>
+        <v>-28.9</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1831,13 +1831,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="D9" t="n">
         <v>-44.9</v>
       </c>
       <c r="E9" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2061,21 +2061,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>35.3</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="E18" t="n">
-        <v>41</v>
+        <v>40.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="D21" t="n">
         <v>-44.9</v>
       </c>
       <c r="E21" t="n">
-        <v>39.2</v>
+        <v>39.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2302,10 +2302,10 @@
         <v>30.9</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="E27" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="D31" t="n">
         <v>-25.1</v>
       </c>
       <c r="E31" t="n">
-        <v>32</v>
+        <v>32.3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2446,52 +2446,52 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>30.9</v>
+        <v>7.2</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1</v>
+        <v>-23.8</v>
       </c>
       <c r="E33" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6.9</v>
+        <v>30.9</v>
       </c>
       <c r="D34" t="n">
-        <v>-23.8</v>
+        <v>0.1</v>
       </c>
       <c r="E34" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2562,10 +2562,10 @@
         <v>35.3</v>
       </c>
       <c r="D37" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="E37" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2689,13 +2689,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="D42" t="n">
         <v>-17.5</v>
       </c>
       <c r="E42" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2706,104 +2706,104 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>30.9</v>
+        <v>0.1</v>
       </c>
       <c r="D43" t="n">
-        <v>6.9</v>
+        <v>-23.8</v>
       </c>
       <c r="E43" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.1</v>
+        <v>30.9</v>
       </c>
       <c r="D44" t="n">
-        <v>-23.8</v>
+        <v>7.2</v>
       </c>
       <c r="E44" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-3.3</v>
+        <v>7.2</v>
       </c>
       <c r="D45" t="n">
-        <v>-25.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E45" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6.9</v>
+        <v>-3.3</v>
       </c>
       <c r="D46" t="n">
-        <v>-14.9</v>
+        <v>-25.1</v>
       </c>
       <c r="E46" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2949,13 +2949,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="D52" t="n">
         <v>-25.1</v>
       </c>
       <c r="E52" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3053,13 +3053,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="D56" t="n">
         <v>-23.8</v>
       </c>
       <c r="E56" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3174,52 +3174,52 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.1</v>
+        <v>7.2</v>
       </c>
       <c r="D61" t="n">
-        <v>-14.9</v>
+        <v>-8.1</v>
       </c>
       <c r="E61" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6.9</v>
+        <v>0.1</v>
       </c>
       <c r="D62" t="n">
-        <v>-8.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E62" t="n">
         <v>15</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -3261,13 +3261,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="D64" t="n">
         <v>-5.9</v>
       </c>
       <c r="E64" t="n">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3287,13 +3287,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="D65" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="E65" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3313,13 +3313,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="D66" t="n">
         <v>-5.4</v>
       </c>
       <c r="E66" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3391,13 +3391,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="D69" t="n">
         <v>-17.5</v>
       </c>
       <c r="E69" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3460,52 +3460,52 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-14.9</v>
+        <v>7.2</v>
       </c>
       <c r="D72" t="n">
-        <v>-25.1</v>
+        <v>-3.3</v>
       </c>
       <c r="E72" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6.9</v>
+        <v>-14.9</v>
       </c>
       <c r="D73" t="n">
-        <v>-3.3</v>
+        <v>-25.1</v>
       </c>
       <c r="E73" t="n">
         <v>10.2</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -3538,52 +3538,52 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="D75" t="n">
-        <v>-5.7</v>
+        <v>-17.5</v>
       </c>
       <c r="E75" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-8.1</v>
+        <v>4.1</v>
       </c>
       <c r="D76" t="n">
-        <v>-17.5</v>
+        <v>-5.4</v>
       </c>
       <c r="E76" t="n">
         <v>9.5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="D79" t="n">
         <v>-14.9</v>
       </c>
       <c r="E79" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3798,52 +3798,52 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-8.1</v>
+        <v>7.2</v>
       </c>
       <c r="D85" t="n">
-        <v>-14.9</v>
+        <v>0.1</v>
       </c>
       <c r="E85" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6.9</v>
+        <v>-8.1</v>
       </c>
       <c r="D86" t="n">
-        <v>0.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E86" t="n">
         <v>6.8</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3914,10 +3914,10 @@
         <v>0.1</v>
       </c>
       <c r="D89" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="E89" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4067,13 +4067,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="D95" t="n">
         <v>4.1</v>
       </c>
       <c r="E95" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4162,52 +4162,52 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-3.3</v>
+        <v>-5.4</v>
       </c>
       <c r="D99" t="n">
-        <v>-5.7</v>
+        <v>-8.1</v>
       </c>
       <c r="E99" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>DHT</t>
-        </is>
-      </c>
       <c r="C100" t="n">
-        <v>-5.7</v>
+        <v>-3.3</v>
       </c>
       <c r="D100" t="n">
-        <v>-8.1</v>
+        <v>-5.4</v>
       </c>
       <c r="E100" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -4318,52 +4318,52 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>-5.4</v>
       </c>
       <c r="D105" t="n">
-        <v>-5.7</v>
+        <v>-5.9</v>
       </c>
       <c r="E105" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>ASC</t>
-        </is>
-      </c>
       <c r="C106" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="D106" t="n">
-        <v>-5.9</v>
+        <v>-5.4</v>
       </c>
       <c r="E106" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -1400,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1488,7 +1488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>17.25</v>
       </c>
       <c r="E2" t="n">
-        <v>32.91</v>
+        <v>33.91</v>
       </c>
       <c r="F2" t="n">
-        <v>26.54</v>
+        <v>28.77</v>
       </c>
       <c r="G2" t="n">
-        <v>22.44</v>
+        <v>25.87</v>
       </c>
       <c r="H2" t="n">
-        <v>19.5</v>
+        <v>23.76</v>
       </c>
       <c r="I2" t="n">
-        <v>25.73</v>
+        <v>28.32</v>
       </c>
       <c r="J2" t="n">
-        <v>37.1</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>-18.8</v>
+        <v>37.8</v>
       </c>
       <c r="L2" t="n">
-        <v>7.2</v>
+        <v>64.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1537,47 +1537,96 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>dry_bulk</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="F3" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="H3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="J3" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-18.8</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>whole-company</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>dry_bulk</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>27.2</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>32.72</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>26.35</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G4" t="n">
         <v>22.94</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H4" t="n">
         <v>19.34</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>25.72</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>20.3</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>-28.9</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" t="n">
         <v>-5.4</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
@@ -1594,7 +1643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1640,7 +1689,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1649,195 +1698,195 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35.3</v>
+        <v>64.2</v>
       </c>
       <c r="D2" t="n">
         <v>-44.9</v>
       </c>
       <c r="E2" t="n">
-        <v>80.2</v>
+        <v>109.1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30.9</v>
+        <v>64.2</v>
       </c>
       <c r="D3" t="n">
-        <v>-44.9</v>
+        <v>-25.1</v>
       </c>
       <c r="E3" t="n">
-        <v>75.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35.3</v>
+        <v>64.2</v>
       </c>
       <c r="D4" t="n">
-        <v>-25.1</v>
+        <v>-23.8</v>
       </c>
       <c r="E4" t="n">
-        <v>60.4</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35.3</v>
+        <v>64.2</v>
       </c>
       <c r="D5" t="n">
-        <v>-23.8</v>
+        <v>-17.5</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>81.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30.9</v>
+        <v>35.3</v>
       </c>
       <c r="D6" t="n">
-        <v>-25.1</v>
+        <v>-44.9</v>
       </c>
       <c r="E6" t="n">
-        <v>56.1</v>
+        <v>80.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30.9</v>
+        <v>64.2</v>
       </c>
       <c r="D7" t="n">
-        <v>-23.8</v>
+        <v>-14.9</v>
       </c>
       <c r="E7" t="n">
-        <v>54.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>35.3</v>
+        <v>30.9</v>
       </c>
       <c r="D8" t="n">
-        <v>-17.5</v>
+        <v>-44.9</v>
       </c>
       <c r="E8" t="n">
-        <v>52.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.2</v>
+        <v>64.2</v>
       </c>
       <c r="D9" t="n">
-        <v>-44.9</v>
+        <v>-8.1</v>
       </c>
       <c r="E9" t="n">
-        <v>52.2</v>
+        <v>72.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1848,130 +1897,130 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>35.3</v>
+        <v>64.2</v>
       </c>
       <c r="D10" t="n">
-        <v>-14.9</v>
+        <v>-5.9</v>
       </c>
       <c r="E10" t="n">
-        <v>50.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.1</v>
+        <v>64.2</v>
       </c>
       <c r="D11" t="n">
-        <v>-44.9</v>
+        <v>-5.4</v>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.9</v>
+        <v>64.2</v>
       </c>
       <c r="D12" t="n">
-        <v>-17.5</v>
+        <v>-5.4</v>
       </c>
       <c r="E12" t="n">
-        <v>48.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30.9</v>
+        <v>64.2</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.9</v>
+        <v>-3.3</v>
       </c>
       <c r="E13" t="n">
-        <v>45.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C14" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="D14" t="n">
         <v>0.1</v>
       </c>
-      <c r="D14" t="n">
-        <v>-44.9</v>
-      </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
@@ -1983,47 +2032,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>35.3</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.1</v>
+        <v>-25.1</v>
       </c>
       <c r="E15" t="n">
-        <v>43.4</v>
+        <v>60.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-3.3</v>
+        <v>64.2</v>
       </c>
       <c r="D16" t="n">
-        <v>-44.9</v>
+        <v>4.1</v>
       </c>
       <c r="E16" t="n">
-        <v>41.7</v>
+        <v>60.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -2035,132 +2084,132 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>35.3</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.9</v>
+        <v>-23.8</v>
       </c>
       <c r="E17" t="n">
-        <v>41.2</v>
+        <v>59</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>35.3</v>
+        <v>64.2</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.4</v>
+        <v>7.2</v>
       </c>
       <c r="E18" t="n">
-        <v>40.7</v>
+        <v>57</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>35.3</v>
+        <v>30.9</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.4</v>
+        <v>-25.1</v>
       </c>
       <c r="E19" t="n">
-        <v>40.7</v>
+        <v>56.1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-5.4</v>
+        <v>30.9</v>
       </c>
       <c r="D20" t="n">
-        <v>-44.9</v>
+        <v>-23.8</v>
       </c>
       <c r="E20" t="n">
-        <v>39.5</v>
+        <v>54.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-5.4</v>
+        <v>35.3</v>
       </c>
       <c r="D21" t="n">
-        <v>-44.9</v>
+        <v>-17.5</v>
       </c>
       <c r="E21" t="n">
-        <v>39.5</v>
+        <v>52.8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2169,95 +2218,95 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-5.9</v>
+        <v>7.2</v>
       </c>
       <c r="D22" t="n">
         <v>-44.9</v>
       </c>
       <c r="E22" t="n">
-        <v>39</v>
+        <v>52.2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30.9</v>
+        <v>35.3</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E23" t="n">
-        <v>39</v>
+        <v>50.2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>35.3</v>
+        <v>4.1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3</v>
+        <v>-44.9</v>
       </c>
       <c r="E24" t="n">
-        <v>38.6</v>
+        <v>49</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-8.1</v>
+        <v>30.9</v>
       </c>
       <c r="D25" t="n">
-        <v>-44.9</v>
+        <v>-17.5</v>
       </c>
       <c r="E25" t="n">
-        <v>36.9</v>
+        <v>48.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2269,151 +2318,151 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>30.9</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.9</v>
+        <v>-14.9</v>
       </c>
       <c r="E26" t="n">
-        <v>36.9</v>
+        <v>45.8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>30.9</v>
+        <v>0.1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.4</v>
+        <v>-44.9</v>
       </c>
       <c r="E27" t="n">
-        <v>36.4</v>
+        <v>45</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>30.9</v>
+        <v>35.3</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.4</v>
+        <v>-8.1</v>
       </c>
       <c r="E28" t="n">
-        <v>36.3</v>
+        <v>43.4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>35.3</v>
+        <v>-3.3</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1</v>
+        <v>-44.9</v>
       </c>
       <c r="E29" t="n">
-        <v>35.2</v>
+        <v>41.7</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.9</v>
+        <v>35.3</v>
       </c>
       <c r="D30" t="n">
-        <v>-3.3</v>
+        <v>-5.9</v>
       </c>
       <c r="E30" t="n">
-        <v>34.2</v>
+        <v>41.2</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7.2</v>
+        <v>35.3</v>
       </c>
       <c r="D31" t="n">
-        <v>-25.1</v>
+        <v>-5.4</v>
       </c>
       <c r="E31" t="n">
-        <v>32.3</v>
+        <v>40.7</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -2425,80 +2474,80 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>35.3</v>
       </c>
       <c r="D32" t="n">
-        <v>4.1</v>
+        <v>-5.4</v>
       </c>
       <c r="E32" t="n">
-        <v>31.2</v>
+        <v>40.7</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.2</v>
+        <v>-5.4</v>
       </c>
       <c r="D33" t="n">
-        <v>-23.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E33" t="n">
-        <v>31</v>
+        <v>39.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>30.9</v>
+        <v>-5.4</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1</v>
+        <v>-44.9</v>
       </c>
       <c r="E34" t="n">
-        <v>30.8</v>
+        <v>39.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2507,43 +2556,43 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-14.9</v>
+        <v>-5.9</v>
       </c>
       <c r="D35" t="n">
         <v>-44.9</v>
       </c>
       <c r="E35" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.1</v>
+        <v>30.9</v>
       </c>
       <c r="D36" t="n">
-        <v>-25.1</v>
+        <v>-8.1</v>
       </c>
       <c r="E36" t="n">
-        <v>29.2</v>
+        <v>39</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2555,73 +2604,73 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>35.3</v>
       </c>
       <c r="D37" t="n">
-        <v>7.2</v>
+        <v>-3.3</v>
       </c>
       <c r="E37" t="n">
-        <v>28.1</v>
+        <v>38.6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="D38" t="n">
-        <v>-23.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E38" t="n">
-        <v>27.9</v>
+        <v>36.9</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-17.5</v>
+        <v>30.9</v>
       </c>
       <c r="D39" t="n">
-        <v>-44.9</v>
+        <v>-5.9</v>
       </c>
       <c r="E39" t="n">
-        <v>27.4</v>
+        <v>36.9</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2633,125 +2682,125 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>30.9</v>
       </c>
       <c r="D40" t="n">
-        <v>4.1</v>
+        <v>-5.4</v>
       </c>
       <c r="E40" t="n">
-        <v>26.8</v>
+        <v>36.4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.1</v>
+        <v>30.9</v>
       </c>
       <c r="D41" t="n">
-        <v>-25.1</v>
+        <v>-5.4</v>
       </c>
       <c r="E41" t="n">
-        <v>25.2</v>
+        <v>36.3</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7.2</v>
+        <v>35.3</v>
       </c>
       <c r="D42" t="n">
-        <v>-17.5</v>
+        <v>0.1</v>
       </c>
       <c r="E42" t="n">
-        <v>24.8</v>
+        <v>35.2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.1</v>
+        <v>30.9</v>
       </c>
       <c r="D43" t="n">
-        <v>-23.8</v>
+        <v>-3.3</v>
       </c>
       <c r="E43" t="n">
-        <v>23.9</v>
+        <v>34.2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>GNK</t>
-        </is>
-      </c>
       <c r="C44" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="D44" t="n">
         <v>30.9</v>
       </c>
-      <c r="D44" t="n">
-        <v>7.2</v>
-      </c>
       <c r="E44" t="n">
-        <v>23.7</v>
+        <v>33.2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2763,251 +2812,251 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>7.2</v>
       </c>
       <c r="D45" t="n">
-        <v>-14.9</v>
+        <v>-25.1</v>
       </c>
       <c r="E45" t="n">
-        <v>22.1</v>
+        <v>32.3</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-3.3</v>
+        <v>35.3</v>
       </c>
       <c r="D46" t="n">
-        <v>-25.1</v>
+        <v>4.1</v>
       </c>
       <c r="E46" t="n">
-        <v>21.9</v>
+        <v>31.2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="D47" t="n">
-        <v>-17.5</v>
+        <v>-23.8</v>
       </c>
       <c r="E47" t="n">
-        <v>21.6</v>
+        <v>31</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-23.8</v>
+        <v>30.9</v>
       </c>
       <c r="D48" t="n">
-        <v>-44.9</v>
+        <v>0.1</v>
       </c>
       <c r="E48" t="n">
-        <v>21.2</v>
+        <v>30.8</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-3.3</v>
+        <v>-14.9</v>
       </c>
       <c r="D49" t="n">
-        <v>-23.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E49" t="n">
-        <v>20.5</v>
+        <v>30</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>HAFN</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C50" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D50" t="n">
         <v>-25.1</v>
       </c>
-      <c r="D50" t="n">
-        <v>-44.9</v>
-      </c>
       <c r="E50" t="n">
-        <v>19.8</v>
+        <v>29.2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-5.4</v>
+        <v>64.2</v>
       </c>
       <c r="D51" t="n">
-        <v>-25.1</v>
+        <v>35.3</v>
       </c>
       <c r="E51" t="n">
-        <v>19.7</v>
+        <v>28.9</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-5.4</v>
+        <v>35.3</v>
       </c>
       <c r="D52" t="n">
-        <v>-25.1</v>
+        <v>7.2</v>
       </c>
       <c r="E52" t="n">
-        <v>19.7</v>
+        <v>28.1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-5.9</v>
+        <v>4.1</v>
       </c>
       <c r="D53" t="n">
-        <v>-25.1</v>
+        <v>-23.8</v>
       </c>
       <c r="E53" t="n">
-        <v>19.2</v>
+        <v>27.9</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4.1</v>
+        <v>-17.5</v>
       </c>
       <c r="D54" t="n">
-        <v>-14.9</v>
+        <v>-44.9</v>
       </c>
       <c r="E54" t="n">
-        <v>19</v>
+        <v>27.4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3018,78 +3067,78 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-5.4</v>
+        <v>30.9</v>
       </c>
       <c r="D55" t="n">
-        <v>-23.8</v>
+        <v>4.1</v>
       </c>
       <c r="E55" t="n">
-        <v>18.3</v>
+        <v>26.8</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-5.4</v>
+        <v>0.1</v>
       </c>
       <c r="D56" t="n">
-        <v>-23.8</v>
+        <v>-25.1</v>
       </c>
       <c r="E56" t="n">
-        <v>18.3</v>
+        <v>25.2</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-5.9</v>
+        <v>7.2</v>
       </c>
       <c r="D57" t="n">
-        <v>-23.8</v>
+        <v>-17.5</v>
       </c>
       <c r="E57" t="n">
-        <v>17.8</v>
+        <v>24.8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3101,433 +3150,433 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>0.1</v>
       </c>
       <c r="D58" t="n">
-        <v>-17.5</v>
+        <v>-23.8</v>
       </c>
       <c r="E58" t="n">
-        <v>17.6</v>
+        <v>23.9</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-8.1</v>
+        <v>30.9</v>
       </c>
       <c r="D59" t="n">
-        <v>-25.1</v>
+        <v>7.2</v>
       </c>
       <c r="E59" t="n">
-        <v>17.1</v>
+        <v>23.7</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-8.1</v>
+        <v>7.2</v>
       </c>
       <c r="D60" t="n">
-        <v>-23.8</v>
+        <v>-14.9</v>
       </c>
       <c r="E60" t="n">
-        <v>15.7</v>
+        <v>22.1</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7.2</v>
+        <v>-3.3</v>
       </c>
       <c r="D61" t="n">
-        <v>-8.1</v>
+        <v>-25.1</v>
       </c>
       <c r="E61" t="n">
-        <v>15.3</v>
+        <v>21.9</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="D62" t="n">
-        <v>-14.9</v>
+        <v>-17.5</v>
       </c>
       <c r="E62" t="n">
-        <v>15</v>
+        <v>21.6</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-3.3</v>
+        <v>-23.8</v>
       </c>
       <c r="D63" t="n">
-        <v>-17.5</v>
+        <v>-44.9</v>
       </c>
       <c r="E63" t="n">
-        <v>14.3</v>
+        <v>21.2</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7.2</v>
+        <v>-3.3</v>
       </c>
       <c r="D64" t="n">
-        <v>-5.9</v>
+        <v>-23.8</v>
       </c>
       <c r="E64" t="n">
-        <v>13.2</v>
+        <v>20.5</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7.2</v>
+        <v>-25.1</v>
       </c>
       <c r="D65" t="n">
-        <v>-5.4</v>
+        <v>-44.9</v>
       </c>
       <c r="E65" t="n">
-        <v>12.7</v>
+        <v>19.8</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7.2</v>
+        <v>-5.4</v>
       </c>
       <c r="D66" t="n">
-        <v>-5.4</v>
+        <v>-25.1</v>
       </c>
       <c r="E66" t="n">
-        <v>12.6</v>
+        <v>19.7</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4.1</v>
+        <v>-5.4</v>
       </c>
       <c r="D67" t="n">
-        <v>-8.1</v>
+        <v>-25.1</v>
       </c>
       <c r="E67" t="n">
-        <v>12.2</v>
+        <v>19.7</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-5.4</v>
+        <v>-5.9</v>
       </c>
       <c r="D68" t="n">
-        <v>-17.5</v>
+        <v>-25.1</v>
       </c>
       <c r="E68" t="n">
-        <v>12.1</v>
+        <v>19.2</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-5.4</v>
+        <v>4.1</v>
       </c>
       <c r="D69" t="n">
-        <v>-17.5</v>
+        <v>-14.9</v>
       </c>
       <c r="E69" t="n">
-        <v>12.1</v>
+        <v>19</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-3.3</v>
+        <v>-5.4</v>
       </c>
       <c r="D70" t="n">
-        <v>-14.9</v>
+        <v>-23.8</v>
       </c>
       <c r="E70" t="n">
-        <v>11.6</v>
+        <v>18.3</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-5.9</v>
+        <v>-5.4</v>
       </c>
       <c r="D71" t="n">
-        <v>-17.5</v>
+        <v>-23.8</v>
       </c>
       <c r="E71" t="n">
-        <v>11.6</v>
+        <v>18.3</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7.2</v>
+        <v>-5.9</v>
       </c>
       <c r="D72" t="n">
-        <v>-3.3</v>
+        <v>-23.8</v>
       </c>
       <c r="E72" t="n">
-        <v>10.5</v>
+        <v>17.8</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-14.9</v>
+        <v>0.1</v>
       </c>
       <c r="D73" t="n">
-        <v>-25.1</v>
+        <v>-17.5</v>
       </c>
       <c r="E73" t="n">
-        <v>10.2</v>
+        <v>17.6</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="D74" t="n">
-        <v>-5.9</v>
+        <v>-25.1</v>
       </c>
       <c r="E74" t="n">
-        <v>10</v>
+        <v>17.1</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3543,95 +3592,95 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>-8.1</v>
       </c>
       <c r="D75" t="n">
-        <v>-17.5</v>
+        <v>-23.8</v>
       </c>
       <c r="E75" t="n">
-        <v>9.5</v>
+        <v>15.7</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="D76" t="n">
-        <v>-5.4</v>
+        <v>-8.1</v>
       </c>
       <c r="E76" t="n">
-        <v>9.5</v>
+        <v>15.3</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4.1</v>
+        <v>0.1</v>
       </c>
       <c r="D77" t="n">
-        <v>-5.4</v>
+        <v>-14.9</v>
       </c>
       <c r="E77" t="n">
-        <v>9.5</v>
+        <v>15</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-5.4</v>
+        <v>-3.3</v>
       </c>
       <c r="D78" t="n">
-        <v>-14.9</v>
+        <v>-17.5</v>
       </c>
       <c r="E78" t="n">
-        <v>9.5</v>
+        <v>14.3</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3642,85 +3691,85 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-5.4</v>
+        <v>7.2</v>
       </c>
       <c r="D79" t="n">
-        <v>-14.9</v>
+        <v>-5.9</v>
       </c>
       <c r="E79" t="n">
-        <v>9.5</v>
+        <v>13.2</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-5.9</v>
+        <v>7.2</v>
       </c>
       <c r="D80" t="n">
-        <v>-14.9</v>
+        <v>-5.4</v>
       </c>
       <c r="E80" t="n">
-        <v>9</v>
+        <v>12.7</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-14.9</v>
+        <v>7.2</v>
       </c>
       <c r="D81" t="n">
-        <v>-23.8</v>
+        <v>-5.4</v>
       </c>
       <c r="E81" t="n">
-        <v>8.800000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3729,388 +3778,388 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="D82" t="n">
         <v>-8.1</v>
       </c>
       <c r="E82" t="n">
-        <v>8.199999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>ECO</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>HAFN</t>
-        </is>
-      </c>
       <c r="C83" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="D83" t="n">
         <v>-17.5</v>
       </c>
-      <c r="D83" t="n">
-        <v>-25.1</v>
-      </c>
       <c r="E83" t="n">
-        <v>7.6</v>
+        <v>12.1</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4.1</v>
+        <v>-5.4</v>
       </c>
       <c r="D84" t="n">
-        <v>-3.3</v>
+        <v>-17.5</v>
       </c>
       <c r="E84" t="n">
-        <v>7.4</v>
+        <v>12.1</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7.2</v>
+        <v>-3.3</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E85" t="n">
-        <v>7.1</v>
+        <v>11.6</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-8.1</v>
+        <v>-5.9</v>
       </c>
       <c r="D86" t="n">
-        <v>-14.9</v>
+        <v>-17.5</v>
       </c>
       <c r="E86" t="n">
-        <v>6.8</v>
+        <v>11.6</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-17.5</v>
+        <v>7.2</v>
       </c>
       <c r="D87" t="n">
-        <v>-23.8</v>
+        <v>-3.3</v>
       </c>
       <c r="E87" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.1</v>
+        <v>-14.9</v>
       </c>
       <c r="D88" t="n">
-        <v>-5.9</v>
+        <v>-25.1</v>
       </c>
       <c r="E88" t="n">
-        <v>6.1</v>
+        <v>10.2</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="D89" t="n">
-        <v>-5.4</v>
+        <v>-5.9</v>
       </c>
       <c r="E89" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.1</v>
+        <v>-8.1</v>
       </c>
       <c r="D90" t="n">
-        <v>-5.4</v>
+        <v>-17.5</v>
       </c>
       <c r="E90" t="n">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-3.3</v>
+        <v>4.1</v>
       </c>
       <c r="D91" t="n">
-        <v>-8.1</v>
+        <v>-5.4</v>
       </c>
       <c r="E91" t="n">
-        <v>4.8</v>
+        <v>9.5</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>35.3</v>
+        <v>4.1</v>
       </c>
       <c r="D92" t="n">
-        <v>30.9</v>
+        <v>-5.4</v>
       </c>
       <c r="E92" t="n">
-        <v>4.4</v>
+        <v>9.5</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4.1</v>
+        <v>-5.4</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.1</v>
+        <v>-5.4</v>
       </c>
       <c r="D94" t="n">
-        <v>-3.3</v>
+        <v>-14.9</v>
       </c>
       <c r="E94" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>7.2</v>
+        <v>-5.9</v>
       </c>
       <c r="D95" t="n">
-        <v>4.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E95" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-3.3</v>
+        <v>-14.9</v>
       </c>
       <c r="D96" t="n">
-        <v>-5.9</v>
+        <v>-23.8</v>
       </c>
       <c r="E96" t="n">
-        <v>2.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4119,117 +4168,117 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-5.4</v>
+        <v>0.1</v>
       </c>
       <c r="D97" t="n">
         <v>-8.1</v>
       </c>
       <c r="E97" t="n">
-        <v>2.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-14.9</v>
+        <v>-17.5</v>
       </c>
       <c r="D98" t="n">
-        <v>-17.5</v>
+        <v>-25.1</v>
       </c>
       <c r="E98" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-5.4</v>
+        <v>4.1</v>
       </c>
       <c r="D99" t="n">
-        <v>-8.1</v>
+        <v>-3.3</v>
       </c>
       <c r="E99" t="n">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-3.3</v>
+        <v>7.2</v>
       </c>
       <c r="D100" t="n">
-        <v>-5.4</v>
+        <v>0.1</v>
       </c>
       <c r="E100" t="n">
-        <v>2.2</v>
+        <v>7.1</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-3.3</v>
+        <v>-8.1</v>
       </c>
       <c r="D101" t="n">
-        <v>-5.4</v>
+        <v>-14.9</v>
       </c>
       <c r="E101" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4240,128 +4289,518 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-5.9</v>
+        <v>-17.5</v>
       </c>
       <c r="D102" t="n">
-        <v>-8.1</v>
+        <v>-23.8</v>
       </c>
       <c r="E102" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-23.8</v>
+        <v>0.1</v>
       </c>
       <c r="D103" t="n">
-        <v>-25.1</v>
+        <v>-5.9</v>
       </c>
       <c r="E103" t="n">
-        <v>1.4</v>
+        <v>6.1</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C104" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D104" t="n">
         <v>-5.4</v>
       </c>
-      <c r="D104" t="n">
-        <v>-5.9</v>
-      </c>
       <c r="E104" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C105" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D105" t="n">
         <v>-5.4</v>
       </c>
-      <c r="D105" t="n">
-        <v>-5.9</v>
-      </c>
       <c r="E105" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TEN (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="D107" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E107" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E108" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs lng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="E109" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D110" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>TRMD</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="C106" t="n">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
         <v>-5.4</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D114" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="D115" t="n">
         <v>-5.4</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E115" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="E116" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>-23.8</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="E121" t="n">
         <v>0</v>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -1505,28 +1505,28 @@
         <v>17.25</v>
       </c>
       <c r="E2" t="n">
-        <v>33.91</v>
+        <v>23.74</v>
       </c>
       <c r="F2" t="n">
-        <v>28.77</v>
+        <v>20.14</v>
       </c>
       <c r="G2" t="n">
-        <v>25.87</v>
+        <v>18.11</v>
       </c>
       <c r="H2" t="n">
-        <v>23.76</v>
+        <v>16.64</v>
       </c>
       <c r="I2" t="n">
-        <v>28.32</v>
+        <v>19.82</v>
       </c>
       <c r="J2" t="n">
-        <v>96.59999999999999</v>
+        <v>37.6</v>
       </c>
       <c r="K2" t="n">
-        <v>37.8</v>
+        <v>-3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>64.2</v>
+        <v>14.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1698,69 +1698,69 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>64.2</v>
+        <v>35.3</v>
       </c>
       <c r="D2" t="n">
         <v>-44.9</v>
       </c>
       <c r="E2" t="n">
-        <v>109.1</v>
+        <v>80.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>64.2</v>
+        <v>30.9</v>
       </c>
       <c r="D3" t="n">
-        <v>-25.1</v>
+        <v>-44.9</v>
       </c>
       <c r="E3" t="n">
-        <v>89.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64.2</v>
+        <v>35.3</v>
       </c>
       <c r="D4" t="n">
-        <v>-23.8</v>
+        <v>-25.1</v>
       </c>
       <c r="E4" t="n">
-        <v>87.90000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -1772,17 +1772,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64.2</v>
+        <v>14.9</v>
       </c>
       <c r="D5" t="n">
-        <v>-17.5</v>
+        <v>-44.9</v>
       </c>
       <c r="E5" t="n">
-        <v>81.7</v>
+        <v>59.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1798,47 +1798,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>35.3</v>
       </c>
       <c r="D6" t="n">
-        <v>-44.9</v>
+        <v>-23.8</v>
       </c>
       <c r="E6" t="n">
-        <v>80.2</v>
+        <v>59</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>64.2</v>
+        <v>30.9</v>
       </c>
       <c r="D7" t="n">
-        <v>-14.9</v>
+        <v>-25.1</v>
       </c>
       <c r="E7" t="n">
-        <v>79.09999999999999</v>
+        <v>56.1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -1850,121 +1850,121 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>30.9</v>
       </c>
       <c r="D8" t="n">
-        <v>-44.9</v>
+        <v>-23.8</v>
       </c>
       <c r="E8" t="n">
-        <v>75.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>64.2</v>
+        <v>35.3</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.1</v>
+        <v>-17.5</v>
       </c>
       <c r="E9" t="n">
-        <v>72.2</v>
+        <v>52.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>64.2</v>
+        <v>7.2</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.9</v>
+        <v>-44.9</v>
       </c>
       <c r="E10" t="n">
-        <v>70.09999999999999</v>
+        <v>52.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>64.2</v>
+        <v>35.3</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4</v>
+        <v>-14.9</v>
       </c>
       <c r="E11" t="n">
-        <v>69.59999999999999</v>
+        <v>50.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>64.2</v>
+        <v>4.1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4</v>
+        <v>-44.9</v>
       </c>
       <c r="E12" t="n">
-        <v>69.59999999999999</v>
+        <v>49</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1975,241 +1975,241 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>64.2</v>
+        <v>30.9</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3</v>
+        <v>-17.5</v>
       </c>
       <c r="E13" t="n">
-        <v>67.40000000000001</v>
+        <v>48.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>64.2</v>
+        <v>30.9</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E14" t="n">
-        <v>64.09999999999999</v>
+        <v>45.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>35.3</v>
+        <v>0.1</v>
       </c>
       <c r="D15" t="n">
-        <v>-25.1</v>
+        <v>-44.9</v>
       </c>
       <c r="E15" t="n">
-        <v>60.4</v>
+        <v>45</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>64.2</v>
+        <v>35.3</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="E16" t="n">
-        <v>60.1</v>
+        <v>43.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>35.3</v>
+        <v>-3.3</v>
       </c>
       <c r="D17" t="n">
-        <v>-23.8</v>
+        <v>-44.9</v>
       </c>
       <c r="E17" t="n">
-        <v>59</v>
+        <v>41.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>64.2</v>
+        <v>35.3</v>
       </c>
       <c r="D18" t="n">
-        <v>7.2</v>
+        <v>-5.9</v>
       </c>
       <c r="E18" t="n">
-        <v>57</v>
+        <v>41.2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>30.9</v>
+        <v>35.3</v>
       </c>
       <c r="D19" t="n">
-        <v>-25.1</v>
+        <v>-5.4</v>
       </c>
       <c r="E19" t="n">
-        <v>56.1</v>
+        <v>40.7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>30.9</v>
+        <v>35.3</v>
       </c>
       <c r="D20" t="n">
-        <v>-23.8</v>
+        <v>-5.4</v>
       </c>
       <c r="E20" t="n">
-        <v>54.7</v>
+        <v>40.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35.3</v>
+        <v>14.9</v>
       </c>
       <c r="D21" t="n">
-        <v>-17.5</v>
+        <v>-25.1</v>
       </c>
       <c r="E21" t="n">
-        <v>52.8</v>
+        <v>40</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2218,50 +2218,50 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7.2</v>
+        <v>-5.4</v>
       </c>
       <c r="D22" t="n">
         <v>-44.9</v>
       </c>
       <c r="E22" t="n">
-        <v>52.2</v>
+        <v>39.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35.3</v>
+        <v>-5.4</v>
       </c>
       <c r="D23" t="n">
-        <v>-14.9</v>
+        <v>-44.9</v>
       </c>
       <c r="E23" t="n">
-        <v>50.2</v>
+        <v>39.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2270,17 +2270,17 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.1</v>
+        <v>-5.9</v>
       </c>
       <c r="D24" t="n">
         <v>-44.9</v>
       </c>
       <c r="E24" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -2292,17 +2292,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>30.9</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.5</v>
+        <v>-8.1</v>
       </c>
       <c r="E25" t="n">
-        <v>48.5</v>
+        <v>39</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2313,137 +2313,137 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>30.9</v>
+        <v>14.9</v>
       </c>
       <c r="D26" t="n">
-        <v>-14.9</v>
+        <v>-23.8</v>
       </c>
       <c r="E26" t="n">
-        <v>45.8</v>
+        <v>38.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.1</v>
+        <v>35.3</v>
       </c>
       <c r="D27" t="n">
-        <v>-44.9</v>
+        <v>-3.3</v>
       </c>
       <c r="E27" t="n">
-        <v>45</v>
+        <v>38.6</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>35.3</v>
+        <v>-8.1</v>
       </c>
       <c r="D28" t="n">
-        <v>-8.1</v>
+        <v>-44.9</v>
       </c>
       <c r="E28" t="n">
-        <v>43.4</v>
+        <v>36.9</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-3.3</v>
+        <v>30.9</v>
       </c>
       <c r="D29" t="n">
-        <v>-44.9</v>
+        <v>-5.9</v>
       </c>
       <c r="E29" t="n">
-        <v>41.7</v>
+        <v>36.9</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>35.3</v>
+        <v>30.9</v>
       </c>
       <c r="D30" t="n">
-        <v>-5.9</v>
+        <v>-5.4</v>
       </c>
       <c r="E30" t="n">
-        <v>41.2</v>
+        <v>36.4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2452,17 +2452,17 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>35.3</v>
+        <v>30.9</v>
       </c>
       <c r="D31" t="n">
         <v>-5.4</v>
       </c>
       <c r="E31" t="n">
-        <v>40.7</v>
+        <v>36.3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2474,69 +2474,69 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>35.3</v>
       </c>
       <c r="D32" t="n">
-        <v>-5.4</v>
+        <v>0.1</v>
       </c>
       <c r="E32" t="n">
-        <v>40.7</v>
+        <v>35.2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-5.4</v>
+        <v>30.9</v>
       </c>
       <c r="D33" t="n">
-        <v>-44.9</v>
+        <v>-3.3</v>
       </c>
       <c r="E33" t="n">
-        <v>39.5</v>
+        <v>34.2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-5.4</v>
+        <v>14.9</v>
       </c>
       <c r="D34" t="n">
-        <v>-44.9</v>
+        <v>-17.5</v>
       </c>
       <c r="E34" t="n">
-        <v>39.5</v>
+        <v>32.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2547,182 +2547,182 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-5.9</v>
+        <v>7.2</v>
       </c>
       <c r="D35" t="n">
-        <v>-44.9</v>
+        <v>-25.1</v>
       </c>
       <c r="E35" t="n">
-        <v>39</v>
+        <v>32.3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>30.9</v>
+        <v>35.3</v>
       </c>
       <c r="D36" t="n">
-        <v>-8.1</v>
+        <v>4.1</v>
       </c>
       <c r="E36" t="n">
-        <v>39</v>
+        <v>31.2</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>35.3</v>
+        <v>7.2</v>
       </c>
       <c r="D37" t="n">
-        <v>-3.3</v>
+        <v>-23.8</v>
       </c>
       <c r="E37" t="n">
-        <v>38.6</v>
+        <v>31</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-8.1</v>
+        <v>30.9</v>
       </c>
       <c r="D38" t="n">
-        <v>-44.9</v>
+        <v>0.1</v>
       </c>
       <c r="E38" t="n">
-        <v>36.9</v>
+        <v>30.8</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>30.9</v>
+        <v>-14.9</v>
       </c>
       <c r="D39" t="n">
-        <v>-5.9</v>
+        <v>-44.9</v>
       </c>
       <c r="E39" t="n">
-        <v>36.9</v>
+        <v>30</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>30.9</v>
+        <v>14.9</v>
       </c>
       <c r="D40" t="n">
-        <v>-5.4</v>
+        <v>-14.9</v>
       </c>
       <c r="E40" t="n">
-        <v>36.4</v>
+        <v>29.8</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>30.9</v>
+        <v>4.1</v>
       </c>
       <c r="D41" t="n">
-        <v>-5.4</v>
+        <v>-25.1</v>
       </c>
       <c r="E41" t="n">
-        <v>36.3</v>
+        <v>29.2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -2734,125 +2734,125 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>35.3</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1</v>
+        <v>7.2</v>
       </c>
       <c r="E42" t="n">
-        <v>35.2</v>
+        <v>28.1</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>30.9</v>
+        <v>4.1</v>
       </c>
       <c r="D43" t="n">
-        <v>-3.3</v>
+        <v>-23.8</v>
       </c>
       <c r="E43" t="n">
-        <v>34.2</v>
+        <v>27.9</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>64.2</v>
+        <v>-17.5</v>
       </c>
       <c r="D44" t="n">
-        <v>30.9</v>
+        <v>-44.9</v>
       </c>
       <c r="E44" t="n">
-        <v>33.2</v>
+        <v>27.4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7.2</v>
+        <v>30.9</v>
       </c>
       <c r="D45" t="n">
-        <v>-25.1</v>
+        <v>4.1</v>
       </c>
       <c r="E45" t="n">
-        <v>32.3</v>
+        <v>26.8</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>35.3</v>
+        <v>0.1</v>
       </c>
       <c r="D46" t="n">
-        <v>4.1</v>
+        <v>-25.1</v>
       </c>
       <c r="E46" t="n">
-        <v>31.2</v>
+        <v>25.2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -2864,151 +2864,151 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>7.2</v>
       </c>
       <c r="D47" t="n">
-        <v>-23.8</v>
+        <v>-17.5</v>
       </c>
       <c r="E47" t="n">
-        <v>31</v>
+        <v>24.8</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>30.9</v>
+        <v>0.1</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1</v>
+        <v>-23.8</v>
       </c>
       <c r="E48" t="n">
-        <v>30.8</v>
+        <v>23.9</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-14.9</v>
+        <v>30.9</v>
       </c>
       <c r="D49" t="n">
-        <v>-44.9</v>
+        <v>7.2</v>
       </c>
       <c r="E49" t="n">
-        <v>30</v>
+        <v>23.7</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4.1</v>
+        <v>14.9</v>
       </c>
       <c r="D50" t="n">
-        <v>-25.1</v>
+        <v>-8.1</v>
       </c>
       <c r="E50" t="n">
-        <v>29.2</v>
+        <v>23</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>64.2</v>
+        <v>7.2</v>
       </c>
       <c r="D51" t="n">
-        <v>35.3</v>
+        <v>-14.9</v>
       </c>
       <c r="E51" t="n">
-        <v>28.9</v>
+        <v>22.1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>35.3</v>
+        <v>-3.3</v>
       </c>
       <c r="D52" t="n">
-        <v>7.2</v>
+        <v>-25.1</v>
       </c>
       <c r="E52" t="n">
-        <v>28.1</v>
+        <v>21.9</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3020,28 +3020,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>4.1</v>
       </c>
       <c r="D53" t="n">
-        <v>-23.8</v>
+        <v>-17.5</v>
       </c>
       <c r="E53" t="n">
-        <v>27.9</v>
+        <v>21.6</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3050,180 +3050,180 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-17.5</v>
+        <v>-23.8</v>
       </c>
       <c r="D54" t="n">
         <v>-44.9</v>
       </c>
       <c r="E54" t="n">
-        <v>27.4</v>
+        <v>21.2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>30.9</v>
+        <v>14.9</v>
       </c>
       <c r="D55" t="n">
-        <v>4.1</v>
+        <v>-5.9</v>
       </c>
       <c r="E55" t="n">
-        <v>26.8</v>
+        <v>20.9</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.1</v>
+        <v>-3.3</v>
       </c>
       <c r="D56" t="n">
-        <v>-25.1</v>
+        <v>-23.8</v>
       </c>
       <c r="E56" t="n">
-        <v>25.2</v>
+        <v>20.5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7.2</v>
+        <v>35.3</v>
       </c>
       <c r="D57" t="n">
-        <v>-17.5</v>
+        <v>14.9</v>
       </c>
       <c r="E57" t="n">
-        <v>24.8</v>
+        <v>20.4</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.1</v>
+        <v>14.9</v>
       </c>
       <c r="D58" t="n">
-        <v>-23.8</v>
+        <v>-5.4</v>
       </c>
       <c r="E58" t="n">
-        <v>23.9</v>
+        <v>20.4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>30.9</v>
+        <v>14.9</v>
       </c>
       <c r="D59" t="n">
-        <v>7.2</v>
+        <v>-5.4</v>
       </c>
       <c r="E59" t="n">
-        <v>23.7</v>
+        <v>20.3</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7.2</v>
+        <v>-25.1</v>
       </c>
       <c r="D60" t="n">
-        <v>-14.9</v>
+        <v>-44.9</v>
       </c>
       <c r="E60" t="n">
-        <v>22.1</v>
+        <v>19.8</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-3.3</v>
+        <v>-5.4</v>
       </c>
       <c r="D61" t="n">
         <v>-25.1</v>
       </c>
       <c r="E61" t="n">
-        <v>21.9</v>
+        <v>19.7</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3249,152 +3249,152 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4.1</v>
+        <v>-5.4</v>
       </c>
       <c r="D62" t="n">
-        <v>-17.5</v>
+        <v>-25.1</v>
       </c>
       <c r="E62" t="n">
-        <v>21.6</v>
+        <v>19.7</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-23.8</v>
+        <v>-5.9</v>
       </c>
       <c r="D63" t="n">
-        <v>-44.9</v>
+        <v>-25.1</v>
       </c>
       <c r="E63" t="n">
-        <v>21.2</v>
+        <v>19.2</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-3.3</v>
+        <v>4.1</v>
       </c>
       <c r="D64" t="n">
-        <v>-23.8</v>
+        <v>-14.9</v>
       </c>
       <c r="E64" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-25.1</v>
+        <v>-5.4</v>
       </c>
       <c r="D65" t="n">
-        <v>-44.9</v>
+        <v>-23.8</v>
       </c>
       <c r="E65" t="n">
-        <v>19.8</v>
+        <v>18.3</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>-5.4</v>
       </c>
       <c r="D66" t="n">
-        <v>-25.1</v>
+        <v>-23.8</v>
       </c>
       <c r="E66" t="n">
-        <v>19.7</v>
+        <v>18.3</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-5.4</v>
+        <v>14.9</v>
       </c>
       <c r="D67" t="n">
-        <v>-25.1</v>
+        <v>-3.3</v>
       </c>
       <c r="E67" t="n">
-        <v>19.7</v>
+        <v>18.2</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3410,106 +3410,106 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>-5.9</v>
       </c>
       <c r="D68" t="n">
-        <v>-25.1</v>
+        <v>-23.8</v>
       </c>
       <c r="E68" t="n">
-        <v>19.2</v>
+        <v>17.8</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4.1</v>
+        <v>0.1</v>
       </c>
       <c r="D69" t="n">
-        <v>-14.9</v>
+        <v>-17.5</v>
       </c>
       <c r="E69" t="n">
-        <v>19</v>
+        <v>17.6</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-5.4</v>
+        <v>-8.1</v>
       </c>
       <c r="D70" t="n">
-        <v>-23.8</v>
+        <v>-25.1</v>
       </c>
       <c r="E70" t="n">
-        <v>18.3</v>
+        <v>17.1</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-5.4</v>
+        <v>30.9</v>
       </c>
       <c r="D71" t="n">
-        <v>-23.8</v>
+        <v>14.9</v>
       </c>
       <c r="E71" t="n">
-        <v>18.3</v>
+        <v>16</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3518,173 +3518,173 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-5.9</v>
+        <v>-8.1</v>
       </c>
       <c r="D72" t="n">
         <v>-23.8</v>
       </c>
       <c r="E72" t="n">
-        <v>17.8</v>
+        <v>15.7</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.1</v>
+        <v>7.2</v>
       </c>
       <c r="D73" t="n">
-        <v>-17.5</v>
+        <v>-8.1</v>
       </c>
       <c r="E73" t="n">
-        <v>17.6</v>
+        <v>15.3</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-8.1</v>
+        <v>0.1</v>
       </c>
       <c r="D74" t="n">
-        <v>-25.1</v>
+        <v>-14.9</v>
       </c>
       <c r="E74" t="n">
-        <v>17.1</v>
+        <v>15</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-8.1</v>
+        <v>14.9</v>
       </c>
       <c r="D75" t="n">
-        <v>-23.8</v>
+        <v>0.1</v>
       </c>
       <c r="E75" t="n">
-        <v>15.7</v>
+        <v>14.8</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7.2</v>
+        <v>-3.3</v>
       </c>
       <c r="D76" t="n">
-        <v>-8.1</v>
+        <v>-17.5</v>
       </c>
       <c r="E76" t="n">
-        <v>15.3</v>
+        <v>14.3</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.1</v>
+        <v>7.2</v>
       </c>
       <c r="D77" t="n">
-        <v>-14.9</v>
+        <v>-5.9</v>
       </c>
       <c r="E77" t="n">
-        <v>15</v>
+        <v>13.2</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-3.3</v>
+        <v>7.2</v>
       </c>
       <c r="D78" t="n">
-        <v>-17.5</v>
+        <v>-5.4</v>
       </c>
       <c r="E78" t="n">
-        <v>14.3</v>
+        <v>12.7</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3696,17 +3696,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>7.2</v>
       </c>
       <c r="D79" t="n">
-        <v>-5.9</v>
+        <v>-5.4</v>
       </c>
       <c r="E79" t="n">
-        <v>13.2</v>
+        <v>12.6</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3717,22 +3717,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="D80" t="n">
-        <v>-5.4</v>
+        <v>-8.1</v>
       </c>
       <c r="E80" t="n">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3743,74 +3743,74 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7.2</v>
+        <v>-5.4</v>
       </c>
       <c r="D81" t="n">
-        <v>-5.4</v>
+        <v>-17.5</v>
       </c>
       <c r="E81" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4.1</v>
+        <v>-5.4</v>
       </c>
       <c r="D82" t="n">
-        <v>-8.1</v>
+        <v>-17.5</v>
       </c>
       <c r="E82" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-5.4</v>
+        <v>-3.3</v>
       </c>
       <c r="D83" t="n">
-        <v>-17.5</v>
+        <v>-14.9</v>
       </c>
       <c r="E83" t="n">
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3830,117 +3830,117 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-5.4</v>
+        <v>-5.9</v>
       </c>
       <c r="D84" t="n">
         <v>-17.5</v>
       </c>
       <c r="E84" t="n">
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-3.3</v>
+        <v>14.9</v>
       </c>
       <c r="D85" t="n">
-        <v>-14.9</v>
+        <v>4.1</v>
       </c>
       <c r="E85" t="n">
-        <v>11.6</v>
+        <v>10.8</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-5.9</v>
+        <v>7.2</v>
       </c>
       <c r="D86" t="n">
-        <v>-17.5</v>
+        <v>-3.3</v>
       </c>
       <c r="E86" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7.2</v>
+        <v>-14.9</v>
       </c>
       <c r="D87" t="n">
-        <v>-3.3</v>
+        <v>-25.1</v>
       </c>
       <c r="E87" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-14.9</v>
+        <v>4.1</v>
       </c>
       <c r="D88" t="n">
-        <v>-25.1</v>
+        <v>-5.9</v>
       </c>
       <c r="E88" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3951,52 +3951,52 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="D89" t="n">
-        <v>-5.9</v>
+        <v>-17.5</v>
       </c>
       <c r="E89" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-8.1</v>
+        <v>4.1</v>
       </c>
       <c r="D90" t="n">
-        <v>-17.5</v>
+        <v>-5.4</v>
       </c>
       <c r="E90" t="n">
         <v>9.5</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -4022,40 +4022,40 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4.1</v>
+        <v>-5.4</v>
       </c>
       <c r="D92" t="n">
-        <v>-5.4</v>
+        <v>-14.9</v>
       </c>
       <c r="E92" t="n">
         <v>9.5</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4074,14 +4074,14 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4090,95 +4090,95 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-5.4</v>
+        <v>-5.9</v>
       </c>
       <c r="D94" t="n">
         <v>-14.9</v>
       </c>
       <c r="E94" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-5.9</v>
+        <v>-14.9</v>
       </c>
       <c r="D95" t="n">
-        <v>-14.9</v>
+        <v>-23.8</v>
       </c>
       <c r="E95" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-14.9</v>
+        <v>0.1</v>
       </c>
       <c r="D96" t="n">
-        <v>-23.8</v>
+        <v>-8.1</v>
       </c>
       <c r="E96" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.1</v>
+        <v>14.9</v>
       </c>
       <c r="D97" t="n">
-        <v>-8.1</v>
+        <v>7.2</v>
       </c>
       <c r="E97" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>37.14</v>
       </c>
       <c r="E2" t="n">
         <v>75</v>
@@ -541,13 +541,13 @@
         <v>57.61</v>
       </c>
       <c r="J2" t="n">
-        <v>70.40000000000001</v>
+        <v>101.9</v>
       </c>
       <c r="K2" t="n">
-        <v>-21.2</v>
+        <v>-6.6</v>
       </c>
       <c r="L2" t="n">
-        <v>30.9</v>
+        <v>55.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>70.8</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>85.68000000000001</v>
@@ -590,13 +590,13 @@
         <v>73.7</v>
       </c>
       <c r="J3" t="n">
-        <v>21</v>
+        <v>17.8</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.9</v>
+        <v>-18.1</v>
       </c>
       <c r="L3" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="E4" t="n">
         <v>19.63</v>
@@ -639,13 +639,13 @@
         <v>15.08</v>
       </c>
       <c r="J4" t="n">
-        <v>19.7</v>
+        <v>18.3</v>
       </c>
       <c r="K4" t="n">
-        <v>-44.7</v>
+        <v>-45.4</v>
       </c>
       <c r="L4" t="n">
-        <v>-8.1</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34.5</v>
+        <v>36.28</v>
       </c>
       <c r="E5" t="n">
         <v>40.78</v>
@@ -688,13 +688,13 @@
         <v>29.36</v>
       </c>
       <c r="J5" t="n">
-        <v>18.2</v>
+        <v>12.4</v>
       </c>
       <c r="K5" t="n">
-        <v>-59.5</v>
+        <v>-61.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-14.9</v>
+        <v>-19.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>47.7</v>
+        <v>49.2</v>
       </c>
       <c r="E6" t="n">
         <v>54.22</v>
@@ -737,13 +737,13 @@
         <v>39.33</v>
       </c>
       <c r="J6" t="n">
-        <v>13.7</v>
+        <v>10.2</v>
       </c>
       <c r="K6" t="n">
-        <v>-58.9</v>
+        <v>-60.1</v>
       </c>
       <c r="L6" t="n">
-        <v>-17.5</v>
+        <v>-20.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>82.61</v>
       </c>
       <c r="E7" t="n">
         <v>74.11</v>
@@ -786,13 +786,13 @@
         <v>59.47</v>
       </c>
       <c r="J7" t="n">
-        <v>-5</v>
+        <v>-10.3</v>
       </c>
       <c r="K7" t="n">
-        <v>-51.1</v>
+        <v>-53.8</v>
       </c>
       <c r="L7" t="n">
-        <v>-23.8</v>
+        <v>-28</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="E8" t="n">
         <v>4.17</v>
@@ -835,13 +835,13 @@
         <v>2.86</v>
       </c>
       <c r="J8" t="n">
-        <v>-19.8</v>
+        <v>-19.5</v>
       </c>
       <c r="K8" t="n">
-        <v>-77.09999999999999</v>
+        <v>-77</v>
       </c>
       <c r="L8" t="n">
-        <v>-44.9</v>
+        <v>-44.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.9</v>
+        <v>21.46</v>
       </c>
       <c r="E2" t="n">
         <v>48.52</v>
@@ -1001,13 +1001,13 @@
         <v>29.63</v>
       </c>
       <c r="K2" t="n">
-        <v>121.5</v>
+        <v>126.1</v>
       </c>
       <c r="L2" t="n">
         <v>-102.1</v>
       </c>
       <c r="M2" t="n">
-        <v>35.3</v>
+        <v>38.1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.7</v>
+        <v>30.34</v>
       </c>
       <c r="E3" t="n">
         <v>39.76</v>
@@ -1059,13 +1059,13 @@
         <v>29.73</v>
       </c>
       <c r="K3" t="n">
-        <v>33.9</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
-        <v>-53.5</v>
+        <v>-54.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1</v>
+        <v>-2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>75.59999999999999</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>90.78</v>
@@ -1219,13 +1219,13 @@
         <v>73.13</v>
       </c>
       <c r="K2" t="n">
-        <v>20.1</v>
+        <v>18.7</v>
       </c>
       <c r="L2" t="n">
-        <v>-36.7</v>
+        <v>-37.4</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.3</v>
+        <v>-4.4</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1250,34 +1250,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.2</v>
+        <v>16.43</v>
       </c>
       <c r="E3" t="n">
-        <v>39.1</v>
+        <v>18.05</v>
       </c>
       <c r="F3" t="n">
-        <v>32.74</v>
+        <v>15.92</v>
       </c>
       <c r="G3" t="n">
-        <v>16.68</v>
+        <v>13.54</v>
       </c>
       <c r="H3" t="n">
-        <v>13.84</v>
+        <v>11.31</v>
       </c>
       <c r="I3" t="n">
-        <v>10.86</v>
+        <v>9.41</v>
       </c>
       <c r="J3" t="n">
-        <v>26.68</v>
+        <v>15.05</v>
       </c>
       <c r="K3" t="n">
-        <v>38.7</v>
+        <v>9.9</v>
       </c>
       <c r="L3" t="n">
-        <v>-61.5</v>
+        <v>-42.7</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.4</v>
+        <v>-8.4</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1302,34 +1302,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>29.18</v>
       </c>
       <c r="E4" t="n">
-        <v>18.05</v>
+        <v>39.1</v>
       </c>
       <c r="F4" t="n">
-        <v>15.92</v>
+        <v>32.74</v>
       </c>
       <c r="G4" t="n">
-        <v>13.54</v>
+        <v>16.68</v>
       </c>
       <c r="H4" t="n">
-        <v>11.31</v>
+        <v>13.84</v>
       </c>
       <c r="I4" t="n">
-        <v>9.41</v>
+        <v>10.86</v>
       </c>
       <c r="J4" t="n">
-        <v>15.05</v>
+        <v>26.68</v>
       </c>
       <c r="K4" t="n">
-        <v>12.8</v>
+        <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>-41.2</v>
+        <v>-62.8</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.9</v>
+        <v>-8.6</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7.7</v>
+        <v>7.36</v>
       </c>
       <c r="E5" t="n">
         <v>8.279999999999999</v>
@@ -1375,13 +1375,13 @@
         <v>5.77</v>
       </c>
       <c r="K5" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-65.59999999999999</v>
+        <v>-64</v>
       </c>
       <c r="M5" t="n">
-        <v>-25.1</v>
+        <v>-21.7</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.25</v>
+        <v>17.24</v>
       </c>
       <c r="E2" t="n">
         <v>23.74</v>
@@ -1520,13 +1520,13 @@
         <v>19.82</v>
       </c>
       <c r="J2" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="E3" t="n">
         <v>32.91</v>
@@ -1569,13 +1569,13 @@
         <v>25.73</v>
       </c>
       <c r="J3" t="n">
-        <v>37.1</v>
+        <v>40</v>
       </c>
       <c r="K3" t="n">
-        <v>-18.8</v>
+        <v>-17</v>
       </c>
       <c r="L3" t="n">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.2</v>
+        <v>26.57</v>
       </c>
       <c r="E4" t="n">
         <v>32.72</v>
@@ -1618,17 +1618,17 @@
         <v>25.72</v>
       </c>
       <c r="J4" t="n">
-        <v>20.3</v>
+        <v>23.2</v>
       </c>
       <c r="K4" t="n">
-        <v>-28.9</v>
+        <v>-27.2</v>
       </c>
       <c r="L4" t="n">
-        <v>-5.4</v>
+        <v>-3.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1698,17 +1698,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35.3</v>
+        <v>55.1</v>
       </c>
       <c r="D2" t="n">
-        <v>-44.9</v>
+        <v>-44.7</v>
       </c>
       <c r="E2" t="n">
-        <v>80.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -1720,21 +1720,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30.9</v>
+        <v>55.1</v>
       </c>
       <c r="D3" t="n">
-        <v>-44.9</v>
+        <v>-28</v>
       </c>
       <c r="E3" t="n">
-        <v>75.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1746,73 +1746,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35.3</v>
+        <v>38.1</v>
       </c>
       <c r="D4" t="n">
-        <v>-25.1</v>
+        <v>-44.7</v>
       </c>
       <c r="E4" t="n">
-        <v>60.4</v>
+        <v>82.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14.9</v>
+        <v>55.1</v>
       </c>
       <c r="D5" t="n">
-        <v>-44.9</v>
+        <v>-21.7</v>
       </c>
       <c r="E5" t="n">
-        <v>59.9</v>
+        <v>76.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35.3</v>
+        <v>55.1</v>
       </c>
       <c r="D6" t="n">
-        <v>-23.8</v>
+        <v>-20.1</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>75.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -1824,28 +1824,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30.9</v>
+        <v>55.1</v>
       </c>
       <c r="D7" t="n">
-        <v>-25.1</v>
+        <v>-19.1</v>
       </c>
       <c r="E7" t="n">
-        <v>56.1</v>
+        <v>74.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1854,147 +1854,147 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30.9</v>
+        <v>38.1</v>
       </c>
       <c r="D8" t="n">
-        <v>-23.8</v>
+        <v>-28</v>
       </c>
       <c r="E8" t="n">
-        <v>54.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35.3</v>
+        <v>55.1</v>
       </c>
       <c r="D9" t="n">
-        <v>-17.5</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>52.8</v>
+        <v>64.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.2</v>
+        <v>55.1</v>
       </c>
       <c r="D10" t="n">
-        <v>-44.9</v>
+        <v>-8.6</v>
       </c>
       <c r="E10" t="n">
-        <v>52.2</v>
+        <v>63.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.3</v>
+        <v>55.1</v>
       </c>
       <c r="D11" t="n">
-        <v>-14.9</v>
+        <v>-8.4</v>
       </c>
       <c r="E11" t="n">
-        <v>50.2</v>
+        <v>63.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.1</v>
+        <v>38.1</v>
       </c>
       <c r="D12" t="n">
-        <v>-44.9</v>
+        <v>-21.7</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>59.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30.9</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.5</v>
+        <v>-44.7</v>
       </c>
       <c r="E13" t="n">
-        <v>48.5</v>
+        <v>59.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -2006,47 +2006,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>30.9</v>
+        <v>55.1</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.9</v>
+        <v>-4.4</v>
       </c>
       <c r="E14" t="n">
-        <v>45.8</v>
+        <v>59.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1</v>
+        <v>55.1</v>
       </c>
       <c r="D15" t="n">
-        <v>-44.9</v>
+        <v>-3.2</v>
       </c>
       <c r="E15" t="n">
-        <v>45</v>
+        <v>58.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2058,17 +2058,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>35.3</v>
+        <v>38.1</v>
       </c>
       <c r="D16" t="n">
-        <v>-8.1</v>
+        <v>-20.1</v>
       </c>
       <c r="E16" t="n">
-        <v>43.4</v>
+        <v>58.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2079,189 +2079,189 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-3.3</v>
+        <v>38.1</v>
       </c>
       <c r="D17" t="n">
-        <v>-44.9</v>
+        <v>-19.1</v>
       </c>
       <c r="E17" t="n">
-        <v>41.7</v>
+        <v>57.1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>35.3</v>
+        <v>55.1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.9</v>
+        <v>-2</v>
       </c>
       <c r="E18" t="n">
-        <v>41.2</v>
+        <v>57.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>35.3</v>
+        <v>9.5</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.4</v>
+        <v>-44.7</v>
       </c>
       <c r="E19" t="n">
-        <v>40.7</v>
+        <v>54.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>35.3</v>
+        <v>55.1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.4</v>
+        <v>1.3</v>
       </c>
       <c r="E20" t="n">
-        <v>40.7</v>
+        <v>53.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14.9</v>
+        <v>38.1</v>
       </c>
       <c r="D21" t="n">
-        <v>-25.1</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>40</v>
+        <v>47.2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>TRMD</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C22" t="n">
-        <v>-5.4</v>
+        <v>38.1</v>
       </c>
       <c r="D22" t="n">
-        <v>-44.9</v>
+        <v>-8.6</v>
       </c>
       <c r="E22" t="n">
-        <v>39.5</v>
+        <v>46.6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-5.4</v>
+        <v>38.1</v>
       </c>
       <c r="D23" t="n">
-        <v>-44.9</v>
+        <v>-8.4</v>
       </c>
       <c r="E23" t="n">
-        <v>39.5</v>
+        <v>46.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2270,17 +2270,17 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-5.9</v>
+        <v>1.3</v>
       </c>
       <c r="D24" t="n">
-        <v>-44.9</v>
+        <v>-44.7</v>
       </c>
       <c r="E24" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2292,21 +2292,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>30.9</v>
+        <v>55.1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.1</v>
+        <v>9.5</v>
       </c>
       <c r="E25" t="n">
-        <v>39</v>
+        <v>45.6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2322,13 +2322,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="D26" t="n">
-        <v>-23.8</v>
+        <v>-28</v>
       </c>
       <c r="E26" t="n">
-        <v>38.7</v>
+        <v>43</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2339,85 +2339,85 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>35.3</v>
+        <v>-2</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.3</v>
+        <v>-44.7</v>
       </c>
       <c r="E27" t="n">
-        <v>38.6</v>
+        <v>42.7</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-8.1</v>
+        <v>38.1</v>
       </c>
       <c r="D28" t="n">
-        <v>-44.9</v>
+        <v>-4.4</v>
       </c>
       <c r="E28" t="n">
-        <v>36.9</v>
+        <v>42.4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>30.9</v>
+        <v>-3.2</v>
       </c>
       <c r="D29" t="n">
-        <v>-5.9</v>
+        <v>-44.7</v>
       </c>
       <c r="E29" t="n">
-        <v>36.9</v>
+        <v>41.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2426,43 +2426,43 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.9</v>
+        <v>38.1</v>
       </c>
       <c r="D30" t="n">
-        <v>-5.4</v>
+        <v>-3.2</v>
       </c>
       <c r="E30" t="n">
-        <v>36.4</v>
+        <v>41.3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30.9</v>
+        <v>-4.4</v>
       </c>
       <c r="D31" t="n">
-        <v>-5.4</v>
+        <v>-44.7</v>
       </c>
       <c r="E31" t="n">
-        <v>36.3</v>
+        <v>40.4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>35.3</v>
+        <v>38.1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1</v>
+        <v>-2</v>
       </c>
       <c r="E32" t="n">
-        <v>35.2</v>
+        <v>40.1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2500,158 +2500,158 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>30.9</v>
+        <v>55.1</v>
       </c>
       <c r="D33" t="n">
-        <v>-3.3</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>34.2</v>
+        <v>40.1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14.9</v>
+        <v>9.5</v>
       </c>
       <c r="D34" t="n">
-        <v>-17.5</v>
+        <v>-28</v>
       </c>
       <c r="E34" t="n">
-        <v>32.5</v>
+        <v>37.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7.2</v>
+        <v>38.1</v>
       </c>
       <c r="D35" t="n">
-        <v>-25.1</v>
+        <v>1.3</v>
       </c>
       <c r="E35" t="n">
-        <v>32.3</v>
+        <v>36.8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>35.3</v>
+        <v>15</v>
       </c>
       <c r="D36" t="n">
-        <v>4.1</v>
+        <v>-21.7</v>
       </c>
       <c r="E36" t="n">
-        <v>31.2</v>
+        <v>36.6</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7.2</v>
+        <v>-8.4</v>
       </c>
       <c r="D37" t="n">
-        <v>-23.8</v>
+        <v>-44.7</v>
       </c>
       <c r="E37" t="n">
-        <v>31</v>
+        <v>36.3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>30.9</v>
+        <v>-8.6</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1</v>
+        <v>-44.7</v>
       </c>
       <c r="E38" t="n">
-        <v>30.8</v>
+        <v>36.1</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2660,13 +2660,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-14.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>-44.9</v>
+        <v>-44.7</v>
       </c>
       <c r="E39" t="n">
-        <v>30</v>
+        <v>35.6</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="D40" t="n">
-        <v>-14.9</v>
+        <v>-20.1</v>
       </c>
       <c r="E40" t="n">
-        <v>29.8</v>
+        <v>35</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2703,282 +2703,282 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="D41" t="n">
-        <v>-25.1</v>
+        <v>-19.1</v>
       </c>
       <c r="E41" t="n">
-        <v>29.2</v>
+        <v>34.1</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>35.3</v>
+        <v>9.5</v>
       </c>
       <c r="D42" t="n">
-        <v>7.2</v>
+        <v>-21.7</v>
       </c>
       <c r="E42" t="n">
-        <v>28.1</v>
+        <v>31.2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4.1</v>
+        <v>9.5</v>
       </c>
       <c r="D43" t="n">
-        <v>-23.8</v>
+        <v>-20.1</v>
       </c>
       <c r="E43" t="n">
-        <v>27.9</v>
+        <v>29.6</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-17.5</v>
+        <v>1.3</v>
       </c>
       <c r="D44" t="n">
-        <v>-44.9</v>
+        <v>-28</v>
       </c>
       <c r="E44" t="n">
-        <v>27.4</v>
+        <v>29.3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>30.9</v>
+        <v>38.1</v>
       </c>
       <c r="D45" t="n">
-        <v>4.1</v>
+        <v>9.5</v>
       </c>
       <c r="E45" t="n">
-        <v>26.8</v>
+        <v>28.6</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.1</v>
+        <v>9.5</v>
       </c>
       <c r="D46" t="n">
-        <v>-25.1</v>
+        <v>-19.1</v>
       </c>
       <c r="E46" t="n">
-        <v>25.2</v>
+        <v>28.6</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7.2</v>
+        <v>-2</v>
       </c>
       <c r="D47" t="n">
-        <v>-17.5</v>
+        <v>-28</v>
       </c>
       <c r="E47" t="n">
-        <v>24.8</v>
+        <v>26</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.1</v>
+        <v>-19.1</v>
       </c>
       <c r="D48" t="n">
-        <v>-23.8</v>
+        <v>-44.7</v>
       </c>
       <c r="E48" t="n">
-        <v>23.9</v>
+        <v>25.6</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>30.9</v>
+        <v>-3.2</v>
       </c>
       <c r="D49" t="n">
-        <v>7.2</v>
+        <v>-28</v>
       </c>
       <c r="E49" t="n">
-        <v>23.7</v>
+        <v>24.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>14.9</v>
+        <v>-20.1</v>
       </c>
       <c r="D50" t="n">
-        <v>-8.1</v>
+        <v>-44.7</v>
       </c>
       <c r="E50" t="n">
-        <v>23</v>
+        <v>24.7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="D51" t="n">
-        <v>-14.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>22.1</v>
+        <v>24.2</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2994,173 +2994,173 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-3.3</v>
+        <v>-4.4</v>
       </c>
       <c r="D52" t="n">
-        <v>-25.1</v>
+        <v>-28</v>
       </c>
       <c r="E52" t="n">
-        <v>21.9</v>
+        <v>23.7</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="D53" t="n">
-        <v>-17.5</v>
+        <v>-8.6</v>
       </c>
       <c r="E53" t="n">
-        <v>21.6</v>
+        <v>23.6</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-23.8</v>
+        <v>15</v>
       </c>
       <c r="D54" t="n">
-        <v>-44.9</v>
+        <v>-8.4</v>
       </c>
       <c r="E54" t="n">
-        <v>21.2</v>
+        <v>23.4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>CMDB</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>ASC</t>
-        </is>
-      </c>
       <c r="C55" t="n">
-        <v>14.9</v>
+        <v>38.1</v>
       </c>
       <c r="D55" t="n">
-        <v>-5.9</v>
+        <v>15</v>
       </c>
       <c r="E55" t="n">
-        <v>20.9</v>
+        <v>23.1</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-3.3</v>
+        <v>-21.7</v>
       </c>
       <c r="D56" t="n">
-        <v>-23.8</v>
+        <v>-44.7</v>
       </c>
       <c r="E56" t="n">
-        <v>20.5</v>
+        <v>23.1</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>35.3</v>
+        <v>1.3</v>
       </c>
       <c r="D57" t="n">
-        <v>14.9</v>
+        <v>-21.7</v>
       </c>
       <c r="E57" t="n">
-        <v>20.4</v>
+        <v>23</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>14.9</v>
+        <v>1.3</v>
       </c>
       <c r="D58" t="n">
-        <v>-5.4</v>
+        <v>-20.1</v>
       </c>
       <c r="E58" t="n">
-        <v>20.4</v>
+        <v>21.4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3171,182 +3171,182 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>14.9</v>
+        <v>1.3</v>
       </c>
       <c r="D59" t="n">
-        <v>-5.4</v>
+        <v>-19.1</v>
       </c>
       <c r="E59" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>HAFN</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C60" t="n">
-        <v>-25.1</v>
+        <v>-2</v>
       </c>
       <c r="D60" t="n">
-        <v>-44.9</v>
+        <v>-21.7</v>
       </c>
       <c r="E60" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-5.4</v>
+        <v>-8.4</v>
       </c>
       <c r="D61" t="n">
-        <v>-25.1</v>
+        <v>-28</v>
       </c>
       <c r="E61" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-5.4</v>
+        <v>-8.6</v>
       </c>
       <c r="D62" t="n">
-        <v>-25.1</v>
+        <v>-28</v>
       </c>
       <c r="E62" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-5.9</v>
+        <v>15</v>
       </c>
       <c r="D63" t="n">
-        <v>-25.1</v>
+        <v>-4.4</v>
       </c>
       <c r="E63" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4.1</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D64" t="n">
-        <v>-14.9</v>
+        <v>-28</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-5.4</v>
+        <v>9.5</v>
       </c>
       <c r="D65" t="n">
-        <v>-23.8</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>18.3</v>
+        <v>18.7</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3358,21 +3358,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-5.4</v>
+        <v>-3.2</v>
       </c>
       <c r="D66" t="n">
-        <v>-23.8</v>
+        <v>-21.7</v>
       </c>
       <c r="E66" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -3384,567 +3384,567 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="D67" t="n">
-        <v>-3.3</v>
+        <v>-3.2</v>
       </c>
       <c r="E67" t="n">
         <v>18.2</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-5.9</v>
+        <v>-2</v>
       </c>
       <c r="D68" t="n">
-        <v>-23.8</v>
+        <v>-20.1</v>
       </c>
       <c r="E68" t="n">
-        <v>17.8</v>
+        <v>18.1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.1</v>
+        <v>9.5</v>
       </c>
       <c r="D69" t="n">
-        <v>-17.5</v>
+        <v>-8.6</v>
       </c>
       <c r="E69" t="n">
-        <v>17.6</v>
+        <v>18.1</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-8.1</v>
+        <v>9.5</v>
       </c>
       <c r="D70" t="n">
-        <v>-25.1</v>
+        <v>-8.4</v>
       </c>
       <c r="E70" t="n">
-        <v>17.1</v>
+        <v>17.9</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>30.9</v>
+        <v>-4.4</v>
       </c>
       <c r="D71" t="n">
-        <v>14.9</v>
+        <v>-21.7</v>
       </c>
       <c r="E71" t="n">
-        <v>16</v>
+        <v>17.3</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-8.1</v>
+        <v>-2</v>
       </c>
       <c r="D72" t="n">
-        <v>-23.8</v>
+        <v>-19.1</v>
       </c>
       <c r="E72" t="n">
-        <v>15.7</v>
+        <v>17.1</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7.2</v>
+        <v>55.1</v>
       </c>
       <c r="D73" t="n">
-        <v>-8.1</v>
+        <v>38.1</v>
       </c>
       <c r="E73" t="n">
-        <v>15.3</v>
+        <v>17.1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>FRO</t>
-        </is>
-      </c>
       <c r="C74" t="n">
-        <v>0.1</v>
+        <v>15</v>
       </c>
       <c r="D74" t="n">
-        <v>-14.9</v>
+        <v>-2</v>
       </c>
       <c r="E74" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14.9</v>
+        <v>-3.2</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1</v>
+        <v>-20.1</v>
       </c>
       <c r="E75" t="n">
-        <v>14.8</v>
+        <v>16.9</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-3.3</v>
+        <v>-28</v>
       </c>
       <c r="D76" t="n">
-        <v>-17.5</v>
+        <v>-44.7</v>
       </c>
       <c r="E76" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7.2</v>
+        <v>-3.2</v>
       </c>
       <c r="D77" t="n">
-        <v>-5.9</v>
+        <v>-19.1</v>
       </c>
       <c r="E77" t="n">
-        <v>13.2</v>
+        <v>15.9</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7.2</v>
+        <v>-4.4</v>
       </c>
       <c r="D78" t="n">
-        <v>-5.4</v>
+        <v>-20.1</v>
       </c>
       <c r="E78" t="n">
-        <v>12.7</v>
+        <v>15.7</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>7.2</v>
+        <v>-4.4</v>
       </c>
       <c r="D79" t="n">
-        <v>-5.4</v>
+        <v>-19.1</v>
       </c>
       <c r="E79" t="n">
-        <v>12.6</v>
+        <v>14.7</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4.1</v>
+        <v>9.5</v>
       </c>
       <c r="D80" t="n">
-        <v>-8.1</v>
+        <v>-4.4</v>
       </c>
       <c r="E80" t="n">
-        <v>12.2</v>
+        <v>13.9</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-5.4</v>
+        <v>15</v>
       </c>
       <c r="D81" t="n">
-        <v>-17.5</v>
+        <v>1.3</v>
       </c>
       <c r="E81" t="n">
-        <v>12.1</v>
+        <v>13.7</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-5.4</v>
+        <v>-8.4</v>
       </c>
       <c r="D82" t="n">
-        <v>-17.5</v>
+        <v>-21.7</v>
       </c>
       <c r="E82" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-3.3</v>
+        <v>-8.6</v>
       </c>
       <c r="D83" t="n">
-        <v>-14.9</v>
+        <v>-21.7</v>
       </c>
       <c r="E83" t="n">
-        <v>11.6</v>
+        <v>13.1</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-5.9</v>
+        <v>9.5</v>
       </c>
       <c r="D84" t="n">
-        <v>-17.5</v>
+        <v>-3.2</v>
       </c>
       <c r="E84" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>14.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D85" t="n">
-        <v>4.1</v>
+        <v>-21.7</v>
       </c>
       <c r="E85" t="n">
-        <v>10.8</v>
+        <v>12.5</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7.2</v>
+        <v>-8.4</v>
       </c>
       <c r="D86" t="n">
-        <v>-3.3</v>
+        <v>-20.1</v>
       </c>
       <c r="E86" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-14.9</v>
+        <v>-8.6</v>
       </c>
       <c r="D87" t="n">
-        <v>-25.1</v>
+        <v>-20.1</v>
       </c>
       <c r="E87" t="n">
-        <v>10.2</v>
+        <v>11.5</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4.1</v>
+        <v>9.5</v>
       </c>
       <c r="D88" t="n">
-        <v>-5.9</v>
+        <v>-2</v>
       </c>
       <c r="E88" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
@@ -3960,13 +3960,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-8.1</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D89" t="n">
-        <v>-17.5</v>
+        <v>-20.1</v>
       </c>
       <c r="E89" t="n">
-        <v>9.5</v>
+        <v>10.9</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3977,26 +3977,26 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4.1</v>
+        <v>-8.4</v>
       </c>
       <c r="D90" t="n">
-        <v>-5.4</v>
+        <v>-19.1</v>
       </c>
       <c r="E90" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -4008,21 +4008,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="D91" t="n">
-        <v>-5.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -4038,13 +4038,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-5.4</v>
+        <v>-8.6</v>
       </c>
       <c r="D92" t="n">
-        <v>-14.9</v>
+        <v>-19.1</v>
       </c>
       <c r="E92" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4064,121 +4064,121 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-5.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D93" t="n">
-        <v>-14.9</v>
+        <v>-19.1</v>
       </c>
       <c r="E93" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-5.9</v>
+        <v>1.3</v>
       </c>
       <c r="D94" t="n">
-        <v>-14.9</v>
+        <v>-8.6</v>
       </c>
       <c r="E94" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-14.9</v>
+        <v>1.3</v>
       </c>
       <c r="D95" t="n">
-        <v>-23.8</v>
+        <v>-8.4</v>
       </c>
       <c r="E95" t="n">
-        <v>8.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.1</v>
+        <v>-19.1</v>
       </c>
       <c r="D96" t="n">
-        <v>-8.1</v>
+        <v>-28</v>
       </c>
       <c r="E96" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>14.9</v>
+        <v>9.5</v>
       </c>
       <c r="D97" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="E97" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -4190,106 +4190,106 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-17.5</v>
+        <v>-20.1</v>
       </c>
       <c r="D98" t="n">
-        <v>-25.1</v>
+        <v>-28</v>
       </c>
       <c r="E98" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4.1</v>
+        <v>-2</v>
       </c>
       <c r="D99" t="n">
-        <v>-3.3</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E99" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>7.2</v>
+        <v>-2</v>
       </c>
       <c r="D100" t="n">
-        <v>0.1</v>
+        <v>-8.6</v>
       </c>
       <c r="E100" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-8.1</v>
+        <v>-2</v>
       </c>
       <c r="D101" t="n">
-        <v>-14.9</v>
+        <v>-8.4</v>
       </c>
       <c r="E101" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4298,225 +4298,225 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-17.5</v>
+        <v>-21.7</v>
       </c>
       <c r="D102" t="n">
-        <v>-23.8</v>
+        <v>-28</v>
       </c>
       <c r="E102" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.1</v>
+        <v>-3.2</v>
       </c>
       <c r="D103" t="n">
-        <v>-5.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E103" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="D104" t="n">
-        <v>-5.4</v>
+        <v>-4.4</v>
       </c>
       <c r="E104" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.1</v>
+        <v>15</v>
       </c>
       <c r="D105" t="n">
-        <v>-5.4</v>
+        <v>9.5</v>
       </c>
       <c r="E105" t="n">
         <v>5.5</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>-3.3</v>
+        <v>-3.2</v>
       </c>
       <c r="D106" t="n">
-        <v>-8.1</v>
+        <v>-8.6</v>
       </c>
       <c r="E106" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>35.3</v>
+        <v>-3.2</v>
       </c>
       <c r="D107" t="n">
-        <v>30.9</v>
+        <v>-8.4</v>
       </c>
       <c r="E107" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4.1</v>
+        <v>-4.4</v>
       </c>
       <c r="D108" t="n">
-        <v>0.1</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E108" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="D109" t="n">
-        <v>-3.3</v>
+        <v>-3.2</v>
       </c>
       <c r="E109" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>7.2</v>
+        <v>-4.4</v>
       </c>
       <c r="D110" t="n">
-        <v>4.1</v>
+        <v>-8.6</v>
       </c>
       <c r="E110" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -4532,13 +4532,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-3.3</v>
+        <v>-4.4</v>
       </c>
       <c r="D111" t="n">
-        <v>-5.9</v>
+        <v>-8.4</v>
       </c>
       <c r="E111" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -4549,26 +4549,26 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-5.4</v>
+        <v>1.3</v>
       </c>
       <c r="D112" t="n">
-        <v>-8.1</v>
+        <v>-2</v>
       </c>
       <c r="E112" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
@@ -4580,229 +4580,229 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-14.9</v>
+        <v>-19.1</v>
       </c>
       <c r="D113" t="n">
-        <v>-17.5</v>
+        <v>-21.7</v>
       </c>
       <c r="E113" t="n">
         <v>2.6</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-5.4</v>
+        <v>-2</v>
       </c>
       <c r="D114" t="n">
-        <v>-8.1</v>
+        <v>-4.4</v>
       </c>
       <c r="E114" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-3.3</v>
+        <v>-20.1</v>
       </c>
       <c r="D115" t="n">
-        <v>-5.4</v>
+        <v>-21.7</v>
       </c>
       <c r="E115" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-3.3</v>
+        <v>-2</v>
       </c>
       <c r="D116" t="n">
-        <v>-5.4</v>
+        <v>-3.2</v>
       </c>
       <c r="E116" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-5.9</v>
+        <v>-3.2</v>
       </c>
       <c r="D117" t="n">
-        <v>-8.1</v>
+        <v>-4.4</v>
       </c>
       <c r="E117" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-23.8</v>
+        <v>-19.1</v>
       </c>
       <c r="D118" t="n">
-        <v>-25.1</v>
+        <v>-20.1</v>
       </c>
       <c r="E118" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-5.4</v>
+        <v>-8.4</v>
       </c>
       <c r="D119" t="n">
-        <v>-5.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E119" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-5.4</v>
+        <v>-8.6</v>
       </c>
       <c r="D120" t="n">
-        <v>-5.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E120" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>TRMD</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>SBLK</t>
-        </is>
-      </c>
       <c r="C121" t="n">
-        <v>-5.4</v>
+        <v>-8.4</v>
       </c>
       <c r="D121" t="n">
-        <v>-5.4</v>
+        <v>-8.6</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>37.14</v>
+        <v>37.99</v>
       </c>
       <c r="E2" t="n">
         <v>75</v>
@@ -541,13 +541,13 @@
         <v>57.61</v>
       </c>
       <c r="J2" t="n">
-        <v>101.9</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>-6.6</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>55.1</v>
+        <v>51.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,42 +572,42 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>72.76000000000001</v>
+        <v>12.74</v>
       </c>
       <c r="E3" t="n">
-        <v>85.68000000000001</v>
+        <v>24.52</v>
       </c>
       <c r="F3" t="n">
-        <v>75.81</v>
+        <v>19.94</v>
       </c>
       <c r="G3" t="n">
-        <v>61.21</v>
+        <v>9.23</v>
       </c>
       <c r="H3" t="n">
-        <v>59.57</v>
+        <v>7.59</v>
       </c>
       <c r="I3" t="n">
-        <v>73.7</v>
+        <v>17.68</v>
       </c>
       <c r="J3" t="n">
-        <v>17.8</v>
+        <v>92.5</v>
       </c>
       <c r="K3" t="n">
-        <v>-18.1</v>
+        <v>-40.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>38.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -621,42 +621,42 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.6</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>19.63</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>16.23</v>
+        <v>75.81</v>
       </c>
       <c r="G4" t="n">
-        <v>9.890000000000001</v>
+        <v>61.21</v>
       </c>
       <c r="H4" t="n">
-        <v>9.07</v>
+        <v>59.57</v>
       </c>
       <c r="I4" t="n">
-        <v>15.08</v>
+        <v>73.7</v>
       </c>
       <c r="J4" t="n">
-        <v>18.3</v>
+        <v>15.7</v>
       </c>
       <c r="K4" t="n">
-        <v>-45.4</v>
+        <v>-19.6</v>
       </c>
       <c r="L4" t="n">
-        <v>-9.199999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,31 +670,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.28</v>
+        <v>16.925</v>
       </c>
       <c r="E5" t="n">
-        <v>40.78</v>
+        <v>19.63</v>
       </c>
       <c r="F5" t="n">
-        <v>32.42</v>
+        <v>16.23</v>
       </c>
       <c r="G5" t="n">
-        <v>16.1</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>13.98</v>
+        <v>9.07</v>
       </c>
       <c r="I5" t="n">
-        <v>29.36</v>
+        <v>15.08</v>
       </c>
       <c r="J5" t="n">
-        <v>12.4</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>-61.5</v>
+        <v>-46.4</v>
       </c>
       <c r="L5" t="n">
-        <v>-19.1</v>
+        <v>-10.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>49.2</v>
+        <v>50.57</v>
       </c>
       <c r="E6" t="n">
         <v>54.22</v>
@@ -737,13 +737,13 @@
         <v>39.33</v>
       </c>
       <c r="J6" t="n">
-        <v>10.2</v>
+        <v>7.2</v>
       </c>
       <c r="K6" t="n">
-        <v>-60.1</v>
+        <v>-61.2</v>
       </c>
       <c r="L6" t="n">
-        <v>-20.1</v>
+        <v>-22.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -754,12 +754,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -768,31 +768,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>82.61</v>
+        <v>38.08</v>
       </c>
       <c r="E7" t="n">
-        <v>74.11</v>
+        <v>40.78</v>
       </c>
       <c r="F7" t="n">
-        <v>63.97</v>
+        <v>32.42</v>
       </c>
       <c r="G7" t="n">
-        <v>42.1</v>
+        <v>16.1</v>
       </c>
       <c r="H7" t="n">
-        <v>38.16</v>
+        <v>13.98</v>
       </c>
       <c r="I7" t="n">
-        <v>59.47</v>
+        <v>29.36</v>
       </c>
       <c r="J7" t="n">
-        <v>-10.3</v>
+        <v>7.1</v>
       </c>
       <c r="K7" t="n">
-        <v>-53.8</v>
+        <v>-63.3</v>
       </c>
       <c r="L7" t="n">
-        <v>-28</v>
+        <v>-22.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -803,47 +803,96 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>INSW</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>crude</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>84.295</v>
+      </c>
+      <c r="E8" t="n">
+        <v>74.11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>63.97</v>
+      </c>
+      <c r="G8" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>38.16</v>
+      </c>
+      <c r="I8" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-54.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-29.4</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>whole-company</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>crude</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D9" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="E9" t="n">
         <v>4.17</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>3.19</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G9" t="n">
         <v>1.34</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H9" t="n">
         <v>1.19</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I9" t="n">
         <v>2.86</v>
       </c>
-      <c r="J8" t="n">
-        <v>-19.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-77</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-44.7</v>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="J9" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-77.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-45.6</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
@@ -980,7 +1029,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.46</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="n">
         <v>48.52</v>
@@ -1001,13 +1050,13 @@
         <v>29.63</v>
       </c>
       <c r="K2" t="n">
-        <v>126.1</v>
+        <v>118.5</v>
       </c>
       <c r="L2" t="n">
-        <v>-102.1</v>
+        <v>-102</v>
       </c>
       <c r="M2" t="n">
-        <v>38.1</v>
+        <v>33.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1038,7 +1087,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30.34</v>
+        <v>31.098</v>
       </c>
       <c r="E3" t="n">
         <v>39.76</v>
@@ -1059,13 +1108,13 @@
         <v>29.73</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>27.8</v>
       </c>
       <c r="L3" t="n">
-        <v>-54.5</v>
+        <v>-55.6</v>
       </c>
       <c r="M3" t="n">
-        <v>-2</v>
+        <v>-4.4</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1198,7 +1247,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>76.45999999999999</v>
+        <v>77.94</v>
       </c>
       <c r="E2" t="n">
         <v>90.78</v>
@@ -1219,17 +1268,17 @@
         <v>73.13</v>
       </c>
       <c r="K2" t="n">
-        <v>18.7</v>
+        <v>16.5</v>
       </c>
       <c r="L2" t="n">
-        <v>-37.4</v>
+        <v>-38.6</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.4</v>
+        <v>-6.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1299,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.43</v>
+        <v>16.89</v>
       </c>
       <c r="E3" t="n">
         <v>18.05</v>
@@ -1271,13 +1320,13 @@
         <v>15.05</v>
       </c>
       <c r="K3" t="n">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
       <c r="L3" t="n">
-        <v>-42.7</v>
+        <v>-44.3</v>
       </c>
       <c r="M3" t="n">
-        <v>-8.4</v>
+        <v>-10.9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1302,7 +1351,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.18</v>
+        <v>29.98</v>
       </c>
       <c r="E4" t="n">
         <v>39.1</v>
@@ -1323,13 +1372,13 @@
         <v>26.68</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>30.4</v>
       </c>
       <c r="L4" t="n">
-        <v>-62.8</v>
+        <v>-63.8</v>
       </c>
       <c r="M4" t="n">
-        <v>-8.6</v>
+        <v>-11</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1354,7 +1403,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7.36</v>
+        <v>7.44</v>
       </c>
       <c r="E5" t="n">
         <v>8.279999999999999</v>
@@ -1375,13 +1424,13 @@
         <v>5.77</v>
       </c>
       <c r="K5" t="n">
-        <v>12.5</v>
+        <v>11.3</v>
       </c>
       <c r="L5" t="n">
-        <v>-64</v>
+        <v>-64.40000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-21.7</v>
+        <v>-22.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1502,7 +1551,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.24</v>
+        <v>17.39</v>
       </c>
       <c r="E2" t="n">
         <v>23.74</v>
@@ -1520,13 +1569,13 @@
         <v>19.82</v>
       </c>
       <c r="J2" t="n">
-        <v>37.7</v>
+        <v>36.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.5</v>
+        <v>-4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1551,7 +1600,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.5</v>
+        <v>23.805</v>
       </c>
       <c r="E3" t="n">
         <v>32.91</v>
@@ -1569,13 +1618,13 @@
         <v>25.73</v>
       </c>
       <c r="J3" t="n">
-        <v>40</v>
+        <v>38.2</v>
       </c>
       <c r="K3" t="n">
-        <v>-17</v>
+        <v>-18.1</v>
       </c>
       <c r="L3" t="n">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1600,7 +1649,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26.57</v>
+        <v>27.06</v>
       </c>
       <c r="E4" t="n">
         <v>32.72</v>
@@ -1618,13 +1667,13 @@
         <v>25.72</v>
       </c>
       <c r="J4" t="n">
-        <v>23.2</v>
+        <v>20.9</v>
       </c>
       <c r="K4" t="n">
-        <v>-27.2</v>
+        <v>-28.5</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.2</v>
+        <v>-5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1643,7 +1692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1698,13 +1747,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.1</v>
+        <v>51.7</v>
       </c>
       <c r="D2" t="n">
-        <v>-44.7</v>
+        <v>-45.6</v>
       </c>
       <c r="E2" t="n">
-        <v>99.90000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1715,22 +1764,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>55.1</v>
+        <v>38.8</v>
       </c>
       <c r="D3" t="n">
-        <v>-28</v>
+        <v>-45.6</v>
       </c>
       <c r="E3" t="n">
-        <v>83.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1741,52 +1790,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38.1</v>
+        <v>51.7</v>
       </c>
       <c r="D4" t="n">
-        <v>-44.7</v>
+        <v>-29.4</v>
       </c>
       <c r="E4" t="n">
-        <v>82.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55.1</v>
+        <v>33.5</v>
       </c>
       <c r="D5" t="n">
-        <v>-21.7</v>
+        <v>-45.6</v>
       </c>
       <c r="E5" t="n">
-        <v>76.8</v>
+        <v>79</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1847,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.1</v>
+        <v>51.7</v>
       </c>
       <c r="D6" t="n">
-        <v>-20.1</v>
+        <v>-22.9</v>
       </c>
       <c r="E6" t="n">
-        <v>75.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1824,69 +1873,69 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55.1</v>
+        <v>51.7</v>
       </c>
       <c r="D7" t="n">
-        <v>-19.1</v>
+        <v>-22.5</v>
       </c>
       <c r="E7" t="n">
         <v>74.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38.1</v>
+        <v>51.7</v>
       </c>
       <c r="D8" t="n">
-        <v>-28</v>
+        <v>-22.2</v>
       </c>
       <c r="E8" t="n">
-        <v>66.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>55.1</v>
+        <v>38.8</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.199999999999999</v>
+        <v>-29.4</v>
       </c>
       <c r="E9" t="n">
-        <v>64.3</v>
+        <v>68.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1897,26 +1946,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>55.1</v>
+        <v>33.5</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.6</v>
+        <v>-29.4</v>
       </c>
       <c r="E10" t="n">
-        <v>63.7</v>
+        <v>62.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -1928,17 +1977,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>55.1</v>
+        <v>51.7</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.4</v>
+        <v>-11</v>
       </c>
       <c r="E11" t="n">
-        <v>63.5</v>
+        <v>62.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1949,111 +1998,111 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38.1</v>
+        <v>51.7</v>
       </c>
       <c r="D12" t="n">
-        <v>-21.7</v>
+        <v>-10.9</v>
       </c>
       <c r="E12" t="n">
-        <v>59.7</v>
+        <v>62.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>51.7</v>
       </c>
       <c r="D13" t="n">
-        <v>-44.7</v>
+        <v>-10.9</v>
       </c>
       <c r="E13" t="n">
-        <v>59.7</v>
+        <v>62.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>55.1</v>
+        <v>38.8</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.4</v>
+        <v>-22.9</v>
       </c>
       <c r="E14" t="n">
-        <v>59.5</v>
+        <v>61.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55.1</v>
+        <v>38.8</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.2</v>
+        <v>-22.5</v>
       </c>
       <c r="E15" t="n">
-        <v>58.3</v>
+        <v>61.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2062,43 +2111,43 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38.1</v>
+        <v>38.8</v>
       </c>
       <c r="D16" t="n">
-        <v>-20.1</v>
+        <v>-22.2</v>
       </c>
       <c r="E16" t="n">
-        <v>58.1</v>
+        <v>61</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38.1</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>-19.1</v>
+        <v>-45.6</v>
       </c>
       <c r="E17" t="n">
-        <v>57.1</v>
+        <v>59.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -2110,73 +2159,73 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>55.1</v>
+        <v>51.7</v>
       </c>
       <c r="D18" t="n">
-        <v>-2</v>
+        <v>-6.2</v>
       </c>
       <c r="E18" t="n">
-        <v>57.1</v>
+        <v>57.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.5</v>
+        <v>51.7</v>
       </c>
       <c r="D19" t="n">
-        <v>-44.7</v>
+        <v>-5</v>
       </c>
       <c r="E19" t="n">
-        <v>54.2</v>
+        <v>56.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>55.1</v>
+        <v>33.5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3</v>
+        <v>-22.9</v>
       </c>
       <c r="E20" t="n">
-        <v>53.8</v>
+        <v>56.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -2188,47 +2237,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38.1</v>
+        <v>33.5</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.199999999999999</v>
+        <v>-22.5</v>
       </c>
       <c r="E21" t="n">
-        <v>47.2</v>
+        <v>56</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38.1</v>
+        <v>51.7</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.6</v>
+        <v>-4.4</v>
       </c>
       <c r="E22" t="n">
-        <v>46.6</v>
+        <v>56</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2240,28 +2289,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38.1</v>
+        <v>33.5</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.4</v>
+        <v>-22.2</v>
       </c>
       <c r="E23" t="n">
-        <v>46.5</v>
+        <v>55.7</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2270,17 +2319,17 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="D24" t="n">
-        <v>-44.7</v>
+        <v>-45.6</v>
       </c>
       <c r="E24" t="n">
-        <v>46</v>
+        <v>53.7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -2292,106 +2341,106 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>55.1</v>
+        <v>51.7</v>
       </c>
       <c r="D25" t="n">
-        <v>9.5</v>
+        <v>-0.5</v>
       </c>
       <c r="E25" t="n">
-        <v>45.6</v>
+        <v>52.1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>38.8</v>
       </c>
       <c r="D26" t="n">
-        <v>-28</v>
+        <v>-11</v>
       </c>
       <c r="E26" t="n">
-        <v>43</v>
+        <v>49.8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-2</v>
+        <v>38.8</v>
       </c>
       <c r="D27" t="n">
-        <v>-44.7</v>
+        <v>-10.9</v>
       </c>
       <c r="E27" t="n">
-        <v>42.7</v>
+        <v>49.7</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38.1</v>
+        <v>38.8</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.4</v>
+        <v>-10.9</v>
       </c>
       <c r="E28" t="n">
-        <v>42.4</v>
+        <v>49.6</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2400,69 +2449,69 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-3.2</v>
+        <v>-0.5</v>
       </c>
       <c r="D29" t="n">
-        <v>-44.7</v>
+        <v>-45.6</v>
       </c>
       <c r="E29" t="n">
-        <v>41.5</v>
+        <v>45.1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38.1</v>
+        <v>38.8</v>
       </c>
       <c r="D30" t="n">
-        <v>-3.2</v>
+        <v>-6.2</v>
       </c>
       <c r="E30" t="n">
-        <v>41.3</v>
+        <v>44.9</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-4.4</v>
+        <v>33.5</v>
       </c>
       <c r="D31" t="n">
-        <v>-44.7</v>
+        <v>-11</v>
       </c>
       <c r="E31" t="n">
-        <v>40.4</v>
+        <v>44.5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -2474,99 +2523,99 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38.1</v>
+        <v>33.5</v>
       </c>
       <c r="D32" t="n">
-        <v>-2</v>
+        <v>-10.9</v>
       </c>
       <c r="E32" t="n">
-        <v>40.1</v>
+        <v>44.4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>55.1</v>
+        <v>33.5</v>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>-10.9</v>
       </c>
       <c r="E33" t="n">
-        <v>40.1</v>
+        <v>44.4</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9.5</v>
+        <v>38.8</v>
       </c>
       <c r="D34" t="n">
-        <v>-28</v>
+        <v>-5</v>
       </c>
       <c r="E34" t="n">
-        <v>37.5</v>
+        <v>43.7</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38.1</v>
+        <v>51.7</v>
       </c>
       <c r="D35" t="n">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="E35" t="n">
-        <v>36.8</v>
+        <v>43.6</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2578,54 +2627,54 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D36" t="n">
-        <v>-21.7</v>
+        <v>-29.4</v>
       </c>
       <c r="E36" t="n">
-        <v>36.6</v>
+        <v>43.4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-8.4</v>
+        <v>38.8</v>
       </c>
       <c r="D37" t="n">
-        <v>-44.7</v>
+        <v>-4.4</v>
       </c>
       <c r="E37" t="n">
-        <v>36.3</v>
+        <v>43.1</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2634,24 +2683,24 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-8.6</v>
+        <v>-4.4</v>
       </c>
       <c r="D38" t="n">
-        <v>-44.7</v>
+        <v>-45.6</v>
       </c>
       <c r="E38" t="n">
-        <v>36.1</v>
+        <v>41.2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2660,173 +2709,173 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-9.199999999999999</v>
+        <v>-5</v>
       </c>
       <c r="D39" t="n">
-        <v>-44.7</v>
+        <v>-45.6</v>
       </c>
       <c r="E39" t="n">
-        <v>35.6</v>
+        <v>40.6</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>15</v>
+        <v>33.5</v>
       </c>
       <c r="D40" t="n">
-        <v>-20.1</v>
+        <v>-6.2</v>
       </c>
       <c r="E40" t="n">
-        <v>35</v>
+        <v>39.6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>15</v>
+        <v>-6.2</v>
       </c>
       <c r="D41" t="n">
-        <v>-19.1</v>
+        <v>-45.6</v>
       </c>
       <c r="E41" t="n">
-        <v>34.1</v>
+        <v>39.4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9.5</v>
+        <v>38.8</v>
       </c>
       <c r="D42" t="n">
-        <v>-21.7</v>
+        <v>-0.5</v>
       </c>
       <c r="E42" t="n">
-        <v>31.2</v>
+        <v>39.2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9.5</v>
+        <v>33.5</v>
       </c>
       <c r="D43" t="n">
-        <v>-20.1</v>
+        <v>-5</v>
       </c>
       <c r="E43" t="n">
-        <v>29.6</v>
+        <v>38.4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.3</v>
+        <v>33.5</v>
       </c>
       <c r="D44" t="n">
-        <v>-28</v>
+        <v>-4.4</v>
       </c>
       <c r="E44" t="n">
-        <v>29.3</v>
+        <v>37.9</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38.1</v>
+        <v>51.7</v>
       </c>
       <c r="D45" t="n">
-        <v>9.5</v>
+        <v>14</v>
       </c>
       <c r="E45" t="n">
-        <v>28.6</v>
+        <v>37.7</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2838,106 +2887,106 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="D46" t="n">
-        <v>-19.1</v>
+        <v>-29.4</v>
       </c>
       <c r="E46" t="n">
-        <v>28.6</v>
+        <v>37.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="D47" t="n">
-        <v>-28</v>
+        <v>-22.9</v>
       </c>
       <c r="E47" t="n">
-        <v>26</v>
+        <v>36.9</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-19.1</v>
+        <v>14</v>
       </c>
       <c r="D48" t="n">
-        <v>-44.7</v>
+        <v>-22.5</v>
       </c>
       <c r="E48" t="n">
-        <v>25.6</v>
+        <v>36.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-3.2</v>
+        <v>14</v>
       </c>
       <c r="D49" t="n">
-        <v>-28</v>
+        <v>-22.2</v>
       </c>
       <c r="E49" t="n">
-        <v>24.8</v>
+        <v>36.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2946,13 +2995,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-20.1</v>
+        <v>-10.9</v>
       </c>
       <c r="D50" t="n">
-        <v>-44.7</v>
+        <v>-45.6</v>
       </c>
       <c r="E50" t="n">
-        <v>24.7</v>
+        <v>34.7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2963,182 +3012,182 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>15</v>
+        <v>-10.9</v>
       </c>
       <c r="D51" t="n">
-        <v>-9.199999999999999</v>
+        <v>-45.6</v>
       </c>
       <c r="E51" t="n">
-        <v>24.2</v>
+        <v>34.7</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-4.4</v>
+        <v>-11</v>
       </c>
       <c r="D52" t="n">
-        <v>-28</v>
+        <v>-45.6</v>
       </c>
       <c r="E52" t="n">
-        <v>23.7</v>
+        <v>34.5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>15</v>
+        <v>33.5</v>
       </c>
       <c r="D53" t="n">
-        <v>-8.6</v>
+        <v>-0.5</v>
       </c>
       <c r="E53" t="n">
-        <v>23.6</v>
+        <v>34</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>15</v>
+        <v>8.1</v>
       </c>
       <c r="D54" t="n">
-        <v>-8.4</v>
+        <v>-22.9</v>
       </c>
       <c r="E54" t="n">
-        <v>23.4</v>
+        <v>31</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38.1</v>
+        <v>38.8</v>
       </c>
       <c r="D55" t="n">
-        <v>15</v>
+        <v>8.1</v>
       </c>
       <c r="E55" t="n">
-        <v>23.1</v>
+        <v>30.7</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>HAFN</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C56" t="n">
-        <v>-21.7</v>
+        <v>8.1</v>
       </c>
       <c r="D56" t="n">
-        <v>-44.7</v>
+        <v>-22.5</v>
       </c>
       <c r="E56" t="n">
-        <v>23.1</v>
+        <v>30.6</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="D57" t="n">
-        <v>-21.7</v>
+        <v>-22.2</v>
       </c>
       <c r="E57" t="n">
-        <v>23</v>
+        <v>30.3</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3150,47 +3199,47 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="D58" t="n">
-        <v>-20.1</v>
+        <v>-29.4</v>
       </c>
       <c r="E58" t="n">
-        <v>21.4</v>
+        <v>29</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.3</v>
+        <v>33.5</v>
       </c>
       <c r="D59" t="n">
-        <v>-19.1</v>
+        <v>8.1</v>
       </c>
       <c r="E59" t="n">
-        <v>20.4</v>
+        <v>25.4</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -3202,73 +3251,73 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-2</v>
+        <v>-4.4</v>
       </c>
       <c r="D60" t="n">
-        <v>-21.7</v>
+        <v>-29.4</v>
       </c>
       <c r="E60" t="n">
-        <v>19.7</v>
+        <v>25.1</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-8.4</v>
+        <v>14</v>
       </c>
       <c r="D61" t="n">
-        <v>-28</v>
+        <v>-11</v>
       </c>
       <c r="E61" t="n">
-        <v>19.6</v>
+        <v>25</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-8.6</v>
+        <v>14</v>
       </c>
       <c r="D62" t="n">
-        <v>-28</v>
+        <v>-10.9</v>
       </c>
       <c r="E62" t="n">
-        <v>19.4</v>
+        <v>24.9</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3280,17 +3329,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D63" t="n">
-        <v>-4.4</v>
+        <v>-10.9</v>
       </c>
       <c r="E63" t="n">
-        <v>19.3</v>
+        <v>24.9</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3301,189 +3350,189 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-9.199999999999999</v>
+        <v>38.8</v>
       </c>
       <c r="D64" t="n">
-        <v>-28</v>
+        <v>14</v>
       </c>
       <c r="E64" t="n">
-        <v>18.8</v>
+        <v>24.8</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>9.5</v>
+        <v>-5</v>
       </c>
       <c r="D65" t="n">
-        <v>-9.199999999999999</v>
+        <v>-29.4</v>
       </c>
       <c r="E65" t="n">
-        <v>18.7</v>
+        <v>24.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-3.2</v>
+        <v>-22.2</v>
       </c>
       <c r="D66" t="n">
-        <v>-21.7</v>
+        <v>-45.6</v>
       </c>
       <c r="E66" t="n">
-        <v>18.5</v>
+        <v>23.3</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>15</v>
+        <v>-6.2</v>
       </c>
       <c r="D67" t="n">
-        <v>-3.2</v>
+        <v>-29.4</v>
       </c>
       <c r="E67" t="n">
-        <v>18.2</v>
+        <v>23.3</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-2</v>
+        <v>-22.5</v>
       </c>
       <c r="D68" t="n">
-        <v>-20.1</v>
+        <v>-45.6</v>
       </c>
       <c r="E68" t="n">
-        <v>18.1</v>
+        <v>23.1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9.5</v>
+        <v>-22.9</v>
       </c>
       <c r="D69" t="n">
-        <v>-8.6</v>
+        <v>-45.6</v>
       </c>
       <c r="E69" t="n">
-        <v>18.1</v>
+        <v>22.7</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9.5</v>
+        <v>-0.5</v>
       </c>
       <c r="D70" t="n">
-        <v>-8.4</v>
+        <v>-22.9</v>
       </c>
       <c r="E70" t="n">
-        <v>17.9</v>
+        <v>22.4</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3492,362 +3541,362 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-4.4</v>
+        <v>-0.5</v>
       </c>
       <c r="D71" t="n">
-        <v>-21.7</v>
+        <v>-22.5</v>
       </c>
       <c r="E71" t="n">
-        <v>17.3</v>
+        <v>22</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-2</v>
+        <v>-0.5</v>
       </c>
       <c r="D72" t="n">
-        <v>-19.1</v>
+        <v>-22.2</v>
       </c>
       <c r="E72" t="n">
-        <v>17.1</v>
+        <v>21.7</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>55.1</v>
+        <v>14</v>
       </c>
       <c r="D73" t="n">
-        <v>38.1</v>
+        <v>-6.2</v>
       </c>
       <c r="E73" t="n">
-        <v>17.1</v>
+        <v>20.2</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>CMDB</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>FLNG</t>
-        </is>
-      </c>
       <c r="C74" t="n">
-        <v>15</v>
+        <v>33.5</v>
       </c>
       <c r="D74" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="E74" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-3.2</v>
+        <v>8.1</v>
       </c>
       <c r="D75" t="n">
-        <v>-20.1</v>
+        <v>-11</v>
       </c>
       <c r="E75" t="n">
-        <v>16.9</v>
+        <v>19.1</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-28</v>
+        <v>8.1</v>
       </c>
       <c r="D76" t="n">
-        <v>-44.7</v>
+        <v>-10.9</v>
       </c>
       <c r="E76" t="n">
-        <v>16.7</v>
+        <v>19</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-3.2</v>
+        <v>8.1</v>
       </c>
       <c r="D77" t="n">
-        <v>-19.1</v>
+        <v>-10.9</v>
       </c>
       <c r="E77" t="n">
-        <v>15.9</v>
+        <v>19</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-4.4</v>
+        <v>14</v>
       </c>
       <c r="D78" t="n">
-        <v>-20.1</v>
+        <v>-5</v>
       </c>
       <c r="E78" t="n">
-        <v>15.7</v>
+        <v>18.9</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-4.4</v>
+        <v>-10.9</v>
       </c>
       <c r="D79" t="n">
-        <v>-19.1</v>
+        <v>-29.4</v>
       </c>
       <c r="E79" t="n">
-        <v>14.7</v>
+        <v>18.5</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9.5</v>
+        <v>-4.4</v>
       </c>
       <c r="D80" t="n">
-        <v>-4.4</v>
+        <v>-22.9</v>
       </c>
       <c r="E80" t="n">
-        <v>13.9</v>
+        <v>18.5</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>15</v>
+        <v>-10.9</v>
       </c>
       <c r="D81" t="n">
-        <v>1.3</v>
+        <v>-29.4</v>
       </c>
       <c r="E81" t="n">
-        <v>13.7</v>
+        <v>18.5</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-8.4</v>
+        <v>-11</v>
       </c>
       <c r="D82" t="n">
-        <v>-21.7</v>
+        <v>-29.4</v>
       </c>
       <c r="E82" t="n">
-        <v>13.3</v>
+        <v>18.4</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-8.6</v>
+        <v>14</v>
       </c>
       <c r="D83" t="n">
-        <v>-21.7</v>
+        <v>-4.4</v>
       </c>
       <c r="E83" t="n">
-        <v>13.1</v>
+        <v>18.4</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9.5</v>
+        <v>51.7</v>
       </c>
       <c r="D84" t="n">
-        <v>-3.2</v>
+        <v>33.5</v>
       </c>
       <c r="E84" t="n">
-        <v>12.7</v>
+        <v>18.2</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3856,50 +3905,50 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-9.199999999999999</v>
+        <v>-4.4</v>
       </c>
       <c r="D85" t="n">
-        <v>-21.7</v>
+        <v>-22.5</v>
       </c>
       <c r="E85" t="n">
-        <v>12.5</v>
+        <v>18.1</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-8.4</v>
+        <v>-5</v>
       </c>
       <c r="D86" t="n">
-        <v>-20.1</v>
+        <v>-22.9</v>
       </c>
       <c r="E86" t="n">
-        <v>11.6</v>
+        <v>18</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3908,50 +3957,50 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-8.6</v>
+        <v>-4.4</v>
       </c>
       <c r="D87" t="n">
-        <v>-20.1</v>
+        <v>-22.2</v>
       </c>
       <c r="E87" t="n">
-        <v>11.5</v>
+        <v>17.8</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9.5</v>
+        <v>-5</v>
       </c>
       <c r="D88" t="n">
-        <v>-2</v>
+        <v>-22.5</v>
       </c>
       <c r="E88" t="n">
-        <v>11.5</v>
+        <v>17.6</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3960,24 +4009,24 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-9.199999999999999</v>
+        <v>-5</v>
       </c>
       <c r="D89" t="n">
-        <v>-20.1</v>
+        <v>-22.2</v>
       </c>
       <c r="E89" t="n">
-        <v>10.9</v>
+        <v>17.3</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3986,13 +4035,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-8.4</v>
+        <v>-6.2</v>
       </c>
       <c r="D90" t="n">
-        <v>-19.1</v>
+        <v>-22.9</v>
       </c>
       <c r="E90" t="n">
-        <v>10.7</v>
+        <v>16.7</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4003,22 +4052,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1.3</v>
+        <v>-6.2</v>
       </c>
       <c r="D91" t="n">
-        <v>-9.199999999999999</v>
+        <v>-22.5</v>
       </c>
       <c r="E91" t="n">
-        <v>10.5</v>
+        <v>16.3</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4029,360 +4078,360 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-8.6</v>
+        <v>-29.4</v>
       </c>
       <c r="D92" t="n">
-        <v>-19.1</v>
+        <v>-45.6</v>
       </c>
       <c r="E92" t="n">
-        <v>10.5</v>
+        <v>16.1</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-9.199999999999999</v>
+        <v>-6.2</v>
       </c>
       <c r="D93" t="n">
-        <v>-19.1</v>
+        <v>-22.2</v>
       </c>
       <c r="E93" t="n">
-        <v>9.9</v>
+        <v>16</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>TNK</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>TRMD</t>
-        </is>
-      </c>
       <c r="C94" t="n">
-        <v>1.3</v>
+        <v>14</v>
       </c>
       <c r="D94" t="n">
-        <v>-8.6</v>
+        <v>-0.5</v>
       </c>
       <c r="E94" t="n">
-        <v>9.9</v>
+        <v>14.5</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="D95" t="n">
-        <v>-8.4</v>
+        <v>-6.2</v>
       </c>
       <c r="E95" t="n">
-        <v>9.699999999999999</v>
+        <v>14.3</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-19.1</v>
+        <v>8.1</v>
       </c>
       <c r="D96" t="n">
-        <v>-28</v>
+        <v>-5</v>
       </c>
       <c r="E96" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>9.5</v>
+        <v>51.7</v>
       </c>
       <c r="D97" t="n">
-        <v>1.3</v>
+        <v>38.8</v>
       </c>
       <c r="E97" t="n">
-        <v>8.199999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-20.1</v>
+        <v>8.1</v>
       </c>
       <c r="D98" t="n">
-        <v>-28</v>
+        <v>-4.4</v>
       </c>
       <c r="E98" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-2</v>
+        <v>-10.9</v>
       </c>
       <c r="D99" t="n">
-        <v>-9.199999999999999</v>
+        <v>-22.9</v>
       </c>
       <c r="E99" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-2</v>
+        <v>-10.9</v>
       </c>
       <c r="D100" t="n">
-        <v>-8.6</v>
+        <v>-22.9</v>
       </c>
       <c r="E100" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="D101" t="n">
-        <v>-8.4</v>
+        <v>-22.9</v>
       </c>
       <c r="E101" t="n">
-        <v>6.4</v>
+        <v>11.9</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>HAFN</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>INSW (WHOLE-CO)</t>
-        </is>
-      </c>
       <c r="C102" t="n">
-        <v>-21.7</v>
+        <v>-10.9</v>
       </c>
       <c r="D102" t="n">
-        <v>-28</v>
+        <v>-22.5</v>
       </c>
       <c r="E102" t="n">
-        <v>6.3</v>
+        <v>11.6</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-3.2</v>
+        <v>-10.9</v>
       </c>
       <c r="D103" t="n">
-        <v>-9.199999999999999</v>
+        <v>-22.5</v>
       </c>
       <c r="E103" t="n">
-        <v>6</v>
+        <v>11.6</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1.3</v>
+        <v>-11</v>
       </c>
       <c r="D104" t="n">
-        <v>-4.4</v>
+        <v>-22.5</v>
       </c>
       <c r="E104" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>15</v>
+        <v>-10.9</v>
       </c>
       <c r="D105" t="n">
-        <v>9.5</v>
+        <v>-22.2</v>
       </c>
       <c r="E105" t="n">
-        <v>5.5</v>
+        <v>11.3</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -4393,78 +4442,78 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>-3.2</v>
+        <v>-10.9</v>
       </c>
       <c r="D106" t="n">
-        <v>-8.6</v>
+        <v>-22.2</v>
       </c>
       <c r="E106" t="n">
-        <v>5.4</v>
+        <v>11.3</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-3.2</v>
+        <v>-11</v>
       </c>
       <c r="D107" t="n">
-        <v>-8.4</v>
+        <v>-22.2</v>
       </c>
       <c r="E107" t="n">
-        <v>5.2</v>
+        <v>11.2</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>-4.4</v>
+        <v>-0.5</v>
       </c>
       <c r="D108" t="n">
-        <v>-9.199999999999999</v>
+        <v>-11</v>
       </c>
       <c r="E108" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -4476,125 +4525,125 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="D109" t="n">
-        <v>-3.2</v>
+        <v>-10.9</v>
       </c>
       <c r="E109" t="n">
-        <v>4.5</v>
+        <v>10.4</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-4.4</v>
+        <v>-0.5</v>
       </c>
       <c r="D110" t="n">
-        <v>-8.6</v>
+        <v>-10.9</v>
       </c>
       <c r="E110" t="n">
-        <v>4.2</v>
+        <v>10.4</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-4.4</v>
+        <v>8.1</v>
       </c>
       <c r="D111" t="n">
-        <v>-8.4</v>
+        <v>-0.5</v>
       </c>
       <c r="E111" t="n">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1.3</v>
+        <v>-22.2</v>
       </c>
       <c r="D112" t="n">
-        <v>-2</v>
+        <v>-29.4</v>
       </c>
       <c r="E112" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-19.1</v>
+        <v>-22.5</v>
       </c>
       <c r="D113" t="n">
-        <v>-21.7</v>
+        <v>-29.4</v>
       </c>
       <c r="E113" t="n">
-        <v>2.6</v>
+        <v>6.9</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4606,17 +4655,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-2</v>
+        <v>-4.4</v>
       </c>
       <c r="D114" t="n">
-        <v>-4.4</v>
+        <v>-11</v>
       </c>
       <c r="E114" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -4627,26 +4676,26 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-20.1</v>
+        <v>-22.9</v>
       </c>
       <c r="D115" t="n">
-        <v>-21.7</v>
+        <v>-29.4</v>
       </c>
       <c r="E115" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4658,80 +4707,80 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-2</v>
+        <v>-4.4</v>
       </c>
       <c r="D116" t="n">
-        <v>-3.2</v>
+        <v>-10.9</v>
       </c>
       <c r="E116" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-3.2</v>
+        <v>-4.4</v>
       </c>
       <c r="D117" t="n">
-        <v>-4.4</v>
+        <v>-10.9</v>
       </c>
       <c r="E117" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-19.1</v>
+        <v>-5</v>
       </c>
       <c r="D118" t="n">
-        <v>-20.1</v>
+        <v>-11</v>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4740,69 +4789,485 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-8.4</v>
+        <v>-5</v>
       </c>
       <c r="D119" t="n">
-        <v>-9.199999999999999</v>
+        <v>-10.9</v>
       </c>
       <c r="E119" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-8.6</v>
+        <v>14</v>
       </c>
       <c r="D120" t="n">
-        <v>-9.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="E120" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>ASC</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="C121" t="n">
+        <v>-5</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="E121" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="E122" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>CAPT</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D123" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E123" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs lng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
         <is>
           <t>TRMD</t>
         </is>
       </c>
-      <c r="C121" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="D121" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="E121" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F121" t="inlineStr">
+      <c r="C124" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-11</v>
+      </c>
+      <c r="E124" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="E125" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="E126" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E127" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="E128" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs lng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>-5</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>-22.2</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-22.9</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-22.9</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>-22.2</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-11</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-11</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -526,28 +526,28 @@
         <v>37.99</v>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>80.95</v>
       </c>
       <c r="F2" t="n">
-        <v>61.65</v>
+        <v>66.91</v>
       </c>
       <c r="G2" t="n">
-        <v>38.67</v>
+        <v>42.25</v>
       </c>
       <c r="H2" t="n">
-        <v>34.68</v>
+        <v>38.38</v>
       </c>
       <c r="I2" t="n">
-        <v>57.61</v>
+        <v>62.56</v>
       </c>
       <c r="J2" t="n">
-        <v>97.40000000000001</v>
+        <v>113.1</v>
       </c>
       <c r="K2" t="n">
-        <v>-8.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>51.7</v>
+        <v>64.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1747,13 +1747,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>51.7</v>
+        <v>64.7</v>
       </c>
       <c r="D2" t="n">
         <v>-45.6</v>
       </c>
       <c r="E2" t="n">
-        <v>97.2</v>
+        <v>110.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1764,22 +1764,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38.8</v>
+        <v>64.7</v>
       </c>
       <c r="D3" t="n">
-        <v>-45.6</v>
+        <v>-29.4</v>
       </c>
       <c r="E3" t="n">
-        <v>84.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>51.7</v>
+        <v>64.7</v>
       </c>
       <c r="D4" t="n">
-        <v>-29.4</v>
+        <v>-22.9</v>
       </c>
       <c r="E4" t="n">
-        <v>81.09999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33.5</v>
+        <v>64.7</v>
       </c>
       <c r="D5" t="n">
-        <v>-45.6</v>
+        <v>-22.5</v>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>87.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -1847,17 +1847,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>51.7</v>
+        <v>64.7</v>
       </c>
       <c r="D6" t="n">
-        <v>-22.9</v>
+        <v>-22.2</v>
       </c>
       <c r="E6" t="n">
-        <v>74.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1868,104 +1868,104 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51.7</v>
+        <v>38.8</v>
       </c>
       <c r="D7" t="n">
-        <v>-22.5</v>
+        <v>-45.6</v>
       </c>
       <c r="E7" t="n">
-        <v>74.2</v>
+        <v>84.3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>51.7</v>
+        <v>33.5</v>
       </c>
       <c r="D8" t="n">
-        <v>-22.2</v>
+        <v>-45.6</v>
       </c>
       <c r="E8" t="n">
-        <v>73.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38.8</v>
+        <v>64.7</v>
       </c>
       <c r="D9" t="n">
-        <v>-29.4</v>
+        <v>-11</v>
       </c>
       <c r="E9" t="n">
-        <v>68.2</v>
+        <v>75.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>33.5</v>
+        <v>64.7</v>
       </c>
       <c r="D10" t="n">
-        <v>-29.4</v>
+        <v>-10.9</v>
       </c>
       <c r="E10" t="n">
-        <v>62.9</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -1977,17 +1977,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>51.7</v>
+        <v>64.7</v>
       </c>
       <c r="D11" t="n">
-        <v>-11</v>
+        <v>-10.9</v>
       </c>
       <c r="E11" t="n">
-        <v>62.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>51.7</v>
+        <v>64.7</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.9</v>
+        <v>-6.2</v>
       </c>
       <c r="E12" t="n">
-        <v>62.6</v>
+        <v>70.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2029,47 +2029,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>51.7</v>
+        <v>64.7</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.9</v>
+        <v>-5</v>
       </c>
       <c r="E13" t="n">
-        <v>62.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.8</v>
+        <v>64.7</v>
       </c>
       <c r="D14" t="n">
-        <v>-22.9</v>
+        <v>-4.4</v>
       </c>
       <c r="E14" t="n">
-        <v>61.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2081,177 +2081,177 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>38.8</v>
       </c>
       <c r="D15" t="n">
-        <v>-22.5</v>
+        <v>-29.4</v>
       </c>
       <c r="E15" t="n">
-        <v>61.3</v>
+        <v>68.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38.8</v>
+        <v>64.7</v>
       </c>
       <c r="D16" t="n">
-        <v>-22.2</v>
+        <v>-0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>61</v>
+        <v>65.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>33.5</v>
       </c>
       <c r="D17" t="n">
-        <v>-45.6</v>
+        <v>-29.4</v>
       </c>
       <c r="E17" t="n">
-        <v>59.6</v>
+        <v>62.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>51.7</v>
+        <v>38.8</v>
       </c>
       <c r="D18" t="n">
-        <v>-6.2</v>
+        <v>-22.9</v>
       </c>
       <c r="E18" t="n">
-        <v>57.8</v>
+        <v>61.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>51.7</v>
+        <v>38.8</v>
       </c>
       <c r="D19" t="n">
-        <v>-5</v>
+        <v>-22.5</v>
       </c>
       <c r="E19" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>33.5</v>
+        <v>38.8</v>
       </c>
       <c r="D20" t="n">
-        <v>-22.9</v>
+        <v>-22.2</v>
       </c>
       <c r="E20" t="n">
-        <v>56.4</v>
+        <v>61</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>33.5</v>
+        <v>14</v>
       </c>
       <c r="D21" t="n">
-        <v>-22.5</v>
+        <v>-45.6</v>
       </c>
       <c r="E21" t="n">
-        <v>56</v>
+        <v>59.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -2263,21 +2263,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>51.7</v>
+        <v>64.7</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4</v>
+        <v>8.1</v>
       </c>
       <c r="E22" t="n">
-        <v>56</v>
+        <v>56.6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2289,17 +2289,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>33.5</v>
       </c>
       <c r="D23" t="n">
-        <v>-22.2</v>
+        <v>-22.9</v>
       </c>
       <c r="E23" t="n">
-        <v>55.7</v>
+        <v>56.4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2310,104 +2310,104 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.1</v>
+        <v>33.5</v>
       </c>
       <c r="D24" t="n">
-        <v>-45.6</v>
+        <v>-22.5</v>
       </c>
       <c r="E24" t="n">
-        <v>53.7</v>
+        <v>56</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>51.7</v>
+        <v>33.5</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5</v>
+        <v>-22.2</v>
       </c>
       <c r="E25" t="n">
-        <v>52.1</v>
+        <v>55.7</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38.8</v>
+        <v>8.1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11</v>
+        <v>-45.6</v>
       </c>
       <c r="E26" t="n">
-        <v>49.8</v>
+        <v>53.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38.8</v>
+        <v>64.7</v>
       </c>
       <c r="D27" t="n">
-        <v>-10.9</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
-        <v>49.7</v>
+        <v>50.7</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2419,17 +2419,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>38.8</v>
       </c>
       <c r="D28" t="n">
-        <v>-10.9</v>
+        <v>-11</v>
       </c>
       <c r="E28" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2440,22 +2440,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.5</v>
+        <v>38.8</v>
       </c>
       <c r="D29" t="n">
-        <v>-45.6</v>
+        <v>-10.9</v>
       </c>
       <c r="E29" t="n">
-        <v>45.1</v>
+        <v>49.7</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2471,17 +2471,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>38.8</v>
       </c>
       <c r="D30" t="n">
-        <v>-6.2</v>
+        <v>-10.9</v>
       </c>
       <c r="E30" t="n">
-        <v>44.9</v>
+        <v>49.6</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2492,52 +2492,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>33.5</v>
+        <v>-0.5</v>
       </c>
       <c r="D31" t="n">
-        <v>-11</v>
+        <v>-45.6</v>
       </c>
       <c r="E31" t="n">
-        <v>44.5</v>
+        <v>45.1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>33.5</v>
+        <v>38.8</v>
       </c>
       <c r="D32" t="n">
-        <v>-10.9</v>
+        <v>-6.2</v>
       </c>
       <c r="E32" t="n">
-        <v>44.4</v>
+        <v>44.9</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -2549,17 +2549,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>33.5</v>
       </c>
       <c r="D33" t="n">
-        <v>-10.9</v>
+        <v>-11</v>
       </c>
       <c r="E33" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2570,137 +2570,137 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38.8</v>
+        <v>33.5</v>
       </c>
       <c r="D34" t="n">
-        <v>-5</v>
+        <v>-10.9</v>
       </c>
       <c r="E34" t="n">
-        <v>43.7</v>
+        <v>44.4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>51.7</v>
+        <v>33.5</v>
       </c>
       <c r="D35" t="n">
-        <v>8.1</v>
+        <v>-10.9</v>
       </c>
       <c r="E35" t="n">
-        <v>43.6</v>
+        <v>44.4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14</v>
+        <v>38.8</v>
       </c>
       <c r="D36" t="n">
-        <v>-29.4</v>
+        <v>-5</v>
       </c>
       <c r="E36" t="n">
-        <v>43.4</v>
+        <v>43.7</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38.8</v>
+        <v>14</v>
       </c>
       <c r="D37" t="n">
-        <v>-4.4</v>
+        <v>-29.4</v>
       </c>
       <c r="E37" t="n">
-        <v>43.1</v>
+        <v>43.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>CAPT</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C38" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D38" t="n">
         <v>-4.4</v>
       </c>
-      <c r="D38" t="n">
-        <v>-45.6</v>
-      </c>
       <c r="E38" t="n">
-        <v>41.2</v>
+        <v>43.1</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2709,121 +2709,121 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-5</v>
+        <v>-4.4</v>
       </c>
       <c r="D39" t="n">
         <v>-45.6</v>
       </c>
       <c r="E39" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>33.5</v>
+        <v>-5</v>
       </c>
       <c r="D40" t="n">
-        <v>-6.2</v>
+        <v>-45.6</v>
       </c>
       <c r="E40" t="n">
-        <v>39.6</v>
+        <v>40.6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>STNG</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C41" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D41" t="n">
         <v>-6.2</v>
       </c>
-      <c r="D41" t="n">
-        <v>-45.6</v>
-      </c>
       <c r="E41" t="n">
-        <v>39.4</v>
+        <v>39.6</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38.8</v>
+        <v>-6.2</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.5</v>
+        <v>-45.6</v>
       </c>
       <c r="E42" t="n">
-        <v>39.2</v>
+        <v>39.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>33.5</v>
+        <v>38.8</v>
       </c>
       <c r="D43" t="n">
-        <v>-5</v>
+        <v>-0.5</v>
       </c>
       <c r="E43" t="n">
-        <v>38.4</v>
+        <v>39.2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2835,47 +2835,47 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>33.5</v>
       </c>
       <c r="D44" t="n">
-        <v>-4.4</v>
+        <v>-5</v>
       </c>
       <c r="E44" t="n">
-        <v>37.9</v>
+        <v>38.4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>51.7</v>
+        <v>33.5</v>
       </c>
       <c r="D45" t="n">
-        <v>14</v>
+        <v>-4.4</v>
       </c>
       <c r="E45" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3090,78 +3090,78 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8.1</v>
+        <v>64.7</v>
       </c>
       <c r="D54" t="n">
-        <v>-22.9</v>
+        <v>33.5</v>
       </c>
       <c r="E54" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38.8</v>
+        <v>8.1</v>
       </c>
       <c r="D55" t="n">
-        <v>8.1</v>
+        <v>-22.9</v>
       </c>
       <c r="E55" t="n">
-        <v>30.7</v>
+        <v>31</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>CAPT</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>HAFN</t>
-        </is>
-      </c>
       <c r="C56" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D56" t="n">
         <v>8.1</v>
       </c>
-      <c r="D56" t="n">
-        <v>-22.5</v>
-      </c>
       <c r="E56" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -3173,151 +3173,151 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>8.1</v>
       </c>
       <c r="D57" t="n">
-        <v>-22.2</v>
+        <v>-22.5</v>
       </c>
       <c r="E57" t="n">
-        <v>30.3</v>
+        <v>30.6</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.5</v>
+        <v>8.1</v>
       </c>
       <c r="D58" t="n">
-        <v>-29.4</v>
+        <v>-22.2</v>
       </c>
       <c r="E58" t="n">
-        <v>29</v>
+        <v>30.3</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>33.5</v>
+        <v>-0.5</v>
       </c>
       <c r="D59" t="n">
-        <v>8.1</v>
+        <v>-29.4</v>
       </c>
       <c r="E59" t="n">
-        <v>25.4</v>
+        <v>29</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-4.4</v>
+        <v>64.7</v>
       </c>
       <c r="D60" t="n">
-        <v>-29.4</v>
+        <v>38.8</v>
       </c>
       <c r="E60" t="n">
-        <v>25.1</v>
+        <v>25.9</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>14</v>
+        <v>33.5</v>
       </c>
       <c r="D61" t="n">
-        <v>-11</v>
+        <v>8.1</v>
       </c>
       <c r="E61" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>14</v>
+        <v>-4.4</v>
       </c>
       <c r="D62" t="n">
-        <v>-10.9</v>
+        <v>-29.4</v>
       </c>
       <c r="E62" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3329,17 +3329,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>14</v>
       </c>
       <c r="D63" t="n">
-        <v>-10.9</v>
+        <v>-11</v>
       </c>
       <c r="E63" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3350,85 +3350,85 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>38.8</v>
+        <v>14</v>
       </c>
       <c r="D64" t="n">
-        <v>14</v>
+        <v>-10.9</v>
       </c>
       <c r="E64" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-5</v>
+        <v>14</v>
       </c>
       <c r="D65" t="n">
-        <v>-29.4</v>
+        <v>-10.9</v>
       </c>
       <c r="E65" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-22.2</v>
+        <v>38.8</v>
       </c>
       <c r="D66" t="n">
-        <v>-45.6</v>
+        <v>14</v>
       </c>
       <c r="E66" t="n">
-        <v>23.3</v>
+        <v>24.8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3437,24 +3437,24 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-6.2</v>
+        <v>-5</v>
       </c>
       <c r="D67" t="n">
         <v>-29.4</v>
       </c>
       <c r="E67" t="n">
-        <v>23.3</v>
+        <v>24.5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3463,95 +3463,95 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-22.5</v>
+        <v>-22.2</v>
       </c>
       <c r="D68" t="n">
         <v>-45.6</v>
       </c>
       <c r="E68" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-22.9</v>
+        <v>-6.2</v>
       </c>
       <c r="D69" t="n">
-        <v>-45.6</v>
+        <v>-29.4</v>
       </c>
       <c r="E69" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.5</v>
+        <v>-22.5</v>
       </c>
       <c r="D70" t="n">
-        <v>-22.9</v>
+        <v>-45.6</v>
       </c>
       <c r="E70" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-0.5</v>
+        <v>-22.9</v>
       </c>
       <c r="D71" t="n">
-        <v>-22.5</v>
+        <v>-45.6</v>
       </c>
       <c r="E71" t="n">
-        <v>22</v>
+        <v>22.7</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3563,17 +3563,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>-0.5</v>
       </c>
       <c r="D72" t="n">
-        <v>-22.2</v>
+        <v>-22.9</v>
       </c>
       <c r="E72" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3584,74 +3584,74 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>14</v>
+        <v>-0.5</v>
       </c>
       <c r="D73" t="n">
-        <v>-6.2</v>
+        <v>-22.5</v>
       </c>
       <c r="E73" t="n">
-        <v>20.2</v>
+        <v>22</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>33.5</v>
+        <v>-0.5</v>
       </c>
       <c r="D74" t="n">
-        <v>14</v>
+        <v>-22.2</v>
       </c>
       <c r="E74" t="n">
-        <v>19.5</v>
+        <v>21.7</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8.1</v>
+        <v>14</v>
       </c>
       <c r="D75" t="n">
-        <v>-11</v>
+        <v>-6.2</v>
       </c>
       <c r="E75" t="n">
-        <v>19.1</v>
+        <v>20.2</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3662,26 +3662,26 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8.1</v>
+        <v>33.5</v>
       </c>
       <c r="D76" t="n">
-        <v>-10.9</v>
+        <v>14</v>
       </c>
       <c r="E76" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -3693,17 +3693,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>8.1</v>
       </c>
       <c r="D77" t="n">
-        <v>-10.9</v>
+        <v>-11</v>
       </c>
       <c r="E77" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3714,85 +3714,85 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>14</v>
+        <v>8.1</v>
       </c>
       <c r="D78" t="n">
-        <v>-5</v>
+        <v>-10.9</v>
       </c>
       <c r="E78" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C79" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D79" t="n">
         <v>-10.9</v>
       </c>
-      <c r="D79" t="n">
-        <v>-29.4</v>
-      </c>
       <c r="E79" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-4.4</v>
+        <v>14</v>
       </c>
       <c r="D80" t="n">
-        <v>-22.9</v>
+        <v>-5</v>
       </c>
       <c r="E80" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3811,189 +3811,189 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-11</v>
+        <v>-4.4</v>
       </c>
       <c r="D82" t="n">
-        <v>-29.4</v>
+        <v>-22.9</v>
       </c>
       <c r="E82" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>14</v>
+        <v>-10.9</v>
       </c>
       <c r="D83" t="n">
-        <v>-4.4</v>
+        <v>-29.4</v>
       </c>
       <c r="E83" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>51.7</v>
+        <v>-11</v>
       </c>
       <c r="D84" t="n">
-        <v>33.5</v>
+        <v>-29.4</v>
       </c>
       <c r="E84" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>HAFN</t>
-        </is>
-      </c>
       <c r="C85" t="n">
+        <v>14</v>
+      </c>
+      <c r="D85" t="n">
         <v>-4.4</v>
       </c>
-      <c r="D85" t="n">
-        <v>-22.5</v>
-      </c>
       <c r="E85" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-5</v>
+        <v>-4.4</v>
       </c>
       <c r="D86" t="n">
-        <v>-22.9</v>
+        <v>-22.5</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-4.4</v>
+        <v>-5</v>
       </c>
       <c r="D87" t="n">
-        <v>-22.2</v>
+        <v>-22.9</v>
       </c>
       <c r="E87" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-5</v>
+        <v>-4.4</v>
       </c>
       <c r="D88" t="n">
-        <v>-22.5</v>
+        <v>-22.2</v>
       </c>
       <c r="E88" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -4005,47 +4005,47 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>-5</v>
       </c>
       <c r="D89" t="n">
-        <v>-22.2</v>
+        <v>-22.5</v>
       </c>
       <c r="E89" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-6.2</v>
+        <v>-5</v>
       </c>
       <c r="D90" t="n">
-        <v>-22.9</v>
+        <v>-22.2</v>
       </c>
       <c r="E90" t="n">
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -4057,125 +4057,125 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>-6.2</v>
       </c>
       <c r="D91" t="n">
-        <v>-22.5</v>
+        <v>-22.9</v>
       </c>
       <c r="E91" t="n">
-        <v>16.3</v>
+        <v>16.7</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-29.4</v>
+        <v>-6.2</v>
       </c>
       <c r="D92" t="n">
-        <v>-45.6</v>
+        <v>-22.5</v>
       </c>
       <c r="E92" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-6.2</v>
+        <v>-29.4</v>
       </c>
       <c r="D93" t="n">
-        <v>-22.2</v>
+        <v>-45.6</v>
       </c>
       <c r="E93" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>14</v>
+        <v>-6.2</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.5</v>
+        <v>-22.2</v>
       </c>
       <c r="E94" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>8.1</v>
+        <v>14</v>
       </c>
       <c r="D95" t="n">
-        <v>-6.2</v>
+        <v>-0.5</v>
       </c>
       <c r="E95" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -4187,47 +4187,47 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>8.1</v>
       </c>
       <c r="D96" t="n">
-        <v>-5</v>
+        <v>-6.2</v>
       </c>
       <c r="E96" t="n">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>51.7</v>
+        <v>8.1</v>
       </c>
       <c r="D97" t="n">
-        <v>38.8</v>
+        <v>-5</v>
       </c>
       <c r="E97" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>37.99</v>
+        <v>37.11</v>
       </c>
       <c r="E2" t="n">
         <v>80.95</v>
@@ -541,13 +541,13 @@
         <v>62.56</v>
       </c>
       <c r="J2" t="n">
-        <v>113.1</v>
+        <v>118.1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.74</v>
+        <v>12.79</v>
       </c>
       <c r="E3" t="n">
         <v>24.52</v>
@@ -590,13 +590,13 @@
         <v>17.68</v>
       </c>
       <c r="J3" t="n">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
       <c r="K3" t="n">
-        <v>-40.4</v>
+        <v>-40.7</v>
       </c>
       <c r="L3" t="n">
-        <v>38.8</v>
+        <v>38.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>74.06999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="E4" t="n">
         <v>85.68000000000001</v>
@@ -639,13 +639,13 @@
         <v>73.7</v>
       </c>
       <c r="J4" t="n">
-        <v>15.7</v>
+        <v>18.2</v>
       </c>
       <c r="K4" t="n">
-        <v>-19.6</v>
+        <v>-17.8</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5</v>
+        <v>1.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.925</v>
+        <v>16.65</v>
       </c>
       <c r="E5" t="n">
         <v>19.63</v>
@@ -688,13 +688,13 @@
         <v>15.08</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>17.9</v>
       </c>
       <c r="K5" t="n">
-        <v>-46.4</v>
+        <v>-45.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-10.9</v>
+        <v>-9.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -719,31 +719,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50.57</v>
+        <v>37.13</v>
       </c>
       <c r="E6" t="n">
-        <v>54.22</v>
+        <v>40.78</v>
       </c>
       <c r="F6" t="n">
-        <v>43.18</v>
+        <v>32.42</v>
       </c>
       <c r="G6" t="n">
-        <v>22.16</v>
+        <v>16.1</v>
       </c>
       <c r="H6" t="n">
-        <v>19.63</v>
+        <v>13.98</v>
       </c>
       <c r="I6" t="n">
-        <v>39.33</v>
+        <v>29.36</v>
       </c>
       <c r="J6" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>-61.2</v>
+        <v>-62.3</v>
       </c>
       <c r="L6" t="n">
-        <v>-22.2</v>
+        <v>-20.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,31 +768,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>38.08</v>
+        <v>49.76</v>
       </c>
       <c r="E7" t="n">
-        <v>40.78</v>
+        <v>54.22</v>
       </c>
       <c r="F7" t="n">
-        <v>32.42</v>
+        <v>43.18</v>
       </c>
       <c r="G7" t="n">
-        <v>16.1</v>
+        <v>22.16</v>
       </c>
       <c r="H7" t="n">
-        <v>13.98</v>
+        <v>19.63</v>
       </c>
       <c r="I7" t="n">
-        <v>29.36</v>
+        <v>39.33</v>
       </c>
       <c r="J7" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>-63.3</v>
+        <v>-60.6</v>
       </c>
       <c r="L7" t="n">
-        <v>-22.9</v>
+        <v>-21</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>84.295</v>
+        <v>82.56</v>
       </c>
       <c r="E8" t="n">
         <v>74.11</v>
@@ -835,13 +835,13 @@
         <v>59.47</v>
       </c>
       <c r="J8" t="n">
-        <v>-12.1</v>
+        <v>-10.2</v>
       </c>
       <c r="K8" t="n">
-        <v>-54.7</v>
+        <v>-53.8</v>
       </c>
       <c r="L8" t="n">
-        <v>-29.4</v>
+        <v>-28</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.26</v>
+        <v>5.15</v>
       </c>
       <c r="E9" t="n">
         <v>4.17</v>
@@ -884,13 +884,13 @@
         <v>2.86</v>
       </c>
       <c r="J9" t="n">
-        <v>-20.7</v>
+        <v>-19</v>
       </c>
       <c r="K9" t="n">
-        <v>-77.3</v>
+        <v>-76.90000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-45.6</v>
+        <v>-44.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>21.51</v>
       </c>
       <c r="E2" t="n">
         <v>48.52</v>
@@ -1050,13 +1050,13 @@
         <v>29.63</v>
       </c>
       <c r="K2" t="n">
-        <v>118.5</v>
+        <v>125.6</v>
       </c>
       <c r="L2" t="n">
-        <v>-102</v>
+        <v>-102.1</v>
       </c>
       <c r="M2" t="n">
-        <v>33.5</v>
+        <v>37.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.098</v>
+        <v>30.5</v>
       </c>
       <c r="E3" t="n">
         <v>39.76</v>
@@ -1108,13 +1108,13 @@
         <v>29.73</v>
       </c>
       <c r="K3" t="n">
-        <v>27.8</v>
+        <v>30.4</v>
       </c>
       <c r="L3" t="n">
-        <v>-55.6</v>
+        <v>-54.7</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.4</v>
+        <v>-2.5</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>77.94</v>
+        <v>76.17</v>
       </c>
       <c r="E2" t="n">
         <v>90.78</v>
@@ -1268,24 +1268,24 @@
         <v>73.13</v>
       </c>
       <c r="K2" t="n">
-        <v>16.5</v>
+        <v>19.2</v>
       </c>
       <c r="L2" t="n">
-        <v>-38.6</v>
+        <v>-37.1</v>
       </c>
       <c r="M2" t="n">
-        <v>-6.2</v>
+        <v>-4</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1299,34 +1299,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.89</v>
+        <v>28.95</v>
       </c>
       <c r="E3" t="n">
-        <v>18.05</v>
+        <v>39.1</v>
       </c>
       <c r="F3" t="n">
-        <v>15.92</v>
+        <v>32.74</v>
       </c>
       <c r="G3" t="n">
-        <v>13.54</v>
+        <v>16.68</v>
       </c>
       <c r="H3" t="n">
-        <v>11.31</v>
+        <v>13.84</v>
       </c>
       <c r="I3" t="n">
-        <v>9.41</v>
+        <v>10.86</v>
       </c>
       <c r="J3" t="n">
-        <v>15.05</v>
+        <v>26.68</v>
       </c>
       <c r="K3" t="n">
-        <v>6.9</v>
+        <v>35.1</v>
       </c>
       <c r="L3" t="n">
-        <v>-44.3</v>
+        <v>-62.5</v>
       </c>
       <c r="M3" t="n">
-        <v>-10.9</v>
+        <v>-7.9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,34 +1351,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.98</v>
+        <v>16.38</v>
       </c>
       <c r="E4" t="n">
-        <v>39.1</v>
+        <v>18.05</v>
       </c>
       <c r="F4" t="n">
-        <v>32.74</v>
+        <v>15.92</v>
       </c>
       <c r="G4" t="n">
-        <v>16.68</v>
+        <v>13.54</v>
       </c>
       <c r="H4" t="n">
-        <v>13.84</v>
+        <v>11.31</v>
       </c>
       <c r="I4" t="n">
-        <v>10.86</v>
+        <v>9.41</v>
       </c>
       <c r="J4" t="n">
-        <v>26.68</v>
+        <v>15.05</v>
       </c>
       <c r="K4" t="n">
-        <v>30.4</v>
+        <v>10.2</v>
       </c>
       <c r="L4" t="n">
-        <v>-63.8</v>
+        <v>-42.5</v>
       </c>
       <c r="M4" t="n">
-        <v>-11</v>
+        <v>-8.1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7.44</v>
+        <v>7.28</v>
       </c>
       <c r="E5" t="n">
         <v>8.279999999999999</v>
@@ -1424,13 +1424,13 @@
         <v>5.77</v>
       </c>
       <c r="K5" t="n">
-        <v>11.3</v>
+        <v>13.7</v>
       </c>
       <c r="L5" t="n">
-        <v>-64.40000000000001</v>
+        <v>-63.6</v>
       </c>
       <c r="M5" t="n">
-        <v>-22.5</v>
+        <v>-20.8</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.39</v>
+        <v>17.6</v>
       </c>
       <c r="E2" t="n">
         <v>23.74</v>
@@ -1569,13 +1569,13 @@
         <v>19.82</v>
       </c>
       <c r="J2" t="n">
-        <v>36.5</v>
+        <v>34.9</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.3</v>
+        <v>-5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>12.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.805</v>
+        <v>23.69</v>
       </c>
       <c r="E3" t="n">
         <v>32.91</v>
@@ -1618,13 +1618,13 @@
         <v>25.73</v>
       </c>
       <c r="J3" t="n">
-        <v>38.2</v>
+        <v>38.9</v>
       </c>
       <c r="K3" t="n">
-        <v>-18.1</v>
+        <v>-17.7</v>
       </c>
       <c r="L3" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.06</v>
+        <v>27.15</v>
       </c>
       <c r="E4" t="n">
         <v>32.72</v>
@@ -1667,17 +1667,17 @@
         <v>25.72</v>
       </c>
       <c r="J4" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="K4" t="n">
-        <v>-28.5</v>
+        <v>-28.8</v>
       </c>
       <c r="L4" t="n">
-        <v>-5</v>
+        <v>-5.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
     </row>
@@ -1747,13 +1747,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>-45.6</v>
+        <v>-44.4</v>
       </c>
       <c r="E2" t="n">
-        <v>110.2</v>
+        <v>113</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>-29.4</v>
+        <v>-28</v>
       </c>
       <c r="E3" t="n">
-        <v>94.09999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1795,17 +1795,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>-22.9</v>
+        <v>-21</v>
       </c>
       <c r="E4" t="n">
-        <v>87.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>-22.5</v>
+        <v>-20.9</v>
       </c>
       <c r="E5" t="n">
-        <v>87.2</v>
+        <v>89.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -1847,21 +1847,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>-22.2</v>
+        <v>-20.8</v>
       </c>
       <c r="E6" t="n">
-        <v>86.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38.8</v>
+        <v>38.2</v>
       </c>
       <c r="D7" t="n">
-        <v>-45.6</v>
+        <v>-44.4</v>
       </c>
       <c r="E7" t="n">
-        <v>84.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>33.5</v>
+        <v>37.7</v>
       </c>
       <c r="D8" t="n">
-        <v>-45.6</v>
+        <v>-44.4</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>82.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>-11</v>
+        <v>-9.4</v>
       </c>
       <c r="E9" t="n">
-        <v>75.7</v>
+        <v>78</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -1951,21 +1951,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.9</v>
+        <v>-8.1</v>
       </c>
       <c r="E10" t="n">
-        <v>75.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -1977,17 +1977,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.9</v>
+        <v>-7.9</v>
       </c>
       <c r="E11" t="n">
-        <v>75.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.2</v>
+        <v>-5.3</v>
       </c>
       <c r="E12" t="n">
-        <v>70.8</v>
+        <v>73.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2029,21 +2029,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="E13" t="n">
-        <v>69.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.4</v>
+        <v>-2.5</v>
       </c>
       <c r="E14" t="n">
-        <v>69.09999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,22 +2076,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>-29.4</v>
+        <v>1.7</v>
       </c>
       <c r="E15" t="n">
-        <v>68.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2102,22 +2102,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>64.7</v>
+        <v>38.2</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5</v>
+        <v>-28</v>
       </c>
       <c r="E16" t="n">
-        <v>65.2</v>
+        <v>66.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>33.5</v>
+        <v>37.7</v>
       </c>
       <c r="D17" t="n">
-        <v>-29.4</v>
+        <v>-28</v>
       </c>
       <c r="E17" t="n">
-        <v>62.9</v>
+        <v>65.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2154,26 +2154,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>-22.9</v>
+        <v>8.6</v>
       </c>
       <c r="E18" t="n">
-        <v>61.7</v>
+        <v>60</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2185,21 +2185,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38.8</v>
+        <v>38.2</v>
       </c>
       <c r="D19" t="n">
-        <v>-22.5</v>
+        <v>-21</v>
       </c>
       <c r="E19" t="n">
-        <v>61.3</v>
+        <v>59.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2211,17 +2211,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>38.8</v>
+        <v>38.2</v>
       </c>
       <c r="D20" t="n">
-        <v>-22.2</v>
+        <v>-20.9</v>
       </c>
       <c r="E20" t="n">
-        <v>61</v>
+        <v>59.1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2232,52 +2232,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>38.2</v>
       </c>
       <c r="D21" t="n">
-        <v>-45.6</v>
+        <v>-20.8</v>
       </c>
       <c r="E21" t="n">
-        <v>59.6</v>
+        <v>59</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>64.7</v>
+        <v>37.7</v>
       </c>
       <c r="D22" t="n">
-        <v>8.1</v>
+        <v>-21</v>
       </c>
       <c r="E22" t="n">
-        <v>56.6</v>
+        <v>58.7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>33.5</v>
+        <v>37.7</v>
       </c>
       <c r="D23" t="n">
-        <v>-22.9</v>
+        <v>-20.9</v>
       </c>
       <c r="E23" t="n">
-        <v>56.4</v>
+        <v>58.7</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>33.5</v>
+        <v>37.7</v>
       </c>
       <c r="D24" t="n">
-        <v>-22.5</v>
+        <v>-20.8</v>
       </c>
       <c r="E24" t="n">
-        <v>56</v>
+        <v>58.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2336,78 +2336,78 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>33.5</v>
+        <v>12.6</v>
       </c>
       <c r="D25" t="n">
-        <v>-22.2</v>
+        <v>-44.4</v>
       </c>
       <c r="E25" t="n">
-        <v>55.7</v>
+        <v>57</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8.1</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-45.6</v>
+        <v>12.6</v>
       </c>
       <c r="E26" t="n">
-        <v>53.7</v>
+        <v>55.9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>64.7</v>
+        <v>8.6</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>-44.4</v>
       </c>
       <c r="E27" t="n">
-        <v>50.7</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -2419,28 +2419,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38.8</v>
+        <v>38.2</v>
       </c>
       <c r="D28" t="n">
-        <v>-11</v>
+        <v>-9.4</v>
       </c>
       <c r="E28" t="n">
-        <v>49.8</v>
+        <v>47.6</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2449,17 +2449,17 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38.8</v>
+        <v>37.7</v>
       </c>
       <c r="D29" t="n">
-        <v>-10.9</v>
+        <v>-9.4</v>
       </c>
       <c r="E29" t="n">
-        <v>49.7</v>
+        <v>47.2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38.8</v>
+        <v>38.2</v>
       </c>
       <c r="D30" t="n">
-        <v>-10.9</v>
+        <v>-8.1</v>
       </c>
       <c r="E30" t="n">
-        <v>49.6</v>
+        <v>46.3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.5</v>
+        <v>1.7</v>
       </c>
       <c r="D31" t="n">
-        <v>-45.6</v>
+        <v>-44.4</v>
       </c>
       <c r="E31" t="n">
-        <v>45.1</v>
+        <v>46.1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2523,17 +2523,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38.8</v>
+        <v>38.2</v>
       </c>
       <c r="D32" t="n">
-        <v>-6.2</v>
+        <v>-7.9</v>
       </c>
       <c r="E32" t="n">
-        <v>44.9</v>
+        <v>46.1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2549,17 +2549,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>33.5</v>
+        <v>37.7</v>
       </c>
       <c r="D33" t="n">
-        <v>-11</v>
+        <v>-8.1</v>
       </c>
       <c r="E33" t="n">
-        <v>44.5</v>
+        <v>45.9</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2575,54 +2575,54 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.5</v>
+        <v>37.7</v>
       </c>
       <c r="D34" t="n">
-        <v>-10.9</v>
+        <v>-7.9</v>
       </c>
       <c r="E34" t="n">
-        <v>44.4</v>
+        <v>45.6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>33.5</v>
+        <v>38.2</v>
       </c>
       <c r="D35" t="n">
-        <v>-10.9</v>
+        <v>-5.3</v>
       </c>
       <c r="E35" t="n">
-        <v>44.4</v>
+        <v>43.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2631,147 +2631,147 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38.8</v>
+        <v>37.7</v>
       </c>
       <c r="D36" t="n">
-        <v>-5</v>
+        <v>-5.3</v>
       </c>
       <c r="E36" t="n">
-        <v>43.7</v>
+        <v>43</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>14</v>
+        <v>38.2</v>
       </c>
       <c r="D37" t="n">
-        <v>-29.4</v>
+        <v>-4</v>
       </c>
       <c r="E37" t="n">
-        <v>43.4</v>
+        <v>42.2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>38.8</v>
+        <v>-2.5</v>
       </c>
       <c r="D38" t="n">
-        <v>-4.4</v>
+        <v>-44.4</v>
       </c>
       <c r="E38" t="n">
-        <v>43.1</v>
+        <v>41.9</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-4.4</v>
+        <v>37.7</v>
       </c>
       <c r="D39" t="n">
-        <v>-45.6</v>
+        <v>-4</v>
       </c>
       <c r="E39" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-5</v>
+        <v>38.2</v>
       </c>
       <c r="D40" t="n">
-        <v>-45.6</v>
+        <v>-2.5</v>
       </c>
       <c r="E40" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>33.5</v>
+        <v>12.6</v>
       </c>
       <c r="D41" t="n">
-        <v>-6.2</v>
+        <v>-28</v>
       </c>
       <c r="E41" t="n">
-        <v>39.6</v>
+        <v>40.6</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2787,13 +2787,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-6.2</v>
+        <v>-4</v>
       </c>
       <c r="D42" t="n">
-        <v>-45.6</v>
+        <v>-44.4</v>
       </c>
       <c r="E42" t="n">
-        <v>39.4</v>
+        <v>40.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2804,22 +2804,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38.8</v>
+        <v>37.7</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E43" t="n">
-        <v>39.2</v>
+        <v>40.3</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2830,52 +2830,52 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>33.5</v>
+        <v>-5.3</v>
       </c>
       <c r="D44" t="n">
-        <v>-5</v>
+        <v>-44.4</v>
       </c>
       <c r="E44" t="n">
-        <v>38.4</v>
+        <v>39.1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>33.5</v>
+        <v>-7.9</v>
       </c>
       <c r="D45" t="n">
-        <v>-4.4</v>
+        <v>-44.4</v>
       </c>
       <c r="E45" t="n">
-        <v>37.9</v>
+        <v>36.6</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="D46" t="n">
-        <v>-29.4</v>
+        <v>-28</v>
       </c>
       <c r="E46" t="n">
-        <v>37.5</v>
+        <v>36.6</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2908,78 +2908,78 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>14</v>
+        <v>38.2</v>
       </c>
       <c r="D47" t="n">
-        <v>-22.9</v>
+        <v>1.7</v>
       </c>
       <c r="E47" t="n">
-        <v>36.9</v>
+        <v>36.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>14</v>
+        <v>-8.1</v>
       </c>
       <c r="D48" t="n">
-        <v>-22.5</v>
+        <v>-44.4</v>
       </c>
       <c r="E48" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>14</v>
+        <v>37.7</v>
       </c>
       <c r="D49" t="n">
-        <v>-22.2</v>
+        <v>1.7</v>
       </c>
       <c r="E49" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -2995,13 +2995,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-10.9</v>
+        <v>-9.4</v>
       </c>
       <c r="D50" t="n">
-        <v>-45.6</v>
+        <v>-44.4</v>
       </c>
       <c r="E50" t="n">
-        <v>34.7</v>
+        <v>35</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3012,78 +3012,78 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-10.9</v>
+        <v>12.6</v>
       </c>
       <c r="D51" t="n">
-        <v>-45.6</v>
+        <v>-21</v>
       </c>
       <c r="E51" t="n">
-        <v>34.7</v>
+        <v>33.6</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-11</v>
+        <v>12.6</v>
       </c>
       <c r="D52" t="n">
-        <v>-45.6</v>
+        <v>-20.9</v>
       </c>
       <c r="E52" t="n">
-        <v>34.5</v>
+        <v>33.6</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>33.5</v>
+        <v>12.6</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5</v>
+        <v>-20.8</v>
       </c>
       <c r="E53" t="n">
-        <v>34</v>
+        <v>33.4</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -3099,13 +3099,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>33.5</v>
+        <v>37.7</v>
       </c>
       <c r="E54" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3116,52 +3116,52 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8.1</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>-22.9</v>
+        <v>38.2</v>
       </c>
       <c r="E55" t="n">
-        <v>31</v>
+        <v>30.4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38.8</v>
+        <v>1.7</v>
       </c>
       <c r="D56" t="n">
-        <v>8.1</v>
+        <v>-28</v>
       </c>
       <c r="E56" t="n">
-        <v>30.7</v>
+        <v>29.6</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3173,21 +3173,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="D57" t="n">
-        <v>-22.5</v>
+        <v>-21</v>
       </c>
       <c r="E57" t="n">
-        <v>30.6</v>
+        <v>29.6</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3199,17 +3199,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="D58" t="n">
-        <v>-22.2</v>
+        <v>-20.9</v>
       </c>
       <c r="E58" t="n">
-        <v>30.3</v>
+        <v>29.6</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3220,52 +3220,52 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-0.5</v>
+        <v>38.2</v>
       </c>
       <c r="D59" t="n">
-        <v>-29.4</v>
+        <v>8.6</v>
       </c>
       <c r="E59" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>64.7</v>
+        <v>8.6</v>
       </c>
       <c r="D60" t="n">
-        <v>38.8</v>
+        <v>-20.8</v>
       </c>
       <c r="E60" t="n">
-        <v>25.9</v>
+        <v>29.4</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -3281,13 +3281,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>33.5</v>
+        <v>37.7</v>
       </c>
       <c r="D61" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="E61" t="n">
-        <v>25.4</v>
+        <v>29.1</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3298,163 +3298,163 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-4.4</v>
+        <v>38.2</v>
       </c>
       <c r="D62" t="n">
-        <v>-29.4</v>
+        <v>12.6</v>
       </c>
       <c r="E62" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>14</v>
+        <v>-2.5</v>
       </c>
       <c r="D63" t="n">
-        <v>-11</v>
+        <v>-28</v>
       </c>
       <c r="E63" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>CMDB</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>DHT</t>
-        </is>
-      </c>
       <c r="C64" t="n">
-        <v>14</v>
+        <v>37.7</v>
       </c>
       <c r="D64" t="n">
-        <v>-10.9</v>
+        <v>12.6</v>
       </c>
       <c r="E64" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>14</v>
+        <v>-4</v>
       </c>
       <c r="D65" t="n">
-        <v>-10.9</v>
+        <v>-28</v>
       </c>
       <c r="E65" t="n">
-        <v>24.9</v>
+        <v>24</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38.8</v>
+        <v>-20.8</v>
       </c>
       <c r="D66" t="n">
-        <v>14</v>
+        <v>-44.4</v>
       </c>
       <c r="E66" t="n">
-        <v>24.8</v>
+        <v>23.6</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-5</v>
+        <v>-21</v>
       </c>
       <c r="D67" t="n">
-        <v>-29.4</v>
+        <v>-44.4</v>
       </c>
       <c r="E67" t="n">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3463,13 +3463,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-22.2</v>
+        <v>-20.9</v>
       </c>
       <c r="D68" t="n">
-        <v>-45.6</v>
+        <v>-44.4</v>
       </c>
       <c r="E68" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3489,65 +3489,65 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-6.2</v>
+        <v>-5.3</v>
       </c>
       <c r="D69" t="n">
-        <v>-29.4</v>
+        <v>-28</v>
       </c>
       <c r="E69" t="n">
-        <v>23.3</v>
+        <v>22.7</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-22.5</v>
+        <v>1.7</v>
       </c>
       <c r="D70" t="n">
-        <v>-45.6</v>
+        <v>-21</v>
       </c>
       <c r="E70" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>FRO</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C71" t="n">
-        <v>-22.9</v>
+        <v>1.7</v>
       </c>
       <c r="D71" t="n">
-        <v>-45.6</v>
+        <v>-20.9</v>
       </c>
       <c r="E71" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3563,73 +3563,73 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-0.5</v>
+        <v>1.7</v>
       </c>
       <c r="D72" t="n">
-        <v>-22.9</v>
+        <v>-20.8</v>
       </c>
       <c r="E72" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-0.5</v>
+        <v>12.6</v>
       </c>
       <c r="D73" t="n">
-        <v>-22.5</v>
+        <v>-9.4</v>
       </c>
       <c r="E73" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-0.5</v>
+        <v>12.6</v>
       </c>
       <c r="D74" t="n">
-        <v>-22.2</v>
+        <v>-8.1</v>
       </c>
       <c r="E74" t="n">
-        <v>21.7</v>
+        <v>20.8</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -3641,17 +3641,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14</v>
+        <v>12.6</v>
       </c>
       <c r="D75" t="n">
-        <v>-6.2</v>
+        <v>-7.9</v>
       </c>
       <c r="E75" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3662,267 +3662,267 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>33.5</v>
+        <v>-7.9</v>
       </c>
       <c r="D76" t="n">
-        <v>14</v>
+        <v>-28</v>
       </c>
       <c r="E76" t="n">
-        <v>19.5</v>
+        <v>20.1</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8.1</v>
+        <v>-8.1</v>
       </c>
       <c r="D77" t="n">
-        <v>-11</v>
+        <v>-28</v>
       </c>
       <c r="E77" t="n">
-        <v>19.1</v>
+        <v>19.8</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8.1</v>
+        <v>-9.4</v>
       </c>
       <c r="D78" t="n">
-        <v>-10.9</v>
+        <v>-28</v>
       </c>
       <c r="E78" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8.1</v>
+        <v>-2.5</v>
       </c>
       <c r="D79" t="n">
-        <v>-10.9</v>
+        <v>-21</v>
       </c>
       <c r="E79" t="n">
-        <v>19</v>
+        <v>18.4</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>14</v>
+        <v>-2.5</v>
       </c>
       <c r="D80" t="n">
-        <v>-5</v>
+        <v>-20.9</v>
       </c>
       <c r="E80" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-10.9</v>
+        <v>-2.5</v>
       </c>
       <c r="D81" t="n">
-        <v>-29.4</v>
+        <v>-20.8</v>
       </c>
       <c r="E81" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-4.4</v>
+        <v>8.6</v>
       </c>
       <c r="D82" t="n">
-        <v>-22.9</v>
+        <v>-9.4</v>
       </c>
       <c r="E82" t="n">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-10.9</v>
+        <v>12.6</v>
       </c>
       <c r="D83" t="n">
-        <v>-29.4</v>
+        <v>-5.3</v>
       </c>
       <c r="E83" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="D84" t="n">
-        <v>-29.4</v>
+        <v>-21</v>
       </c>
       <c r="E84" t="n">
-        <v>18.4</v>
+        <v>17</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>14</v>
+        <v>-4</v>
       </c>
       <c r="D85" t="n">
-        <v>-4.4</v>
+        <v>-20.9</v>
       </c>
       <c r="E85" t="n">
-        <v>18.4</v>
+        <v>16.9</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3931,91 +3931,91 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-4.4</v>
+        <v>-4</v>
       </c>
       <c r="D86" t="n">
-        <v>-22.5</v>
+        <v>-20.8</v>
       </c>
       <c r="E86" t="n">
-        <v>18.1</v>
+        <v>16.8</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-5</v>
+        <v>8.6</v>
       </c>
       <c r="D87" t="n">
-        <v>-22.9</v>
+        <v>-8.1</v>
       </c>
       <c r="E87" t="n">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-4.4</v>
+        <v>12.6</v>
       </c>
       <c r="D88" t="n">
-        <v>-22.2</v>
+        <v>-4</v>
       </c>
       <c r="E88" t="n">
-        <v>17.8</v>
+        <v>16.6</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-5</v>
+        <v>8.6</v>
       </c>
       <c r="D89" t="n">
-        <v>-22.5</v>
+        <v>-7.9</v>
       </c>
       <c r="E89" t="n">
-        <v>17.6</v>
+        <v>16.5</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4026,260 +4026,260 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-5</v>
+        <v>-28</v>
       </c>
       <c r="D90" t="n">
-        <v>-22.2</v>
+        <v>-44.4</v>
       </c>
       <c r="E90" t="n">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-6.2</v>
+        <v>-5.3</v>
       </c>
       <c r="D91" t="n">
-        <v>-22.9</v>
+        <v>-21</v>
       </c>
       <c r="E91" t="n">
-        <v>16.7</v>
+        <v>15.7</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-6.2</v>
+        <v>-5.3</v>
       </c>
       <c r="D92" t="n">
-        <v>-22.5</v>
+        <v>-20.9</v>
       </c>
       <c r="E92" t="n">
-        <v>16.3</v>
+        <v>15.7</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-29.4</v>
+        <v>-5.3</v>
       </c>
       <c r="D93" t="n">
-        <v>-45.6</v>
+        <v>-20.8</v>
       </c>
       <c r="E93" t="n">
-        <v>16.1</v>
+        <v>15.5</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-6.2</v>
+        <v>12.6</v>
       </c>
       <c r="D94" t="n">
-        <v>-22.2</v>
+        <v>-2.5</v>
       </c>
       <c r="E94" t="n">
-        <v>16</v>
+        <v>15.2</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.5</v>
+        <v>-5.3</v>
       </c>
       <c r="E95" t="n">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8.1</v>
+        <v>-7.9</v>
       </c>
       <c r="D96" t="n">
-        <v>-6.2</v>
+        <v>-21</v>
       </c>
       <c r="E96" t="n">
-        <v>14.3</v>
+        <v>13.1</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>8.1</v>
+        <v>-7.9</v>
       </c>
       <c r="D97" t="n">
-        <v>-5</v>
+        <v>-20.9</v>
       </c>
       <c r="E97" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>8.1</v>
+        <v>-7.9</v>
       </c>
       <c r="D98" t="n">
-        <v>-4.4</v>
+        <v>-20.8</v>
       </c>
       <c r="E98" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-10.9</v>
+        <v>-8.1</v>
       </c>
       <c r="D99" t="n">
-        <v>-22.9</v>
+        <v>-21</v>
       </c>
       <c r="E99" t="n">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -4295,13 +4295,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-10.9</v>
+        <v>-8.1</v>
       </c>
       <c r="D100" t="n">
-        <v>-22.9</v>
+        <v>-20.9</v>
       </c>
       <c r="E100" t="n">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4312,74 +4312,74 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-11</v>
+        <v>-8.1</v>
       </c>
       <c r="D101" t="n">
-        <v>-22.9</v>
+        <v>-20.8</v>
       </c>
       <c r="E101" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-10.9</v>
+        <v>8.6</v>
       </c>
       <c r="D102" t="n">
-        <v>-22.5</v>
+        <v>-4</v>
       </c>
       <c r="E102" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-10.9</v>
+        <v>-9.4</v>
       </c>
       <c r="D103" t="n">
-        <v>-22.5</v>
+        <v>-21</v>
       </c>
       <c r="E103" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4390,19 +4390,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-11</v>
+        <v>-9.4</v>
       </c>
       <c r="D104" t="n">
-        <v>-22.5</v>
+        <v>-20.9</v>
       </c>
       <c r="E104" t="n">
         <v>11.5</v>
@@ -4421,99 +4421,99 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-10.9</v>
+        <v>-9.4</v>
       </c>
       <c r="D105" t="n">
-        <v>-22.2</v>
+        <v>-20.8</v>
       </c>
       <c r="E105" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>-10.9</v>
+        <v>1.7</v>
       </c>
       <c r="D106" t="n">
-        <v>-22.2</v>
+        <v>-9.4</v>
       </c>
       <c r="E106" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-11</v>
+        <v>8.6</v>
       </c>
       <c r="D107" t="n">
-        <v>-22.2</v>
+        <v>-2.5</v>
       </c>
       <c r="E107" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
           <t>TNK</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>TRMD</t>
-        </is>
-      </c>
       <c r="C108" t="n">
-        <v>-0.5</v>
+        <v>12.6</v>
       </c>
       <c r="D108" t="n">
-        <v>-11</v>
+        <v>1.7</v>
       </c>
       <c r="E108" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -4525,21 +4525,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-0.5</v>
+        <v>1.7</v>
       </c>
       <c r="D109" t="n">
-        <v>-10.9</v>
+        <v>-8.1</v>
       </c>
       <c r="E109" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -4551,17 +4551,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-0.5</v>
+        <v>1.7</v>
       </c>
       <c r="D110" t="n">
-        <v>-10.9</v>
+        <v>-7.9</v>
       </c>
       <c r="E110" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4572,26 +4572,26 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>8.1</v>
+        <v>-20.8</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.5</v>
+        <v>-28</v>
       </c>
       <c r="E111" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4607,13 +4607,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-22.2</v>
+        <v>-21</v>
       </c>
       <c r="D112" t="n">
-        <v>-29.4</v>
+        <v>-28</v>
       </c>
       <c r="E112" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4633,69 +4633,69 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-22.5</v>
+        <v>-20.9</v>
       </c>
       <c r="D113" t="n">
-        <v>-29.4</v>
+        <v>-28</v>
       </c>
       <c r="E113" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-4.4</v>
+        <v>8.6</v>
       </c>
       <c r="D114" t="n">
-        <v>-11</v>
+        <v>1.7</v>
       </c>
       <c r="E114" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-22.9</v>
+        <v>1.7</v>
       </c>
       <c r="D115" t="n">
-        <v>-29.4</v>
+        <v>-5.3</v>
       </c>
       <c r="E115" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -4711,13 +4711,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-4.4</v>
+        <v>-2.5</v>
       </c>
       <c r="D116" t="n">
-        <v>-10.9</v>
+        <v>-9.4</v>
       </c>
       <c r="E116" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -4728,59 +4728,59 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-4.4</v>
+        <v>1.7</v>
       </c>
       <c r="D117" t="n">
-        <v>-10.9</v>
+        <v>-4</v>
       </c>
       <c r="E117" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-5</v>
+        <v>-2.5</v>
       </c>
       <c r="D118" t="n">
-        <v>-11</v>
+        <v>-8.1</v>
       </c>
       <c r="E118" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4789,143 +4789,143 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="D119" t="n">
-        <v>-10.9</v>
+        <v>-9.4</v>
       </c>
       <c r="E119" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>14</v>
+        <v>-2.5</v>
       </c>
       <c r="D120" t="n">
-        <v>8.1</v>
+        <v>-7.9</v>
       </c>
       <c r="E120" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>-5</v>
+        <v>1.7</v>
       </c>
       <c r="D121" t="n">
-        <v>-10.9</v>
+        <v>-2.5</v>
       </c>
       <c r="E121" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>-0.5</v>
+        <v>-5.3</v>
       </c>
       <c r="D122" t="n">
-        <v>-6.2</v>
+        <v>-9.4</v>
       </c>
       <c r="E122" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>38.8</v>
+        <v>-4</v>
       </c>
       <c r="D123" t="n">
-        <v>33.5</v>
+        <v>-8.1</v>
       </c>
       <c r="E123" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>-6.2</v>
+        <v>12.6</v>
       </c>
       <c r="D124" t="n">
-        <v>-11</v>
+        <v>8.6</v>
       </c>
       <c r="E124" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -4941,28 +4941,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>-6.2</v>
+        <v>-4</v>
       </c>
       <c r="D125" t="n">
-        <v>-10.9</v>
+        <v>-7.9</v>
       </c>
       <c r="E125" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4971,24 +4971,24 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>-6.2</v>
+        <v>-5.3</v>
       </c>
       <c r="D126" t="n">
-        <v>-10.9</v>
+        <v>-8.1</v>
       </c>
       <c r="E126" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4997,76 +4997,76 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>-0.5</v>
+        <v>-2.5</v>
       </c>
       <c r="D127" t="n">
-        <v>-5</v>
+        <v>-5.3</v>
       </c>
       <c r="E127" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>-0.5</v>
+        <v>-5.3</v>
       </c>
       <c r="D128" t="n">
-        <v>-4.4</v>
+        <v>-7.9</v>
       </c>
       <c r="E128" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>-4.4</v>
+        <v>-7.9</v>
       </c>
       <c r="D129" t="n">
-        <v>-6.2</v>
+        <v>-9.4</v>
       </c>
       <c r="E129" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5075,199 +5075,199 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>-5</v>
+        <v>-2.5</v>
       </c>
       <c r="D130" t="n">
-        <v>-6.2</v>
+        <v>-4</v>
       </c>
       <c r="E130" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>-22.2</v>
+        <v>-4</v>
       </c>
       <c r="D131" t="n">
-        <v>-22.9</v>
+        <v>-5.3</v>
       </c>
       <c r="E131" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>-4.4</v>
+        <v>-8.1</v>
       </c>
       <c r="D132" t="n">
-        <v>-5</v>
+        <v>-9.4</v>
       </c>
       <c r="E132" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>-22.5</v>
+        <v>38.2</v>
       </c>
       <c r="D133" t="n">
-        <v>-22.9</v>
+        <v>37.7</v>
       </c>
       <c r="E133" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>-22.2</v>
+        <v>-7.9</v>
       </c>
       <c r="D134" t="n">
-        <v>-22.5</v>
+        <v>-8.1</v>
       </c>
       <c r="E134" t="n">
         <v>0.3</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>-10.9</v>
+        <v>-20.8</v>
       </c>
       <c r="D135" t="n">
-        <v>-11</v>
+        <v>-21</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>-10.9</v>
+        <v>-20.8</v>
       </c>
       <c r="D136" t="n">
-        <v>-11</v>
+        <v>-20.9</v>
       </c>
       <c r="E136" t="n">
         <v>0.1</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>-10.9</v>
+        <v>-20.9</v>
       </c>
       <c r="D137" t="n">
-        <v>-10.9</v>
+        <v>-21</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Scenario summary (LNG)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Scenario summary (PRODUCT)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Scenario summary (DRY_BULK)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Pair trades" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Scenario summary (CTR)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pair trades" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1692,7 +1693,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>current_price</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>disruption_persists_FV</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>gradual_normalization_FV</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>normalization_plus_overhang_FV</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>demand_recession_FV</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>probability_weighted_FV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>upside_pct</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>downside_pct</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>expected_value_pct</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>position_recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>containerships</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.74</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="H2" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="I2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-26.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>containerships</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-21.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-43.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1769,21 +1964,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>68.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>-28</v>
+        <v>-29.6</v>
       </c>
       <c r="E3" t="n">
-        <v>96.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -1795,21 +1990,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>68.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="E4" t="n">
-        <v>89.5</v>
+        <v>96.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1821,14 +2016,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>68.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>-20.9</v>
+        <v>-21</v>
       </c>
       <c r="E5" t="n">
         <v>89.5</v>
@@ -1847,125 +2042,125 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>68.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>-20.8</v>
+        <v>-20.9</v>
       </c>
       <c r="E6" t="n">
-        <v>89.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>-44.4</v>
+        <v>-20.8</v>
       </c>
       <c r="E7" t="n">
-        <v>82.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>-44.4</v>
+        <v>-18.5</v>
       </c>
       <c r="E8" t="n">
-        <v>82.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>68.59999999999999</v>
+        <v>38.2</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.4</v>
+        <v>-44.4</v>
       </c>
       <c r="E9" t="n">
-        <v>78</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>68.59999999999999</v>
+        <v>37.7</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.1</v>
+        <v>-44.4</v>
       </c>
       <c r="E10" t="n">
-        <v>76.7</v>
+        <v>82.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -1977,21 +2172,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>68.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.9</v>
+        <v>-9.4</v>
       </c>
       <c r="E11" t="n">
-        <v>76.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2003,21 +2198,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>68.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3</v>
+        <v>-8.1</v>
       </c>
       <c r="E12" t="n">
-        <v>73.8</v>
+        <v>76.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2029,17 +2224,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>68.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>-4</v>
+        <v>-7.9</v>
       </c>
       <c r="E13" t="n">
-        <v>72.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2055,21 +2250,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>68.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.5</v>
+        <v>-5.3</v>
       </c>
       <c r="E14" t="n">
-        <v>71.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2081,125 +2276,125 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>68.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7</v>
+        <v>-4</v>
       </c>
       <c r="E15" t="n">
-        <v>66.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>-28</v>
+        <v>-2.5</v>
       </c>
       <c r="E16" t="n">
-        <v>66.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>37.7</v>
+        <v>38.2</v>
       </c>
       <c r="D17" t="n">
-        <v>-28</v>
+        <v>-29.6</v>
       </c>
       <c r="E17" t="n">
-        <v>65.7</v>
+        <v>67.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>68.59999999999999</v>
+        <v>37.7</v>
       </c>
       <c r="D18" t="n">
-        <v>8.6</v>
+        <v>-29.6</v>
       </c>
       <c r="E18" t="n">
-        <v>60</v>
+        <v>67.3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>-21</v>
+        <v>1.7</v>
       </c>
       <c r="E19" t="n">
-        <v>59.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2211,255 +2406,255 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>38.2</v>
       </c>
       <c r="D20" t="n">
-        <v>-20.9</v>
+        <v>-28</v>
       </c>
       <c r="E20" t="n">
-        <v>59.1</v>
+        <v>66.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38.2</v>
+        <v>37.7</v>
       </c>
       <c r="D21" t="n">
-        <v>-20.8</v>
+        <v>-28</v>
       </c>
       <c r="E21" t="n">
-        <v>59</v>
+        <v>65.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-21</v>
+        <v>8.6</v>
       </c>
       <c r="E22" t="n">
-        <v>58.7</v>
+        <v>60</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37.7</v>
+        <v>38.2</v>
       </c>
       <c r="D23" t="n">
-        <v>-20.9</v>
+        <v>-21</v>
       </c>
       <c r="E23" t="n">
-        <v>58.7</v>
+        <v>59.2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37.7</v>
+        <v>38.2</v>
       </c>
       <c r="D24" t="n">
-        <v>-20.8</v>
+        <v>-20.9</v>
       </c>
       <c r="E24" t="n">
-        <v>58.5</v>
+        <v>59.1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12.6</v>
+        <v>38.2</v>
       </c>
       <c r="D25" t="n">
-        <v>-44.4</v>
+        <v>-20.8</v>
       </c>
       <c r="E25" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>68.59999999999999</v>
+        <v>37.7</v>
       </c>
       <c r="D26" t="n">
-        <v>12.6</v>
+        <v>-21</v>
       </c>
       <c r="E26" t="n">
-        <v>55.9</v>
+        <v>58.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.6</v>
+        <v>37.7</v>
       </c>
       <c r="D27" t="n">
-        <v>-44.4</v>
+        <v>-20.9</v>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>58.7</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38.2</v>
+        <v>37.7</v>
       </c>
       <c r="D28" t="n">
-        <v>-9.4</v>
+        <v>-20.8</v>
       </c>
       <c r="E28" t="n">
-        <v>47.6</v>
+        <v>58.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37.7</v>
+        <v>12.6</v>
       </c>
       <c r="D29" t="n">
-        <v>-9.4</v>
+        <v>-44.4</v>
       </c>
       <c r="E29" t="n">
-        <v>47.2</v>
+        <v>57</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -2471,229 +2666,229 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>38.2</v>
       </c>
       <c r="D30" t="n">
-        <v>-8.1</v>
+        <v>-18.5</v>
       </c>
       <c r="E30" t="n">
-        <v>46.3</v>
+        <v>56.8</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.7</v>
+        <v>37.7</v>
       </c>
       <c r="D31" t="n">
-        <v>-44.4</v>
+        <v>-18.5</v>
       </c>
       <c r="E31" t="n">
-        <v>46.1</v>
+        <v>56.3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>-7.9</v>
+        <v>12.6</v>
       </c>
       <c r="E32" t="n">
-        <v>46.1</v>
+        <v>55.9</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37.7</v>
+        <v>8.6</v>
       </c>
       <c r="D33" t="n">
-        <v>-8.1</v>
+        <v>-44.4</v>
       </c>
       <c r="E33" t="n">
-        <v>45.9</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37.7</v>
+        <v>38.2</v>
       </c>
       <c r="D34" t="n">
-        <v>-7.9</v>
+        <v>-9.4</v>
       </c>
       <c r="E34" t="n">
-        <v>45.6</v>
+        <v>47.6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38.2</v>
+        <v>37.7</v>
       </c>
       <c r="D35" t="n">
-        <v>-5.3</v>
+        <v>-9.4</v>
       </c>
       <c r="E35" t="n">
-        <v>43.5</v>
+        <v>47.2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>37.7</v>
+        <v>38.2</v>
       </c>
       <c r="D36" t="n">
-        <v>-5.3</v>
+        <v>-8.1</v>
       </c>
       <c r="E36" t="n">
-        <v>43</v>
+        <v>46.3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38.2</v>
+        <v>1.7</v>
       </c>
       <c r="D37" t="n">
-        <v>-4</v>
+        <v>-44.4</v>
       </c>
       <c r="E37" t="n">
-        <v>42.2</v>
+        <v>46.1</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-2.5</v>
+        <v>38.2</v>
       </c>
       <c r="D38" t="n">
-        <v>-44.4</v>
+        <v>-7.9</v>
       </c>
       <c r="E38" t="n">
-        <v>41.9</v>
+        <v>46.1</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -2705,17 +2900,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>37.7</v>
       </c>
       <c r="D39" t="n">
-        <v>-4</v>
+        <v>-8.1</v>
       </c>
       <c r="E39" t="n">
-        <v>41.7</v>
+        <v>45.9</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2726,137 +2921,137 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38.2</v>
+        <v>37.7</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.5</v>
+        <v>-7.9</v>
       </c>
       <c r="E40" t="n">
-        <v>40.7</v>
+        <v>45.6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>12.6</v>
+        <v>38.2</v>
       </c>
       <c r="D41" t="n">
-        <v>-28</v>
+        <v>-5.3</v>
       </c>
       <c r="E41" t="n">
-        <v>40.6</v>
+        <v>43.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-4</v>
+        <v>37.7</v>
       </c>
       <c r="D42" t="n">
-        <v>-44.4</v>
+        <v>-5.3</v>
       </c>
       <c r="E42" t="n">
-        <v>40.4</v>
+        <v>43</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37.7</v>
+        <v>12.6</v>
       </c>
       <c r="D43" t="n">
-        <v>-2.5</v>
+        <v>-29.6</v>
       </c>
       <c r="E43" t="n">
-        <v>40.3</v>
+        <v>42.2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-5.3</v>
+        <v>38.2</v>
       </c>
       <c r="D44" t="n">
-        <v>-44.4</v>
+        <v>-4</v>
       </c>
       <c r="E44" t="n">
-        <v>39.1</v>
+        <v>42.2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2865,43 +3060,43 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-7.9</v>
+        <v>-2.5</v>
       </c>
       <c r="D45" t="n">
         <v>-44.4</v>
       </c>
       <c r="E45" t="n">
-        <v>36.6</v>
+        <v>41.9</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8.6</v>
+        <v>37.7</v>
       </c>
       <c r="D46" t="n">
-        <v>-28</v>
+        <v>-4</v>
       </c>
       <c r="E46" t="n">
-        <v>36.6</v>
+        <v>41.7</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -2913,95 +3108,95 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>38.2</v>
       </c>
       <c r="D47" t="n">
-        <v>1.7</v>
+        <v>-2.5</v>
       </c>
       <c r="E47" t="n">
-        <v>36.5</v>
+        <v>40.7</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-8.1</v>
+        <v>12.6</v>
       </c>
       <c r="D48" t="n">
-        <v>-44.4</v>
+        <v>-28</v>
       </c>
       <c r="E48" t="n">
-        <v>36.3</v>
+        <v>40.6</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>37.7</v>
+        <v>-4</v>
       </c>
       <c r="D49" t="n">
-        <v>1.7</v>
+        <v>-44.4</v>
       </c>
       <c r="E49" t="n">
-        <v>36.1</v>
+        <v>40.4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-9.4</v>
+        <v>37.7</v>
       </c>
       <c r="D50" t="n">
-        <v>-44.4</v>
+        <v>-2.5</v>
       </c>
       <c r="E50" t="n">
-        <v>35</v>
+        <v>40.3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3012,22 +3207,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>12.6</v>
+        <v>-5.3</v>
       </c>
       <c r="D51" t="n">
-        <v>-21</v>
+        <v>-44.4</v>
       </c>
       <c r="E51" t="n">
-        <v>33.6</v>
+        <v>39.1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3038,657 +3233,657 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>12.6</v>
+        <v>8.6</v>
       </c>
       <c r="D52" t="n">
-        <v>-20.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E52" t="n">
-        <v>33.6</v>
+        <v>38.2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>12.6</v>
+        <v>-7.9</v>
       </c>
       <c r="D53" t="n">
-        <v>-20.8</v>
+        <v>-44.4</v>
       </c>
       <c r="E53" t="n">
-        <v>33.4</v>
+        <v>36.6</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>68.59999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="D54" t="n">
-        <v>37.7</v>
+        <v>-28</v>
       </c>
       <c r="E54" t="n">
-        <v>30.8</v>
+        <v>36.6</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>68.59999999999999</v>
+        <v>38.2</v>
       </c>
       <c r="D55" t="n">
-        <v>38.2</v>
+        <v>1.7</v>
       </c>
       <c r="E55" t="n">
-        <v>30.4</v>
+        <v>36.5</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.7</v>
+        <v>-8.1</v>
       </c>
       <c r="D56" t="n">
-        <v>-28</v>
+        <v>-44.4</v>
       </c>
       <c r="E56" t="n">
-        <v>29.6</v>
+        <v>36.3</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8.6</v>
+        <v>37.7</v>
       </c>
       <c r="D57" t="n">
-        <v>-21</v>
+        <v>1.7</v>
       </c>
       <c r="E57" t="n">
-        <v>29.6</v>
+        <v>36.1</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8.6</v>
+        <v>-9.4</v>
       </c>
       <c r="D58" t="n">
-        <v>-20.9</v>
+        <v>-44.4</v>
       </c>
       <c r="E58" t="n">
-        <v>29.6</v>
+        <v>35</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38.2</v>
+        <v>12.6</v>
       </c>
       <c r="D59" t="n">
-        <v>8.6</v>
+        <v>-21</v>
       </c>
       <c r="E59" t="n">
-        <v>29.6</v>
+        <v>33.6</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>8.6</v>
+        <v>12.6</v>
       </c>
       <c r="D60" t="n">
-        <v>-20.8</v>
+        <v>-20.9</v>
       </c>
       <c r="E60" t="n">
-        <v>29.4</v>
+        <v>33.6</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>37.7</v>
+        <v>12.6</v>
       </c>
       <c r="D61" t="n">
-        <v>8.6</v>
+        <v>-20.8</v>
       </c>
       <c r="E61" t="n">
-        <v>29.1</v>
+        <v>33.4</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>38.2</v>
+        <v>1.7</v>
       </c>
       <c r="D62" t="n">
-        <v>12.6</v>
+        <v>-29.6</v>
       </c>
       <c r="E62" t="n">
-        <v>25.6</v>
+        <v>31.2</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-2.5</v>
+        <v>12.6</v>
       </c>
       <c r="D63" t="n">
-        <v>-28</v>
+        <v>-18.5</v>
       </c>
       <c r="E63" t="n">
-        <v>25.4</v>
+        <v>31.2</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>TEN (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>CCEC</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>CMDB</t>
-        </is>
-      </c>
       <c r="C64" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="D64" t="n">
         <v>37.7</v>
       </c>
-      <c r="D64" t="n">
-        <v>12.6</v>
-      </c>
       <c r="E64" t="n">
-        <v>25.1</v>
+        <v>30.8</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-4</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>-28</v>
+        <v>38.2</v>
       </c>
       <c r="E65" t="n">
-        <v>24</v>
+        <v>30.4</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-20.8</v>
+        <v>1.7</v>
       </c>
       <c r="D66" t="n">
-        <v>-44.4</v>
+        <v>-28</v>
       </c>
       <c r="E66" t="n">
-        <v>23.6</v>
+        <v>29.6</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>ECO</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C67" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D67" t="n">
         <v>-21</v>
       </c>
-      <c r="D67" t="n">
-        <v>-44.4</v>
-      </c>
       <c r="E67" t="n">
-        <v>23.5</v>
+        <v>29.6</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>FRO</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C68" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D68" t="n">
         <v>-20.9</v>
       </c>
-      <c r="D68" t="n">
-        <v>-44.4</v>
-      </c>
       <c r="E68" t="n">
-        <v>23.5</v>
+        <v>29.6</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-5.3</v>
+        <v>38.2</v>
       </c>
       <c r="D69" t="n">
-        <v>-28</v>
+        <v>8.6</v>
       </c>
       <c r="E69" t="n">
-        <v>22.7</v>
+        <v>29.6</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.7</v>
+        <v>8.6</v>
       </c>
       <c r="D70" t="n">
-        <v>-21</v>
+        <v>-20.8</v>
       </c>
       <c r="E70" t="n">
-        <v>22.6</v>
+        <v>29.4</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.7</v>
+        <v>37.7</v>
       </c>
       <c r="D71" t="n">
-        <v>-20.9</v>
+        <v>8.6</v>
       </c>
       <c r="E71" t="n">
-        <v>22.6</v>
+        <v>29.1</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.7</v>
+        <v>8.6</v>
       </c>
       <c r="D72" t="n">
-        <v>-20.8</v>
+        <v>-18.5</v>
       </c>
       <c r="E72" t="n">
-        <v>22.5</v>
+        <v>27.2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>12.6</v>
+        <v>-2.5</v>
       </c>
       <c r="D73" t="n">
-        <v>-9.4</v>
+        <v>-29.6</v>
       </c>
       <c r="E73" t="n">
-        <v>22.1</v>
+        <v>27</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>12.6</v>
+        <v>-18.5</v>
       </c>
       <c r="D74" t="n">
-        <v>-8.1</v>
+        <v>-44.4</v>
       </c>
       <c r="E74" t="n">
-        <v>20.8</v>
+        <v>25.9</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>12.6</v>
+        <v>-4</v>
       </c>
       <c r="D75" t="n">
-        <v>-7.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E75" t="n">
-        <v>20.5</v>
+        <v>25.6</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-7.9</v>
+        <v>38.2</v>
       </c>
       <c r="D76" t="n">
-        <v>-28</v>
+        <v>12.6</v>
       </c>
       <c r="E76" t="n">
-        <v>20.1</v>
+        <v>25.6</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3697,169 +3892,169 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-8.1</v>
+        <v>-2.5</v>
       </c>
       <c r="D77" t="n">
         <v>-28</v>
       </c>
       <c r="E77" t="n">
-        <v>19.8</v>
+        <v>25.4</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-9.4</v>
+        <v>37.7</v>
       </c>
       <c r="D78" t="n">
-        <v>-28</v>
+        <v>12.6</v>
       </c>
       <c r="E78" t="n">
-        <v>18.5</v>
+        <v>25.1</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-2.5</v>
+        <v>-5.3</v>
       </c>
       <c r="D79" t="n">
-        <v>-21</v>
+        <v>-29.6</v>
       </c>
       <c r="E79" t="n">
-        <v>18.4</v>
+        <v>24.3</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-2.5</v>
+        <v>-4</v>
       </c>
       <c r="D80" t="n">
-        <v>-20.9</v>
+        <v>-28</v>
       </c>
       <c r="E80" t="n">
-        <v>18.4</v>
+        <v>24</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-2.5</v>
+        <v>-20.8</v>
       </c>
       <c r="D81" t="n">
-        <v>-20.8</v>
+        <v>-44.4</v>
       </c>
       <c r="E81" t="n">
-        <v>18.3</v>
+        <v>23.6</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>8.6</v>
+        <v>-21</v>
       </c>
       <c r="D82" t="n">
-        <v>-9.4</v>
+        <v>-44.4</v>
       </c>
       <c r="E82" t="n">
-        <v>18.1</v>
+        <v>23.5</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>12.6</v>
+        <v>-20.9</v>
       </c>
       <c r="D83" t="n">
-        <v>-5.3</v>
+        <v>-44.4</v>
       </c>
       <c r="E83" t="n">
-        <v>17.9</v>
+        <v>23.5</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3870,74 +4065,74 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-4</v>
+        <v>-5.3</v>
       </c>
       <c r="D84" t="n">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="E84" t="n">
-        <v>17</v>
+        <v>22.7</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-4</v>
+        <v>1.7</v>
       </c>
       <c r="D85" t="n">
-        <v>-20.9</v>
+        <v>-21</v>
       </c>
       <c r="E85" t="n">
-        <v>16.9</v>
+        <v>22.6</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-4</v>
+        <v>1.7</v>
       </c>
       <c r="D86" t="n">
-        <v>-20.8</v>
+        <v>-20.9</v>
       </c>
       <c r="E86" t="n">
-        <v>16.8</v>
+        <v>22.6</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3948,26 +4143,26 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8.6</v>
+        <v>1.7</v>
       </c>
       <c r="D87" t="n">
-        <v>-8.1</v>
+        <v>-20.8</v>
       </c>
       <c r="E87" t="n">
-        <v>16.7</v>
+        <v>22.5</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -3979,392 +4174,392 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>12.6</v>
       </c>
       <c r="D88" t="n">
-        <v>-4</v>
+        <v>-9.4</v>
       </c>
       <c r="E88" t="n">
-        <v>16.6</v>
+        <v>22.1</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8.6</v>
+        <v>-7.9</v>
       </c>
       <c r="D89" t="n">
-        <v>-7.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E89" t="n">
-        <v>16.5</v>
+        <v>21.7</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-28</v>
+        <v>-8.1</v>
       </c>
       <c r="D90" t="n">
-        <v>-44.4</v>
+        <v>-29.6</v>
       </c>
       <c r="E90" t="n">
-        <v>16.4</v>
+        <v>21.4</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-5.3</v>
+        <v>12.6</v>
       </c>
       <c r="D91" t="n">
-        <v>-21</v>
+        <v>-8.1</v>
       </c>
       <c r="E91" t="n">
-        <v>15.7</v>
+        <v>20.8</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-5.3</v>
+        <v>12.6</v>
       </c>
       <c r="D92" t="n">
-        <v>-20.9</v>
+        <v>-7.9</v>
       </c>
       <c r="E92" t="n">
-        <v>15.7</v>
+        <v>20.5</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-5.3</v>
+        <v>1.7</v>
       </c>
       <c r="D93" t="n">
-        <v>-20.8</v>
+        <v>-18.5</v>
       </c>
       <c r="E93" t="n">
-        <v>15.5</v>
+        <v>20.2</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>12.6</v>
+        <v>-9.4</v>
       </c>
       <c r="D94" t="n">
-        <v>-2.5</v>
+        <v>-29.6</v>
       </c>
       <c r="E94" t="n">
-        <v>15.2</v>
+        <v>20.1</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>8.6</v>
+        <v>-7.9</v>
       </c>
       <c r="D95" t="n">
-        <v>-5.3</v>
+        <v>-28</v>
       </c>
       <c r="E95" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-7.9</v>
+        <v>-8.1</v>
       </c>
       <c r="D96" t="n">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="E96" t="n">
-        <v>13.1</v>
+        <v>19.8</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-7.9</v>
+        <v>-9.4</v>
       </c>
       <c r="D97" t="n">
-        <v>-20.9</v>
+        <v>-28</v>
       </c>
       <c r="E97" t="n">
-        <v>13.1</v>
+        <v>18.5</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-7.9</v>
+        <v>-2.5</v>
       </c>
       <c r="D98" t="n">
-        <v>-20.8</v>
+        <v>-21</v>
       </c>
       <c r="E98" t="n">
-        <v>12.9</v>
+        <v>18.4</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-8.1</v>
+        <v>-2.5</v>
       </c>
       <c r="D99" t="n">
-        <v>-21</v>
+        <v>-20.9</v>
       </c>
       <c r="E99" t="n">
-        <v>12.8</v>
+        <v>18.4</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-8.1</v>
+        <v>-2.5</v>
       </c>
       <c r="D100" t="n">
-        <v>-20.9</v>
+        <v>-20.8</v>
       </c>
       <c r="E100" t="n">
-        <v>12.8</v>
+        <v>18.3</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-8.1</v>
+        <v>8.6</v>
       </c>
       <c r="D101" t="n">
-        <v>-20.8</v>
+        <v>-9.4</v>
       </c>
       <c r="E101" t="n">
-        <v>12.7</v>
+        <v>18.1</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>8.6</v>
+        <v>12.6</v>
       </c>
       <c r="D102" t="n">
-        <v>-4</v>
+        <v>-5.3</v>
       </c>
       <c r="E102" t="n">
-        <v>12.6</v>
+        <v>17.9</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4373,24 +4568,24 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-9.4</v>
+        <v>-4</v>
       </c>
       <c r="D103" t="n">
         <v>-21</v>
       </c>
       <c r="E103" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4399,24 +4594,24 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-9.4</v>
+        <v>-4</v>
       </c>
       <c r="D104" t="n">
         <v>-20.9</v>
       </c>
       <c r="E104" t="n">
-        <v>11.5</v>
+        <v>16.9</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4425,377 +4620,377 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-9.4</v>
+        <v>-4</v>
       </c>
       <c r="D105" t="n">
         <v>-20.8</v>
       </c>
       <c r="E105" t="n">
-        <v>11.4</v>
+        <v>16.8</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1.7</v>
+        <v>8.6</v>
       </c>
       <c r="D106" t="n">
-        <v>-9.4</v>
+        <v>-8.1</v>
       </c>
       <c r="E106" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>8.6</v>
+        <v>12.6</v>
       </c>
       <c r="D107" t="n">
-        <v>-2.5</v>
+        <v>-4</v>
       </c>
       <c r="E107" t="n">
-        <v>11.1</v>
+        <v>16.6</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>12.6</v>
+        <v>8.6</v>
       </c>
       <c r="D108" t="n">
-        <v>1.7</v>
+        <v>-7.9</v>
       </c>
       <c r="E108" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1.7</v>
+        <v>-28</v>
       </c>
       <c r="D109" t="n">
-        <v>-8.1</v>
+        <v>-44.4</v>
       </c>
       <c r="E109" t="n">
-        <v>9.800000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1.7</v>
+        <v>-2.5</v>
       </c>
       <c r="D110" t="n">
-        <v>-7.9</v>
+        <v>-18.5</v>
       </c>
       <c r="E110" t="n">
-        <v>9.5</v>
+        <v>16</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-20.8</v>
+        <v>-5.3</v>
       </c>
       <c r="D111" t="n">
-        <v>-28</v>
+        <v>-21</v>
       </c>
       <c r="E111" t="n">
-        <v>7.2</v>
+        <v>15.7</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-21</v>
+        <v>-5.3</v>
       </c>
       <c r="D112" t="n">
-        <v>-28</v>
+        <v>-20.9</v>
       </c>
       <c r="E112" t="n">
-        <v>7</v>
+        <v>15.7</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-20.9</v>
+        <v>-5.3</v>
       </c>
       <c r="D113" t="n">
-        <v>-28</v>
+        <v>-20.8</v>
       </c>
       <c r="E113" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>8.6</v>
+        <v>12.6</v>
       </c>
       <c r="D114" t="n">
-        <v>1.7</v>
+        <v>-2.5</v>
       </c>
       <c r="E114" t="n">
-        <v>7</v>
+        <v>15.2</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1.7</v>
+        <v>-29.6</v>
       </c>
       <c r="D115" t="n">
-        <v>-5.3</v>
+        <v>-44.4</v>
       </c>
       <c r="E115" t="n">
-        <v>6.9</v>
+        <v>14.8</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-2.5</v>
+        <v>-4</v>
       </c>
       <c r="D116" t="n">
-        <v>-9.4</v>
+        <v>-18.5</v>
       </c>
       <c r="E116" t="n">
-        <v>6.9</v>
+        <v>14.6</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1.7</v>
+        <v>8.6</v>
       </c>
       <c r="D117" t="n">
-        <v>-4</v>
+        <v>-5.3</v>
       </c>
       <c r="E117" t="n">
-        <v>5.7</v>
+        <v>13.9</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-2.5</v>
+        <v>-5.3</v>
       </c>
       <c r="D118" t="n">
-        <v>-8.1</v>
+        <v>-18.5</v>
       </c>
       <c r="E118" t="n">
-        <v>5.6</v>
+        <v>13.3</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-4</v>
+        <v>-7.9</v>
       </c>
       <c r="D119" t="n">
-        <v>-9.4</v>
+        <v>-21</v>
       </c>
       <c r="E119" t="n">
-        <v>5.4</v>
+        <v>13.1</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4806,126 +5001,126 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-2.5</v>
+        <v>-7.9</v>
       </c>
       <c r="D120" t="n">
-        <v>-7.9</v>
+        <v>-20.9</v>
       </c>
       <c r="E120" t="n">
-        <v>5.3</v>
+        <v>13.1</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1.7</v>
+        <v>-7.9</v>
       </c>
       <c r="D121" t="n">
-        <v>-2.5</v>
+        <v>-20.8</v>
       </c>
       <c r="E121" t="n">
-        <v>4.2</v>
+        <v>12.9</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>-5.3</v>
+        <v>-8.1</v>
       </c>
       <c r="D122" t="n">
-        <v>-9.4</v>
+        <v>-21</v>
       </c>
       <c r="E122" t="n">
-        <v>4.2</v>
+        <v>12.8</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>-4</v>
+        <v>-8.1</v>
       </c>
       <c r="D123" t="n">
-        <v>-8.1</v>
+        <v>-20.9</v>
       </c>
       <c r="E123" t="n">
-        <v>4.1</v>
+        <v>12.8</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>12.6</v>
+        <v>-8.1</v>
       </c>
       <c r="D124" t="n">
-        <v>8.6</v>
+        <v>-20.8</v>
       </c>
       <c r="E124" t="n">
-        <v>4</v>
+        <v>12.7</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -4936,111 +5131,111 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
           <t>STNG</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>TRMD</t>
-        </is>
-      </c>
       <c r="C125" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D125" t="n">
         <v>-4</v>
       </c>
-      <c r="D125" t="n">
-        <v>-7.9</v>
-      </c>
       <c r="E125" t="n">
-        <v>3.9</v>
+        <v>12.6</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>-5.3</v>
+        <v>-9.4</v>
       </c>
       <c r="D126" t="n">
-        <v>-8.1</v>
+        <v>-21</v>
       </c>
       <c r="E126" t="n">
-        <v>2.9</v>
+        <v>11.5</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>-2.5</v>
+        <v>-9.4</v>
       </c>
       <c r="D127" t="n">
-        <v>-5.3</v>
+        <v>-20.9</v>
       </c>
       <c r="E127" t="n">
-        <v>2.8</v>
+        <v>11.5</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>-5.3</v>
+        <v>-9.4</v>
       </c>
       <c r="D128" t="n">
-        <v>-7.9</v>
+        <v>-20.8</v>
       </c>
       <c r="E128" t="n">
-        <v>2.6</v>
+        <v>11.4</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5049,223 +5244,1133 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>-7.9</v>
+        <v>1.7</v>
       </c>
       <c r="D129" t="n">
         <v>-9.4</v>
       </c>
       <c r="E129" t="n">
-        <v>1.6</v>
+        <v>11.1</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>STNG</t>
-        </is>
-      </c>
       <c r="C130" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D130" t="n">
         <v>-2.5</v>
       </c>
-      <c r="D130" t="n">
-        <v>-4</v>
-      </c>
       <c r="E130" t="n">
-        <v>1.5</v>
+        <v>11.1</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>-4</v>
+        <v>12.6</v>
       </c>
       <c r="D131" t="n">
-        <v>-5.3</v>
+        <v>1.7</v>
       </c>
       <c r="E131" t="n">
-        <v>1.3</v>
+        <v>11</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>-8.1</v>
+        <v>-18.5</v>
       </c>
       <c r="D132" t="n">
-        <v>-9.4</v>
+        <v>-29.6</v>
       </c>
       <c r="E132" t="n">
-        <v>1.3</v>
+        <v>11</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>38.2</v>
+        <v>-7.9</v>
       </c>
       <c r="D133" t="n">
-        <v>37.7</v>
+        <v>-18.5</v>
       </c>
       <c r="E133" t="n">
-        <v>0.5</v>
+        <v>10.7</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>-7.9</v>
+        <v>-8.1</v>
       </c>
       <c r="D134" t="n">
-        <v>-8.1</v>
+        <v>-18.5</v>
       </c>
       <c r="E134" t="n">
-        <v>0.3</v>
+        <v>10.4</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>-20.8</v>
+        <v>1.7</v>
       </c>
       <c r="D135" t="n">
-        <v>-21</v>
+        <v>-8.1</v>
       </c>
       <c r="E135" t="n">
-        <v>0.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>-20.8</v>
+        <v>1.7</v>
       </c>
       <c r="D136" t="n">
-        <v>-20.9</v>
+        <v>-7.9</v>
       </c>
       <c r="E136" t="n">
-        <v>0.1</v>
+        <v>9.5</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-28</v>
+      </c>
+      <c r="E137" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="E138" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs containerships)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="E139" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs containerships)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>-21</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="E140" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs containerships)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>FRO</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="E141" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs containerships)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-28</v>
+      </c>
+      <c r="E142" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>ECO</t>
         </is>
       </c>
-      <c r="C137" t="n">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>-21</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-28</v>
+      </c>
+      <c r="E143" t="n">
+        <v>7</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
         <v>-20.9</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D144" t="n">
+        <v>-28</v>
+      </c>
+      <c r="E144" t="n">
+        <v>7</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E145" t="n">
+        <v>7</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="E146" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="D147" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="E147" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E148" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="D149" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="E150" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="D151" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="E151" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D152" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="E152" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs lng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="D153" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="E153" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D155" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E155" t="n">
+        <v>4</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D156" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="E156" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="D157" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="D158" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="E158" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="E159" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="D160" t="n">
         <v>-21</v>
       </c>
-      <c r="E137" t="n">
+      <c r="E160" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="D161" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="E161" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="D162" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>-28</v>
+      </c>
+      <c r="D163" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="D164" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="D165" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D166" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="D167" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>CAPT</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="D168" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs lng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="D169" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="D170" t="n">
+        <v>-21</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="D171" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="D172" t="n">
+        <v>-21</v>
+      </c>
+      <c r="E172" t="n">
         <v>0</v>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>yes</t>
         </is>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -527,28 +527,28 @@
         <v>37.11</v>
       </c>
       <c r="E2" t="n">
-        <v>80.95</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>66.91</v>
+        <v>66.58</v>
       </c>
       <c r="G2" t="n">
-        <v>42.25</v>
+        <v>42.01</v>
       </c>
       <c r="H2" t="n">
-        <v>38.38</v>
+        <v>38.15</v>
       </c>
       <c r="I2" t="n">
-        <v>62.56</v>
+        <v>62.23</v>
       </c>
       <c r="J2" t="n">
-        <v>118.1</v>
+        <v>117</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="L2" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -625,19 +625,19 @@
         <v>72.5</v>
       </c>
       <c r="E4" t="n">
-        <v>85.68000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>75.81</v>
+        <v>75.83</v>
       </c>
       <c r="G4" t="n">
-        <v>61.21</v>
+        <v>61.22</v>
       </c>
       <c r="H4" t="n">
-        <v>59.57</v>
+        <v>59.58</v>
       </c>
       <c r="I4" t="n">
-        <v>73.7</v>
+        <v>73.72</v>
       </c>
       <c r="J4" t="n">
         <v>18.2</v>
@@ -821,7 +821,7 @@
         <v>82.56</v>
       </c>
       <c r="E8" t="n">
-        <v>74.11</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>63.97</v>
@@ -1555,28 +1555,28 @@
         <v>17.6</v>
       </c>
       <c r="E2" t="n">
-        <v>23.74</v>
+        <v>23.92</v>
       </c>
       <c r="F2" t="n">
-        <v>20.14</v>
+        <v>20.29</v>
       </c>
       <c r="G2" t="n">
-        <v>18.11</v>
+        <v>18.25</v>
       </c>
       <c r="H2" t="n">
-        <v>16.64</v>
+        <v>16.76</v>
       </c>
       <c r="I2" t="n">
-        <v>19.82</v>
+        <v>19.98</v>
       </c>
       <c r="J2" t="n">
-        <v>34.9</v>
+        <v>35.9</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.5</v>
+        <v>-4.8</v>
       </c>
       <c r="L2" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1604,28 +1604,28 @@
         <v>23.69</v>
       </c>
       <c r="E3" t="n">
-        <v>32.91</v>
+        <v>32.94</v>
       </c>
       <c r="F3" t="n">
-        <v>26.54</v>
+        <v>26.57</v>
       </c>
       <c r="G3" t="n">
-        <v>22.44</v>
+        <v>22.46</v>
       </c>
       <c r="H3" t="n">
-        <v>19.5</v>
+        <v>19.52</v>
       </c>
       <c r="I3" t="n">
-        <v>25.73</v>
+        <v>25.76</v>
       </c>
       <c r="J3" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.7</v>
+        <v>-17.6</v>
       </c>
       <c r="L3" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1653,32 +1653,32 @@
         <v>27.15</v>
       </c>
       <c r="E4" t="n">
-        <v>32.72</v>
+        <v>33.04</v>
       </c>
       <c r="F4" t="n">
-        <v>26.35</v>
+        <v>26.61</v>
       </c>
       <c r="G4" t="n">
-        <v>22.94</v>
+        <v>23.18</v>
       </c>
       <c r="H4" t="n">
-        <v>19.34</v>
+        <v>19.55</v>
       </c>
       <c r="I4" t="n">
-        <v>25.72</v>
+        <v>25.98</v>
       </c>
       <c r="J4" t="n">
-        <v>20.5</v>
+        <v>21.7</v>
       </c>
       <c r="K4" t="n">
-        <v>-28.8</v>
+        <v>-28</v>
       </c>
       <c r="L4" t="n">
-        <v>-5.3</v>
+        <v>-4.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
     </row>
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D2" t="n">
         <v>-44.4</v>
       </c>
       <c r="E2" t="n">
-        <v>113</v>
+        <v>112.1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D3" t="n">
         <v>-29.6</v>
       </c>
       <c r="E3" t="n">
-        <v>98.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D4" t="n">
         <v>-28</v>
       </c>
       <c r="E4" t="n">
-        <v>96.5</v>
+        <v>95.7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2020,13 +2020,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D5" t="n">
         <v>-21</v>
       </c>
       <c r="E5" t="n">
-        <v>89.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D6" t="n">
         <v>-20.9</v>
       </c>
       <c r="E6" t="n">
-        <v>89.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D7" t="n">
         <v>-20.8</v>
       </c>
       <c r="E7" t="n">
-        <v>89.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D8" t="n">
         <v>-18.5</v>
       </c>
       <c r="E8" t="n">
-        <v>87.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2176,13 +2176,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D11" t="n">
         <v>-9.4</v>
       </c>
       <c r="E11" t="n">
-        <v>78</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2202,13 +2202,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D12" t="n">
         <v>-8.1</v>
       </c>
       <c r="E12" t="n">
-        <v>76.7</v>
+        <v>75.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D13" t="n">
         <v>-7.9</v>
       </c>
       <c r="E13" t="n">
-        <v>76.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2254,13 +2254,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.3</v>
+        <v>-4.3</v>
       </c>
       <c r="E14" t="n">
-        <v>73.8</v>
+        <v>72</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D15" t="n">
         <v>-4</v>
       </c>
       <c r="E15" t="n">
-        <v>72.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2306,13 +2306,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D16" t="n">
         <v>-2.5</v>
       </c>
       <c r="E16" t="n">
-        <v>71.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2375,22 +2375,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>68.59999999999999</v>
+        <v>38.2</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7</v>
+        <v>-28</v>
       </c>
       <c r="E19" t="n">
-        <v>66.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2401,22 +2401,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>38.2</v>
+        <v>67.7</v>
       </c>
       <c r="D20" t="n">
-        <v>-28</v>
+        <v>1.7</v>
       </c>
       <c r="E20" t="n">
-        <v>66.2</v>
+        <v>66</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2453,26 +2453,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>68.59999999999999</v>
+        <v>38.2</v>
       </c>
       <c r="D22" t="n">
-        <v>8.6</v>
+        <v>-21</v>
       </c>
       <c r="E22" t="n">
-        <v>60</v>
+        <v>59.2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2484,17 +2484,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>38.2</v>
       </c>
       <c r="D23" t="n">
-        <v>-21</v>
+        <v>-20.9</v>
       </c>
       <c r="E23" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2505,26 +2505,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38.2</v>
+        <v>67.7</v>
       </c>
       <c r="D24" t="n">
-        <v>-20.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2644,13 +2644,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="D29" t="n">
         <v>-44.4</v>
       </c>
       <c r="E29" t="n">
-        <v>57</v>
+        <v>57.9</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>-18.5</v>
       </c>
       <c r="E30" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D32" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="E32" t="n">
-        <v>55.9</v>
+        <v>54.2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D33" t="n">
         <v>-44.4</v>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2947,33 +2947,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38.2</v>
+        <v>13.5</v>
       </c>
       <c r="D41" t="n">
-        <v>-5.3</v>
+        <v>-29.6</v>
       </c>
       <c r="E41" t="n">
-        <v>43.5</v>
+        <v>43.1</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2982,69 +2982,69 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37.7</v>
+        <v>38.2</v>
       </c>
       <c r="D42" t="n">
-        <v>-5.3</v>
+        <v>-4.3</v>
       </c>
       <c r="E42" t="n">
-        <v>43</v>
+        <v>42.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>12.6</v>
+        <v>38.2</v>
       </c>
       <c r="D43" t="n">
-        <v>-29.6</v>
+        <v>-4</v>
       </c>
       <c r="E43" t="n">
         <v>42.2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38.2</v>
+        <v>37.7</v>
       </c>
       <c r="D44" t="n">
-        <v>-4</v>
+        <v>-4.3</v>
       </c>
       <c r="E44" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -3103,52 +3103,52 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38.2</v>
+        <v>13.5</v>
       </c>
       <c r="D47" t="n">
-        <v>-2.5</v>
+        <v>-28</v>
       </c>
       <c r="E47" t="n">
-        <v>40.7</v>
+        <v>41.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>12.6</v>
+        <v>38.2</v>
       </c>
       <c r="D48" t="n">
-        <v>-28</v>
+        <v>-2.5</v>
       </c>
       <c r="E48" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-5.3</v>
+        <v>-4.3</v>
       </c>
       <c r="D51" t="n">
         <v>-44.4</v>
       </c>
       <c r="E51" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D52" t="n">
         <v>-29.6</v>
       </c>
       <c r="E52" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3259,52 +3259,52 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>-44.4</v>
+        <v>-28</v>
       </c>
       <c r="E53" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8.6</v>
+        <v>-7.9</v>
       </c>
       <c r="D54" t="n">
-        <v>-28</v>
+        <v>-44.4</v>
       </c>
       <c r="E54" t="n">
         <v>36.6</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="D59" t="n">
         <v>-21</v>
       </c>
       <c r="E59" t="n">
-        <v>33.6</v>
+        <v>34.5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3450,13 +3450,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="D60" t="n">
         <v>-20.9</v>
       </c>
       <c r="E60" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3476,13 +3476,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="D61" t="n">
         <v>-20.8</v>
       </c>
       <c r="E61" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3493,52 +3493,52 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1.7</v>
+        <v>13.5</v>
       </c>
       <c r="D62" t="n">
-        <v>-29.6</v>
+        <v>-18.5</v>
       </c>
       <c r="E62" t="n">
-        <v>31.2</v>
+        <v>32</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>12.6</v>
+        <v>1.7</v>
       </c>
       <c r="D63" t="n">
-        <v>-18.5</v>
+        <v>-29.6</v>
       </c>
       <c r="E63" t="n">
         <v>31.2</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
@@ -3554,13 +3554,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D64" t="n">
         <v>37.7</v>
       </c>
       <c r="E64" t="n">
-        <v>30.8</v>
+        <v>29.9</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3571,22 +3571,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>68.59999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="D65" t="n">
-        <v>38.2</v>
+        <v>-28</v>
       </c>
       <c r="E65" t="n">
-        <v>30.4</v>
+        <v>29.7</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3597,26 +3597,26 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>-28</v>
+        <v>-21</v>
       </c>
       <c r="E66" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3628,17 +3628,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D67" t="n">
-        <v>-21</v>
+        <v>-20.9</v>
       </c>
       <c r="E67" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3649,78 +3649,78 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8.6</v>
+        <v>67.7</v>
       </c>
       <c r="D68" t="n">
-        <v>-20.9</v>
+        <v>38.2</v>
       </c>
       <c r="E68" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>38.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>8.6</v>
+        <v>-20.8</v>
       </c>
       <c r="E69" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>CAPT</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>HAFN</t>
-        </is>
-      </c>
       <c r="C70" t="n">
-        <v>8.6</v>
+        <v>38.2</v>
       </c>
       <c r="D70" t="n">
-        <v>-20.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E70" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -3739,10 +3739,10 @@
         <v>37.7</v>
       </c>
       <c r="D71" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3762,13 +3762,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D72" t="n">
         <v>-18.5</v>
       </c>
       <c r="E72" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3857,59 +3857,59 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>38.2</v>
+        <v>-2.5</v>
       </c>
       <c r="D76" t="n">
-        <v>12.6</v>
+        <v>-28</v>
       </c>
       <c r="E76" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-2.5</v>
+        <v>-4.3</v>
       </c>
       <c r="D77" t="n">
-        <v>-28</v>
+        <v>-29.6</v>
       </c>
       <c r="E77" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3918,43 +3918,43 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>37.7</v>
+        <v>38.2</v>
       </c>
       <c r="D78" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="E78" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-5.3</v>
+        <v>37.7</v>
       </c>
       <c r="D79" t="n">
-        <v>-29.6</v>
+        <v>13.5</v>
       </c>
       <c r="E79" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -4013,33 +4013,33 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-21</v>
+        <v>-4.3</v>
       </c>
       <c r="D82" t="n">
-        <v>-44.4</v>
+        <v>-28</v>
       </c>
       <c r="E82" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-20.9</v>
+        <v>-21</v>
       </c>
       <c r="D83" t="n">
         <v>-44.4</v>
@@ -4065,52 +4065,52 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-5.3</v>
+        <v>-20.9</v>
       </c>
       <c r="D84" t="n">
-        <v>-28</v>
+        <v>-44.4</v>
       </c>
       <c r="E84" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1.7</v>
+        <v>13.5</v>
       </c>
       <c r="D85" t="n">
-        <v>-21</v>
+        <v>-9.4</v>
       </c>
       <c r="E85" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -4122,14 +4122,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>1.7</v>
       </c>
       <c r="D86" t="n">
-        <v>-20.9</v>
+        <v>-21</v>
       </c>
       <c r="E86" t="n">
         <v>22.6</v>
@@ -4148,47 +4148,47 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>1.7</v>
       </c>
       <c r="D87" t="n">
-        <v>-20.8</v>
+        <v>-20.9</v>
       </c>
       <c r="E87" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>12.6</v>
+        <v>1.7</v>
       </c>
       <c r="D88" t="n">
-        <v>-9.4</v>
+        <v>-20.8</v>
       </c>
       <c r="E88" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -4221,52 +4221,52 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>ASC</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>MPCC</t>
-        </is>
-      </c>
       <c r="C90" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D90" t="n">
         <v>-8.1</v>
       </c>
-      <c r="D90" t="n">
-        <v>-29.6</v>
-      </c>
       <c r="E90" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>12.6</v>
+        <v>-8.1</v>
       </c>
       <c r="D91" t="n">
-        <v>-8.1</v>
+        <v>-29.6</v>
       </c>
       <c r="E91" t="n">
-        <v>20.8</v>
+        <v>21.4</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
@@ -4282,13 +4282,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="D92" t="n">
         <v>-7.9</v>
       </c>
       <c r="E92" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4516,13 +4516,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D101" t="n">
         <v>-9.4</v>
       </c>
       <c r="E101" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4542,13 +4542,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="D102" t="n">
-        <v>-5.3</v>
+        <v>-4.3</v>
       </c>
       <c r="E102" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4559,26 +4559,26 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
           <t>STNG</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>ECO</t>
-        </is>
-      </c>
       <c r="C103" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D103" t="n">
         <v>-4</v>
       </c>
-      <c r="D103" t="n">
-        <v>-21</v>
-      </c>
       <c r="E103" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -4590,17 +4590,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>-4</v>
       </c>
       <c r="D104" t="n">
-        <v>-20.9</v>
+        <v>-21</v>
       </c>
       <c r="E104" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4616,69 +4616,69 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>-4</v>
       </c>
       <c r="D105" t="n">
-        <v>-20.8</v>
+        <v>-20.9</v>
       </c>
       <c r="E105" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8.6</v>
+        <v>-4</v>
       </c>
       <c r="D106" t="n">
-        <v>-8.1</v>
+        <v>-20.8</v>
       </c>
       <c r="E106" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>12.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D107" t="n">
-        <v>-4</v>
+        <v>-8.1</v>
       </c>
       <c r="E107" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -4689,78 +4689,78 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>8.6</v>
+        <v>-4.3</v>
       </c>
       <c r="D108" t="n">
-        <v>-7.9</v>
+        <v>-21</v>
       </c>
       <c r="E108" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-28</v>
+        <v>-4.3</v>
       </c>
       <c r="D109" t="n">
-        <v>-44.4</v>
+        <v>-20.9</v>
       </c>
       <c r="E109" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-2.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D110" t="n">
-        <v>-18.5</v>
+        <v>-7.9</v>
       </c>
       <c r="E110" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -4772,73 +4772,73 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-5.3</v>
+        <v>-4.3</v>
       </c>
       <c r="D111" t="n">
-        <v>-21</v>
+        <v>-20.8</v>
       </c>
       <c r="E111" t="n">
-        <v>15.7</v>
+        <v>16.5</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-5.3</v>
+        <v>-28</v>
       </c>
       <c r="D112" t="n">
-        <v>-20.9</v>
+        <v>-44.4</v>
       </c>
       <c r="E112" t="n">
-        <v>15.7</v>
+        <v>16.4</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-5.3</v>
+        <v>-2.5</v>
       </c>
       <c r="D113" t="n">
-        <v>-20.8</v>
+        <v>-18.5</v>
       </c>
       <c r="E113" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
@@ -4854,13 +4854,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="D114" t="n">
         <v>-2.5</v>
       </c>
       <c r="E114" t="n">
-        <v>15.2</v>
+        <v>16</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -4923,52 +4923,52 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>8.6</v>
+        <v>-4.3</v>
       </c>
       <c r="D117" t="n">
-        <v>-5.3</v>
+        <v>-18.5</v>
       </c>
       <c r="E117" t="n">
-        <v>13.9</v>
+        <v>14.2</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-5.3</v>
+        <v>-7.9</v>
       </c>
       <c r="D118" t="n">
-        <v>-18.5</v>
+        <v>-21</v>
       </c>
       <c r="E118" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -4980,14 +4980,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>-7.9</v>
       </c>
       <c r="D119" t="n">
-        <v>-21</v>
+        <v>-20.9</v>
       </c>
       <c r="E119" t="n">
         <v>13.1</v>
@@ -5001,26 +5001,26 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D120" t="n">
-        <v>-20.9</v>
+        <v>-4.3</v>
       </c>
       <c r="E120" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -5140,13 +5140,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D125" t="n">
         <v>-4</v>
       </c>
       <c r="E125" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5157,26 +5157,26 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>-9.4</v>
+        <v>13.5</v>
       </c>
       <c r="D126" t="n">
-        <v>-21</v>
+        <v>1.7</v>
       </c>
       <c r="E126" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>-9.4</v>
       </c>
       <c r="D127" t="n">
-        <v>-20.9</v>
+        <v>-21</v>
       </c>
       <c r="E127" t="n">
         <v>11.5</v>
@@ -5214,47 +5214,47 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C128" t="n">
         <v>-9.4</v>
       </c>
       <c r="D128" t="n">
-        <v>-20.8</v>
+        <v>-20.9</v>
       </c>
       <c r="E128" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1.7</v>
+        <v>-9.4</v>
       </c>
       <c r="D129" t="n">
-        <v>-9.4</v>
+        <v>-20.8</v>
       </c>
       <c r="E129" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D130" t="n">
         <v>-2.5</v>
       </c>
       <c r="E130" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -5287,26 +5287,26 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>12.6</v>
+        <v>1.7</v>
       </c>
       <c r="D131" t="n">
-        <v>1.7</v>
+        <v>-9.4</v>
       </c>
       <c r="E131" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D145" t="n">
         <v>1.7</v>
@@ -5677,52 +5677,52 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1.7</v>
+        <v>-2.5</v>
       </c>
       <c r="D146" t="n">
-        <v>-5.3</v>
+        <v>-9.4</v>
       </c>
       <c r="E146" t="n">
         <v>6.9</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>-2.5</v>
+        <v>1.7</v>
       </c>
       <c r="D147" t="n">
-        <v>-9.4</v>
+        <v>-4.3</v>
       </c>
       <c r="E147" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -5833,100 +5833,100 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1.7</v>
+        <v>-4.3</v>
       </c>
       <c r="D152" t="n">
-        <v>-2.5</v>
+        <v>-9.4</v>
       </c>
       <c r="E152" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>-5.3</v>
+        <v>13.5</v>
       </c>
       <c r="D153" t="n">
-        <v>-9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E153" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>-4</v>
+        <v>1.7</v>
       </c>
       <c r="D154" t="n">
-        <v>-8.1</v>
+        <v>-2.5</v>
       </c>
       <c r="E154" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>12.6</v>
+        <v>-4</v>
       </c>
       <c r="D155" t="n">
-        <v>8.6</v>
+        <v>-8.1</v>
       </c>
       <c r="E155" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>-5.3</v>
+        <v>-4.3</v>
       </c>
       <c r="D157" t="n">
         <v>-8.1</v>
       </c>
       <c r="E157" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -5989,52 +5989,52 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>-2.5</v>
+        <v>-4.3</v>
       </c>
       <c r="D158" t="n">
-        <v>-5.3</v>
+        <v>-7.9</v>
       </c>
       <c r="E158" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>-5.3</v>
+        <v>-18.5</v>
       </c>
       <c r="D159" t="n">
-        <v>-7.9</v>
+        <v>-21</v>
       </c>
       <c r="E159" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
@@ -6046,14 +6046,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C160" t="n">
         <v>-18.5</v>
       </c>
       <c r="D160" t="n">
-        <v>-21</v>
+        <v>-20.9</v>
       </c>
       <c r="E160" t="n">
         <v>2.4</v>
@@ -6072,47 +6072,47 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C161" t="n">
         <v>-18.5</v>
       </c>
       <c r="D161" t="n">
-        <v>-20.9</v>
+        <v>-20.8</v>
       </c>
       <c r="E161" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>-18.5</v>
+        <v>-2.5</v>
       </c>
       <c r="D162" t="n">
-        <v>-20.8</v>
+        <v>-4.3</v>
       </c>
       <c r="E162" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -6197,78 +6197,78 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>-4</v>
+        <v>-8.1</v>
       </c>
       <c r="D166" t="n">
-        <v>-5.3</v>
+        <v>-9.4</v>
       </c>
       <c r="E166" t="n">
         <v>1.3</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>-8.1</v>
+        <v>38.2</v>
       </c>
       <c r="D167" t="n">
-        <v>-9.4</v>
+        <v>37.7</v>
       </c>
       <c r="E167" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>38.2</v>
+        <v>-4</v>
       </c>
       <c r="D168" t="n">
-        <v>37.7</v>
+        <v>-4.3</v>
       </c>
       <c r="E168" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -510,12 +510,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -524,31 +524,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>37.11</v>
+        <v>5.4</v>
       </c>
       <c r="E2" t="n">
-        <v>80.51000000000001</v>
+        <v>17.04</v>
       </c>
       <c r="F2" t="n">
-        <v>66.58</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>42.01</v>
+        <v>2.35</v>
       </c>
       <c r="H2" t="n">
-        <v>38.15</v>
+        <v>0.99</v>
       </c>
       <c r="I2" t="n">
-        <v>62.23</v>
+        <v>10.65</v>
       </c>
       <c r="J2" t="n">
-        <v>117</v>
+        <v>215.6</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8</v>
+        <v>-81.59999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -559,12 +559,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -573,31 +573,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.79</v>
+        <v>38.29</v>
       </c>
       <c r="E3" t="n">
-        <v>24.52</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>19.94</v>
+        <v>66.58</v>
       </c>
       <c r="G3" t="n">
-        <v>9.23</v>
+        <v>42.01</v>
       </c>
       <c r="H3" t="n">
-        <v>7.59</v>
+        <v>38.15</v>
       </c>
       <c r="I3" t="n">
-        <v>17.68</v>
+        <v>62.23</v>
       </c>
       <c r="J3" t="n">
-        <v>91.7</v>
+        <v>110.3</v>
       </c>
       <c r="K3" t="n">
-        <v>-40.7</v>
+        <v>-0.4</v>
       </c>
       <c r="L3" t="n">
-        <v>38.2</v>
+        <v>62.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,42 +622,42 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>72.5</v>
+        <v>13.24</v>
       </c>
       <c r="E4" t="n">
-        <v>85.70999999999999</v>
+        <v>22.69</v>
       </c>
       <c r="F4" t="n">
-        <v>75.83</v>
+        <v>18.31</v>
       </c>
       <c r="G4" t="n">
-        <v>61.22</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>59.58</v>
+        <v>6.86</v>
       </c>
       <c r="I4" t="n">
-        <v>73.72</v>
+        <v>16.2</v>
       </c>
       <c r="J4" t="n">
-        <v>18.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-17.8</v>
+        <v>-48.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7</v>
+        <v>22.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -671,42 +671,42 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.65</v>
+        <v>74.45</v>
       </c>
       <c r="E5" t="n">
-        <v>19.63</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>16.23</v>
+        <v>75.83</v>
       </c>
       <c r="G5" t="n">
-        <v>9.890000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="H5" t="n">
-        <v>9.07</v>
+        <v>59.58</v>
       </c>
       <c r="I5" t="n">
-        <v>15.08</v>
+        <v>73.72</v>
       </c>
       <c r="J5" t="n">
-        <v>17.9</v>
+        <v>15.1</v>
       </c>
       <c r="K5" t="n">
-        <v>-45.5</v>
+        <v>-20</v>
       </c>
       <c r="L5" t="n">
-        <v>-9.4</v>
+        <v>-1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>37.13</v>
+        <v>18.89</v>
       </c>
       <c r="E6" t="n">
-        <v>40.78</v>
+        <v>19.63</v>
       </c>
       <c r="F6" t="n">
-        <v>32.42</v>
+        <v>16.23</v>
       </c>
       <c r="G6" t="n">
-        <v>16.1</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>13.98</v>
+        <v>9.07</v>
       </c>
       <c r="I6" t="n">
-        <v>29.36</v>
+        <v>15.08</v>
       </c>
       <c r="J6" t="n">
-        <v>9.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>-62.3</v>
+        <v>-52</v>
       </c>
       <c r="L6" t="n">
-        <v>-20.9</v>
+        <v>-20.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>49.76</v>
+        <v>52.48</v>
       </c>
       <c r="E7" t="n">
         <v>54.22</v>
@@ -787,13 +787,13 @@
         <v>39.33</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>-60.6</v>
+        <v>-62.6</v>
       </c>
       <c r="L7" t="n">
-        <v>-21</v>
+        <v>-25.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -804,12 +804,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82.56</v>
+        <v>40.93</v>
       </c>
       <c r="E8" t="n">
-        <v>74.09999999999999</v>
+        <v>40.56</v>
       </c>
       <c r="F8" t="n">
-        <v>63.97</v>
+        <v>32.23</v>
       </c>
       <c r="G8" t="n">
-        <v>42.1</v>
+        <v>15.97</v>
       </c>
       <c r="H8" t="n">
-        <v>38.16</v>
+        <v>13.86</v>
       </c>
       <c r="I8" t="n">
-        <v>59.47</v>
+        <v>29.18</v>
       </c>
       <c r="J8" t="n">
-        <v>-10.2</v>
+        <v>-0.9</v>
       </c>
       <c r="K8" t="n">
-        <v>-53.8</v>
+        <v>-66.09999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-28</v>
+        <v>-28.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -853,47 +853,96 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>INSW</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>crude</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>84.48999999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>63.97</v>
+      </c>
+      <c r="G9" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>38.16</v>
+      </c>
+      <c r="I9" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-54.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>whole-company</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>crude</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D10" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="E10" t="n">
         <v>4.17</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>3.19</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" t="n">
         <v>1.34</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H10" t="n">
         <v>1.19</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>2.86</v>
       </c>
-      <c r="J9" t="n">
-        <v>-19</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-76.90000000000001</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-44.4</v>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="J10" t="n">
+        <v>-28.7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-79.59999999999999</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-51.1</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
@@ -1030,7 +1079,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.51</v>
+        <v>20.03</v>
       </c>
       <c r="E2" t="n">
         <v>48.52</v>
@@ -1051,13 +1100,13 @@
         <v>29.63</v>
       </c>
       <c r="K2" t="n">
-        <v>125.6</v>
+        <v>142.2</v>
       </c>
       <c r="L2" t="n">
-        <v>-102.1</v>
+        <v>-102.2</v>
       </c>
       <c r="M2" t="n">
-        <v>37.7</v>
+        <v>47.9</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1088,7 +1137,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30.5</v>
+        <v>29.74</v>
       </c>
       <c r="E3" t="n">
         <v>39.76</v>
@@ -1109,13 +1158,13 @@
         <v>29.73</v>
       </c>
       <c r="K3" t="n">
-        <v>30.4</v>
+        <v>33.7</v>
       </c>
       <c r="L3" t="n">
-        <v>-54.7</v>
+        <v>-53.6</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5</v>
+        <v>-0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1248,7 +1297,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>76.17</v>
+        <v>80.58</v>
       </c>
       <c r="E2" t="n">
         <v>90.78</v>
@@ -1269,17 +1318,17 @@
         <v>73.13</v>
       </c>
       <c r="K2" t="n">
-        <v>19.2</v>
+        <v>12.7</v>
       </c>
       <c r="L2" t="n">
-        <v>-37.1</v>
+        <v>-40.6</v>
       </c>
       <c r="M2" t="n">
-        <v>-4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1349,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.95</v>
+        <v>29.41</v>
       </c>
       <c r="E3" t="n">
         <v>39.1</v>
@@ -1321,13 +1370,13 @@
         <v>26.68</v>
       </c>
       <c r="K3" t="n">
-        <v>35.1</v>
+        <v>32.9</v>
       </c>
       <c r="L3" t="n">
-        <v>-62.5</v>
+        <v>-63.1</v>
       </c>
       <c r="M3" t="n">
-        <v>-7.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1352,7 +1401,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.38</v>
+        <v>17.07</v>
       </c>
       <c r="E4" t="n">
         <v>18.05</v>
@@ -1373,13 +1422,13 @@
         <v>15.05</v>
       </c>
       <c r="K4" t="n">
-        <v>10.2</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>-42.5</v>
+        <v>-44.9</v>
       </c>
       <c r="M4" t="n">
-        <v>-8.1</v>
+        <v>-11.8</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1404,7 +1453,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7.28</v>
+        <v>7.23</v>
       </c>
       <c r="E5" t="n">
         <v>8.279999999999999</v>
@@ -1425,13 +1474,13 @@
         <v>5.77</v>
       </c>
       <c r="K5" t="n">
-        <v>13.7</v>
+        <v>14.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-63.6</v>
+        <v>-63.4</v>
       </c>
       <c r="M5" t="n">
-        <v>-20.8</v>
+        <v>-20.3</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1552,7 +1601,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
       <c r="E2" t="n">
         <v>23.92</v>
@@ -1570,13 +1619,13 @@
         <v>19.98</v>
       </c>
       <c r="J2" t="n">
-        <v>35.9</v>
+        <v>41.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.8</v>
+        <v>-0.8</v>
       </c>
       <c r="L2" t="n">
-        <v>13.5</v>
+        <v>18.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1601,7 +1650,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.69</v>
+        <v>23.68</v>
       </c>
       <c r="E3" t="n">
         <v>32.94</v>
@@ -1619,13 +1668,13 @@
         <v>25.76</v>
       </c>
       <c r="J3" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="K3" t="n">
         <v>-17.6</v>
       </c>
       <c r="L3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1650,7 +1699,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.15</v>
+        <v>25.81</v>
       </c>
       <c r="E4" t="n">
         <v>33.04</v>
@@ -1668,13 +1717,13 @@
         <v>25.98</v>
       </c>
       <c r="J4" t="n">
-        <v>21.7</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>-28</v>
+        <v>-24.3</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.3</v>
+        <v>0.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1795,7 +1844,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>38.99</v>
+        <v>37.89</v>
       </c>
       <c r="E2" t="n">
         <v>34.74</v>
@@ -1813,13 +1862,13 @@
         <v>31.76</v>
       </c>
       <c r="J2" t="n">
-        <v>-10.9</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>-26.8</v>
+        <v>-24.7</v>
       </c>
       <c r="L2" t="n">
-        <v>-18.5</v>
+        <v>-16.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1844,31 +1893,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="E3" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="H3" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="I3" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.1</v>
+        <v>-19.1</v>
       </c>
       <c r="K3" t="n">
-        <v>-43.6</v>
+        <v>-41.9</v>
       </c>
       <c r="L3" t="n">
-        <v>-29.6</v>
+        <v>-27.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1887,7 +1936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F172"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1933,7 +1982,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1942,65 +1991,65 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="D2" t="n">
-        <v>-44.4</v>
+        <v>-51.1</v>
       </c>
       <c r="E2" t="n">
-        <v>112.1</v>
+        <v>148.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="D3" t="n">
         <v>-29.6</v>
       </c>
       <c r="E3" t="n">
-        <v>97.2</v>
+        <v>126.9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="D4" t="n">
-        <v>-28</v>
+        <v>-28.7</v>
       </c>
       <c r="E4" t="n">
-        <v>95.7</v>
+        <v>126</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2011,111 +2060,111 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="D5" t="n">
-        <v>-21</v>
+        <v>-27.3</v>
       </c>
       <c r="E5" t="n">
-        <v>88.59999999999999</v>
+        <v>124.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="D6" t="n">
-        <v>-20.9</v>
+        <v>-25.1</v>
       </c>
       <c r="E6" t="n">
-        <v>88.59999999999999</v>
+        <v>122.3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="D7" t="n">
-        <v>-20.8</v>
+        <v>-20.2</v>
       </c>
       <c r="E7" t="n">
-        <v>88.5</v>
+        <v>117.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="D8" t="n">
-        <v>-18.5</v>
+        <v>-20.3</v>
       </c>
       <c r="E8" t="n">
-        <v>86.2</v>
+        <v>117.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2124,180 +2173,180 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38.2</v>
+        <v>62.5</v>
       </c>
       <c r="D9" t="n">
-        <v>-44.4</v>
+        <v>-51.1</v>
       </c>
       <c r="E9" t="n">
-        <v>82.59999999999999</v>
+        <v>113.6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37.7</v>
+        <v>97.3</v>
       </c>
       <c r="D10" t="n">
-        <v>-44.4</v>
+        <v>-16.2</v>
       </c>
       <c r="E10" t="n">
-        <v>82.2</v>
+        <v>113.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.4</v>
+        <v>-11.8</v>
       </c>
       <c r="E11" t="n">
-        <v>77.09999999999999</v>
+        <v>109.1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>75.8</v>
+        <v>106.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>75.5</v>
+        <v>106.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>67.7</v>
+        <v>47.9</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.3</v>
+        <v>-51.1</v>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="D15" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="E15" t="n">
-        <v>71.7</v>
+        <v>98.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2306,91 +2355,91 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.5</v>
+        <v>-0</v>
       </c>
       <c r="E16" t="n">
-        <v>70.2</v>
+        <v>97.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38.2</v>
+        <v>97.3</v>
       </c>
       <c r="D17" t="n">
-        <v>-29.6</v>
+        <v>0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>67.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>37.7</v>
+        <v>62.5</v>
       </c>
       <c r="D18" t="n">
         <v>-29.6</v>
       </c>
       <c r="E18" t="n">
-        <v>67.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38.2</v>
+        <v>62.5</v>
       </c>
       <c r="D19" t="n">
-        <v>-28</v>
+        <v>-28.7</v>
       </c>
       <c r="E19" t="n">
-        <v>66.2</v>
+        <v>91.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2406,54 +2455,54 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>67.7</v>
+        <v>62.5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7</v>
+        <v>-27.3</v>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>89.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37.7</v>
+        <v>97.3</v>
       </c>
       <c r="D21" t="n">
-        <v>-28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>65.7</v>
+        <v>88.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2462,43 +2511,43 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38.2</v>
+        <v>62.5</v>
       </c>
       <c r="D22" t="n">
-        <v>-21</v>
+        <v>-25.1</v>
       </c>
       <c r="E22" t="n">
-        <v>59.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38.2</v>
+        <v>62.5</v>
       </c>
       <c r="D23" t="n">
-        <v>-20.9</v>
+        <v>-20.3</v>
       </c>
       <c r="E23" t="n">
-        <v>59.1</v>
+        <v>82.8</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2510,73 +2559,73 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>67.7</v>
+        <v>62.5</v>
       </c>
       <c r="D24" t="n">
-        <v>8.699999999999999</v>
+        <v>-20.2</v>
       </c>
       <c r="E24" t="n">
-        <v>59</v>
+        <v>82.7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38.2</v>
+        <v>97.3</v>
       </c>
       <c r="D25" t="n">
-        <v>-20.8</v>
+        <v>18.2</v>
       </c>
       <c r="E25" t="n">
-        <v>59</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37.7</v>
+        <v>62.5</v>
       </c>
       <c r="D26" t="n">
-        <v>-21</v>
+        <v>-16.2</v>
       </c>
       <c r="E26" t="n">
-        <v>58.7</v>
+        <v>78.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2588,21 +2637,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>37.7</v>
+        <v>47.9</v>
       </c>
       <c r="D27" t="n">
-        <v>-20.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E27" t="n">
-        <v>58.7</v>
+        <v>77.5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2614,281 +2663,281 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37.7</v>
+        <v>47.9</v>
       </c>
       <c r="D28" t="n">
-        <v>-20.8</v>
+        <v>-28.7</v>
       </c>
       <c r="E28" t="n">
-        <v>58.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>13.5</v>
+        <v>47.9</v>
       </c>
       <c r="D29" t="n">
-        <v>-44.4</v>
+        <v>-27.3</v>
       </c>
       <c r="E29" t="n">
-        <v>57.9</v>
+        <v>75.2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>BRUT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>CAPT</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>GSL</t>
-        </is>
-      </c>
       <c r="C30" t="n">
-        <v>38.2</v>
+        <v>97.3</v>
       </c>
       <c r="D30" t="n">
-        <v>-18.5</v>
+        <v>22.4</v>
       </c>
       <c r="E30" t="n">
-        <v>56.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37.7</v>
+        <v>62.5</v>
       </c>
       <c r="D31" t="n">
-        <v>-18.5</v>
+        <v>-11.8</v>
       </c>
       <c r="E31" t="n">
-        <v>56.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>67.7</v>
+        <v>22.4</v>
       </c>
       <c r="D32" t="n">
-        <v>13.5</v>
+        <v>-51.1</v>
       </c>
       <c r="E32" t="n">
-        <v>54.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8.699999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="D33" t="n">
-        <v>-44.4</v>
+        <v>-25.1</v>
       </c>
       <c r="E33" t="n">
-        <v>53.1</v>
+        <v>73</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38.2</v>
+        <v>62.5</v>
       </c>
       <c r="D34" t="n">
-        <v>-9.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>47.6</v>
+        <v>71.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37.7</v>
+        <v>62.5</v>
       </c>
       <c r="D35" t="n">
-        <v>-9.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>47.2</v>
+        <v>71.8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38.2</v>
+        <v>18.2</v>
       </c>
       <c r="D36" t="n">
-        <v>-8.1</v>
+        <v>-51.1</v>
       </c>
       <c r="E36" t="n">
-        <v>46.3</v>
+        <v>69.3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.7</v>
+        <v>47.9</v>
       </c>
       <c r="D37" t="n">
-        <v>-44.4</v>
+        <v>-20.3</v>
       </c>
       <c r="E37" t="n">
-        <v>46.1</v>
+        <v>68.2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>38.2</v>
+        <v>47.9</v>
       </c>
       <c r="D38" t="n">
-        <v>-7.9</v>
+        <v>-20.2</v>
       </c>
       <c r="E38" t="n">
-        <v>46.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -2900,80 +2949,80 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>37.7</v>
+        <v>47.9</v>
       </c>
       <c r="D39" t="n">
-        <v>-8.1</v>
+        <v>-16.2</v>
       </c>
       <c r="E39" t="n">
-        <v>45.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>37.7</v>
+        <v>62.5</v>
       </c>
       <c r="D40" t="n">
-        <v>-7.9</v>
+        <v>-1</v>
       </c>
       <c r="E40" t="n">
-        <v>45.6</v>
+        <v>63.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>13.5</v>
+        <v>62.5</v>
       </c>
       <c r="D41" t="n">
-        <v>-29.6</v>
+        <v>-0</v>
       </c>
       <c r="E41" t="n">
-        <v>43.1</v>
+        <v>62.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2982,95 +3031,95 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38.2</v>
+        <v>62.5</v>
       </c>
       <c r="D42" t="n">
-        <v>-4.3</v>
+        <v>0.6</v>
       </c>
       <c r="E42" t="n">
-        <v>42.5</v>
+        <v>61.9</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38.2</v>
+        <v>47.9</v>
       </c>
       <c r="D43" t="n">
-        <v>-4</v>
+        <v>-11.8</v>
       </c>
       <c r="E43" t="n">
-        <v>42.2</v>
+        <v>59.8</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>37.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>-4.3</v>
+        <v>-51.1</v>
       </c>
       <c r="E44" t="n">
-        <v>42.1</v>
+        <v>59.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-2.5</v>
+        <v>47.9</v>
       </c>
       <c r="D45" t="n">
-        <v>-44.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>41.9</v>
+        <v>57.2</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -3082,17 +3131,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37.7</v>
+        <v>47.9</v>
       </c>
       <c r="D46" t="n">
-        <v>-4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>41.7</v>
+        <v>57.2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3103,26 +3152,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>13.5</v>
+        <v>62.5</v>
       </c>
       <c r="D47" t="n">
-        <v>-28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>41.5</v>
+        <v>53.7</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3134,28 +3183,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38.2</v>
+        <v>22.4</v>
       </c>
       <c r="D48" t="n">
-        <v>-2.5</v>
+        <v>-29.6</v>
       </c>
       <c r="E48" t="n">
-        <v>40.7</v>
+        <v>52</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3164,39 +3213,39 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-4</v>
+        <v>0.6</v>
       </c>
       <c r="D49" t="n">
-        <v>-44.4</v>
+        <v>-51.1</v>
       </c>
       <c r="E49" t="n">
-        <v>40.4</v>
+        <v>51.7</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37.7</v>
+        <v>22.4</v>
       </c>
       <c r="D50" t="n">
-        <v>-2.5</v>
+        <v>-28.7</v>
       </c>
       <c r="E50" t="n">
-        <v>40.3</v>
+        <v>51.1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3207,7 +3256,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3216,102 +3265,102 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-4.3</v>
+        <v>-0</v>
       </c>
       <c r="D51" t="n">
-        <v>-44.4</v>
+        <v>-51.1</v>
       </c>
       <c r="E51" t="n">
-        <v>40.1</v>
+        <v>51</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8.699999999999999</v>
+        <v>-1</v>
       </c>
       <c r="D52" t="n">
-        <v>-29.6</v>
+        <v>-51.1</v>
       </c>
       <c r="E52" t="n">
-        <v>38.3</v>
+        <v>50.1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8.699999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="D53" t="n">
-        <v>-28</v>
+        <v>-27.3</v>
       </c>
       <c r="E53" t="n">
-        <v>36.7</v>
+        <v>49.6</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-7.9</v>
+        <v>97.3</v>
       </c>
       <c r="D54" t="n">
-        <v>-44.4</v>
+        <v>47.9</v>
       </c>
       <c r="E54" t="n">
-        <v>36.6</v>
+        <v>49.4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3320,91 +3369,91 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38.2</v>
+        <v>47.9</v>
       </c>
       <c r="D55" t="n">
-        <v>1.7</v>
+        <v>-1</v>
       </c>
       <c r="E55" t="n">
-        <v>36.5</v>
+        <v>48.9</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-8.1</v>
+        <v>47.9</v>
       </c>
       <c r="D56" t="n">
-        <v>-44.4</v>
+        <v>-0</v>
       </c>
       <c r="E56" t="n">
-        <v>36.3</v>
+        <v>47.9</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37.7</v>
+        <v>18.2</v>
       </c>
       <c r="D57" t="n">
-        <v>1.7</v>
+        <v>-29.6</v>
       </c>
       <c r="E57" t="n">
-        <v>36.1</v>
+        <v>47.8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-9.4</v>
+        <v>22.4</v>
       </c>
       <c r="D58" t="n">
-        <v>-44.4</v>
+        <v>-25.1</v>
       </c>
       <c r="E58" t="n">
-        <v>35</v>
+        <v>47.4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3415,26 +3464,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>13.5</v>
+        <v>47.9</v>
       </c>
       <c r="D59" t="n">
-        <v>-21</v>
+        <v>0.6</v>
       </c>
       <c r="E59" t="n">
-        <v>34.5</v>
+        <v>47.3</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -3450,13 +3499,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>13.5</v>
+        <v>18.2</v>
       </c>
       <c r="D60" t="n">
-        <v>-20.9</v>
+        <v>-28.7</v>
       </c>
       <c r="E60" t="n">
-        <v>34.4</v>
+        <v>46.9</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3472,177 +3521,177 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>13.5</v>
+        <v>18.2</v>
       </c>
       <c r="D61" t="n">
-        <v>-20.8</v>
+        <v>-27.3</v>
       </c>
       <c r="E61" t="n">
-        <v>34.3</v>
+        <v>45.5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>TEN (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>CMDB</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>GSL</t>
-        </is>
-      </c>
       <c r="C62" t="n">
-        <v>13.5</v>
+        <v>62.5</v>
       </c>
       <c r="D62" t="n">
-        <v>-18.5</v>
+        <v>18.2</v>
       </c>
       <c r="E62" t="n">
-        <v>32</v>
+        <v>44.3</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1.7</v>
+        <v>18.2</v>
       </c>
       <c r="D63" t="n">
-        <v>-29.6</v>
+        <v>-25.1</v>
       </c>
       <c r="E63" t="n">
-        <v>31.2</v>
+        <v>43.3</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>67.7</v>
+        <v>22.4</v>
       </c>
       <c r="D64" t="n">
-        <v>37.7</v>
+        <v>-20.3</v>
       </c>
       <c r="E64" t="n">
-        <v>29.9</v>
+        <v>42.6</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1.7</v>
+        <v>22.4</v>
       </c>
       <c r="D65" t="n">
-        <v>-28</v>
+        <v>-20.2</v>
       </c>
       <c r="E65" t="n">
-        <v>29.7</v>
+        <v>42.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8.699999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>-21</v>
+        <v>-51.1</v>
       </c>
       <c r="E66" t="n">
-        <v>29.7</v>
+        <v>41.8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8.699999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="D67" t="n">
-        <v>-20.9</v>
+        <v>-51.1</v>
       </c>
       <c r="E67" t="n">
-        <v>29.7</v>
+        <v>41.8</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -3658,13 +3707,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>67.7</v>
+        <v>62.5</v>
       </c>
       <c r="D68" t="n">
-        <v>38.2</v>
+        <v>22.4</v>
       </c>
       <c r="E68" t="n">
-        <v>29.5</v>
+        <v>40.2</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3675,85 +3724,85 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>HAFN</t>
-        </is>
-      </c>
       <c r="C69" t="n">
-        <v>8.699999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="D69" t="n">
-        <v>-20.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>29.5</v>
+        <v>39.2</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>38.2</v>
+        <v>-11.8</v>
       </c>
       <c r="D70" t="n">
-        <v>8.699999999999999</v>
+        <v>-51.1</v>
       </c>
       <c r="E70" t="n">
-        <v>29.5</v>
+        <v>39.2</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37.7</v>
+        <v>18.2</v>
       </c>
       <c r="D71" t="n">
-        <v>8.699999999999999</v>
+        <v>-20.3</v>
       </c>
       <c r="E71" t="n">
-        <v>29</v>
+        <v>38.5</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3762,310 +3811,310 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8.699999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="D72" t="n">
-        <v>-18.5</v>
+        <v>-16.2</v>
       </c>
       <c r="E72" t="n">
-        <v>27.3</v>
+        <v>38.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-2.5</v>
+        <v>18.2</v>
       </c>
       <c r="D73" t="n">
-        <v>-29.6</v>
+        <v>-20.2</v>
       </c>
       <c r="E73" t="n">
-        <v>27</v>
+        <v>38.4</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-18.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D74" t="n">
-        <v>-44.4</v>
+        <v>-29.6</v>
       </c>
       <c r="E74" t="n">
-        <v>25.9</v>
+        <v>38.4</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D75" t="n">
-        <v>-29.6</v>
+        <v>-28.7</v>
       </c>
       <c r="E75" t="n">
-        <v>25.6</v>
+        <v>37.5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>-28</v>
+        <v>-27.3</v>
       </c>
       <c r="E76" t="n">
-        <v>25.5</v>
+        <v>36</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-4.3</v>
+        <v>-16.2</v>
       </c>
       <c r="D77" t="n">
-        <v>-29.6</v>
+        <v>-51.1</v>
       </c>
       <c r="E77" t="n">
-        <v>25.2</v>
+        <v>34.9</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>38.2</v>
+        <v>97.3</v>
       </c>
       <c r="D78" t="n">
-        <v>13.5</v>
+        <v>62.5</v>
       </c>
       <c r="E78" t="n">
-        <v>24.7</v>
+        <v>34.8</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>37.7</v>
+        <v>18.2</v>
       </c>
       <c r="D79" t="n">
-        <v>13.5</v>
+        <v>-16.2</v>
       </c>
       <c r="E79" t="n">
-        <v>24.2</v>
+        <v>34.4</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-4</v>
+        <v>22.4</v>
       </c>
       <c r="D80" t="n">
-        <v>-28</v>
+        <v>-11.8</v>
       </c>
       <c r="E80" t="n">
-        <v>24</v>
+        <v>34.2</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-20.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D81" t="n">
-        <v>-44.4</v>
+        <v>-25.1</v>
       </c>
       <c r="E81" t="n">
-        <v>23.6</v>
+        <v>33.8</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-4.3</v>
+        <v>22.4</v>
       </c>
       <c r="D82" t="n">
-        <v>-28</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>23.6</v>
+        <v>31.7</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-21</v>
+        <v>22.4</v>
       </c>
       <c r="D83" t="n">
-        <v>-44.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>23.5</v>
+        <v>31.6</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4074,13 +4123,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-20.9</v>
+        <v>-20.2</v>
       </c>
       <c r="D84" t="n">
-        <v>-44.4</v>
+        <v>-51.1</v>
       </c>
       <c r="E84" t="n">
-        <v>23.5</v>
+        <v>30.9</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4091,364 +4140,364 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>13.5</v>
+        <v>-20.3</v>
       </c>
       <c r="D85" t="n">
-        <v>-9.4</v>
+        <v>-51.1</v>
       </c>
       <c r="E85" t="n">
-        <v>22.9</v>
+        <v>30.8</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="D86" t="n">
-        <v>-21</v>
+        <v>-29.6</v>
       </c>
       <c r="E86" t="n">
-        <v>22.6</v>
+        <v>30.3</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.7</v>
+        <v>18.2</v>
       </c>
       <c r="D87" t="n">
-        <v>-20.9</v>
+        <v>-11.8</v>
       </c>
       <c r="E87" t="n">
-        <v>22.6</v>
+        <v>30</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1.7</v>
+        <v>47.9</v>
       </c>
       <c r="D88" t="n">
-        <v>-20.8</v>
+        <v>18.2</v>
       </c>
       <c r="E88" t="n">
-        <v>22.5</v>
+        <v>29.7</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-7.9</v>
+        <v>-0</v>
       </c>
       <c r="D89" t="n">
         <v>-29.6</v>
       </c>
       <c r="E89" t="n">
-        <v>21.7</v>
+        <v>29.6</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>13.5</v>
+        <v>0.6</v>
       </c>
       <c r="D90" t="n">
-        <v>-8.1</v>
+        <v>-28.7</v>
       </c>
       <c r="E90" t="n">
-        <v>21.6</v>
+        <v>29.3</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D91" t="n">
-        <v>-29.6</v>
+        <v>-20.3</v>
       </c>
       <c r="E91" t="n">
-        <v>21.4</v>
+        <v>29</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D92" t="n">
-        <v>-7.9</v>
+        <v>-20.2</v>
       </c>
       <c r="E92" t="n">
-        <v>21.4</v>
+        <v>28.9</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1.7</v>
+        <v>-0</v>
       </c>
       <c r="D93" t="n">
-        <v>-18.5</v>
+        <v>-28.7</v>
       </c>
       <c r="E93" t="n">
-        <v>20.2</v>
+        <v>28.7</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-9.4</v>
+        <v>-1</v>
       </c>
       <c r="D94" t="n">
         <v>-29.6</v>
       </c>
       <c r="E94" t="n">
-        <v>20.1</v>
+        <v>28.6</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-7.9</v>
+        <v>0.6</v>
       </c>
       <c r="D95" t="n">
-        <v>-28</v>
+        <v>-27.3</v>
       </c>
       <c r="E95" t="n">
-        <v>20.1</v>
+        <v>27.9</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-8.1</v>
+        <v>-1</v>
       </c>
       <c r="D96" t="n">
-        <v>-28</v>
+        <v>-28.7</v>
       </c>
       <c r="E96" t="n">
-        <v>19.8</v>
+        <v>27.7</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-9.4</v>
+        <v>18.2</v>
       </c>
       <c r="D97" t="n">
-        <v>-28</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="E97" t="n">
-        <v>18.5</v>
+        <v>27.5</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-2.5</v>
+        <v>18.2</v>
       </c>
       <c r="D98" t="n">
-        <v>-21</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E98" t="n">
-        <v>18.4</v>
+        <v>27.4</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -4460,132 +4509,132 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-2.5</v>
+        <v>-0</v>
       </c>
       <c r="D99" t="n">
-        <v>-20.9</v>
+        <v>-27.3</v>
       </c>
       <c r="E99" t="n">
-        <v>18.4</v>
+        <v>27.2</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-2.5</v>
+        <v>-1</v>
       </c>
       <c r="D100" t="n">
-        <v>-20.8</v>
+        <v>-27.3</v>
       </c>
       <c r="E100" t="n">
-        <v>18.3</v>
+        <v>26.3</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>8.699999999999999</v>
+        <v>-25.1</v>
       </c>
       <c r="D101" t="n">
-        <v>-9.4</v>
+        <v>-51.1</v>
       </c>
       <c r="E101" t="n">
-        <v>18.2</v>
+        <v>26</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>13.5</v>
+        <v>0.6</v>
       </c>
       <c r="D102" t="n">
-        <v>-4.3</v>
+        <v>-25.1</v>
       </c>
       <c r="E102" t="n">
-        <v>17.8</v>
+        <v>25.7</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>13.5</v>
+        <v>47.9</v>
       </c>
       <c r="D103" t="n">
-        <v>-4</v>
+        <v>22.4</v>
       </c>
       <c r="E103" t="n">
-        <v>17.5</v>
+        <v>25.6</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4594,65 +4643,65 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-4</v>
+        <v>-0</v>
       </c>
       <c r="D104" t="n">
-        <v>-21</v>
+        <v>-25.1</v>
       </c>
       <c r="E104" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D105" t="n">
-        <v>-20.9</v>
+        <v>-16.2</v>
       </c>
       <c r="E105" t="n">
-        <v>16.9</v>
+        <v>24.9</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="D106" t="n">
-        <v>-20.8</v>
+        <v>-25.1</v>
       </c>
       <c r="E106" t="n">
-        <v>16.8</v>
+        <v>24.1</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -4663,130 +4712,130 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>8.699999999999999</v>
+        <v>-27.3</v>
       </c>
       <c r="D107" t="n">
-        <v>-8.1</v>
+        <v>-51.1</v>
       </c>
       <c r="E107" t="n">
-        <v>16.8</v>
+        <v>23.8</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>-4.3</v>
+        <v>22.4</v>
       </c>
       <c r="D108" t="n">
-        <v>-21</v>
+        <v>-1</v>
       </c>
       <c r="E108" t="n">
-        <v>16.6</v>
+        <v>23.3</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-4.3</v>
+        <v>-28.7</v>
       </c>
       <c r="D109" t="n">
-        <v>-20.9</v>
+        <v>-51.1</v>
       </c>
       <c r="E109" t="n">
-        <v>16.6</v>
+        <v>22.4</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>8.699999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="D110" t="n">
-        <v>-7.9</v>
+        <v>-0</v>
       </c>
       <c r="E110" t="n">
-        <v>16.6</v>
+        <v>22.4</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>CAPT</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>HAFN</t>
-        </is>
-      </c>
       <c r="C111" t="n">
-        <v>-4.3</v>
+        <v>22.4</v>
       </c>
       <c r="D111" t="n">
-        <v>-20.8</v>
+        <v>0.6</v>
       </c>
       <c r="E111" t="n">
-        <v>16.5</v>
+        <v>21.7</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -4802,13 +4851,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-28</v>
+        <v>-29.6</v>
       </c>
       <c r="D112" t="n">
-        <v>-44.4</v>
+        <v>-51.1</v>
       </c>
       <c r="E112" t="n">
-        <v>16.4</v>
+        <v>21.4</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -4819,78 +4868,78 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-2.5</v>
+        <v>0.6</v>
       </c>
       <c r="D113" t="n">
-        <v>-18.5</v>
+        <v>-20.3</v>
       </c>
       <c r="E113" t="n">
-        <v>16</v>
+        <v>20.9</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>13.5</v>
+        <v>0.6</v>
       </c>
       <c r="D114" t="n">
-        <v>-2.5</v>
+        <v>-20.2</v>
       </c>
       <c r="E114" t="n">
-        <v>16</v>
+        <v>20.8</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-29.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D115" t="n">
-        <v>-44.4</v>
+        <v>-11.8</v>
       </c>
       <c r="E115" t="n">
-        <v>14.8</v>
+        <v>20.6</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -4902,125 +4951,125 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D116" t="n">
-        <v>-18.5</v>
+        <v>-29.6</v>
       </c>
       <c r="E116" t="n">
-        <v>14.6</v>
+        <v>20.4</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-4.3</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="D117" t="n">
-        <v>-18.5</v>
+        <v>-29.6</v>
       </c>
       <c r="E117" t="n">
-        <v>14.2</v>
+        <v>20.3</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-7.9</v>
+        <v>-0</v>
       </c>
       <c r="D118" t="n">
-        <v>-21</v>
+        <v>-20.2</v>
       </c>
       <c r="E118" t="n">
-        <v>13.1</v>
+        <v>20.2</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-7.9</v>
+        <v>-0</v>
       </c>
       <c r="D119" t="n">
-        <v>-20.9</v>
+        <v>-20.3</v>
       </c>
       <c r="E119" t="n">
-        <v>13.1</v>
+        <v>20.2</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>8.699999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D120" t="n">
-        <v>-4.3</v>
+        <v>-28.7</v>
       </c>
       <c r="E120" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -5032,277 +5081,277 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>-7.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="D121" t="n">
-        <v>-20.8</v>
+        <v>-28.7</v>
       </c>
       <c r="E121" t="n">
-        <v>12.9</v>
+        <v>19.4</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>-8.1</v>
+        <v>-1</v>
       </c>
       <c r="D122" t="n">
-        <v>-21</v>
+        <v>-20.3</v>
       </c>
       <c r="E122" t="n">
-        <v>12.8</v>
+        <v>19.3</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>-8.1</v>
+        <v>-1</v>
       </c>
       <c r="D123" t="n">
-        <v>-20.9</v>
+        <v>-20.2</v>
       </c>
       <c r="E123" t="n">
-        <v>12.8</v>
+        <v>19.2</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>-8.1</v>
+        <v>18.2</v>
       </c>
       <c r="D124" t="n">
-        <v>-20.8</v>
+        <v>-1</v>
       </c>
       <c r="E124" t="n">
-        <v>12.7</v>
+        <v>19.2</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>8.699999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="D125" t="n">
-        <v>-4</v>
+        <v>-0</v>
       </c>
       <c r="E125" t="n">
-        <v>12.7</v>
+        <v>18.2</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D126" t="n">
-        <v>1.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="E126" t="n">
-        <v>11.8</v>
+        <v>18.1</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>-9.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D127" t="n">
-        <v>-21</v>
+        <v>-27.3</v>
       </c>
       <c r="E127" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>-9.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="D128" t="n">
-        <v>-20.9</v>
+        <v>-27.3</v>
       </c>
       <c r="E128" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>-9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D129" t="n">
-        <v>-20.8</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E129" t="n">
-        <v>11.4</v>
+        <v>18</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>8.699999999999999</v>
+        <v>-11.8</v>
       </c>
       <c r="D130" t="n">
-        <v>-2.5</v>
+        <v>-29.6</v>
       </c>
       <c r="E130" t="n">
-        <v>11.2</v>
+        <v>17.8</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1.7</v>
+        <v>18.2</v>
       </c>
       <c r="D131" t="n">
-        <v>-9.4</v>
+        <v>0.6</v>
       </c>
       <c r="E131" t="n">
-        <v>11.1</v>
+        <v>17.6</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -5313,33 +5362,33 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>-18.5</v>
+        <v>-11.8</v>
       </c>
       <c r="D132" t="n">
-        <v>-29.6</v>
+        <v>-28.7</v>
       </c>
       <c r="E132" t="n">
-        <v>11</v>
+        <v>16.9</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5348,24 +5397,24 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>-7.9</v>
+        <v>0.6</v>
       </c>
       <c r="D133" t="n">
-        <v>-18.5</v>
+        <v>-16.2</v>
       </c>
       <c r="E133" t="n">
-        <v>10.7</v>
+        <v>16.8</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5374,102 +5423,102 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>-8.1</v>
+        <v>-0</v>
       </c>
       <c r="D134" t="n">
-        <v>-18.5</v>
+        <v>-16.2</v>
       </c>
       <c r="E134" t="n">
-        <v>10.4</v>
+        <v>16.2</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1.7</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D135" t="n">
-        <v>-8.1</v>
+        <v>-25.1</v>
       </c>
       <c r="E135" t="n">
-        <v>9.800000000000001</v>
+        <v>15.8</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="D136" t="n">
-        <v>-7.9</v>
+        <v>-25.1</v>
       </c>
       <c r="E136" t="n">
-        <v>9.5</v>
+        <v>15.8</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>-18.5</v>
+        <v>-11.8</v>
       </c>
       <c r="D137" t="n">
-        <v>-28</v>
+        <v>-27.3</v>
       </c>
       <c r="E137" t="n">
-        <v>9.4</v>
+        <v>15.4</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5478,13 +5527,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>-9.4</v>
+        <v>-1</v>
       </c>
       <c r="D138" t="n">
-        <v>-18.5</v>
+        <v>-16.2</v>
       </c>
       <c r="E138" t="n">
-        <v>9.1</v>
+        <v>15.2</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -5495,267 +5544,267 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>-20.8</v>
+        <v>62.5</v>
       </c>
       <c r="D139" t="n">
-        <v>-29.6</v>
+        <v>47.9</v>
       </c>
       <c r="E139" t="n">
-        <v>8.800000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>-21</v>
+        <v>22.4</v>
       </c>
       <c r="D140" t="n">
-        <v>-29.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E140" t="n">
-        <v>8.6</v>
+        <v>13.6</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>-20.9</v>
+        <v>-16.2</v>
       </c>
       <c r="D141" t="n">
         <v>-29.6</v>
       </c>
       <c r="E141" t="n">
-        <v>8.6</v>
+        <v>13.4</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>-20.8</v>
+        <v>-11.8</v>
       </c>
       <c r="D142" t="n">
-        <v>-28</v>
+        <v>-25.1</v>
       </c>
       <c r="E142" t="n">
-        <v>7.2</v>
+        <v>13.2</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>-21</v>
+        <v>0.6</v>
       </c>
       <c r="D143" t="n">
-        <v>-28</v>
+        <v>-11.8</v>
       </c>
       <c r="E143" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
           <t>FRO</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>INSW (WHOLE-CO)</t>
-        </is>
-      </c>
       <c r="C144" t="n">
-        <v>-20.9</v>
+        <v>-16.2</v>
       </c>
       <c r="D144" t="n">
-        <v>-28</v>
+        <v>-28.7</v>
       </c>
       <c r="E144" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>8.699999999999999</v>
+        <v>-0</v>
       </c>
       <c r="D145" t="n">
-        <v>1.7</v>
+        <v>-11.8</v>
       </c>
       <c r="E145" t="n">
-        <v>7</v>
+        <v>11.8</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>-2.5</v>
+        <v>-16.2</v>
       </c>
       <c r="D146" t="n">
-        <v>-9.4</v>
+        <v>-27.3</v>
       </c>
       <c r="E146" t="n">
-        <v>6.9</v>
+        <v>11.1</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1.7</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D147" t="n">
-        <v>-4.3</v>
+        <v>-20.3</v>
       </c>
       <c r="E147" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="D148" t="n">
-        <v>-4</v>
+        <v>-20.3</v>
       </c>
       <c r="E148" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5764,17 +5813,17 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>-2.5</v>
+        <v>-1</v>
       </c>
       <c r="D149" t="n">
-        <v>-8.1</v>
+        <v>-11.8</v>
       </c>
       <c r="E149" t="n">
-        <v>5.6</v>
+        <v>10.9</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -5790,13 +5839,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>-4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D150" t="n">
-        <v>-9.4</v>
+        <v>-20.2</v>
       </c>
       <c r="E150" t="n">
-        <v>5.4</v>
+        <v>10.9</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -5807,26 +5856,26 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>-2.5</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="D151" t="n">
-        <v>-7.9</v>
+        <v>-20.2</v>
       </c>
       <c r="E151" t="n">
-        <v>5.3</v>
+        <v>10.9</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -5838,158 +5887,158 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>-4.3</v>
+        <v>0.6</v>
       </c>
       <c r="D152" t="n">
-        <v>-9.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E152" t="n">
-        <v>5.1</v>
+        <v>9.9</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>13.5</v>
+        <v>0.6</v>
       </c>
       <c r="D153" t="n">
-        <v>8.699999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="E153" t="n">
-        <v>4.8</v>
+        <v>9.9</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
           <t>TNK</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>FLNG</t>
-        </is>
-      </c>
       <c r="C154" t="n">
-        <v>1.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D154" t="n">
-        <v>-2.5</v>
+        <v>-1</v>
       </c>
       <c r="E154" t="n">
-        <v>4.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>-4</v>
+        <v>-20.2</v>
       </c>
       <c r="D155" t="n">
-        <v>-8.1</v>
+        <v>-29.6</v>
       </c>
       <c r="E155" t="n">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>-4</v>
+        <v>-20.3</v>
       </c>
       <c r="D156" t="n">
-        <v>-7.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E156" t="n">
-        <v>3.9</v>
+        <v>9.4</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>-4.3</v>
+        <v>18.2</v>
       </c>
       <c r="D157" t="n">
-        <v>-8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E157" t="n">
-        <v>3.8</v>
+        <v>9.4</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5998,43 +6047,43 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>-4.3</v>
+        <v>-0</v>
       </c>
       <c r="D158" t="n">
-        <v>-7.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="E158" t="n">
-        <v>3.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>-18.5</v>
+        <v>-0</v>
       </c>
       <c r="D159" t="n">
-        <v>-21</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E159" t="n">
-        <v>2.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -6046,17 +6095,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>-18.5</v>
+        <v>-16.2</v>
       </c>
       <c r="D160" t="n">
-        <v>-20.9</v>
+        <v>-25.1</v>
       </c>
       <c r="E160" t="n">
-        <v>2.4</v>
+        <v>8.9</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -6067,111 +6116,111 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>-18.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D161" t="n">
-        <v>-20.8</v>
+        <v>-0</v>
       </c>
       <c r="E161" t="n">
-        <v>2.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>-2.5</v>
+        <v>-20.2</v>
       </c>
       <c r="D162" t="n">
-        <v>-4.3</v>
+        <v>-28.7</v>
       </c>
       <c r="E162" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>-28</v>
+        <v>-20.3</v>
       </c>
       <c r="D163" t="n">
-        <v>-29.6</v>
+        <v>-28.7</v>
       </c>
       <c r="E163" t="n">
-        <v>1.6</v>
+        <v>8.4</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>-7.9</v>
+        <v>-11.8</v>
       </c>
       <c r="D164" t="n">
-        <v>-9.4</v>
+        <v>-20.3</v>
       </c>
       <c r="E164" t="n">
-        <v>1.6</v>
+        <v>8.4</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6180,76 +6229,76 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>-2.5</v>
+        <v>-1</v>
       </c>
       <c r="D165" t="n">
-        <v>-4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E165" t="n">
-        <v>1.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>-8.1</v>
+        <v>-1</v>
       </c>
       <c r="D166" t="n">
-        <v>-9.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="E166" t="n">
-        <v>1.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>38.2</v>
+        <v>-11.8</v>
       </c>
       <c r="D167" t="n">
-        <v>37.7</v>
+        <v>-20.2</v>
       </c>
       <c r="E167" t="n">
-        <v>0.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6258,43 +6307,43 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>-4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D168" t="n">
-        <v>-4.3</v>
+        <v>0.6</v>
       </c>
       <c r="E168" t="n">
-        <v>0.3</v>
+        <v>8.1</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>-7.9</v>
+        <v>-20.2</v>
       </c>
       <c r="D169" t="n">
-        <v>-8.1</v>
+        <v>-27.3</v>
       </c>
       <c r="E169" t="n">
-        <v>0.3</v>
+        <v>7.1</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
@@ -6306,71 +6355,565 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>-20.8</v>
+        <v>-20.3</v>
       </c>
       <c r="D170" t="n">
-        <v>-21</v>
+        <v>-27.3</v>
       </c>
       <c r="E170" t="n">
-        <v>0.2</v>
+        <v>7</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>-20.8</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D171" t="n">
-        <v>-20.9</v>
+        <v>-16.2</v>
       </c>
       <c r="E171" t="n">
-        <v>0.1</v>
+        <v>6.9</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="D172" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="E172" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs containerships)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="D173" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="E173" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>-20.3</v>
+      </c>
+      <c r="D174" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="E174" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="D175" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="E175" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="D176" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="E176" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs containerships)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>CAPT</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D177" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E177" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="D178" t="n">
+        <v>-20.3</v>
+      </c>
+      <c r="E178" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="D179" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="E179" t="n">
+        <v>4</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
           <t>FRO</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="C180" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="D180" t="n">
+        <v>-28.7</v>
+      </c>
+      <c r="E180" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="D181" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="D182" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="E182" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>-27.3</v>
+      </c>
+      <c r="D183" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="E183" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
         <is>
           <t>ECO</t>
         </is>
       </c>
-      <c r="C172" t="n">
-        <v>-20.9</v>
-      </c>
-      <c r="D172" t="n">
-        <v>-21</v>
-      </c>
-      <c r="E172" t="n">
-        <v>0</v>
-      </c>
-      <c r="F172" t="inlineStr">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="D184" t="n">
+        <v>-27.3</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs containerships)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>-27.3</v>
+      </c>
+      <c r="D186" t="n">
+        <v>-28.7</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>-28.7</v>
+      </c>
+      <c r="D188" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D189" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="D190" t="n">
+        <v>-20.3</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="D191" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F191" t="inlineStr">
         <is>
           <t>yes</t>
         </is>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -3599,21 +3599,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>22.4</v>
       </c>
       <c r="D64" t="n">
-        <v>-20.3</v>
+        <v>-20.2</v>
       </c>
       <c r="E64" t="n">
         <v>42.6</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3625,21 +3625,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>22.4</v>
       </c>
       <c r="D65" t="n">
-        <v>-20.2</v>
+        <v>-20.3</v>
       </c>
       <c r="E65" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -3713,7 +3713,7 @@
         <v>22.4</v>
       </c>
       <c r="E68" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3776,52 +3776,52 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>18.2</v>
+        <v>22.4</v>
       </c>
       <c r="D71" t="n">
-        <v>-20.3</v>
+        <v>-16.2</v>
       </c>
       <c r="E71" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>22.4</v>
+        <v>18.2</v>
       </c>
       <c r="D72" t="n">
-        <v>-16.2</v>
+        <v>-20.3</v>
       </c>
       <c r="E72" t="n">
         <v>38.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
         <v>22.4</v>
       </c>
       <c r="E103" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>-1</v>
       </c>
       <c r="E108" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -527,28 +527,28 @@
         <v>5.4</v>
       </c>
       <c r="E2" t="n">
-        <v>17.04</v>
+        <v>17.74</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>13.18</v>
       </c>
       <c r="G2" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>0.99</v>
+        <v>0.63</v>
       </c>
       <c r="I2" t="n">
-        <v>10.65</v>
+        <v>10.8</v>
       </c>
       <c r="J2" t="n">
-        <v>215.6</v>
+        <v>228.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-81.59999999999999</v>
+        <v>-88.3</v>
       </c>
       <c r="L2" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -576,28 +576,28 @@
         <v>38.29</v>
       </c>
       <c r="E3" t="n">
-        <v>80.51000000000001</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>66.58</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>42.01</v>
+        <v>44.59</v>
       </c>
       <c r="H3" t="n">
-        <v>38.15</v>
+        <v>40.77</v>
       </c>
       <c r="I3" t="n">
-        <v>62.23</v>
+        <v>64.84</v>
       </c>
       <c r="J3" t="n">
-        <v>110.3</v>
+        <v>119</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4</v>
+        <v>6.5</v>
       </c>
       <c r="L3" t="n">
-        <v>62.5</v>
+        <v>69.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -625,28 +625,28 @@
         <v>13.24</v>
       </c>
       <c r="E4" t="n">
-        <v>22.69</v>
+        <v>23.94</v>
       </c>
       <c r="F4" t="n">
-        <v>18.31</v>
+        <v>18.9</v>
       </c>
       <c r="G4" t="n">
-        <v>8.140000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>6.86</v>
+        <v>6.95</v>
       </c>
       <c r="I4" t="n">
-        <v>16.2</v>
+        <v>16.77</v>
       </c>
       <c r="J4" t="n">
-        <v>71.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-48.2</v>
+        <v>-47.5</v>
       </c>
       <c r="L4" t="n">
-        <v>22.4</v>
+        <v>26.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -674,32 +674,32 @@
         <v>74.45</v>
       </c>
       <c r="E5" t="n">
-        <v>85.70999999999999</v>
+        <v>94.73</v>
       </c>
       <c r="F5" t="n">
-        <v>75.83</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>61.22</v>
+        <v>64.55</v>
       </c>
       <c r="H5" t="n">
-        <v>59.58</v>
+        <v>62.27</v>
       </c>
       <c r="I5" t="n">
-        <v>73.72</v>
+        <v>79.56</v>
       </c>
       <c r="J5" t="n">
-        <v>15.1</v>
+        <v>27.2</v>
       </c>
       <c r="K5" t="n">
-        <v>-20</v>
+        <v>-16.4</v>
       </c>
       <c r="L5" t="n">
-        <v>-1</v>
+        <v>6.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
     </row>
@@ -723,28 +723,28 @@
         <v>18.89</v>
       </c>
       <c r="E6" t="n">
-        <v>19.63</v>
+        <v>19.25</v>
       </c>
       <c r="F6" t="n">
-        <v>16.23</v>
+        <v>15.89</v>
       </c>
       <c r="G6" t="n">
-        <v>9.890000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="H6" t="n">
-        <v>9.07</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>15.08</v>
+        <v>14.77</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="K6" t="n">
-        <v>-52</v>
+        <v>-53.1</v>
       </c>
       <c r="L6" t="n">
-        <v>-20.2</v>
+        <v>-21.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -772,28 +772,28 @@
         <v>52.48</v>
       </c>
       <c r="E7" t="n">
-        <v>54.22</v>
+        <v>54.89</v>
       </c>
       <c r="F7" t="n">
-        <v>43.18</v>
+        <v>43.25</v>
       </c>
       <c r="G7" t="n">
-        <v>22.16</v>
+        <v>21.79</v>
       </c>
       <c r="H7" t="n">
-        <v>19.63</v>
+        <v>19.2</v>
       </c>
       <c r="I7" t="n">
-        <v>39.33</v>
+        <v>39.41</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-62.6</v>
+        <v>-63.4</v>
       </c>
       <c r="L7" t="n">
-        <v>-25.1</v>
+        <v>-24.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -804,12 +804,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>40.93</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>40.56</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>32.23</v>
+        <v>65.66</v>
       </c>
       <c r="G8" t="n">
-        <v>15.97</v>
+        <v>42.17</v>
       </c>
       <c r="H8" t="n">
-        <v>13.86</v>
+        <v>38.41</v>
       </c>
       <c r="I8" t="n">
-        <v>29.18</v>
+        <v>61.16</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9</v>
+        <v>-8.1</v>
       </c>
       <c r="K8" t="n">
-        <v>-66.09999999999999</v>
+        <v>-54.5</v>
       </c>
       <c r="L8" t="n">
-        <v>-28.7</v>
+        <v>-27.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -853,12 +853,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -867,31 +867,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>84.48999999999999</v>
+        <v>40.93</v>
       </c>
       <c r="E9" t="n">
-        <v>74.09999999999999</v>
+        <v>40.09</v>
       </c>
       <c r="F9" t="n">
-        <v>63.97</v>
+        <v>31.67</v>
       </c>
       <c r="G9" t="n">
-        <v>42.1</v>
+        <v>15.51</v>
       </c>
       <c r="H9" t="n">
-        <v>38.16</v>
+        <v>13.42</v>
       </c>
       <c r="I9" t="n">
-        <v>59.47</v>
+        <v>28.68</v>
       </c>
       <c r="J9" t="n">
-        <v>-12.3</v>
+        <v>-2.1</v>
       </c>
       <c r="K9" t="n">
-        <v>-54.8</v>
+        <v>-67.2</v>
       </c>
       <c r="L9" t="n">
-        <v>-29.6</v>
+        <v>-29.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -919,28 +919,28 @@
         <v>5.85</v>
       </c>
       <c r="E10" t="n">
-        <v>4.17</v>
+        <v>4.07</v>
       </c>
       <c r="F10" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="H10" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="I10" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="J10" t="n">
-        <v>-28.7</v>
+        <v>-30.4</v>
       </c>
       <c r="K10" t="n">
-        <v>-79.59999999999999</v>
+        <v>-80.3</v>
       </c>
       <c r="L10" t="n">
-        <v>-51.1</v>
+        <v>-52.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1082,31 +1082,31 @@
         <v>20.03</v>
       </c>
       <c r="E2" t="n">
-        <v>48.52</v>
+        <v>49.7</v>
       </c>
       <c r="F2" t="n">
-        <v>35.36</v>
+        <v>41.36</v>
       </c>
       <c r="G2" t="n">
-        <v>19.76</v>
+        <v>28.84</v>
       </c>
       <c r="H2" t="n">
-        <v>9.59</v>
+        <v>18.18</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.45</v>
+        <v>7.81</v>
       </c>
       <c r="J2" t="n">
-        <v>29.63</v>
+        <v>35.91</v>
       </c>
       <c r="K2" t="n">
-        <v>142.2</v>
+        <v>148.1</v>
       </c>
       <c r="L2" t="n">
-        <v>-102.2</v>
+        <v>-61</v>
       </c>
       <c r="M2" t="n">
-        <v>47.9</v>
+        <v>79.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>48.97</v>
+        <v>41.9</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="3">
@@ -1140,31 +1140,31 @@
         <v>29.74</v>
       </c>
       <c r="E3" t="n">
-        <v>39.76</v>
+        <v>39.36</v>
       </c>
       <c r="F3" t="n">
-        <v>32.82</v>
+        <v>33.67</v>
       </c>
       <c r="G3" t="n">
-        <v>24.49</v>
+        <v>26.25</v>
       </c>
       <c r="H3" t="n">
-        <v>19.03</v>
+        <v>20.36</v>
       </c>
       <c r="I3" t="n">
-        <v>13.81</v>
+        <v>16.11</v>
       </c>
       <c r="J3" t="n">
-        <v>29.73</v>
+        <v>30.67</v>
       </c>
       <c r="K3" t="n">
-        <v>33.7</v>
+        <v>32.3</v>
       </c>
       <c r="L3" t="n">
-        <v>-53.6</v>
+        <v>-45.8</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>25.95</v>
+        <v>23.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.04</v>
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -1300,35 +1300,35 @@
         <v>80.58</v>
       </c>
       <c r="E2" t="n">
-        <v>90.78</v>
+        <v>105.66</v>
       </c>
       <c r="F2" t="n">
-        <v>85.52</v>
+        <v>93.31</v>
       </c>
       <c r="G2" t="n">
-        <v>56.57</v>
+        <v>58.6</v>
       </c>
       <c r="H2" t="n">
-        <v>52.04</v>
+        <v>53.32</v>
       </c>
       <c r="I2" t="n">
-        <v>47.88</v>
+        <v>47.75</v>
       </c>
       <c r="J2" t="n">
-        <v>73.13</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>12.7</v>
+        <v>31.1</v>
       </c>
       <c r="L2" t="n">
-        <v>-40.6</v>
+        <v>-40.7</v>
       </c>
       <c r="M2" t="n">
-        <v>-9.199999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
     </row>
@@ -1352,31 +1352,31 @@
         <v>29.41</v>
       </c>
       <c r="E3" t="n">
-        <v>39.1</v>
+        <v>40.58</v>
       </c>
       <c r="F3" t="n">
-        <v>32.74</v>
+        <v>33.3</v>
       </c>
       <c r="G3" t="n">
-        <v>16.68</v>
+        <v>16.84</v>
       </c>
       <c r="H3" t="n">
-        <v>13.84</v>
+        <v>14.21</v>
       </c>
       <c r="I3" t="n">
-        <v>10.86</v>
+        <v>11.03</v>
       </c>
       <c r="J3" t="n">
-        <v>26.68</v>
+        <v>27.32</v>
       </c>
       <c r="K3" t="n">
-        <v>32.9</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>-63.1</v>
+        <v>-62.5</v>
       </c>
       <c r="M3" t="n">
-        <v>-9.300000000000001</v>
+        <v>-7.1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1404,31 +1404,31 @@
         <v>17.07</v>
       </c>
       <c r="E4" t="n">
-        <v>18.05</v>
+        <v>18.21</v>
       </c>
       <c r="F4" t="n">
-        <v>15.92</v>
+        <v>15.95</v>
       </c>
       <c r="G4" t="n">
-        <v>13.54</v>
+        <v>13.64</v>
       </c>
       <c r="H4" t="n">
-        <v>11.31</v>
+        <v>11.46</v>
       </c>
       <c r="I4" t="n">
-        <v>9.41</v>
+        <v>9.42</v>
       </c>
       <c r="J4" t="n">
-        <v>15.05</v>
+        <v>15.15</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="L4" t="n">
-        <v>-44.9</v>
+        <v>-44.8</v>
       </c>
       <c r="M4" t="n">
-        <v>-11.8</v>
+        <v>-11.3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1456,31 +1456,31 @@
         <v>7.23</v>
       </c>
       <c r="E5" t="n">
-        <v>8.279999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="F5" t="n">
-        <v>6.88</v>
+        <v>7.01</v>
       </c>
       <c r="G5" t="n">
-        <v>3.81</v>
+        <v>3.87</v>
       </c>
       <c r="H5" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="I5" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="J5" t="n">
-        <v>5.77</v>
+        <v>5.91</v>
       </c>
       <c r="K5" t="n">
-        <v>14.5</v>
+        <v>18.6</v>
       </c>
       <c r="L5" t="n">
-        <v>-63.4</v>
+        <v>-62.4</v>
       </c>
       <c r="M5" t="n">
-        <v>-20.3</v>
+        <v>-18.2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1604,28 +1604,28 @@
         <v>16.9</v>
       </c>
       <c r="E2" t="n">
-        <v>23.92</v>
+        <v>25.32</v>
       </c>
       <c r="F2" t="n">
-        <v>20.29</v>
+        <v>21.48</v>
       </c>
       <c r="G2" t="n">
-        <v>18.25</v>
+        <v>19.54</v>
       </c>
       <c r="H2" t="n">
-        <v>16.76</v>
+        <v>17.25</v>
       </c>
       <c r="I2" t="n">
-        <v>19.98</v>
+        <v>21.13</v>
       </c>
       <c r="J2" t="n">
-        <v>41.5</v>
+        <v>49.8</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8</v>
+        <v>2.1</v>
       </c>
       <c r="L2" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
         <v>23.68</v>
       </c>
       <c r="E3" t="n">
-        <v>32.94</v>
+        <v>32.13</v>
       </c>
       <c r="F3" t="n">
-        <v>26.57</v>
+        <v>26.11</v>
       </c>
       <c r="G3" t="n">
         <v>22.46</v>
@@ -1665,16 +1665,16 @@
         <v>19.52</v>
       </c>
       <c r="I3" t="n">
-        <v>25.76</v>
+        <v>25.41</v>
       </c>
       <c r="J3" t="n">
-        <v>39.1</v>
+        <v>35.7</v>
       </c>
       <c r="K3" t="n">
         <v>-17.6</v>
       </c>
       <c r="L3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1702,28 +1702,28 @@
         <v>25.81</v>
       </c>
       <c r="E4" t="n">
-        <v>33.04</v>
+        <v>32.39</v>
       </c>
       <c r="F4" t="n">
-        <v>26.61</v>
+        <v>26.28</v>
       </c>
       <c r="G4" t="n">
-        <v>23.18</v>
+        <v>23.31</v>
       </c>
       <c r="H4" t="n">
-        <v>19.55</v>
+        <v>19.63</v>
       </c>
       <c r="I4" t="n">
-        <v>25.98</v>
+        <v>25.76</v>
       </c>
       <c r="J4" t="n">
-        <v>28</v>
+        <v>25.5</v>
       </c>
       <c r="K4" t="n">
-        <v>-24.3</v>
+        <v>-24</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1847,32 +1847,32 @@
         <v>37.89</v>
       </c>
       <c r="E2" t="n">
-        <v>34.74</v>
+        <v>44.45</v>
       </c>
       <c r="F2" t="n">
-        <v>32.26</v>
+        <v>41.26</v>
       </c>
       <c r="G2" t="n">
-        <v>29.45</v>
+        <v>37.75</v>
       </c>
       <c r="H2" t="n">
-        <v>28.52</v>
+        <v>36.18</v>
       </c>
       <c r="I2" t="n">
-        <v>31.76</v>
+        <v>40.59</v>
       </c>
       <c r="J2" t="n">
-        <v>-8.300000000000001</v>
+        <v>17.3</v>
       </c>
       <c r="K2" t="n">
-        <v>-24.7</v>
+        <v>-4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>-16.2</v>
+        <v>7.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
     </row>
@@ -1896,28 +1896,28 @@
         <v>2.54</v>
       </c>
       <c r="E3" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="G3" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="I3" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="J3" t="n">
-        <v>-19.1</v>
+        <v>-11.2</v>
       </c>
       <c r="K3" t="n">
-        <v>-41.9</v>
+        <v>-32.3</v>
       </c>
       <c r="L3" t="n">
-        <v>-27.3</v>
+        <v>-17.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1991,13 +1991,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="D2" t="n">
-        <v>-51.1</v>
+        <v>-52.5</v>
       </c>
       <c r="E2" t="n">
-        <v>148.3</v>
+        <v>152.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2008,26 +2008,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>97.3</v>
+        <v>79.3</v>
       </c>
       <c r="D3" t="n">
-        <v>-29.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E3" t="n">
-        <v>126.9</v>
+        <v>131.7</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -2043,13 +2043,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="D4" t="n">
-        <v>-28.7</v>
+        <v>-29.9</v>
       </c>
       <c r="E4" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2065,21 +2065,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="D5" t="n">
-        <v>-27.3</v>
+        <v>-27.6</v>
       </c>
       <c r="E5" t="n">
-        <v>124.5</v>
+        <v>127.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="D6" t="n">
-        <v>-25.1</v>
+        <v>-24.9</v>
       </c>
       <c r="E6" t="n">
-        <v>122.3</v>
+        <v>125</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="D7" t="n">
-        <v>-20.2</v>
+        <v>-21.8</v>
       </c>
       <c r="E7" t="n">
-        <v>117.5</v>
+        <v>121.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2138,52 +2138,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>97.3</v>
+        <v>69.3</v>
       </c>
       <c r="D8" t="n">
-        <v>-20.3</v>
+        <v>-52.5</v>
       </c>
       <c r="E8" t="n">
-        <v>117.5</v>
+        <v>121.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>62.5</v>
+        <v>100.1</v>
       </c>
       <c r="D9" t="n">
-        <v>-51.1</v>
+        <v>-18.2</v>
       </c>
       <c r="E9" t="n">
-        <v>113.6</v>
+        <v>118.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -2195,17 +2195,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="D10" t="n">
-        <v>-16.2</v>
+        <v>-17.1</v>
       </c>
       <c r="E10" t="n">
-        <v>113.5</v>
+        <v>117.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2225,13 +2225,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.8</v>
+        <v>-11.3</v>
       </c>
       <c r="E11" t="n">
-        <v>109.1</v>
+        <v>111.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2242,26 +2242,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>97.3</v>
+        <v>79.3</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.300000000000001</v>
+        <v>-29.9</v>
       </c>
       <c r="E12" t="n">
-        <v>106.6</v>
+        <v>109.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -2273,17 +2273,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.199999999999999</v>
+        <v>-7.1</v>
       </c>
       <c r="E13" t="n">
-        <v>106.5</v>
+        <v>107.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2299,73 +2299,73 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>47.9</v>
+        <v>79.3</v>
       </c>
       <c r="D14" t="n">
-        <v>-51.1</v>
+        <v>-27.6</v>
       </c>
       <c r="E14" t="n">
-        <v>99</v>
+        <v>106.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>97.3</v>
+        <v>79.3</v>
       </c>
       <c r="D15" t="n">
-        <v>-1</v>
+        <v>-24.9</v>
       </c>
       <c r="E15" t="n">
-        <v>98.3</v>
+        <v>104.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>97.3</v>
+        <v>79.3</v>
       </c>
       <c r="D16" t="n">
-        <v>-0</v>
+        <v>-21.8</v>
       </c>
       <c r="E16" t="n">
-        <v>97.3</v>
+        <v>101.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -2377,47 +2377,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="E17" t="n">
-        <v>96.59999999999999</v>
+        <v>100.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>62.5</v>
+        <v>100.1</v>
       </c>
       <c r="D18" t="n">
-        <v>-29.6</v>
+        <v>-0.2</v>
       </c>
       <c r="E18" t="n">
-        <v>92.09999999999999</v>
+        <v>100.3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>62.5</v>
+        <v>69.3</v>
       </c>
       <c r="D19" t="n">
-        <v>-28.7</v>
+        <v>-29.9</v>
       </c>
       <c r="E19" t="n">
-        <v>91.2</v>
+        <v>99.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2450,104 +2450,104 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>62.5</v>
+        <v>79.3</v>
       </c>
       <c r="D20" t="n">
-        <v>-27.3</v>
+        <v>-18.2</v>
       </c>
       <c r="E20" t="n">
-        <v>89.8</v>
+        <v>97.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>97.3</v>
+        <v>69.3</v>
       </c>
       <c r="D21" t="n">
-        <v>8.800000000000001</v>
+        <v>-27.6</v>
       </c>
       <c r="E21" t="n">
-        <v>88.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>62.5</v>
+        <v>100.1</v>
       </c>
       <c r="D22" t="n">
-        <v>-25.1</v>
+        <v>3.1</v>
       </c>
       <c r="E22" t="n">
-        <v>87.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>62.5</v>
+        <v>79.3</v>
       </c>
       <c r="D23" t="n">
-        <v>-20.3</v>
+        <v>-17.1</v>
       </c>
       <c r="E23" t="n">
-        <v>82.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
@@ -2559,17 +2559,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>62.5</v>
+        <v>69.3</v>
       </c>
       <c r="D24" t="n">
-        <v>-20.2</v>
+        <v>-24.9</v>
       </c>
       <c r="E24" t="n">
-        <v>82.7</v>
+        <v>94.2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2585,28 +2585,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="D25" t="n">
-        <v>18.2</v>
+        <v>6.9</v>
       </c>
       <c r="E25" t="n">
-        <v>79.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2615,69 +2615,69 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>62.5</v>
+        <v>100.1</v>
       </c>
       <c r="D26" t="n">
-        <v>-16.2</v>
+        <v>7.1</v>
       </c>
       <c r="E26" t="n">
-        <v>78.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>47.9</v>
+        <v>100.1</v>
       </c>
       <c r="D27" t="n">
-        <v>-29.6</v>
+        <v>7.3</v>
       </c>
       <c r="E27" t="n">
-        <v>77.5</v>
+        <v>92.8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>47.9</v>
+        <v>69.3</v>
       </c>
       <c r="D28" t="n">
-        <v>-28.7</v>
+        <v>-21.8</v>
       </c>
       <c r="E28" t="n">
-        <v>76.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2689,132 +2689,132 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>47.9</v>
+        <v>79.3</v>
       </c>
       <c r="D29" t="n">
-        <v>-27.3</v>
+        <v>-11.3</v>
       </c>
       <c r="E29" t="n">
-        <v>75.2</v>
+        <v>90.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>97.3</v>
+        <v>69.3</v>
       </c>
       <c r="D30" t="n">
-        <v>22.4</v>
+        <v>-18.2</v>
       </c>
       <c r="E30" t="n">
-        <v>74.90000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>62.5</v>
+        <v>79.3</v>
       </c>
       <c r="D31" t="n">
-        <v>-11.8</v>
+        <v>-7.1</v>
       </c>
       <c r="E31" t="n">
-        <v>74.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>22.4</v>
+        <v>69.3</v>
       </c>
       <c r="D32" t="n">
-        <v>-51.1</v>
+        <v>-17.1</v>
       </c>
       <c r="E32" t="n">
-        <v>73.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>47.9</v>
+        <v>69.3</v>
       </c>
       <c r="D33" t="n">
-        <v>-25.1</v>
+        <v>-11.3</v>
       </c>
       <c r="E33" t="n">
-        <v>73</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2823,50 +2823,50 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>62.5</v>
+        <v>79.3</v>
       </c>
       <c r="D34" t="n">
-        <v>-9.199999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="E34" t="n">
-        <v>71.8</v>
+        <v>80</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>62.5</v>
+        <v>79.3</v>
       </c>
       <c r="D35" t="n">
-        <v>-9.300000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="E35" t="n">
-        <v>71.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2875,69 +2875,69 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>18.2</v>
+        <v>26.7</v>
       </c>
       <c r="D36" t="n">
-        <v>-51.1</v>
+        <v>-52.5</v>
       </c>
       <c r="E36" t="n">
-        <v>69.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>47.9</v>
+        <v>25</v>
       </c>
       <c r="D37" t="n">
-        <v>-20.3</v>
+        <v>-52.5</v>
       </c>
       <c r="E37" t="n">
-        <v>68.2</v>
+        <v>77.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>47.9</v>
+        <v>69.3</v>
       </c>
       <c r="D38" t="n">
-        <v>-20.2</v>
+        <v>-7.1</v>
       </c>
       <c r="E38" t="n">
-        <v>68.09999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2949,99 +2949,99 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>47.9</v>
+        <v>79.3</v>
       </c>
       <c r="D39" t="n">
-        <v>-16.2</v>
+        <v>3.1</v>
       </c>
       <c r="E39" t="n">
-        <v>64.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>62.5</v>
+        <v>100.1</v>
       </c>
       <c r="D40" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="E40" t="n">
-        <v>63.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>62.5</v>
+        <v>100.1</v>
       </c>
       <c r="D41" t="n">
-        <v>-0</v>
+        <v>26.7</v>
       </c>
       <c r="E41" t="n">
-        <v>62.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>62.5</v>
+        <v>79.3</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="E42" t="n">
-        <v>61.9</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -3053,54 +3053,54 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>47.9</v>
+        <v>79.3</v>
       </c>
       <c r="D43" t="n">
-        <v>-11.8</v>
+        <v>7.1</v>
       </c>
       <c r="E43" t="n">
-        <v>59.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C44" t="n">
-        <v>8.800000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="D44" t="n">
-        <v>-51.1</v>
+        <v>7.3</v>
       </c>
       <c r="E44" t="n">
-        <v>59.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3109,43 +3109,43 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>47.9</v>
+        <v>69.3</v>
       </c>
       <c r="D45" t="n">
-        <v>-9.199999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="E45" t="n">
-        <v>57.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>47.9</v>
+        <v>69.3</v>
       </c>
       <c r="D46" t="n">
-        <v>-9.300000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="E46" t="n">
-        <v>57.2</v>
+        <v>69.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3157,43 +3157,43 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>62.5</v>
+        <v>69.3</v>
       </c>
       <c r="D47" t="n">
-        <v>8.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="E47" t="n">
-        <v>53.7</v>
+        <v>66.2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>22.4</v>
+        <v>69.3</v>
       </c>
       <c r="D48" t="n">
-        <v>-29.6</v>
+        <v>6.9</v>
       </c>
       <c r="E48" t="n">
-        <v>52</v>
+        <v>62.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3204,59 +3204,59 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.6</v>
+        <v>69.3</v>
       </c>
       <c r="D49" t="n">
-        <v>-51.1</v>
+        <v>7.1</v>
       </c>
       <c r="E49" t="n">
-        <v>51.7</v>
+        <v>62.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>22.4</v>
+        <v>69.3</v>
       </c>
       <c r="D50" t="n">
-        <v>-28.7</v>
+        <v>7.3</v>
       </c>
       <c r="E50" t="n">
-        <v>51.1</v>
+        <v>62</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3265,24 +3265,24 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>7.3</v>
       </c>
       <c r="D51" t="n">
-        <v>-51.1</v>
+        <v>-52.5</v>
       </c>
       <c r="E51" t="n">
-        <v>51</v>
+        <v>59.8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3291,91 +3291,91 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-1</v>
+        <v>7.1</v>
       </c>
       <c r="D52" t="n">
-        <v>-51.1</v>
+        <v>-52.5</v>
       </c>
       <c r="E52" t="n">
-        <v>50.1</v>
+        <v>59.6</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>22.4</v>
+        <v>6.9</v>
       </c>
       <c r="D53" t="n">
-        <v>-27.3</v>
+        <v>-52.5</v>
       </c>
       <c r="E53" t="n">
-        <v>49.6</v>
+        <v>59.3</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>97.3</v>
+        <v>26.7</v>
       </c>
       <c r="D54" t="n">
-        <v>47.9</v>
+        <v>-29.9</v>
       </c>
       <c r="E54" t="n">
-        <v>49.4</v>
+        <v>56.6</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>47.9</v>
+        <v>3.1</v>
       </c>
       <c r="D55" t="n">
-        <v>-1</v>
+        <v>-52.5</v>
       </c>
       <c r="E55" t="n">
-        <v>48.9</v>
+        <v>55.6</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3386,33 +3386,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>47.9</v>
+        <v>25</v>
       </c>
       <c r="D56" t="n">
-        <v>-0</v>
+        <v>-29.9</v>
       </c>
       <c r="E56" t="n">
-        <v>47.9</v>
+        <v>54.9</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3421,43 +3421,43 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>18.2</v>
+        <v>26.7</v>
       </c>
       <c r="D57" t="n">
-        <v>-29.6</v>
+        <v>-27.6</v>
       </c>
       <c r="E57" t="n">
-        <v>47.8</v>
+        <v>54.3</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>22.4</v>
+        <v>79.3</v>
       </c>
       <c r="D58" t="n">
-        <v>-25.1</v>
+        <v>25</v>
       </c>
       <c r="E58" t="n">
-        <v>47.4</v>
+        <v>54.2</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -3469,21 +3469,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>47.9</v>
+        <v>79.3</v>
       </c>
       <c r="D59" t="n">
-        <v>0.6</v>
+        <v>26.7</v>
       </c>
       <c r="E59" t="n">
-        <v>47.3</v>
+        <v>52.6</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -3495,80 +3495,80 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="D60" t="n">
-        <v>-28.7</v>
+        <v>-27.6</v>
       </c>
       <c r="E60" t="n">
-        <v>46.9</v>
+        <v>52.6</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>18.2</v>
+        <v>-0.2</v>
       </c>
       <c r="D61" t="n">
-        <v>-27.3</v>
+        <v>-52.5</v>
       </c>
       <c r="E61" t="n">
-        <v>45.5</v>
+        <v>52.3</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>62.5</v>
+        <v>-0.7</v>
       </c>
       <c r="D62" t="n">
-        <v>18.2</v>
+        <v>-52.5</v>
       </c>
       <c r="E62" t="n">
-        <v>44.3</v>
+        <v>51.7</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3577,43 +3577,43 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>18.2</v>
+        <v>26.7</v>
       </c>
       <c r="D63" t="n">
-        <v>-25.1</v>
+        <v>-24.9</v>
       </c>
       <c r="E63" t="n">
-        <v>43.3</v>
+        <v>51.6</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>22.4</v>
+        <v>25</v>
       </c>
       <c r="D64" t="n">
-        <v>-20.2</v>
+        <v>-24.9</v>
       </c>
       <c r="E64" t="n">
-        <v>42.6</v>
+        <v>49.9</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3625,47 +3625,47 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>22.4</v>
+        <v>26.7</v>
       </c>
       <c r="D65" t="n">
-        <v>-20.3</v>
+        <v>-21.8</v>
       </c>
       <c r="E65" t="n">
-        <v>42.6</v>
+        <v>48.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-9.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="D66" t="n">
-        <v>-51.1</v>
+        <v>-21.8</v>
       </c>
       <c r="E66" t="n">
-        <v>41.8</v>
+        <v>46.8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3681,13 +3681,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-9.300000000000001</v>
+        <v>-7.1</v>
       </c>
       <c r="D67" t="n">
-        <v>-51.1</v>
+        <v>-52.5</v>
       </c>
       <c r="E67" t="n">
-        <v>41.8</v>
+        <v>45.3</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3698,130 +3698,130 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>62.5</v>
+        <v>26.7</v>
       </c>
       <c r="D68" t="n">
-        <v>22.4</v>
+        <v>-18.2</v>
       </c>
       <c r="E68" t="n">
-        <v>40.1</v>
+        <v>44.9</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>47.9</v>
+        <v>69.3</v>
       </c>
       <c r="D69" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="E69" t="n">
-        <v>39.2</v>
+        <v>44.3</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-11.8</v>
+        <v>26.7</v>
       </c>
       <c r="D70" t="n">
-        <v>-51.1</v>
+        <v>-17.1</v>
       </c>
       <c r="E70" t="n">
-        <v>39.2</v>
+        <v>43.8</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>22.4</v>
+        <v>25</v>
       </c>
       <c r="D71" t="n">
-        <v>-16.2</v>
+        <v>-18.2</v>
       </c>
       <c r="E71" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>18.2</v>
+        <v>69.3</v>
       </c>
       <c r="D72" t="n">
-        <v>-20.3</v>
+        <v>26.7</v>
       </c>
       <c r="E72" t="n">
-        <v>38.5</v>
+        <v>42.7</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3833,73 +3833,73 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="D73" t="n">
-        <v>-20.2</v>
+        <v>-17.1</v>
       </c>
       <c r="E73" t="n">
-        <v>38.4</v>
+        <v>42.1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8.800000000000001</v>
+        <v>-11.3</v>
       </c>
       <c r="D74" t="n">
-        <v>-29.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E74" t="n">
-        <v>38.4</v>
+        <v>41.2</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8.800000000000001</v>
+        <v>26.7</v>
       </c>
       <c r="D75" t="n">
-        <v>-28.7</v>
+        <v>-11.3</v>
       </c>
       <c r="E75" t="n">
-        <v>37.5</v>
+        <v>37.9</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -3911,21 +3911,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="D76" t="n">
-        <v>-27.3</v>
+        <v>-29.9</v>
       </c>
       <c r="E76" t="n">
-        <v>36</v>
+        <v>37.2</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3937,17 +3937,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-16.2</v>
+        <v>7.1</v>
       </c>
       <c r="D77" t="n">
-        <v>-51.1</v>
+        <v>-29.9</v>
       </c>
       <c r="E77" t="n">
-        <v>34.9</v>
+        <v>37.1</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3958,26 +3958,26 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>97.3</v>
+        <v>6.9</v>
       </c>
       <c r="D78" t="n">
-        <v>62.5</v>
+        <v>-29.9</v>
       </c>
       <c r="E78" t="n">
-        <v>34.8</v>
+        <v>36.8</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3989,47 +3989,47 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="D79" t="n">
-        <v>-16.2</v>
+        <v>-11.3</v>
       </c>
       <c r="E79" t="n">
-        <v>34.4</v>
+        <v>36.3</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>22.4</v>
+        <v>-17.1</v>
       </c>
       <c r="D80" t="n">
-        <v>-11.8</v>
+        <v>-52.5</v>
       </c>
       <c r="E80" t="n">
-        <v>34.2</v>
+        <v>35.4</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
@@ -4041,80 +4041,80 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="D81" t="n">
-        <v>-25.1</v>
+        <v>-27.6</v>
       </c>
       <c r="E81" t="n">
-        <v>33.8</v>
+        <v>34.9</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>22.4</v>
+        <v>7.1</v>
       </c>
       <c r="D82" t="n">
-        <v>-9.300000000000001</v>
+        <v>-27.6</v>
       </c>
       <c r="E82" t="n">
-        <v>31.7</v>
+        <v>34.7</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>22.4</v>
+        <v>6.9</v>
       </c>
       <c r="D83" t="n">
-        <v>-9.199999999999999</v>
+        <v>-27.6</v>
       </c>
       <c r="E83" t="n">
-        <v>31.6</v>
+        <v>34.5</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4123,381 +4123,381 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-20.2</v>
+        <v>-18.2</v>
       </c>
       <c r="D84" t="n">
-        <v>-51.1</v>
+        <v>-52.5</v>
       </c>
       <c r="E84" t="n">
-        <v>30.9</v>
+        <v>34.2</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-20.3</v>
+        <v>26.7</v>
       </c>
       <c r="D85" t="n">
-        <v>-51.1</v>
+        <v>-7.1</v>
       </c>
       <c r="E85" t="n">
-        <v>30.8</v>
+        <v>33.8</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="D86" t="n">
-        <v>-29.6</v>
+        <v>-29.9</v>
       </c>
       <c r="E86" t="n">
-        <v>30.3</v>
+        <v>33.1</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>18.2</v>
+        <v>7.3</v>
       </c>
       <c r="D87" t="n">
-        <v>-11.8</v>
+        <v>-24.9</v>
       </c>
       <c r="E87" t="n">
-        <v>30</v>
+        <v>32.2</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>47.9</v>
+        <v>25</v>
       </c>
       <c r="D88" t="n">
-        <v>18.2</v>
+        <v>-7.1</v>
       </c>
       <c r="E88" t="n">
-        <v>29.7</v>
+        <v>32.1</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-0</v>
+        <v>7.1</v>
       </c>
       <c r="D89" t="n">
-        <v>-29.6</v>
+        <v>-24.9</v>
       </c>
       <c r="E89" t="n">
-        <v>29.6</v>
+        <v>32</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="D90" t="n">
-        <v>-28.7</v>
+        <v>-24.9</v>
       </c>
       <c r="E90" t="n">
-        <v>29.3</v>
+        <v>31.8</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>8.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="D91" t="n">
-        <v>-20.3</v>
+        <v>-27.6</v>
       </c>
       <c r="E91" t="n">
-        <v>29</v>
+        <v>30.8</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>8.800000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="D92" t="n">
-        <v>-20.2</v>
+        <v>69.3</v>
       </c>
       <c r="E92" t="n">
-        <v>28.9</v>
+        <v>30.7</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-0</v>
+        <v>-21.8</v>
       </c>
       <c r="D93" t="n">
-        <v>-28.7</v>
+        <v>-52.5</v>
       </c>
       <c r="E93" t="n">
-        <v>28.7</v>
+        <v>30.6</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
       <c r="D94" t="n">
-        <v>-29.6</v>
+        <v>-29.9</v>
       </c>
       <c r="E94" t="n">
-        <v>28.6</v>
+        <v>29.7</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="D95" t="n">
-        <v>-27.3</v>
+        <v>-29.9</v>
       </c>
       <c r="E95" t="n">
-        <v>27.9</v>
+        <v>29.2</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-1</v>
+        <v>7.3</v>
       </c>
       <c r="D96" t="n">
-        <v>-28.7</v>
+        <v>-21.8</v>
       </c>
       <c r="E96" t="n">
-        <v>27.7</v>
+        <v>29.1</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>18.2</v>
+        <v>7.1</v>
       </c>
       <c r="D97" t="n">
-        <v>-9.300000000000001</v>
+        <v>-21.8</v>
       </c>
       <c r="E97" t="n">
-        <v>27.5</v>
+        <v>29</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>18.2</v>
+        <v>6.9</v>
       </c>
       <c r="D98" t="n">
-        <v>-9.199999999999999</v>
+        <v>-21.8</v>
       </c>
       <c r="E98" t="n">
-        <v>27.4</v>
+        <v>28.7</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -4509,251 +4509,251 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-0</v>
+        <v>3.1</v>
       </c>
       <c r="D99" t="n">
-        <v>-27.3</v>
+        <v>-24.9</v>
       </c>
       <c r="E99" t="n">
-        <v>27.2</v>
+        <v>28</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-1</v>
+        <v>-24.9</v>
       </c>
       <c r="D100" t="n">
-        <v>-27.3</v>
+        <v>-52.5</v>
       </c>
       <c r="E100" t="n">
-        <v>26.3</v>
+        <v>27.6</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-25.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D101" t="n">
-        <v>-51.1</v>
+        <v>-27.6</v>
       </c>
       <c r="E101" t="n">
-        <v>26</v>
+        <v>27.4</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.6</v>
+        <v>26.7</v>
       </c>
       <c r="D102" t="n">
-        <v>-25.1</v>
+        <v>-0.7</v>
       </c>
       <c r="E102" t="n">
-        <v>25.7</v>
+        <v>27.4</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>47.9</v>
+        <v>-0.7</v>
       </c>
       <c r="D103" t="n">
-        <v>22.4</v>
+        <v>-27.6</v>
       </c>
       <c r="E103" t="n">
-        <v>25.5</v>
+        <v>26.9</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-0</v>
+        <v>26.7</v>
       </c>
       <c r="D104" t="n">
-        <v>-25.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E104" t="n">
-        <v>25</v>
+        <v>26.9</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="D105" t="n">
-        <v>-16.2</v>
+        <v>-0.7</v>
       </c>
       <c r="E105" t="n">
-        <v>24.9</v>
+        <v>25.7</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>-1</v>
+        <v>7.3</v>
       </c>
       <c r="D106" t="n">
-        <v>-25.1</v>
+        <v>-18.2</v>
       </c>
       <c r="E106" t="n">
-        <v>24.1</v>
+        <v>25.5</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-27.3</v>
+        <v>7.1</v>
       </c>
       <c r="D107" t="n">
-        <v>-51.1</v>
+        <v>-18.2</v>
       </c>
       <c r="E107" t="n">
-        <v>23.8</v>
+        <v>25.4</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>22.4</v>
+        <v>25</v>
       </c>
       <c r="D108" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
       <c r="E108" t="n">
-        <v>23.4</v>
+        <v>25.2</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -4764,345 +4764,345 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-28.7</v>
+        <v>6.9</v>
       </c>
       <c r="D109" t="n">
-        <v>-51.1</v>
+        <v>-18.2</v>
       </c>
       <c r="E109" t="n">
-        <v>22.4</v>
+        <v>25.1</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>22.4</v>
+        <v>3.1</v>
       </c>
       <c r="D110" t="n">
-        <v>-0</v>
+        <v>-21.8</v>
       </c>
       <c r="E110" t="n">
-        <v>22.4</v>
+        <v>25</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>22.4</v>
+        <v>-27.6</v>
       </c>
       <c r="D111" t="n">
-        <v>0.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E111" t="n">
-        <v>21.7</v>
+        <v>24.8</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-29.6</v>
+        <v>-0.2</v>
       </c>
       <c r="D112" t="n">
-        <v>-51.1</v>
+        <v>-24.9</v>
       </c>
       <c r="E112" t="n">
-        <v>21.4</v>
+        <v>24.7</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="D113" t="n">
-        <v>-20.3</v>
+        <v>-17.1</v>
       </c>
       <c r="E113" t="n">
-        <v>20.9</v>
+        <v>24.4</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="D114" t="n">
-        <v>-20.2</v>
+        <v>-24.9</v>
       </c>
       <c r="E114" t="n">
-        <v>20.8</v>
+        <v>24.2</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>8.800000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="D115" t="n">
-        <v>-11.8</v>
+        <v>-17.1</v>
       </c>
       <c r="E115" t="n">
-        <v>20.6</v>
+        <v>24.2</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="D116" t="n">
-        <v>-29.6</v>
+        <v>-17.1</v>
       </c>
       <c r="E116" t="n">
-        <v>20.4</v>
+        <v>24</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-9.300000000000001</v>
+        <v>26.7</v>
       </c>
       <c r="D117" t="n">
-        <v>-29.6</v>
+        <v>3.1</v>
       </c>
       <c r="E117" t="n">
-        <v>20.3</v>
+        <v>23.5</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-0</v>
+        <v>-7.1</v>
       </c>
       <c r="D118" t="n">
-        <v>-20.2</v>
+        <v>-29.9</v>
       </c>
       <c r="E118" t="n">
-        <v>20.2</v>
+        <v>22.8</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-0</v>
+        <v>-29.9</v>
       </c>
       <c r="D119" t="n">
-        <v>-20.3</v>
+        <v>-52.5</v>
       </c>
       <c r="E119" t="n">
-        <v>20.2</v>
+        <v>22.5</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-9.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="D120" t="n">
-        <v>-28.7</v>
+        <v>3.1</v>
       </c>
       <c r="E120" t="n">
-        <v>19.5</v>
+        <v>21.9</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>-9.300000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="D121" t="n">
-        <v>-28.7</v>
+        <v>-21.8</v>
       </c>
       <c r="E121" t="n">
-        <v>19.4</v>
+        <v>21.6</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5111,24 +5111,24 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>-1</v>
+        <v>3.1</v>
       </c>
       <c r="D122" t="n">
-        <v>-20.3</v>
+        <v>-18.2</v>
       </c>
       <c r="E122" t="n">
-        <v>19.3</v>
+        <v>21.4</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5137,173 +5137,173 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="D123" t="n">
-        <v>-20.2</v>
+        <v>-21.8</v>
       </c>
       <c r="E123" t="n">
-        <v>19.2</v>
+        <v>21.1</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>18.2</v>
+        <v>100.1</v>
       </c>
       <c r="D124" t="n">
-        <v>-1</v>
+        <v>79.3</v>
       </c>
       <c r="E124" t="n">
-        <v>19.2</v>
+        <v>20.8</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>18.2</v>
+        <v>-7.1</v>
       </c>
       <c r="D125" t="n">
-        <v>-0</v>
+        <v>-27.6</v>
       </c>
       <c r="E125" t="n">
-        <v>18.2</v>
+        <v>20.5</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>8.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="D126" t="n">
-        <v>-9.300000000000001</v>
+        <v>-17.1</v>
       </c>
       <c r="E126" t="n">
-        <v>18.1</v>
+        <v>20.2</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>-9.199999999999999</v>
+        <v>26.7</v>
       </c>
       <c r="D127" t="n">
-        <v>-27.3</v>
+        <v>6.9</v>
       </c>
       <c r="E127" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>-9.300000000000001</v>
+        <v>26.7</v>
       </c>
       <c r="D128" t="n">
-        <v>-27.3</v>
+        <v>7.1</v>
       </c>
       <c r="E128" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>CAPT</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>STNG</t>
-        </is>
-      </c>
       <c r="C129" t="n">
-        <v>8.800000000000001</v>
+        <v>26.7</v>
       </c>
       <c r="D129" t="n">
-        <v>-9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="E129" t="n">
-        <v>18</v>
+        <v>19.4</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -5315,307 +5315,307 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>-11.8</v>
+        <v>-11.3</v>
       </c>
       <c r="D130" t="n">
-        <v>-29.6</v>
+        <v>-29.9</v>
       </c>
       <c r="E130" t="n">
-        <v>17.8</v>
+        <v>18.7</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>18.2</v>
+        <v>7.3</v>
       </c>
       <c r="D131" t="n">
-        <v>0.6</v>
+        <v>-11.3</v>
       </c>
       <c r="E131" t="n">
-        <v>17.6</v>
+        <v>18.6</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
           <t>ASC</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>FRO</t>
-        </is>
-      </c>
       <c r="C132" t="n">
-        <v>-11.8</v>
+        <v>7.1</v>
       </c>
       <c r="D132" t="n">
-        <v>-28.7</v>
+        <v>-11.3</v>
       </c>
       <c r="E132" t="n">
-        <v>16.9</v>
+        <v>18.4</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.6</v>
+        <v>25</v>
       </c>
       <c r="D133" t="n">
-        <v>-16.2</v>
+        <v>6.9</v>
       </c>
       <c r="E133" t="n">
-        <v>16.8</v>
+        <v>18.2</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>-0</v>
+        <v>6.9</v>
       </c>
       <c r="D134" t="n">
-        <v>-16.2</v>
+        <v>-11.3</v>
       </c>
       <c r="E134" t="n">
-        <v>16.2</v>
+        <v>18.1</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>-9.199999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="D135" t="n">
-        <v>-25.1</v>
+        <v>-18.2</v>
       </c>
       <c r="E135" t="n">
-        <v>15.8</v>
+        <v>18</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>-9.300000000000001</v>
+        <v>25</v>
       </c>
       <c r="D136" t="n">
-        <v>-25.1</v>
+        <v>7.1</v>
       </c>
       <c r="E136" t="n">
-        <v>15.8</v>
+        <v>17.9</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>-11.8</v>
+        <v>-7.1</v>
       </c>
       <c r="D137" t="n">
-        <v>-27.3</v>
+        <v>-24.9</v>
       </c>
       <c r="E137" t="n">
-        <v>15.4</v>
+        <v>17.8</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="D138" t="n">
-        <v>-16.2</v>
+        <v>7.3</v>
       </c>
       <c r="E138" t="n">
-        <v>15.2</v>
+        <v>17.7</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>62.5</v>
+        <v>-0.7</v>
       </c>
       <c r="D139" t="n">
-        <v>47.9</v>
+        <v>-18.2</v>
       </c>
       <c r="E139" t="n">
-        <v>14.6</v>
+        <v>17.5</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>22.4</v>
+        <v>-0.2</v>
       </c>
       <c r="D140" t="n">
-        <v>8.800000000000001</v>
+        <v>-17.1</v>
       </c>
       <c r="E140" t="n">
-        <v>13.6</v>
+        <v>16.9</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>-16.2</v>
+        <v>-0.7</v>
       </c>
       <c r="D141" t="n">
-        <v>-29.6</v>
+        <v>-17.1</v>
       </c>
       <c r="E141" t="n">
-        <v>13.4</v>
+        <v>16.4</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
@@ -5627,99 +5627,99 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>-11.8</v>
+        <v>-11.3</v>
       </c>
       <c r="D142" t="n">
-        <v>-25.1</v>
+        <v>-27.6</v>
       </c>
       <c r="E142" t="n">
-        <v>13.2</v>
+        <v>16.3</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.6</v>
+        <v>-7.1</v>
       </c>
       <c r="D143" t="n">
-        <v>-11.8</v>
+        <v>-21.8</v>
       </c>
       <c r="E143" t="n">
-        <v>12.5</v>
+        <v>14.7</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>-16.2</v>
+        <v>3.1</v>
       </c>
       <c r="D144" t="n">
-        <v>-28.7</v>
+        <v>-11.3</v>
       </c>
       <c r="E144" t="n">
-        <v>12.5</v>
+        <v>14.4</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>-0</v>
+        <v>7.3</v>
       </c>
       <c r="D145" t="n">
-        <v>-11.8</v>
+        <v>-7.1</v>
       </c>
       <c r="E145" t="n">
-        <v>11.8</v>
+        <v>14.4</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -5731,121 +5731,121 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>-16.2</v>
+        <v>7.1</v>
       </c>
       <c r="D146" t="n">
-        <v>-27.3</v>
+        <v>-7.1</v>
       </c>
       <c r="E146" t="n">
-        <v>11.1</v>
+        <v>14.2</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>-9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="D147" t="n">
-        <v>-20.3</v>
+        <v>-7.1</v>
       </c>
       <c r="E147" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>-9.300000000000001</v>
+        <v>-11.3</v>
       </c>
       <c r="D148" t="n">
-        <v>-20.3</v>
+        <v>-24.9</v>
       </c>
       <c r="E148" t="n">
-        <v>11</v>
+        <v>13.6</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>-1</v>
+        <v>-17.1</v>
       </c>
       <c r="D149" t="n">
-        <v>-11.8</v>
+        <v>-29.9</v>
       </c>
       <c r="E149" t="n">
-        <v>10.9</v>
+        <v>12.8</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>-9.199999999999999</v>
+        <v>-18.2</v>
       </c>
       <c r="D150" t="n">
-        <v>-20.2</v>
+        <v>-29.9</v>
       </c>
       <c r="E150" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -5861,21 +5861,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>-9.300000000000001</v>
+        <v>-7.1</v>
       </c>
       <c r="D151" t="n">
-        <v>-20.2</v>
+        <v>-18.2</v>
       </c>
       <c r="E151" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -5887,17 +5887,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="D152" t="n">
-        <v>-9.199999999999999</v>
+        <v>-11.3</v>
       </c>
       <c r="E152" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -5908,59 +5908,59 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0.6</v>
+        <v>-11.3</v>
       </c>
       <c r="D153" t="n">
-        <v>-9.300000000000001</v>
+        <v>-21.8</v>
       </c>
       <c r="E153" t="n">
-        <v>9.9</v>
+        <v>10.6</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>8.800000000000001</v>
+        <v>-0.7</v>
       </c>
       <c r="D154" t="n">
-        <v>-1</v>
+        <v>-11.3</v>
       </c>
       <c r="E154" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5969,147 +5969,147 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>-20.2</v>
+        <v>-17.1</v>
       </c>
       <c r="D155" t="n">
-        <v>-29.6</v>
+        <v>-27.6</v>
       </c>
       <c r="E155" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>-20.3</v>
+        <v>3.1</v>
       </c>
       <c r="D156" t="n">
-        <v>-29.6</v>
+        <v>-7.1</v>
       </c>
       <c r="E156" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>18.2</v>
+        <v>-7.1</v>
       </c>
       <c r="D157" t="n">
-        <v>8.800000000000001</v>
+        <v>-17.1</v>
       </c>
       <c r="E157" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>-0</v>
+        <v>79.3</v>
       </c>
       <c r="D158" t="n">
-        <v>-9.300000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="E158" t="n">
-        <v>9.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>-0</v>
+        <v>-18.2</v>
       </c>
       <c r="D159" t="n">
-        <v>-9.199999999999999</v>
+        <v>-27.6</v>
       </c>
       <c r="E159" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>-16.2</v>
+        <v>-21.8</v>
       </c>
       <c r="D160" t="n">
-        <v>-25.1</v>
+        <v>-29.9</v>
       </c>
       <c r="E160" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -6121,199 +6121,199 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="D161" t="n">
-        <v>-0</v>
+        <v>-0.7</v>
       </c>
       <c r="E161" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>-20.2</v>
+        <v>7.1</v>
       </c>
       <c r="D162" t="n">
-        <v>-28.7</v>
+        <v>-0.7</v>
       </c>
       <c r="E162" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>-20.3</v>
+        <v>-17.1</v>
       </c>
       <c r="D163" t="n">
-        <v>-28.7</v>
+        <v>-24.9</v>
       </c>
       <c r="E163" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>-11.8</v>
+        <v>6.9</v>
       </c>
       <c r="D164" t="n">
-        <v>-20.3</v>
+        <v>-0.7</v>
       </c>
       <c r="E164" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>-1</v>
+        <v>7.3</v>
       </c>
       <c r="D165" t="n">
-        <v>-9.199999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="E165" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>-1</v>
+        <v>7.1</v>
       </c>
       <c r="D166" t="n">
-        <v>-9.300000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="E166" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>-11.8</v>
+        <v>6.9</v>
       </c>
       <c r="D167" t="n">
-        <v>-20.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E167" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>8.800000000000001</v>
+        <v>-11.3</v>
       </c>
       <c r="D168" t="n">
-        <v>0.6</v>
+        <v>-18.2</v>
       </c>
       <c r="E168" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -6324,26 +6324,26 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>-20.2</v>
+        <v>-0.2</v>
       </c>
       <c r="D169" t="n">
-        <v>-27.3</v>
+        <v>-7.1</v>
       </c>
       <c r="E169" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -6355,21 +6355,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>-20.3</v>
+        <v>-18.2</v>
       </c>
       <c r="D170" t="n">
-        <v>-27.3</v>
+        <v>-24.9</v>
       </c>
       <c r="E170" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -6381,177 +6381,177 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>-9.199999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="D171" t="n">
-        <v>-16.2</v>
+        <v>-7.1</v>
       </c>
       <c r="E171" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>-9.300000000000001</v>
+        <v>-21.8</v>
       </c>
       <c r="D172" t="n">
-        <v>-16.2</v>
+        <v>-27.6</v>
       </c>
       <c r="E172" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>-20.2</v>
+        <v>-11.3</v>
       </c>
       <c r="D173" t="n">
-        <v>-25.1</v>
+        <v>-17.1</v>
       </c>
       <c r="E173" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>-20.3</v>
+        <v>-24.9</v>
       </c>
       <c r="D174" t="n">
-        <v>-25.1</v>
+        <v>-29.9</v>
       </c>
       <c r="E174" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>-25.1</v>
+        <v>-17.1</v>
       </c>
       <c r="D175" t="n">
-        <v>-29.6</v>
+        <v>-21.8</v>
       </c>
       <c r="E175" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
           <t>ASC</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>GSL</t>
-        </is>
-      </c>
       <c r="C176" t="n">
-        <v>-11.8</v>
+        <v>-7.1</v>
       </c>
       <c r="D176" t="n">
-        <v>-16.2</v>
+        <v>-11.3</v>
       </c>
       <c r="E176" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>22.4</v>
+        <v>7.3</v>
       </c>
       <c r="D177" t="n">
-        <v>18.2</v>
+        <v>3.1</v>
       </c>
       <c r="E177" t="n">
         <v>4.2</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
@@ -6563,151 +6563,151 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>-16.2</v>
+        <v>7.1</v>
       </c>
       <c r="D178" t="n">
-        <v>-20.3</v>
+        <v>3.1</v>
       </c>
       <c r="E178" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (containerships vs lng)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>-16.2</v>
+        <v>3.1</v>
       </c>
       <c r="D179" t="n">
-        <v>-20.2</v>
+        <v>-0.7</v>
       </c>
       <c r="E179" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>-25.1</v>
+        <v>6.9</v>
       </c>
       <c r="D180" t="n">
-        <v>-28.7</v>
+        <v>3.1</v>
       </c>
       <c r="E180" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>-9.199999999999999</v>
+        <v>-18.2</v>
       </c>
       <c r="D181" t="n">
-        <v>-11.8</v>
+        <v>-21.8</v>
       </c>
       <c r="E181" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>-9.300000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="D182" t="n">
-        <v>-11.8</v>
+        <v>-0.2</v>
       </c>
       <c r="E182" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>-27.3</v>
+        <v>-21.8</v>
       </c>
       <c r="D183" t="n">
-        <v>-29.6</v>
+        <v>-24.9</v>
       </c>
       <c r="E183" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -6719,203 +6719,203 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>-25.1</v>
+        <v>-24.9</v>
       </c>
       <c r="D184" t="n">
-        <v>-27.3</v>
+        <v>-27.6</v>
       </c>
       <c r="E184" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0.6</v>
+        <v>-27.6</v>
       </c>
       <c r="D185" t="n">
-        <v>-1</v>
+        <v>-29.9</v>
       </c>
       <c r="E185" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>-27.3</v>
+        <v>26.7</v>
       </c>
       <c r="D186" t="n">
-        <v>-28.7</v>
+        <v>25</v>
       </c>
       <c r="E186" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>-0</v>
+        <v>-17.1</v>
       </c>
       <c r="D187" t="n">
-        <v>-1</v>
+        <v>-18.2</v>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>-28.7</v>
+        <v>-0.2</v>
       </c>
       <c r="D188" t="n">
-        <v>-29.6</v>
+        <v>-0.7</v>
       </c>
       <c r="E188" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="D189" t="n">
-        <v>-0</v>
+        <v>6.9</v>
       </c>
       <c r="E189" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>-20.2</v>
+        <v>7.1</v>
       </c>
       <c r="D190" t="n">
-        <v>-20.3</v>
+        <v>6.9</v>
       </c>
       <c r="E190" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>-9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="D191" t="n">
-        <v>-9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="E191" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -539,10 +539,10 @@
         <v>0.63</v>
       </c>
       <c r="I2" t="n">
-        <v>10.8</v>
+        <v>10.81</v>
       </c>
       <c r="J2" t="n">
-        <v>228.5</v>
+        <v>228.6</v>
       </c>
       <c r="K2" t="n">
         <v>-88.3</v>
@@ -576,28 +576,28 @@
         <v>38.29</v>
       </c>
       <c r="E3" t="n">
-        <v>83.84999999999999</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>68.79000000000001</v>
+        <v>68.89</v>
       </c>
       <c r="G3" t="n">
-        <v>44.59</v>
+        <v>44.66</v>
       </c>
       <c r="H3" t="n">
-        <v>40.77</v>
+        <v>40.82</v>
       </c>
       <c r="I3" t="n">
-        <v>64.84</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>119</v>
+        <v>119.3</v>
       </c>
       <c r="K3" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="L3" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         <v>13.24</v>
       </c>
       <c r="E4" t="n">
-        <v>23.94</v>
+        <v>23.95</v>
       </c>
       <c r="F4" t="n">
         <v>18.9</v>
@@ -674,25 +674,25 @@
         <v>74.45</v>
       </c>
       <c r="E5" t="n">
-        <v>94.73</v>
+        <v>94.77</v>
       </c>
       <c r="F5" t="n">
-        <v>81.73999999999999</v>
+        <v>81.78</v>
       </c>
       <c r="G5" t="n">
-        <v>64.55</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>62.27</v>
+        <v>62.29</v>
       </c>
       <c r="I5" t="n">
-        <v>79.56</v>
+        <v>79.59</v>
       </c>
       <c r="J5" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="K5" t="n">
-        <v>-16.4</v>
+        <v>-16.3</v>
       </c>
       <c r="L5" t="n">
         <v>6.9</v>
@@ -723,28 +723,28 @@
         <v>18.89</v>
       </c>
       <c r="E6" t="n">
-        <v>19.25</v>
+        <v>19.44</v>
       </c>
       <c r="F6" t="n">
-        <v>15.89</v>
+        <v>16.05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.66</v>
+        <v>9.77</v>
       </c>
       <c r="H6" t="n">
-        <v>8.859999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>14.77</v>
+        <v>14.92</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>-53.1</v>
+        <v>-52.5</v>
       </c>
       <c r="L6" t="n">
-        <v>-21.8</v>
+        <v>-21</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -772,28 +772,28 @@
         <v>52.48</v>
       </c>
       <c r="E7" t="n">
-        <v>54.89</v>
+        <v>55.11</v>
       </c>
       <c r="F7" t="n">
-        <v>43.25</v>
+        <v>43.45</v>
       </c>
       <c r="G7" t="n">
-        <v>21.79</v>
+        <v>21.92</v>
       </c>
       <c r="H7" t="n">
-        <v>19.2</v>
+        <v>19.32</v>
       </c>
       <c r="I7" t="n">
-        <v>39.41</v>
+        <v>39.59</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>-63.4</v>
+        <v>-63.2</v>
       </c>
       <c r="L7" t="n">
-        <v>-24.9</v>
+        <v>-24.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -821,28 +821,28 @@
         <v>84.48999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>77.65000000000001</v>
+        <v>77.87</v>
       </c>
       <c r="F8" t="n">
-        <v>65.66</v>
+        <v>65.86</v>
       </c>
       <c r="G8" t="n">
-        <v>42.17</v>
+        <v>42.3</v>
       </c>
       <c r="H8" t="n">
-        <v>38.41</v>
+        <v>38.53</v>
       </c>
       <c r="I8" t="n">
-        <v>61.16</v>
+        <v>61.34</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.1</v>
+        <v>-7.8</v>
       </c>
       <c r="K8" t="n">
-        <v>-54.5</v>
+        <v>-54.4</v>
       </c>
       <c r="L8" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -870,28 +870,28 @@
         <v>40.93</v>
       </c>
       <c r="E9" t="n">
-        <v>40.09</v>
+        <v>40.26</v>
       </c>
       <c r="F9" t="n">
-        <v>31.67</v>
+        <v>31.83</v>
       </c>
       <c r="G9" t="n">
-        <v>15.51</v>
+        <v>15.62</v>
       </c>
       <c r="H9" t="n">
-        <v>13.42</v>
+        <v>13.52</v>
       </c>
       <c r="I9" t="n">
-        <v>28.68</v>
+        <v>28.82</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1</v>
+        <v>-1.6</v>
       </c>
       <c r="K9" t="n">
-        <v>-67.2</v>
+        <v>-67</v>
       </c>
       <c r="L9" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>-52.5</v>
       </c>
       <c r="E2" t="n">
-        <v>152.5</v>
+        <v>152.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
         <v>100.1</v>
       </c>
       <c r="D4" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E4" t="n">
-        <v>130</v>
+        <v>129.7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2072,10 +2072,10 @@
         <v>100.1</v>
       </c>
       <c r="D5" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="E5" t="n">
-        <v>127.7</v>
+        <v>127.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
         <v>100.1</v>
       </c>
       <c r="D6" t="n">
-        <v>-24.9</v>
+        <v>-24.6</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>124.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2112,52 +2112,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>-21.8</v>
+        <v>-52.5</v>
       </c>
       <c r="E7" t="n">
-        <v>121.9</v>
+        <v>122</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>69.3</v>
+        <v>100.1</v>
       </c>
       <c r="D8" t="n">
-        <v>-52.5</v>
+        <v>-21</v>
       </c>
       <c r="E8" t="n">
-        <v>121.8</v>
+        <v>121.1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
         <v>-11.3</v>
       </c>
       <c r="E11" t="n">
-        <v>111.3</v>
+        <v>111.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2254,10 +2254,10 @@
         <v>79.3</v>
       </c>
       <c r="D12" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E12" t="n">
-        <v>109.2</v>
+        <v>108.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2306,10 +2306,10 @@
         <v>79.3</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="E14" t="n">
-        <v>106.9</v>
+        <v>106.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
         <v>79.3</v>
       </c>
       <c r="D15" t="n">
-        <v>-24.9</v>
+        <v>-24.6</v>
       </c>
       <c r="E15" t="n">
-        <v>104.2</v>
+        <v>103.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2346,52 +2346,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>79.3</v>
+        <v>100.1</v>
       </c>
       <c r="D16" t="n">
-        <v>-21.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E16" t="n">
-        <v>101.1</v>
+        <v>100.9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>100.1</v>
+        <v>79.3</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7</v>
+        <v>-21</v>
       </c>
       <c r="E17" t="n">
-        <v>100.8</v>
+        <v>100.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E19" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2485,13 +2485,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="E21" t="n">
-        <v>96.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>3.1</v>
       </c>
       <c r="E22" t="n">
-        <v>96.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-24.9</v>
+        <v>-24.6</v>
       </c>
       <c r="E24" t="n">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>7.1</v>
       </c>
       <c r="E26" t="n">
-        <v>92.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2667,13 +2667,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-21.8</v>
+        <v>-21</v>
       </c>
       <c r="E28" t="n">
-        <v>91.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2719,13 +2719,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D30" t="n">
         <v>-18.2</v>
       </c>
       <c r="E30" t="n">
-        <v>87.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2736,52 +2736,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>79.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-7.1</v>
+        <v>-17.1</v>
       </c>
       <c r="E31" t="n">
-        <v>86.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>69.3</v>
+        <v>79.3</v>
       </c>
       <c r="D32" t="n">
-        <v>-17.1</v>
+        <v>-7.1</v>
       </c>
       <c r="E32" t="n">
         <v>86.40000000000001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -2797,13 +2797,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D33" t="n">
         <v>-11.3</v>
       </c>
       <c r="E33" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D38" t="n">
         <v>-7.1</v>
       </c>
       <c r="E38" t="n">
-        <v>76.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D45" t="n">
         <v>-0.7</v>
       </c>
       <c r="E45" t="n">
-        <v>70.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D46" t="n">
         <v>-0.2</v>
       </c>
       <c r="E46" t="n">
-        <v>69.5</v>
+        <v>69.8</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3161,13 +3161,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D47" t="n">
         <v>3.1</v>
       </c>
       <c r="E47" t="n">
-        <v>66.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3187,13 +3187,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D48" t="n">
         <v>6.9</v>
       </c>
       <c r="E48" t="n">
-        <v>62.5</v>
+        <v>62.7</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3213,13 +3213,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D49" t="n">
         <v>7.1</v>
       </c>
       <c r="E49" t="n">
-        <v>62.2</v>
+        <v>62.4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3239,13 +3239,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D50" t="n">
         <v>7.3</v>
       </c>
       <c r="E50" t="n">
-        <v>62</v>
+        <v>62.3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>-52.5</v>
       </c>
       <c r="E53" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         <v>26.7</v>
       </c>
       <c r="D54" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E54" t="n">
-        <v>56.6</v>
+        <v>56.3</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3398,10 +3398,10 @@
         <v>25</v>
       </c>
       <c r="D56" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E56" t="n">
-        <v>54.9</v>
+        <v>54.6</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3412,52 +3412,52 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>26.7</v>
+        <v>79.3</v>
       </c>
       <c r="D57" t="n">
-        <v>-27.6</v>
+        <v>25</v>
       </c>
       <c r="E57" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>79.3</v>
+        <v>26.7</v>
       </c>
       <c r="D58" t="n">
-        <v>25</v>
+        <v>-27.4</v>
       </c>
       <c r="E58" t="n">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3502,10 +3502,10 @@
         <v>25</v>
       </c>
       <c r="D60" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="E60" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3580,10 +3580,10 @@
         <v>26.7</v>
       </c>
       <c r="D63" t="n">
-        <v>-24.9</v>
+        <v>-24.6</v>
       </c>
       <c r="E63" t="n">
-        <v>51.6</v>
+        <v>51.2</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3606,10 +3606,10 @@
         <v>25</v>
       </c>
       <c r="D64" t="n">
-        <v>-24.9</v>
+        <v>-24.6</v>
       </c>
       <c r="E64" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3632,10 +3632,10 @@
         <v>26.7</v>
       </c>
       <c r="D65" t="n">
-        <v>-21.8</v>
+        <v>-21</v>
       </c>
       <c r="E65" t="n">
-        <v>48.5</v>
+        <v>47.7</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3658,10 +3658,10 @@
         <v>25</v>
       </c>
       <c r="D66" t="n">
-        <v>-21.8</v>
+        <v>-21</v>
       </c>
       <c r="E66" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3733,13 +3733,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D69" t="n">
         <v>25</v>
       </c>
       <c r="E69" t="n">
-        <v>44.3</v>
+        <v>44.6</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3811,13 +3811,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D72" t="n">
         <v>26.7</v>
       </c>
       <c r="E72" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>-11.3</v>
       </c>
       <c r="E75" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3918,10 +3918,10 @@
         <v>7.3</v>
       </c>
       <c r="D76" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E76" t="n">
-        <v>37.2</v>
+        <v>36.9</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>7.1</v>
       </c>
       <c r="D77" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E77" t="n">
-        <v>37.1</v>
+        <v>36.7</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3970,10 +3970,10 @@
         <v>6.9</v>
       </c>
       <c r="D78" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E78" t="n">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4048,10 +4048,10 @@
         <v>7.3</v>
       </c>
       <c r="D81" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="E81" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4074,10 +4074,10 @@
         <v>7.1</v>
       </c>
       <c r="D82" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="E82" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4100,10 +4100,10 @@
         <v>6.9</v>
       </c>
       <c r="D83" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="E83" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4178,10 +4178,10 @@
         <v>3.1</v>
       </c>
       <c r="D86" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E86" t="n">
-        <v>33.1</v>
+        <v>32.7</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -4192,52 +4192,52 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7.3</v>
+        <v>25</v>
       </c>
       <c r="D87" t="n">
-        <v>-24.9</v>
+        <v>-7.1</v>
       </c>
       <c r="E87" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>25</v>
+        <v>7.3</v>
       </c>
       <c r="D88" t="n">
-        <v>-7.1</v>
+        <v>-24.6</v>
       </c>
       <c r="E88" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -4256,10 +4256,10 @@
         <v>7.1</v>
       </c>
       <c r="D89" t="n">
-        <v>-24.9</v>
+        <v>-24.6</v>
       </c>
       <c r="E89" t="n">
-        <v>32</v>
+        <v>31.7</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         <v>6.9</v>
       </c>
       <c r="D90" t="n">
-        <v>-24.9</v>
+        <v>-24.6</v>
       </c>
       <c r="E90" t="n">
-        <v>31.8</v>
+        <v>31.5</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4296,26 +4296,26 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3.1</v>
+        <v>-21</v>
       </c>
       <c r="D91" t="n">
-        <v>-27.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E91" t="n">
-        <v>30.8</v>
+        <v>31.4</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -4334,10 +4334,10 @@
         <v>100.1</v>
       </c>
       <c r="D92" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E92" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4348,26 +4348,26 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-21.8</v>
+        <v>3.1</v>
       </c>
       <c r="D93" t="n">
-        <v>-52.5</v>
+        <v>-27.4</v>
       </c>
       <c r="E93" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4386,10 +4386,10 @@
         <v>-0.2</v>
       </c>
       <c r="D94" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E94" t="n">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -4412,10 +4412,10 @@
         <v>-0.7</v>
       </c>
       <c r="D95" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E95" t="n">
-        <v>29.2</v>
+        <v>28.9</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4438,10 +4438,10 @@
         <v>7.3</v>
       </c>
       <c r="D96" t="n">
-        <v>-21.8</v>
+        <v>-21</v>
       </c>
       <c r="E96" t="n">
-        <v>29.1</v>
+        <v>28.3</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         <v>7.1</v>
       </c>
       <c r="D97" t="n">
-        <v>-21.8</v>
+        <v>-21</v>
       </c>
       <c r="E97" t="n">
-        <v>29</v>
+        <v>28.2</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -4478,22 +4478,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6.9</v>
+        <v>-24.6</v>
       </c>
       <c r="D98" t="n">
-        <v>-21.8</v>
+        <v>-52.5</v>
       </c>
       <c r="E98" t="n">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4504,156 +4504,156 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3.1</v>
+        <v>6.9</v>
       </c>
       <c r="D99" t="n">
-        <v>-24.9</v>
+        <v>-21</v>
       </c>
       <c r="E99" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>ECO</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C100" t="n">
-        <v>-24.9</v>
+        <v>3.1</v>
       </c>
       <c r="D100" t="n">
-        <v>-52.5</v>
+        <v>-24.6</v>
       </c>
       <c r="E100" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-0.2</v>
+        <v>26.7</v>
       </c>
       <c r="D101" t="n">
-        <v>-27.6</v>
+        <v>-0.7</v>
       </c>
       <c r="E101" t="n">
         <v>27.4</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>26.7</v>
+        <v>-0.2</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.7</v>
+        <v>-27.4</v>
       </c>
       <c r="E102" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-0.7</v>
+        <v>26.7</v>
       </c>
       <c r="D103" t="n">
-        <v>-27.6</v>
+        <v>-0.2</v>
       </c>
       <c r="E103" t="n">
         <v>26.9</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C104" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-27.4</v>
+      </c>
+      <c r="E104" t="n">
         <v>26.7</v>
       </c>
-      <c r="D104" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="E104" t="n">
-        <v>26.9</v>
-      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4764,163 +4764,163 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6.9</v>
+        <v>-27.4</v>
       </c>
       <c r="D109" t="n">
-        <v>-18.2</v>
+        <v>-52.5</v>
       </c>
       <c r="E109" t="n">
         <v>25.1</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3.1</v>
+        <v>6.9</v>
       </c>
       <c r="D110" t="n">
-        <v>-21.8</v>
+        <v>-18.2</v>
       </c>
       <c r="E110" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-27.6</v>
+        <v>-0.2</v>
       </c>
       <c r="D111" t="n">
-        <v>-52.5</v>
+        <v>-24.6</v>
       </c>
       <c r="E111" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-0.2</v>
+        <v>7.3</v>
       </c>
       <c r="D112" t="n">
-        <v>-24.9</v>
+        <v>-17.1</v>
       </c>
       <c r="E112" t="n">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="D113" t="n">
-        <v>-17.1</v>
+        <v>-21</v>
       </c>
       <c r="E113" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-0.7</v>
+        <v>7.1</v>
       </c>
       <c r="D114" t="n">
-        <v>-24.9</v>
+        <v>-17.1</v>
       </c>
       <c r="E114" t="n">
         <v>24.2</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4929,43 +4929,43 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="D115" t="n">
         <v>-17.1</v>
       </c>
       <c r="E115" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6.9</v>
+        <v>-0.7</v>
       </c>
       <c r="D116" t="n">
-        <v>-17.1</v>
+        <v>-24.6</v>
       </c>
       <c r="E116" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -4998,52 +4998,52 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-7.1</v>
+        <v>-29.6</v>
       </c>
       <c r="D118" t="n">
-        <v>-29.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E118" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
           <t>FRO</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C119" t="n">
-        <v>-29.9</v>
+        <v>-7.1</v>
       </c>
       <c r="D119" t="n">
-        <v>-52.5</v>
+        <v>-29.6</v>
       </c>
       <c r="E119" t="n">
         <v>22.5</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -5076,59 +5076,59 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>-0.2</v>
+        <v>3.1</v>
       </c>
       <c r="D121" t="n">
-        <v>-21.8</v>
+        <v>-18.2</v>
       </c>
       <c r="E121" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3.1</v>
+        <v>100.1</v>
       </c>
       <c r="D122" t="n">
-        <v>-18.2</v>
+        <v>79.3</v>
       </c>
       <c r="E122" t="n">
-        <v>21.4</v>
+        <v>20.9</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5137,43 +5137,43 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>-0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="D123" t="n">
-        <v>-21.8</v>
+        <v>-21</v>
       </c>
       <c r="E123" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>100.1</v>
+        <v>-0.7</v>
       </c>
       <c r="D124" t="n">
-        <v>79.3</v>
+        <v>-21</v>
       </c>
       <c r="E124" t="n">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -5192,10 +5192,10 @@
         <v>-7.1</v>
       </c>
       <c r="D125" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="E125" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5310,33 +5310,33 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>ASC</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>FRO</t>
-        </is>
-      </c>
       <c r="C130" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D130" t="n">
         <v>-11.3</v>
       </c>
-      <c r="D130" t="n">
-        <v>-29.9</v>
-      </c>
       <c r="E130" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5345,95 +5345,95 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="D131" t="n">
         <v>-11.3</v>
       </c>
       <c r="E131" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>7.1</v>
+        <v>-11.3</v>
       </c>
       <c r="D132" t="n">
-        <v>-11.3</v>
+        <v>-29.6</v>
       </c>
       <c r="E132" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>25</v>
+        <v>6.9</v>
       </c>
       <c r="D133" t="n">
-        <v>6.9</v>
+        <v>-11.3</v>
       </c>
       <c r="E133" t="n">
         <v>18.2</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
           <t>TNK</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>ASC</t>
-        </is>
-      </c>
       <c r="C134" t="n">
+        <v>25</v>
+      </c>
+      <c r="D134" t="n">
         <v>6.9</v>
-      </c>
-      <c r="D134" t="n">
-        <v>-11.3</v>
       </c>
       <c r="E134" t="n">
         <v>18.1</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -5492,48 +5492,48 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>-7.1</v>
+        <v>25</v>
       </c>
       <c r="D137" t="n">
-        <v>-24.9</v>
+        <v>7.3</v>
       </c>
       <c r="E137" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>25</v>
+        <v>-0.7</v>
       </c>
       <c r="D138" t="n">
-        <v>7.3</v>
+        <v>-18.2</v>
       </c>
       <c r="E138" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -5544,26 +5544,26 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>-0.7</v>
+        <v>-7.1</v>
       </c>
       <c r="D139" t="n">
-        <v>-18.2</v>
+        <v>-24.6</v>
       </c>
       <c r="E139" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -5634,10 +5634,10 @@
         <v>-11.3</v>
       </c>
       <c r="D142" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="E142" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -5648,59 +5648,59 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>-7.1</v>
+        <v>3.1</v>
       </c>
       <c r="D143" t="n">
-        <v>-21.8</v>
+        <v>-11.3</v>
       </c>
       <c r="E143" t="n">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="D144" t="n">
-        <v>-11.3</v>
+        <v>-7.1</v>
       </c>
       <c r="E144" t="n">
         <v>14.4</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5709,24 +5709,24 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="D145" t="n">
         <v>-7.1</v>
       </c>
       <c r="E145" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5735,43 +5735,43 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="D146" t="n">
         <v>-7.1</v>
       </c>
       <c r="E146" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>6.9</v>
+        <v>-7.1</v>
       </c>
       <c r="D147" t="n">
-        <v>-7.1</v>
+        <v>-21</v>
       </c>
       <c r="E147" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -5790,10 +5790,10 @@
         <v>-11.3</v>
       </c>
       <c r="D148" t="n">
-        <v>-24.9</v>
+        <v>-24.6</v>
       </c>
       <c r="E148" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -5816,10 +5816,10 @@
         <v>-17.1</v>
       </c>
       <c r="D149" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E149" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -5842,10 +5842,10 @@
         <v>-18.2</v>
       </c>
       <c r="D150" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E150" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -5908,130 +5908,130 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
           <t>ASC</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>DHT</t>
-        </is>
-      </c>
       <c r="C153" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="D153" t="n">
         <v>-11.3</v>
       </c>
-      <c r="D153" t="n">
-        <v>-21.8</v>
-      </c>
       <c r="E153" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>-0.7</v>
+        <v>-17.1</v>
       </c>
       <c r="D154" t="n">
-        <v>-11.3</v>
+        <v>-27.4</v>
       </c>
       <c r="E154" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>-17.1</v>
+        <v>3.1</v>
       </c>
       <c r="D155" t="n">
-        <v>-27.6</v>
+        <v>-7.1</v>
       </c>
       <c r="E155" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3.1</v>
+        <v>-7.1</v>
       </c>
       <c r="D156" t="n">
-        <v>-7.1</v>
+        <v>-17.1</v>
       </c>
       <c r="E156" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>-7.1</v>
+        <v>-11.3</v>
       </c>
       <c r="D157" t="n">
-        <v>-17.1</v>
+        <v>-21</v>
       </c>
       <c r="E157" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -6050,10 +6050,10 @@
         <v>79.3</v>
       </c>
       <c r="D158" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E158" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -6076,10 +6076,10 @@
         <v>-18.2</v>
       </c>
       <c r="D159" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="E159" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -6099,13 +6099,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>-21.8</v>
+        <v>-21</v>
       </c>
       <c r="D160" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E160" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -6168,78 +6168,78 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>-17.1</v>
+        <v>6.9</v>
       </c>
       <c r="D163" t="n">
-        <v>-24.9</v>
+        <v>-0.7</v>
       </c>
       <c r="E163" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="E164" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>7.3</v>
+        <v>-17.1</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.2</v>
+        <v>-24.6</v>
       </c>
       <c r="E165" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
         <v>-0.2</v>
       </c>
       <c r="E167" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -6350,26 +6350,26 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>-18.2</v>
+        <v>-21</v>
       </c>
       <c r="D170" t="n">
-        <v>-24.9</v>
+        <v>-27.4</v>
       </c>
       <c r="E170" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -6402,26 +6402,26 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>-21.8</v>
+        <v>-18.2</v>
       </c>
       <c r="D172" t="n">
-        <v>-27.6</v>
+        <v>-24.6</v>
       </c>
       <c r="E172" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>-24.9</v>
+        <v>-24.6</v>
       </c>
       <c r="D174" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E174" t="n">
         <v>5</v>
@@ -6480,59 +6480,59 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>-17.1</v>
+        <v>-7.1</v>
       </c>
       <c r="D175" t="n">
-        <v>-21.8</v>
+        <v>-11.3</v>
       </c>
       <c r="E175" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>-7.1</v>
+        <v>7.3</v>
       </c>
       <c r="D176" t="n">
-        <v>-11.3</v>
+        <v>3.1</v>
       </c>
       <c r="E176" t="n">
         <v>4.2</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6541,69 +6541,69 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="D177" t="n">
         <v>3.1</v>
       </c>
       <c r="E177" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (containerships vs lng)</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>7.1</v>
+        <v>3.1</v>
       </c>
       <c r="D178" t="n">
-        <v>3.1</v>
+        <v>-0.7</v>
       </c>
       <c r="E178" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs lng)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3.1</v>
+        <v>-17.1</v>
       </c>
       <c r="D179" t="n">
-        <v>-0.7</v>
+        <v>-21</v>
       </c>
       <c r="E179" t="n">
         <v>3.9</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
         <v>3.1</v>
       </c>
       <c r="E180" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -6636,26 +6636,26 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>-18.2</v>
+        <v>-21</v>
       </c>
       <c r="D181" t="n">
-        <v>-21.8</v>
+        <v>-24.6</v>
       </c>
       <c r="E181" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -6688,52 +6688,52 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>-21.8</v>
+        <v>-24.6</v>
       </c>
       <c r="D183" t="n">
-        <v>-24.9</v>
+        <v>-27.4</v>
       </c>
       <c r="E183" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>-24.9</v>
+        <v>-18.2</v>
       </c>
       <c r="D184" t="n">
-        <v>-27.6</v>
+        <v>-21</v>
       </c>
       <c r="E184" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -6749,13 +6749,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="D185" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="E185" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>6.9</v>
       </c>
       <c r="E189" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -6870,52 +6870,52 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
           <t>GSL</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>TNK</t>
-        </is>
-      </c>
       <c r="C190" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D190" t="n">
         <v>7.1</v>
       </c>
-      <c r="D190" t="n">
-        <v>6.9</v>
-      </c>
       <c r="E190" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="D191" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="E191" t="n">
         <v>0.2</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.4</v>
+        <v>5.34</v>
       </c>
       <c r="E2" t="n">
         <v>17.74</v>
@@ -542,13 +542,13 @@
         <v>10.81</v>
       </c>
       <c r="J2" t="n">
-        <v>228.6</v>
+        <v>232.3</v>
       </c>
       <c r="K2" t="n">
-        <v>-88.3</v>
+        <v>-88.2</v>
       </c>
       <c r="L2" t="n">
-        <v>100.1</v>
+        <v>102.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>38.29</v>
+        <v>36.72</v>
       </c>
       <c r="E3" t="n">
         <v>83.95999999999999</v>
@@ -591,13 +591,13 @@
         <v>64.93000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>119.3</v>
+        <v>128.6</v>
       </c>
       <c r="K3" t="n">
-        <v>6.6</v>
+        <v>11.2</v>
       </c>
       <c r="L3" t="n">
-        <v>69.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.24</v>
+        <v>12.79</v>
       </c>
       <c r="E4" t="n">
         <v>23.95</v>
@@ -640,13 +640,13 @@
         <v>16.77</v>
       </c>
       <c r="J4" t="n">
-        <v>80.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="K4" t="n">
-        <v>-47.5</v>
+        <v>-45.7</v>
       </c>
       <c r="L4" t="n">
-        <v>26.7</v>
+        <v>31.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74.45</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>94.77</v>
@@ -689,13 +689,13 @@
         <v>79.59</v>
       </c>
       <c r="J5" t="n">
-        <v>27.3</v>
+        <v>39.4</v>
       </c>
       <c r="K5" t="n">
-        <v>-16.3</v>
+        <v>-8.4</v>
       </c>
       <c r="L5" t="n">
-        <v>6.9</v>
+        <v>17.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -706,12 +706,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -720,42 +720,42 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.89</v>
+        <v>14.1</v>
       </c>
       <c r="E6" t="n">
-        <v>19.44</v>
+        <v>21.52</v>
       </c>
       <c r="F6" t="n">
-        <v>16.05</v>
+        <v>16.15</v>
       </c>
       <c r="G6" t="n">
-        <v>9.77</v>
+        <v>10.84</v>
       </c>
       <c r="H6" t="n">
-        <v>8.960000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="I6" t="n">
-        <v>14.92</v>
+        <v>15.66</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9</v>
+        <v>52.6</v>
       </c>
       <c r="K6" t="n">
-        <v>-52.5</v>
+        <v>-37.4</v>
       </c>
       <c r="L6" t="n">
-        <v>-21</v>
+        <v>11</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -769,31 +769,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>52.48</v>
+        <v>17.65</v>
       </c>
       <c r="E7" t="n">
-        <v>55.11</v>
+        <v>19.44</v>
       </c>
       <c r="F7" t="n">
-        <v>43.45</v>
+        <v>16.05</v>
       </c>
       <c r="G7" t="n">
-        <v>21.92</v>
+        <v>9.77</v>
       </c>
       <c r="H7" t="n">
-        <v>19.32</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>39.59</v>
+        <v>14.92</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>10.1</v>
       </c>
       <c r="K7" t="n">
-        <v>-63.2</v>
+        <v>-49.2</v>
       </c>
       <c r="L7" t="n">
-        <v>-24.6</v>
+        <v>-15.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -804,12 +804,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>84.48999999999999</v>
+        <v>35.52</v>
       </c>
       <c r="E8" t="n">
-        <v>77.87</v>
+        <v>40.26</v>
       </c>
       <c r="F8" t="n">
-        <v>65.86</v>
+        <v>31.83</v>
       </c>
       <c r="G8" t="n">
-        <v>42.3</v>
+        <v>15.62</v>
       </c>
       <c r="H8" t="n">
-        <v>38.53</v>
+        <v>13.52</v>
       </c>
       <c r="I8" t="n">
-        <v>61.34</v>
+        <v>28.82</v>
       </c>
       <c r="J8" t="n">
-        <v>-7.8</v>
+        <v>13.3</v>
       </c>
       <c r="K8" t="n">
-        <v>-54.4</v>
+        <v>-61.9</v>
       </c>
       <c r="L8" t="n">
-        <v>-27.4</v>
+        <v>-18.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -867,31 +867,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>40.93</v>
+        <v>49.88</v>
       </c>
       <c r="E9" t="n">
-        <v>40.26</v>
+        <v>55.11</v>
       </c>
       <c r="F9" t="n">
-        <v>31.83</v>
+        <v>43.45</v>
       </c>
       <c r="G9" t="n">
-        <v>15.62</v>
+        <v>21.92</v>
       </c>
       <c r="H9" t="n">
-        <v>13.52</v>
+        <v>19.32</v>
       </c>
       <c r="I9" t="n">
-        <v>28.82</v>
+        <v>39.59</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6</v>
+        <v>10.5</v>
       </c>
       <c r="K9" t="n">
-        <v>-67</v>
+        <v>-61.3</v>
       </c>
       <c r="L9" t="n">
-        <v>-29.6</v>
+        <v>-20.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -902,47 +902,96 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>INSW</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>crude</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>79.51000000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>77.87</v>
+      </c>
+      <c r="F10" t="n">
+        <v>65.86</v>
+      </c>
+      <c r="G10" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>38.53</v>
+      </c>
+      <c r="I10" t="n">
+        <v>61.34</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>whole-company</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>crude</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>5.85</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E11" t="n">
         <v>4.07</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" t="n">
         <v>3.1</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" t="n">
         <v>1.27</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H11" t="n">
         <v>1.15</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>2.78</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>-30.4</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>-80.3</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>-52.5</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
@@ -1079,7 +1128,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.03</v>
+        <v>20.71</v>
       </c>
       <c r="E2" t="n">
         <v>49.7</v>
@@ -1100,13 +1149,13 @@
         <v>35.91</v>
       </c>
       <c r="K2" t="n">
-        <v>148.1</v>
+        <v>140</v>
       </c>
       <c r="L2" t="n">
-        <v>-61</v>
+        <v>-62.3</v>
       </c>
       <c r="M2" t="n">
-        <v>79.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1137,7 +1186,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.74</v>
+        <v>29.48</v>
       </c>
       <c r="E3" t="n">
         <v>39.36</v>
@@ -1158,13 +1207,13 @@
         <v>30.67</v>
       </c>
       <c r="K3" t="n">
-        <v>32.3</v>
+        <v>33.5</v>
       </c>
       <c r="L3" t="n">
-        <v>-45.8</v>
+        <v>-45.3</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1297,7 +1346,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80.58</v>
+        <v>72.58</v>
       </c>
       <c r="E2" t="n">
         <v>105.66</v>
@@ -1318,17 +1367,17 @@
         <v>79.98999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>31.1</v>
+        <v>45.6</v>
       </c>
       <c r="L2" t="n">
-        <v>-40.7</v>
+        <v>-34.2</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7</v>
+        <v>10.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1398,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.41</v>
+        <v>26.81</v>
       </c>
       <c r="E3" t="n">
         <v>40.58</v>
@@ -1370,17 +1419,17 @@
         <v>27.32</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>51.4</v>
       </c>
       <c r="L3" t="n">
-        <v>-62.5</v>
+        <v>-58.9</v>
       </c>
       <c r="M3" t="n">
-        <v>-7.1</v>
+        <v>1.9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1450,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.07</v>
+        <v>15.12</v>
       </c>
       <c r="E4" t="n">
         <v>18.21</v>
@@ -1422,17 +1471,17 @@
         <v>15.15</v>
       </c>
       <c r="K4" t="n">
-        <v>6.7</v>
+        <v>20.4</v>
       </c>
       <c r="L4" t="n">
-        <v>-44.8</v>
+        <v>-37.7</v>
       </c>
       <c r="M4" t="n">
-        <v>-11.3</v>
+        <v>0.2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1502,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7.23</v>
+        <v>6.97</v>
       </c>
       <c r="E5" t="n">
         <v>8.58</v>
@@ -1474,13 +1523,13 @@
         <v>5.91</v>
       </c>
       <c r="K5" t="n">
-        <v>18.6</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>-62.4</v>
+        <v>-61</v>
       </c>
       <c r="M5" t="n">
-        <v>-18.2</v>
+        <v>-15.2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1601,7 +1650,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.9</v>
+        <v>17.47</v>
       </c>
       <c r="E2" t="n">
         <v>25.32</v>
@@ -1619,13 +1668,13 @@
         <v>21.13</v>
       </c>
       <c r="J2" t="n">
-        <v>49.8</v>
+        <v>44.9</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1</v>
+        <v>-1.2</v>
       </c>
       <c r="L2" t="n">
-        <v>25</v>
+        <v>20.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1650,7 +1699,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.68</v>
+        <v>23.57</v>
       </c>
       <c r="E3" t="n">
         <v>32.13</v>
@@ -1668,13 +1717,13 @@
         <v>25.41</v>
       </c>
       <c r="J3" t="n">
-        <v>35.7</v>
+        <v>36.3</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.6</v>
+        <v>-17.2</v>
       </c>
       <c r="L3" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1699,7 +1748,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.81</v>
+        <v>24.4</v>
       </c>
       <c r="E4" t="n">
         <v>32.39</v>
@@ -1717,17 +1766,17 @@
         <v>25.76</v>
       </c>
       <c r="J4" t="n">
-        <v>25.5</v>
+        <v>32.7</v>
       </c>
       <c r="K4" t="n">
-        <v>-24</v>
+        <v>-19.6</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2</v>
+        <v>5.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1893,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>37.89</v>
+        <v>37.79</v>
       </c>
       <c r="E2" t="n">
         <v>44.45</v>
@@ -1862,13 +1911,13 @@
         <v>40.59</v>
       </c>
       <c r="J2" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.5</v>
+        <v>-4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1893,7 +1942,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="E3" t="n">
         <v>2.26</v>
@@ -1911,13 +1960,13 @@
         <v>2.11</v>
       </c>
       <c r="J3" t="n">
-        <v>-11.2</v>
+        <v>-13.6</v>
       </c>
       <c r="K3" t="n">
-        <v>-32.3</v>
+        <v>-34.2</v>
       </c>
       <c r="L3" t="n">
-        <v>-17.1</v>
+        <v>-19.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1936,7 +1985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1991,13 +2040,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>100.1</v>
+        <v>102.4</v>
       </c>
       <c r="D2" t="n">
         <v>-52.5</v>
       </c>
       <c r="E2" t="n">
-        <v>152.6</v>
+        <v>154.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2008,7 +2057,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2017,43 +2066,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>79.3</v>
+        <v>76.8</v>
       </c>
       <c r="D3" t="n">
         <v>-52.5</v>
       </c>
       <c r="E3" t="n">
-        <v>131.7</v>
+        <v>129.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100.1</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>-29.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E4" t="n">
-        <v>129.7</v>
+        <v>125.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -2069,13 +2118,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>100.1</v>
+        <v>102.4</v>
       </c>
       <c r="D5" t="n">
-        <v>-27.4</v>
+        <v>-22.8</v>
       </c>
       <c r="E5" t="n">
-        <v>127.5</v>
+        <v>125.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2095,13 +2144,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100.1</v>
+        <v>102.4</v>
       </c>
       <c r="D6" t="n">
-        <v>-24.6</v>
+        <v>-20.6</v>
       </c>
       <c r="E6" t="n">
-        <v>124.7</v>
+        <v>123</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2112,26 +2161,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>69.59999999999999</v>
+        <v>102.4</v>
       </c>
       <c r="D7" t="n">
-        <v>-52.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E7" t="n">
-        <v>122</v>
+        <v>121.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
@@ -2143,17 +2192,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100.1</v>
+        <v>102.4</v>
       </c>
       <c r="D8" t="n">
-        <v>-21</v>
+        <v>-18.9</v>
       </c>
       <c r="E8" t="n">
-        <v>121.1</v>
+        <v>121.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2169,21 +2218,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100.1</v>
+        <v>102.4</v>
       </c>
       <c r="D9" t="n">
-        <v>-18.2</v>
+        <v>-15.5</v>
       </c>
       <c r="E9" t="n">
-        <v>118.3</v>
+        <v>117.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2195,21 +2244,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100.1</v>
+        <v>102.4</v>
       </c>
       <c r="D10" t="n">
-        <v>-17.1</v>
+        <v>-15.2</v>
       </c>
       <c r="E10" t="n">
-        <v>117.2</v>
+        <v>117.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -2225,13 +2274,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100.1</v>
+        <v>102.4</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.3</v>
+        <v>0.2</v>
       </c>
       <c r="E11" t="n">
-        <v>111.4</v>
+        <v>102.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2242,85 +2291,85 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>79.3</v>
+        <v>102.4</v>
       </c>
       <c r="D12" t="n">
-        <v>-29.6</v>
+        <v>1.9</v>
       </c>
       <c r="E12" t="n">
-        <v>108.8</v>
+        <v>100.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>100.1</v>
+        <v>76.8</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.1</v>
+        <v>-22.8</v>
       </c>
       <c r="E13" t="n">
-        <v>107.2</v>
+        <v>99.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>79.3</v>
+        <v>102.4</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.4</v>
+        <v>4.1</v>
       </c>
       <c r="E14" t="n">
-        <v>106.7</v>
+        <v>98.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2329,17 +2378,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>79.3</v>
+        <v>76.8</v>
       </c>
       <c r="D15" t="n">
-        <v>-24.6</v>
+        <v>-20.6</v>
       </c>
       <c r="E15" t="n">
-        <v>103.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2351,21 +2400,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>100.1</v>
+        <v>102.4</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7</v>
+        <v>5.6</v>
       </c>
       <c r="E16" t="n">
-        <v>100.9</v>
+        <v>96.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -2377,47 +2426,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>79.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>-21</v>
+        <v>-22.8</v>
       </c>
       <c r="E17" t="n">
-        <v>100.3</v>
+        <v>96.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>100.1</v>
+        <v>76.8</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2</v>
+        <v>-19.3</v>
       </c>
       <c r="E18" t="n">
-        <v>100.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2433,13 +2482,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>69.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="D19" t="n">
-        <v>-29.6</v>
+        <v>-18.9</v>
       </c>
       <c r="E19" t="n">
-        <v>99.2</v>
+        <v>95.7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2450,78 +2499,78 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>79.3</v>
+        <v>102.4</v>
       </c>
       <c r="D20" t="n">
-        <v>-18.2</v>
+        <v>7.4</v>
       </c>
       <c r="E20" t="n">
-        <v>97.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>69.59999999999999</v>
+        <v>102.4</v>
       </c>
       <c r="D21" t="n">
-        <v>-27.4</v>
+        <v>7.8</v>
       </c>
       <c r="E21" t="n">
-        <v>97</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>100.1</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>3.1</v>
+        <v>-20.6</v>
       </c>
       <c r="E22" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -2537,13 +2586,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>79.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>-17.1</v>
+        <v>-19.3</v>
       </c>
       <c r="E23" t="n">
-        <v>96.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2559,17 +2608,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>69.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="D24" t="n">
-        <v>-24.6</v>
+        <v>-15.5</v>
       </c>
       <c r="E24" t="n">
-        <v>94.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2580,26 +2629,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>100.1</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>6.9</v>
+        <v>-18.9</v>
       </c>
       <c r="E25" t="n">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -2611,69 +2660,69 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>100.1</v>
+        <v>102.4</v>
       </c>
       <c r="D26" t="n">
-        <v>7.1</v>
+        <v>10.2</v>
       </c>
       <c r="E26" t="n">
-        <v>93</v>
+        <v>92.2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>100.1</v>
+        <v>76.8</v>
       </c>
       <c r="D27" t="n">
-        <v>7.3</v>
+        <v>-15.2</v>
       </c>
       <c r="E27" t="n">
-        <v>92.8</v>
+        <v>92</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>69.59999999999999</v>
+        <v>102.4</v>
       </c>
       <c r="D28" t="n">
-        <v>-21</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>90.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2689,28 +2738,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>79.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-11.3</v>
+        <v>-15.5</v>
       </c>
       <c r="E29" t="n">
-        <v>90.5</v>
+        <v>88.8</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2719,154 +2768,154 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>69.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-18.2</v>
+        <v>-15.2</v>
       </c>
       <c r="E30" t="n">
-        <v>87.8</v>
+        <v>88.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>69.59999999999999</v>
+        <v>102.4</v>
       </c>
       <c r="D31" t="n">
-        <v>-17.1</v>
+        <v>17.1</v>
       </c>
       <c r="E31" t="n">
-        <v>86.7</v>
+        <v>85.3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>79.3</v>
+        <v>31.1</v>
       </c>
       <c r="D32" t="n">
-        <v>-7.1</v>
+        <v>-52.5</v>
       </c>
       <c r="E32" t="n">
-        <v>86.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>69.59999999999999</v>
+        <v>102.4</v>
       </c>
       <c r="D33" t="n">
-        <v>-11.3</v>
+        <v>20.9</v>
       </c>
       <c r="E33" t="n">
-        <v>80.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>79.3</v>
+        <v>76.8</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7</v>
+        <v>0.2</v>
       </c>
       <c r="E34" t="n">
-        <v>80</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>79.3</v>
+        <v>76.8</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2</v>
+        <v>1.9</v>
       </c>
       <c r="E35" t="n">
-        <v>79.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2875,43 +2924,43 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>26.7</v>
+        <v>20.9</v>
       </c>
       <c r="D36" t="n">
         <v>-52.5</v>
       </c>
       <c r="E36" t="n">
-        <v>79.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>25</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>-52.5</v>
+        <v>0.2</v>
       </c>
       <c r="E37" t="n">
-        <v>77.5</v>
+        <v>73.2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -2923,21 +2972,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>69.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="D38" t="n">
-        <v>-7.1</v>
+        <v>4.1</v>
       </c>
       <c r="E38" t="n">
-        <v>76.7</v>
+        <v>72.8</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2949,47 +2998,47 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>79.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="E39" t="n">
-        <v>76.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>100.1</v>
+        <v>76.8</v>
       </c>
       <c r="D40" t="n">
-        <v>25</v>
+        <v>5.6</v>
       </c>
       <c r="E40" t="n">
-        <v>75.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3005,13 +3054,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>100.1</v>
+        <v>102.4</v>
       </c>
       <c r="D41" t="n">
-        <v>26.7</v>
+        <v>31.1</v>
       </c>
       <c r="E41" t="n">
-        <v>73.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3022,33 +3071,33 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>79.3</v>
+        <v>17.1</v>
       </c>
       <c r="D42" t="n">
-        <v>6.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E42" t="n">
-        <v>72.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3057,17 +3106,17 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>79.3</v>
+        <v>76.8</v>
       </c>
       <c r="D43" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="E43" t="n">
-        <v>72.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3079,21 +3128,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>79.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>7.3</v>
+        <v>4.1</v>
       </c>
       <c r="E44" t="n">
-        <v>71.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3105,28 +3154,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>69.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.7</v>
+        <v>7.8</v>
       </c>
       <c r="E45" t="n">
-        <v>70.3</v>
+        <v>69</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3135,17 +3184,17 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>69.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2</v>
+        <v>5.6</v>
       </c>
       <c r="E46" t="n">
-        <v>69.8</v>
+        <v>67.8</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -3157,47 +3206,47 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>69.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="D47" t="n">
-        <v>3.1</v>
+        <v>10.2</v>
       </c>
       <c r="E47" t="n">
-        <v>66.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>69.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="E48" t="n">
-        <v>62.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3258,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>69.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="D49" t="n">
-        <v>7.1</v>
+        <v>11</v>
       </c>
       <c r="E49" t="n">
-        <v>62.4</v>
+        <v>65.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3239,24 +3288,24 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>69.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="E50" t="n">
-        <v>62.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3265,50 +3314,50 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7.3</v>
+        <v>11</v>
       </c>
       <c r="D51" t="n">
         <v>-52.5</v>
       </c>
       <c r="E51" t="n">
-        <v>59.8</v>
+        <v>63.5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7.1</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>-52.5</v>
+        <v>10.2</v>
       </c>
       <c r="E52" t="n">
-        <v>59.6</v>
+        <v>63.2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3317,50 +3366,50 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6.9</v>
+        <v>10.2</v>
       </c>
       <c r="D53" t="n">
         <v>-52.5</v>
       </c>
       <c r="E53" t="n">
-        <v>59.4</v>
+        <v>62.7</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>26.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>-29.6</v>
+        <v>11</v>
       </c>
       <c r="E54" t="n">
-        <v>56.3</v>
+        <v>62.3</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3369,117 +3418,117 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3.1</v>
+        <v>7.8</v>
       </c>
       <c r="D55" t="n">
         <v>-52.5</v>
       </c>
       <c r="E55" t="n">
-        <v>55.6</v>
+        <v>60.3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>25</v>
+        <v>7.4</v>
       </c>
       <c r="D56" t="n">
-        <v>-29.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E56" t="n">
-        <v>54.6</v>
+        <v>59.9</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>79.3</v>
+        <v>76.8</v>
       </c>
       <c r="D57" t="n">
-        <v>25</v>
+        <v>17.1</v>
       </c>
       <c r="E57" t="n">
-        <v>54.2</v>
+        <v>59.8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>26.7</v>
+        <v>5.6</v>
       </c>
       <c r="D58" t="n">
-        <v>-27.4</v>
+        <v>-52.5</v>
       </c>
       <c r="E58" t="n">
-        <v>54.1</v>
+        <v>58</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>79.3</v>
+        <v>4.1</v>
       </c>
       <c r="D59" t="n">
-        <v>26.7</v>
+        <v>-52.5</v>
       </c>
       <c r="E59" t="n">
-        <v>52.6</v>
+        <v>56.5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3490,59 +3539,59 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>25</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>-27.4</v>
+        <v>17.1</v>
       </c>
       <c r="E60" t="n">
-        <v>52.4</v>
+        <v>56.3</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-0.2</v>
+        <v>76.8</v>
       </c>
       <c r="D61" t="n">
-        <v>-52.5</v>
+        <v>20.9</v>
       </c>
       <c r="E61" t="n">
-        <v>52.3</v>
+        <v>55.9</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3551,13 +3600,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.7</v>
+        <v>1.9</v>
       </c>
       <c r="D62" t="n">
         <v>-52.5</v>
       </c>
       <c r="E62" t="n">
-        <v>51.7</v>
+        <v>54.4</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3573,125 +3622,125 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>26.7</v>
+        <v>31.1</v>
       </c>
       <c r="D63" t="n">
-        <v>-24.6</v>
+        <v>-22.8</v>
       </c>
       <c r="E63" t="n">
-        <v>51.2</v>
+        <v>54</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>25</v>
+        <v>0.2</v>
       </c>
       <c r="D64" t="n">
-        <v>-24.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E64" t="n">
-        <v>49.6</v>
+        <v>52.6</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>26.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D65" t="n">
-        <v>-21</v>
+        <v>20.9</v>
       </c>
       <c r="E65" t="n">
-        <v>47.7</v>
+        <v>52.4</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>25</v>
+        <v>31.1</v>
       </c>
       <c r="D66" t="n">
-        <v>-21</v>
+        <v>-20.6</v>
       </c>
       <c r="E66" t="n">
-        <v>46</v>
+        <v>51.8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-7.1</v>
+        <v>31.1</v>
       </c>
       <c r="D67" t="n">
-        <v>-52.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E67" t="n">
-        <v>45.3</v>
+        <v>50.5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
@@ -3703,47 +3752,47 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>26.7</v>
+        <v>31.1</v>
       </c>
       <c r="D68" t="n">
-        <v>-18.2</v>
+        <v>-18.9</v>
       </c>
       <c r="E68" t="n">
-        <v>44.9</v>
+        <v>50</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>69.59999999999999</v>
+        <v>31.1</v>
       </c>
       <c r="D69" t="n">
-        <v>25</v>
+        <v>-15.5</v>
       </c>
       <c r="E69" t="n">
-        <v>44.6</v>
+        <v>46.6</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3755,184 +3804,184 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>26.7</v>
+        <v>31.1</v>
       </c>
       <c r="D70" t="n">
-        <v>-17.1</v>
+        <v>-15.2</v>
       </c>
       <c r="E70" t="n">
-        <v>43.8</v>
+        <v>46.3</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>25</v>
+        <v>76.8</v>
       </c>
       <c r="D71" t="n">
-        <v>-18.2</v>
+        <v>31.1</v>
       </c>
       <c r="E71" t="n">
-        <v>43.2</v>
+        <v>45.7</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>69.59999999999999</v>
+        <v>20.9</v>
       </c>
       <c r="D72" t="n">
-        <v>26.7</v>
+        <v>-22.8</v>
       </c>
       <c r="E72" t="n">
-        <v>42.9</v>
+        <v>43.8</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D73" t="n">
-        <v>-17.1</v>
+        <v>31.1</v>
       </c>
       <c r="E73" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-11.3</v>
+        <v>20.9</v>
       </c>
       <c r="D74" t="n">
-        <v>-52.5</v>
+        <v>-20.6</v>
       </c>
       <c r="E74" t="n">
-        <v>41.2</v>
+        <v>41.6</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>26.7</v>
+        <v>20.9</v>
       </c>
       <c r="D75" t="n">
-        <v>-11.3</v>
+        <v>-19.3</v>
       </c>
       <c r="E75" t="n">
-        <v>38</v>
+        <v>40.3</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7.3</v>
+        <v>17.1</v>
       </c>
       <c r="D76" t="n">
-        <v>-29.6</v>
+        <v>-22.8</v>
       </c>
       <c r="E76" t="n">
-        <v>36.9</v>
+        <v>39.9</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3941,17 +3990,17 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7.1</v>
+        <v>20.9</v>
       </c>
       <c r="D77" t="n">
-        <v>-29.6</v>
+        <v>-18.9</v>
       </c>
       <c r="E77" t="n">
-        <v>36.7</v>
+        <v>39.8</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3963,17 +4012,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6.9</v>
+        <v>17.1</v>
       </c>
       <c r="D78" t="n">
-        <v>-29.6</v>
+        <v>-20.6</v>
       </c>
       <c r="E78" t="n">
-        <v>36.5</v>
+        <v>37.7</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3984,33 +4033,33 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>25</v>
+        <v>-15.2</v>
       </c>
       <c r="D79" t="n">
-        <v>-11.3</v>
+        <v>-52.5</v>
       </c>
       <c r="E79" t="n">
-        <v>36.3</v>
+        <v>37.3</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4019,251 +4068,251 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-17.1</v>
+        <v>-15.5</v>
       </c>
       <c r="D80" t="n">
         <v>-52.5</v>
       </c>
       <c r="E80" t="n">
-        <v>35.4</v>
+        <v>37</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7.3</v>
+        <v>17.1</v>
       </c>
       <c r="D81" t="n">
-        <v>-27.4</v>
+        <v>-19.3</v>
       </c>
       <c r="E81" t="n">
-        <v>34.7</v>
+        <v>36.4</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>7.1</v>
+        <v>20.9</v>
       </c>
       <c r="D82" t="n">
-        <v>-27.4</v>
+        <v>-15.5</v>
       </c>
       <c r="E82" t="n">
-        <v>34.5</v>
+        <v>36.4</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6.9</v>
+        <v>20.9</v>
       </c>
       <c r="D83" t="n">
-        <v>-27.4</v>
+        <v>-15.2</v>
       </c>
       <c r="E83" t="n">
-        <v>34.3</v>
+        <v>36.1</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-18.2</v>
+        <v>17.1</v>
       </c>
       <c r="D84" t="n">
-        <v>-52.5</v>
+        <v>-18.9</v>
       </c>
       <c r="E84" t="n">
-        <v>34.2</v>
+        <v>35.9</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>26.7</v>
+        <v>11</v>
       </c>
       <c r="D85" t="n">
-        <v>-7.1</v>
+        <v>-22.8</v>
       </c>
       <c r="E85" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3.1</v>
+        <v>-18.9</v>
       </c>
       <c r="D86" t="n">
-        <v>-29.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E86" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>25</v>
+        <v>10.2</v>
       </c>
       <c r="D87" t="n">
-        <v>-7.1</v>
+        <v>-22.8</v>
       </c>
       <c r="E87" t="n">
-        <v>32.1</v>
+        <v>33.1</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>7.3</v>
+        <v>-19.3</v>
       </c>
       <c r="D88" t="n">
-        <v>-24.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E88" t="n">
-        <v>31.9</v>
+        <v>33.1</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>7.1</v>
+        <v>17.1</v>
       </c>
       <c r="D89" t="n">
-        <v>-24.6</v>
+        <v>-15.5</v>
       </c>
       <c r="E89" t="n">
-        <v>31.7</v>
+        <v>32.5</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -4275,28 +4324,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6.9</v>
+        <v>17.1</v>
       </c>
       <c r="D90" t="n">
-        <v>-24.6</v>
+        <v>-15.2</v>
       </c>
       <c r="E90" t="n">
-        <v>31.5</v>
+        <v>32.2</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4305,13 +4354,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-21</v>
+        <v>-20.6</v>
       </c>
       <c r="D91" t="n">
         <v>-52.5</v>
       </c>
       <c r="E91" t="n">
-        <v>31.4</v>
+        <v>31.8</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4322,22 +4371,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>100.1</v>
+        <v>11</v>
       </c>
       <c r="D92" t="n">
-        <v>69.59999999999999</v>
+        <v>-20.6</v>
       </c>
       <c r="E92" t="n">
-        <v>30.6</v>
+        <v>31.7</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4348,104 +4397,104 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3.1</v>
+        <v>31.1</v>
       </c>
       <c r="D93" t="n">
-        <v>-27.4</v>
+        <v>0.2</v>
       </c>
       <c r="E93" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-0.2</v>
+        <v>10.2</v>
       </c>
       <c r="D94" t="n">
-        <v>-29.6</v>
+        <v>-20.6</v>
       </c>
       <c r="E94" t="n">
-        <v>29.4</v>
+        <v>30.8</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-0.7</v>
+        <v>7.8</v>
       </c>
       <c r="D95" t="n">
-        <v>-29.6</v>
+        <v>-22.8</v>
       </c>
       <c r="E95" t="n">
-        <v>28.9</v>
+        <v>30.7</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>7.3</v>
+        <v>11</v>
       </c>
       <c r="D96" t="n">
-        <v>-21</v>
+        <v>-19.3</v>
       </c>
       <c r="E96" t="n">
-        <v>28.3</v>
+        <v>30.4</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4457,99 +4506,99 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="D97" t="n">
-        <v>-21</v>
+        <v>-22.8</v>
       </c>
       <c r="E97" t="n">
-        <v>28.2</v>
+        <v>30.3</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-24.6</v>
+        <v>11</v>
       </c>
       <c r="D98" t="n">
-        <v>-52.5</v>
+        <v>-18.9</v>
       </c>
       <c r="E98" t="n">
-        <v>27.9</v>
+        <v>29.9</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6.9</v>
+        <v>-22.8</v>
       </c>
       <c r="D99" t="n">
-        <v>-21</v>
+        <v>-52.5</v>
       </c>
       <c r="E99" t="n">
-        <v>27.9</v>
+        <v>29.6</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3.1</v>
+        <v>10.2</v>
       </c>
       <c r="D100" t="n">
-        <v>-24.6</v>
+        <v>-19.3</v>
       </c>
       <c r="E100" t="n">
-        <v>27.7</v>
+        <v>29.5</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
@@ -4561,17 +4610,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>26.7</v>
+        <v>31.1</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.7</v>
+        <v>1.9</v>
       </c>
       <c r="E101" t="n">
-        <v>27.4</v>
+        <v>29.2</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4582,59 +4631,59 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-0.2</v>
+        <v>10.2</v>
       </c>
       <c r="D102" t="n">
-        <v>-27.4</v>
+        <v>-18.9</v>
       </c>
       <c r="E102" t="n">
-        <v>27.2</v>
+        <v>29.1</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>26.7</v>
+        <v>102.4</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E103" t="n">
-        <v>26.9</v>
+        <v>29</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4643,303 +4692,303 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-0.7</v>
+        <v>5.6</v>
       </c>
       <c r="D104" t="n">
-        <v>-27.4</v>
+        <v>-22.8</v>
       </c>
       <c r="E104" t="n">
-        <v>26.7</v>
+        <v>28.4</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>25</v>
+        <v>7.8</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.7</v>
+        <v>-20.6</v>
       </c>
       <c r="E105" t="n">
-        <v>25.7</v>
+        <v>28.4</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="D106" t="n">
-        <v>-18.2</v>
+        <v>-20.6</v>
       </c>
       <c r="E106" t="n">
-        <v>25.5</v>
+        <v>28</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="D107" t="n">
-        <v>-18.2</v>
+        <v>-19.3</v>
       </c>
       <c r="E107" t="n">
-        <v>25.4</v>
+        <v>27.1</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>25</v>
+        <v>31.1</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.2</v>
+        <v>4.1</v>
       </c>
       <c r="E108" t="n">
-        <v>25.2</v>
+        <v>27.1</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
           <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C109" t="n">
-        <v>-27.4</v>
+        <v>4.1</v>
       </c>
       <c r="D109" t="n">
-        <v>-52.5</v>
+        <v>-22.8</v>
       </c>
       <c r="E109" t="n">
-        <v>25.1</v>
+        <v>26.9</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="D110" t="n">
-        <v>-18.2</v>
+        <v>-18.9</v>
       </c>
       <c r="E110" t="n">
-        <v>25.1</v>
+        <v>26.7</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-0.2</v>
+        <v>7.4</v>
       </c>
       <c r="D111" t="n">
-        <v>-24.6</v>
+        <v>-19.3</v>
       </c>
       <c r="E111" t="n">
-        <v>24.4</v>
+        <v>26.7</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>7.3</v>
+        <v>11</v>
       </c>
       <c r="D112" t="n">
-        <v>-17.1</v>
+        <v>-15.5</v>
       </c>
       <c r="E112" t="n">
-        <v>24.4</v>
+        <v>26.5</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="D113" t="n">
-        <v>-21</v>
+        <v>-18.9</v>
       </c>
       <c r="E113" t="n">
-        <v>24.2</v>
+        <v>26.3</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>7.1</v>
+        <v>5.6</v>
       </c>
       <c r="D114" t="n">
-        <v>-17.1</v>
+        <v>-20.6</v>
       </c>
       <c r="E114" t="n">
-        <v>24.2</v>
+        <v>26.2</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>6.9</v>
+        <v>11</v>
       </c>
       <c r="D115" t="n">
-        <v>-17.1</v>
+        <v>-15.2</v>
       </c>
       <c r="E115" t="n">
-        <v>24</v>
+        <v>26.2</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4951,17 +5000,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-0.7</v>
+        <v>10.2</v>
       </c>
       <c r="D116" t="n">
-        <v>-24.6</v>
+        <v>-15.5</v>
       </c>
       <c r="E116" t="n">
-        <v>23.8</v>
+        <v>25.7</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -4977,151 +5026,151 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>26.7</v>
+        <v>31.1</v>
       </c>
       <c r="D117" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="E117" t="n">
-        <v>23.5</v>
+        <v>25.6</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-29.6</v>
+        <v>102.4</v>
       </c>
       <c r="D118" t="n">
-        <v>-52.5</v>
+        <v>76.8</v>
       </c>
       <c r="E118" t="n">
-        <v>22.9</v>
+        <v>25.6</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-7.1</v>
+        <v>10.2</v>
       </c>
       <c r="D119" t="n">
-        <v>-29.6</v>
+        <v>-15.2</v>
       </c>
       <c r="E119" t="n">
-        <v>22.5</v>
+        <v>25.4</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>25</v>
+        <v>5.6</v>
       </c>
       <c r="D120" t="n">
-        <v>3.1</v>
+        <v>-19.3</v>
       </c>
       <c r="E120" t="n">
-        <v>21.9</v>
+        <v>24.9</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="D121" t="n">
-        <v>-18.2</v>
+        <v>-22.8</v>
       </c>
       <c r="E121" t="n">
-        <v>21.4</v>
+        <v>24.8</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>100.1</v>
+        <v>4.1</v>
       </c>
       <c r="D122" t="n">
-        <v>79.3</v>
+        <v>-20.6</v>
       </c>
       <c r="E122" t="n">
-        <v>20.9</v>
+        <v>24.7</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -5133,17 +5182,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>-0.2</v>
+        <v>5.6</v>
       </c>
       <c r="D123" t="n">
-        <v>-21</v>
+        <v>-18.9</v>
       </c>
       <c r="E123" t="n">
-        <v>20.8</v>
+        <v>24.4</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -5154,78 +5203,78 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>-0.7</v>
+        <v>31.1</v>
       </c>
       <c r="D124" t="n">
-        <v>-21</v>
+        <v>7.4</v>
       </c>
       <c r="E124" t="n">
-        <v>20.3</v>
+        <v>23.7</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>-7.1</v>
+        <v>4.1</v>
       </c>
       <c r="D125" t="n">
-        <v>-27.4</v>
+        <v>-19.3</v>
       </c>
       <c r="E125" t="n">
-        <v>20.3</v>
+        <v>23.4</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3.1</v>
+        <v>7.8</v>
       </c>
       <c r="D126" t="n">
-        <v>-17.1</v>
+        <v>-15.5</v>
       </c>
       <c r="E126" t="n">
-        <v>20.2</v>
+        <v>23.3</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -5237,99 +5286,99 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>26.7</v>
+        <v>31.1</v>
       </c>
       <c r="D127" t="n">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="E127" t="n">
-        <v>19.8</v>
+        <v>23.3</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>26.7</v>
+        <v>0.2</v>
       </c>
       <c r="D128" t="n">
-        <v>7.1</v>
+        <v>-22.8</v>
       </c>
       <c r="E128" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>26.7</v>
+        <v>7.8</v>
       </c>
       <c r="D129" t="n">
-        <v>7.3</v>
+        <v>-15.2</v>
       </c>
       <c r="E129" t="n">
-        <v>19.4</v>
+        <v>23</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>7.3</v>
+        <v>4.1</v>
       </c>
       <c r="D130" t="n">
-        <v>-11.3</v>
+        <v>-18.9</v>
       </c>
       <c r="E130" t="n">
-        <v>18.6</v>
+        <v>22.9</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -5341,99 +5390,99 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="D131" t="n">
-        <v>-11.3</v>
+        <v>-15.5</v>
       </c>
       <c r="E131" t="n">
-        <v>18.4</v>
+        <v>22.9</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>-11.3</v>
+        <v>7.4</v>
       </c>
       <c r="D132" t="n">
-        <v>-29.6</v>
+        <v>-15.2</v>
       </c>
       <c r="E132" t="n">
-        <v>18.3</v>
+        <v>22.6</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="D133" t="n">
-        <v>-11.3</v>
+        <v>-20.6</v>
       </c>
       <c r="E133" t="n">
-        <v>18.2</v>
+        <v>22.5</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>25</v>
+        <v>1.9</v>
       </c>
       <c r="D134" t="n">
-        <v>6.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E134" t="n">
-        <v>18.1</v>
+        <v>21.2</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
@@ -5445,125 +5494,125 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>-0.2</v>
+        <v>5.6</v>
       </c>
       <c r="D135" t="n">
-        <v>-18.2</v>
+        <v>-15.5</v>
       </c>
       <c r="E135" t="n">
-        <v>18</v>
+        <v>21.1</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>25</v>
+        <v>31.1</v>
       </c>
       <c r="D136" t="n">
-        <v>7.1</v>
+        <v>10.2</v>
       </c>
       <c r="E136" t="n">
-        <v>17.9</v>
+        <v>20.9</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>25</v>
+        <v>1.9</v>
       </c>
       <c r="D137" t="n">
-        <v>7.3</v>
+        <v>-18.9</v>
       </c>
       <c r="E137" t="n">
-        <v>17.7</v>
+        <v>20.8</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>-0.7</v>
+        <v>0.2</v>
       </c>
       <c r="D138" t="n">
-        <v>-18.2</v>
+        <v>-20.6</v>
       </c>
       <c r="E138" t="n">
-        <v>17.5</v>
+        <v>20.8</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>-7.1</v>
+        <v>20.9</v>
       </c>
       <c r="D139" t="n">
-        <v>-24.6</v>
+        <v>0.2</v>
       </c>
       <c r="E139" t="n">
-        <v>17.4</v>
+        <v>20.8</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -5575,158 +5624,158 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>-0.2</v>
+        <v>5.6</v>
       </c>
       <c r="D140" t="n">
-        <v>-17.1</v>
+        <v>-15.2</v>
       </c>
       <c r="E140" t="n">
-        <v>16.9</v>
+        <v>20.8</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>-0.7</v>
+        <v>31.1</v>
       </c>
       <c r="D141" t="n">
-        <v>-17.1</v>
+        <v>11</v>
       </c>
       <c r="E141" t="n">
-        <v>16.4</v>
+        <v>20.1</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>-11.3</v>
+        <v>4.1</v>
       </c>
       <c r="D142" t="n">
-        <v>-27.4</v>
+        <v>-15.5</v>
       </c>
       <c r="E142" t="n">
-        <v>16.1</v>
+        <v>19.5</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="D143" t="n">
-        <v>-11.3</v>
+        <v>-19.3</v>
       </c>
       <c r="E143" t="n">
-        <v>14.4</v>
+        <v>19.5</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>7.3</v>
+        <v>4.1</v>
       </c>
       <c r="D144" t="n">
-        <v>-7.1</v>
+        <v>-15.2</v>
       </c>
       <c r="E144" t="n">
-        <v>14.4</v>
+        <v>19.2</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="D145" t="n">
-        <v>-7.1</v>
+        <v>-18.9</v>
       </c>
       <c r="E145" t="n">
-        <v>14.2</v>
+        <v>19</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5735,17 +5784,17 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>6.9</v>
+        <v>20.9</v>
       </c>
       <c r="D146" t="n">
-        <v>-7.1</v>
+        <v>1.9</v>
       </c>
       <c r="E146" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -5761,13 +5810,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>-7.1</v>
+        <v>1.9</v>
       </c>
       <c r="D147" t="n">
-        <v>-21</v>
+        <v>-15.5</v>
       </c>
       <c r="E147" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -5778,152 +5827,152 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>-11.3</v>
+        <v>1.9</v>
       </c>
       <c r="D148" t="n">
-        <v>-24.6</v>
+        <v>-15.2</v>
       </c>
       <c r="E148" t="n">
-        <v>13.3</v>
+        <v>17.1</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>-17.1</v>
+        <v>17.1</v>
       </c>
       <c r="D149" t="n">
-        <v>-29.6</v>
+        <v>0.2</v>
       </c>
       <c r="E149" t="n">
-        <v>12.5</v>
+        <v>16.9</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>-18.2</v>
+        <v>20.9</v>
       </c>
       <c r="D150" t="n">
-        <v>-29.6</v>
+        <v>4.1</v>
       </c>
       <c r="E150" t="n">
-        <v>11.4</v>
+        <v>16.9</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>-7.1</v>
+        <v>0.2</v>
       </c>
       <c r="D151" t="n">
-        <v>-18.2</v>
+        <v>-15.5</v>
       </c>
       <c r="E151" t="n">
-        <v>11.1</v>
+        <v>15.7</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="D152" t="n">
-        <v>-11.3</v>
+        <v>-15.2</v>
       </c>
       <c r="E152" t="n">
-        <v>11.1</v>
+        <v>15.4</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>-0.7</v>
+        <v>20.9</v>
       </c>
       <c r="D153" t="n">
-        <v>-11.3</v>
+        <v>5.6</v>
       </c>
       <c r="E153" t="n">
-        <v>10.5</v>
+        <v>15.4</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -5934,189 +5983,189 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>-17.1</v>
+        <v>17.1</v>
       </c>
       <c r="D154" t="n">
-        <v>-27.4</v>
+        <v>1.9</v>
       </c>
       <c r="E154" t="n">
-        <v>10.3</v>
+        <v>15.2</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3.1</v>
+        <v>31.1</v>
       </c>
       <c r="D155" t="n">
-        <v>-7.1</v>
+        <v>17.1</v>
       </c>
       <c r="E155" t="n">
-        <v>10.2</v>
+        <v>14.1</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>-7.1</v>
+        <v>20.9</v>
       </c>
       <c r="D156" t="n">
-        <v>-17.1</v>
+        <v>7.4</v>
       </c>
       <c r="E156" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>-11.3</v>
+        <v>20.9</v>
       </c>
       <c r="D157" t="n">
-        <v>-21</v>
+        <v>7.8</v>
       </c>
       <c r="E157" t="n">
-        <v>9.800000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>79.3</v>
+        <v>17.1</v>
       </c>
       <c r="D158" t="n">
-        <v>69.59999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="E158" t="n">
-        <v>9.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>-18.2</v>
+        <v>17.1</v>
       </c>
       <c r="D159" t="n">
-        <v>-27.4</v>
+        <v>5.6</v>
       </c>
       <c r="E159" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>-21</v>
+        <v>11</v>
       </c>
       <c r="D160" t="n">
-        <v>-29.6</v>
+        <v>0.2</v>
       </c>
       <c r="E160" t="n">
-        <v>8.6</v>
+        <v>10.9</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6125,13 +6174,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>7.3</v>
+        <v>20.9</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.7</v>
+        <v>10.2</v>
       </c>
       <c r="E161" t="n">
-        <v>8.1</v>
+        <v>10.7</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -6142,178 +6191,178 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>7.1</v>
+        <v>31.1</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.7</v>
+        <v>20.9</v>
       </c>
       <c r="E162" t="n">
-        <v>7.9</v>
+        <v>10.2</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>6.9</v>
+        <v>10.2</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.7</v>
+        <v>0.2</v>
       </c>
       <c r="E163" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>7.3</v>
+        <v>20.9</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.2</v>
+        <v>11</v>
       </c>
       <c r="E164" t="n">
-        <v>7.5</v>
+        <v>9.9</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>-17.1</v>
+        <v>17.1</v>
       </c>
       <c r="D165" t="n">
-        <v>-24.6</v>
+        <v>7.4</v>
       </c>
       <c r="E165" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>7.1</v>
+        <v>17.1</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.2</v>
+        <v>7.8</v>
       </c>
       <c r="E166" t="n">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>6.9</v>
+        <v>11</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.2</v>
+        <v>1.9</v>
       </c>
       <c r="E167" t="n">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>-11.3</v>
+        <v>10.2</v>
       </c>
       <c r="D168" t="n">
-        <v>-18.2</v>
+        <v>1.9</v>
       </c>
       <c r="E168" t="n">
-        <v>7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -6324,390 +6373,390 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>-0.2</v>
+        <v>-15.2</v>
       </c>
       <c r="D169" t="n">
-        <v>-7.1</v>
+        <v>-22.8</v>
       </c>
       <c r="E169" t="n">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>-21</v>
+        <v>7.8</v>
       </c>
       <c r="D170" t="n">
-        <v>-27.4</v>
+        <v>0.2</v>
       </c>
       <c r="E170" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>-0.7</v>
+        <v>-15.5</v>
       </c>
       <c r="D171" t="n">
-        <v>-7.1</v>
+        <v>-22.8</v>
       </c>
       <c r="E171" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>-18.2</v>
+        <v>7.4</v>
       </c>
       <c r="D172" t="n">
-        <v>-24.6</v>
+        <v>0.2</v>
       </c>
       <c r="E172" t="n">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>-11.3</v>
+        <v>11</v>
       </c>
       <c r="D173" t="n">
-        <v>-17.1</v>
+        <v>4.1</v>
       </c>
       <c r="E173" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>-24.6</v>
+        <v>17.1</v>
       </c>
       <c r="D174" t="n">
-        <v>-29.6</v>
+        <v>10.2</v>
       </c>
       <c r="E174" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>-7.1</v>
+        <v>10.2</v>
       </c>
       <c r="D175" t="n">
-        <v>-11.3</v>
+        <v>4.1</v>
       </c>
       <c r="E175" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs lng)</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>7.3</v>
+        <v>17.1</v>
       </c>
       <c r="D176" t="n">
-        <v>3.1</v>
+        <v>11</v>
       </c>
       <c r="E176" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="D177" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="E177" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.7</v>
+        <v>1.9</v>
       </c>
       <c r="E178" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>-17.1</v>
+        <v>11</v>
       </c>
       <c r="D179" t="n">
-        <v>-21</v>
+        <v>5.6</v>
       </c>
       <c r="E179" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>6.9</v>
+        <v>-15.2</v>
       </c>
       <c r="D180" t="n">
-        <v>3.1</v>
+        <v>-20.6</v>
       </c>
       <c r="E180" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>-21</v>
+        <v>5.6</v>
       </c>
       <c r="D181" t="n">
-        <v>-24.6</v>
+        <v>0.2</v>
       </c>
       <c r="E181" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>3.1</v>
+        <v>-15.5</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.2</v>
+        <v>-20.6</v>
       </c>
       <c r="E182" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>-24.6</v>
+        <v>10.2</v>
       </c>
       <c r="D183" t="n">
-        <v>-27.4</v>
+        <v>5.6</v>
       </c>
       <c r="E183" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -6719,43 +6768,43 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>-18.2</v>
+        <v>-15.2</v>
       </c>
       <c r="D184" t="n">
-        <v>-21</v>
+        <v>-19.3</v>
       </c>
       <c r="E184" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
           <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>FRO</t>
-        </is>
-      </c>
       <c r="C185" t="n">
-        <v>-27.4</v>
+        <v>-18.9</v>
       </c>
       <c r="D185" t="n">
-        <v>-29.6</v>
+        <v>-22.8</v>
       </c>
       <c r="E185" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -6766,78 +6815,78 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>26.7</v>
+        <v>-15.5</v>
       </c>
       <c r="D186" t="n">
-        <v>25</v>
+        <v>-19.3</v>
       </c>
       <c r="E186" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>-17.1</v>
+        <v>4.1</v>
       </c>
       <c r="D187" t="n">
-        <v>-18.2</v>
+        <v>0.2</v>
       </c>
       <c r="E187" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>-0.2</v>
+        <v>20.9</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.7</v>
+        <v>17.1</v>
       </c>
       <c r="E188" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -6849,73 +6898,593 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="D189" t="n">
-        <v>6.9</v>
+        <v>4.1</v>
       </c>
       <c r="E189" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>7.3</v>
+        <v>-15.2</v>
       </c>
       <c r="D190" t="n">
-        <v>7.1</v>
+        <v>-18.9</v>
       </c>
       <c r="E190" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E191" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>CMBT (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
           <t>GSL</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>TNK</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="D191" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E191" t="n">
+      <c r="C192" t="n">
+        <v>11</v>
+      </c>
+      <c r="D192" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E192" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="D193" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="E193" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="D194" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="E194" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>TEN (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="D195" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="E195" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D196" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E196" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs lng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>CMBT (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>11</v>
+      </c>
+      <c r="D197" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E197" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D198" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E198" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs containerships)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D199" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="D200" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="E200" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D201" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="D203" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D204" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D205" t="n">
         <v>0.2</v>
       </c>
-      <c r="F191" t="inlineStr">
+      <c r="E205" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D206" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="D207" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F207" t="inlineStr">
         <is>
           <t>MIXED SECTOR (containerships vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>CMBT (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>11</v>
+      </c>
+      <c r="D208" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="D209" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs containerships)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D210" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="D211" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -723,28 +723,28 @@
         <v>14.1</v>
       </c>
       <c r="E6" t="n">
-        <v>21.52</v>
+        <v>21.51</v>
       </c>
       <c r="F6" t="n">
-        <v>16.15</v>
+        <v>16.13</v>
       </c>
       <c r="G6" t="n">
-        <v>10.84</v>
+        <v>10.82</v>
       </c>
       <c r="H6" t="n">
-        <v>8.82</v>
+        <v>8.81</v>
       </c>
       <c r="I6" t="n">
-        <v>15.66</v>
+        <v>15.64</v>
       </c>
       <c r="J6" t="n">
         <v>52.6</v>
       </c>
       <c r="K6" t="n">
-        <v>-37.4</v>
+        <v>-37.5</v>
       </c>
       <c r="L6" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1653,28 +1653,28 @@
         <v>17.47</v>
       </c>
       <c r="E2" t="n">
-        <v>25.32</v>
+        <v>24.44</v>
       </c>
       <c r="F2" t="n">
-        <v>21.48</v>
+        <v>20.76</v>
       </c>
       <c r="G2" t="n">
-        <v>19.54</v>
+        <v>18.93</v>
       </c>
       <c r="H2" t="n">
-        <v>17.25</v>
+        <v>16.69</v>
       </c>
       <c r="I2" t="n">
-        <v>21.13</v>
+        <v>20.43</v>
       </c>
       <c r="J2" t="n">
-        <v>44.9</v>
+        <v>39.9</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.2</v>
+        <v>-4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>20.9</v>
+        <v>16.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1699,31 +1699,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.57</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="n">
-        <v>32.13</v>
+        <v>32.75</v>
       </c>
       <c r="F3" t="n">
-        <v>26.11</v>
+        <v>26.6</v>
       </c>
       <c r="G3" t="n">
-        <v>22.46</v>
+        <v>23.61</v>
       </c>
       <c r="H3" t="n">
-        <v>19.52</v>
+        <v>19.89</v>
       </c>
       <c r="I3" t="n">
-        <v>25.41</v>
+        <v>26.07</v>
       </c>
       <c r="J3" t="n">
-        <v>36.3</v>
+        <v>34.2</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.2</v>
+        <v>-18.5</v>
       </c>
       <c r="L3" t="n">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1748,35 +1748,35 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24.4</v>
+        <v>23.57</v>
       </c>
       <c r="E4" t="n">
-        <v>32.39</v>
+        <v>30.38</v>
       </c>
       <c r="F4" t="n">
-        <v>26.28</v>
+        <v>24.68</v>
       </c>
       <c r="G4" t="n">
-        <v>23.31</v>
+        <v>21.25</v>
       </c>
       <c r="H4" t="n">
-        <v>19.63</v>
+        <v>18.41</v>
       </c>
       <c r="I4" t="n">
-        <v>25.76</v>
+        <v>24.02</v>
       </c>
       <c r="J4" t="n">
-        <v>32.7</v>
+        <v>28.9</v>
       </c>
       <c r="K4" t="n">
-        <v>-19.6</v>
+        <v>-21.9</v>
       </c>
       <c r="L4" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
     </row>
@@ -2317,104 +2317,104 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>76.8</v>
+        <v>102.4</v>
       </c>
       <c r="D13" t="n">
-        <v>-22.8</v>
+        <v>1.9</v>
       </c>
       <c r="E13" t="n">
-        <v>99.7</v>
+        <v>100.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>102.4</v>
+        <v>76.8</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1</v>
+        <v>-22.8</v>
       </c>
       <c r="E14" t="n">
-        <v>98.3</v>
+        <v>99.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>76.8</v>
+        <v>102.4</v>
       </c>
       <c r="D15" t="n">
-        <v>-20.6</v>
+        <v>4.1</v>
       </c>
       <c r="E15" t="n">
-        <v>97.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>102.4</v>
+        <v>76.8</v>
       </c>
       <c r="D16" t="n">
-        <v>5.6</v>
+        <v>-20.6</v>
       </c>
       <c r="E16" t="n">
-        <v>96.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2504,21 +2504,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>102.4</v>
       </c>
       <c r="D20" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="E20" t="n">
-        <v>94.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -2530,21 +2530,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>102.4</v>
       </c>
       <c r="D21" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="E21" t="n">
-        <v>94.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
@@ -2719,10 +2719,10 @@
         <v>102.4</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="E28" t="n">
-        <v>91.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2790,43 +2790,43 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>102.4</v>
       </c>
       <c r="D31" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="E31" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>31.1</v>
+        <v>102.4</v>
       </c>
       <c r="D32" t="n">
-        <v>-52.5</v>
+        <v>17.1</v>
       </c>
       <c r="E32" t="n">
-        <v>83.59999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2837,26 +2837,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>102.4</v>
+        <v>31.1</v>
       </c>
       <c r="D33" t="n">
-        <v>20.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E33" t="n">
-        <v>81.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2915,26 +2915,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>20.9</v>
+        <v>76.8</v>
       </c>
       <c r="D36" t="n">
-        <v>-52.5</v>
+        <v>1.9</v>
       </c>
       <c r="E36" t="n">
-        <v>73.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3019,26 +3019,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="E40" t="n">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -3071,104 +3071,104 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>17.1</v>
+        <v>76.8</v>
       </c>
       <c r="D42" t="n">
-        <v>-52.5</v>
+        <v>6.9</v>
       </c>
       <c r="E42" t="n">
-        <v>69.5</v>
+        <v>70</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>76.8</v>
+        <v>17.1</v>
       </c>
       <c r="D43" t="n">
-        <v>7.4</v>
+        <v>-52.5</v>
       </c>
       <c r="E43" t="n">
-        <v>69.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>73.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="D44" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="E44" t="n">
-        <v>69.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>76.8</v>
+        <v>16.9</v>
       </c>
       <c r="D45" t="n">
-        <v>7.8</v>
+        <v>-52.5</v>
       </c>
       <c r="E45" t="n">
-        <v>69</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3180,21 +3180,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="E46" t="n">
-        <v>67.8</v>
+        <v>69.3</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3232,73 +3232,73 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="E48" t="n">
-        <v>65.90000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="E49" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>73.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="D50" t="n">
-        <v>7.8</v>
+        <v>10.9</v>
       </c>
       <c r="E50" t="n">
-        <v>65.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="D51" t="n">
         <v>-52.5</v>
       </c>
       <c r="E51" t="n">
-        <v>63.5</v>
+        <v>63.4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3395,10 +3395,10 @@
         <v>73.40000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="E54" t="n">
-        <v>62.3</v>
+        <v>62.4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3409,26 +3409,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7.8</v>
+        <v>76.8</v>
       </c>
       <c r="D55" t="n">
-        <v>-52.5</v>
+        <v>16.9</v>
       </c>
       <c r="E55" t="n">
-        <v>60.3</v>
+        <v>59.9</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3496,13 +3496,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="D58" t="n">
         <v>-52.5</v>
       </c>
       <c r="E58" t="n">
-        <v>58</v>
+        <v>59.3</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3544,47 +3544,47 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="E60" t="n">
-        <v>56.3</v>
+        <v>56.4</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>20.9</v>
+        <v>17.1</v>
       </c>
       <c r="E61" t="n">
-        <v>55.9</v>
+        <v>56.3</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -3617,78 +3617,78 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>31.1</v>
+        <v>1.9</v>
       </c>
       <c r="D63" t="n">
-        <v>-22.8</v>
+        <v>-52.5</v>
       </c>
       <c r="E63" t="n">
-        <v>54</v>
+        <v>54.4</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.2</v>
+        <v>31.1</v>
       </c>
       <c r="D64" t="n">
-        <v>-52.5</v>
+        <v>-22.8</v>
       </c>
       <c r="E64" t="n">
-        <v>52.6</v>
+        <v>54</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>73.40000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D65" t="n">
-        <v>20.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E65" t="n">
-        <v>52.4</v>
+        <v>52.6</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -3851,52 +3851,52 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>20.9</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D72" t="n">
-        <v>-22.8</v>
+        <v>31.1</v>
       </c>
       <c r="E72" t="n">
-        <v>43.8</v>
+        <v>42.2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>73.40000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="D73" t="n">
-        <v>31.1</v>
+        <v>-22.8</v>
       </c>
       <c r="E73" t="n">
-        <v>42.2</v>
+        <v>39.9</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3908,121 +3908,121 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>20.9</v>
+        <v>16.9</v>
       </c>
       <c r="D74" t="n">
-        <v>-20.6</v>
+        <v>-22.8</v>
       </c>
       <c r="E74" t="n">
-        <v>41.6</v>
+        <v>39.8</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>20.9</v>
+        <v>17.1</v>
       </c>
       <c r="D75" t="n">
-        <v>-19.3</v>
+        <v>-20.6</v>
       </c>
       <c r="E75" t="n">
-        <v>40.3</v>
+        <v>37.7</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="D76" t="n">
-        <v>-22.8</v>
+        <v>-20.6</v>
       </c>
       <c r="E76" t="n">
-        <v>39.9</v>
+        <v>37.6</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>20.9</v>
+        <v>-15.2</v>
       </c>
       <c r="D77" t="n">
-        <v>-18.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E77" t="n">
-        <v>39.8</v>
+        <v>37.3</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>17.1</v>
+        <v>-15.5</v>
       </c>
       <c r="D78" t="n">
-        <v>-20.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E78" t="n">
-        <v>37.7</v>
+        <v>37</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4033,52 +4033,52 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-15.2</v>
+        <v>17.1</v>
       </c>
       <c r="D79" t="n">
-        <v>-52.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E79" t="n">
-        <v>37.3</v>
+        <v>36.4</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-15.5</v>
+        <v>16.9</v>
       </c>
       <c r="D80" t="n">
-        <v>-52.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E80" t="n">
-        <v>37</v>
+        <v>36.3</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
@@ -4090,21 +4090,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>17.1</v>
       </c>
       <c r="D81" t="n">
-        <v>-19.3</v>
+        <v>-18.9</v>
       </c>
       <c r="E81" t="n">
-        <v>36.4</v>
+        <v>35.9</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -4116,17 +4116,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>20.9</v>
+        <v>16.9</v>
       </c>
       <c r="D82" t="n">
-        <v>-15.5</v>
+        <v>-18.9</v>
       </c>
       <c r="E82" t="n">
-        <v>36.4</v>
+        <v>35.8</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4137,48 +4137,48 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>20.9</v>
+        <v>10.9</v>
       </c>
       <c r="D83" t="n">
-        <v>-15.2</v>
+        <v>-22.8</v>
       </c>
       <c r="E83" t="n">
-        <v>36.1</v>
+        <v>33.8</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>17.1</v>
+        <v>-18.9</v>
       </c>
       <c r="D84" t="n">
-        <v>-18.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E84" t="n">
-        <v>35.9</v>
+        <v>33.6</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4198,24 +4198,24 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>11</v>
+        <v>10.2</v>
       </c>
       <c r="D85" t="n">
         <v>-22.8</v>
       </c>
       <c r="E85" t="n">
-        <v>33.9</v>
+        <v>33.1</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4224,69 +4224,69 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-18.9</v>
+        <v>-19.3</v>
       </c>
       <c r="D86" t="n">
         <v>-52.5</v>
       </c>
       <c r="E86" t="n">
-        <v>33.6</v>
+        <v>33.1</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10.2</v>
+        <v>17.1</v>
       </c>
       <c r="D87" t="n">
-        <v>-22.8</v>
+        <v>-15.5</v>
       </c>
       <c r="E87" t="n">
-        <v>33.1</v>
+        <v>32.5</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-19.3</v>
+        <v>16.9</v>
       </c>
       <c r="D88" t="n">
-        <v>-52.5</v>
+        <v>-15.5</v>
       </c>
       <c r="E88" t="n">
-        <v>33.1</v>
+        <v>32.4</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -4298,28 +4298,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>17.1</v>
       </c>
       <c r="D89" t="n">
-        <v>-15.5</v>
+        <v>-15.2</v>
       </c>
       <c r="E89" t="n">
-        <v>32.5</v>
+        <v>32.2</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4328,17 +4328,17 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="D90" t="n">
         <v>-15.2</v>
       </c>
       <c r="E90" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -4380,13 +4380,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="D92" t="n">
         <v>-20.6</v>
       </c>
       <c r="E92" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4458,17 +4458,17 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D95" t="n">
         <v>-22.8</v>
       </c>
       <c r="E95" t="n">
-        <v>30.7</v>
+        <v>30.3</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4484,13 +4484,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="D96" t="n">
         <v>-19.3</v>
       </c>
       <c r="E96" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4501,52 +4501,52 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>7.4</v>
+        <v>10.9</v>
       </c>
       <c r="D97" t="n">
-        <v>-22.8</v>
+        <v>-18.9</v>
       </c>
       <c r="E97" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>11</v>
+        <v>6.9</v>
       </c>
       <c r="D98" t="n">
-        <v>-18.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E98" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4631,85 +4631,85 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10.2</v>
+        <v>31.1</v>
       </c>
       <c r="D102" t="n">
-        <v>-18.9</v>
+        <v>1.9</v>
       </c>
       <c r="E102" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>102.4</v>
+        <v>10.2</v>
       </c>
       <c r="D103" t="n">
-        <v>73.40000000000001</v>
+        <v>-18.9</v>
       </c>
       <c r="E103" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5.6</v>
+        <v>102.4</v>
       </c>
       <c r="D104" t="n">
-        <v>-22.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E104" t="n">
-        <v>28.4</v>
+        <v>29</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4718,24 +4718,24 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D105" t="n">
         <v>-20.6</v>
       </c>
       <c r="E105" t="n">
-        <v>28.4</v>
+        <v>28</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4744,121 +4744,121 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="D106" t="n">
         <v>-20.6</v>
       </c>
       <c r="E106" t="n">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>7.8</v>
+        <v>31.1</v>
       </c>
       <c r="D107" t="n">
-        <v>-19.3</v>
+        <v>4.1</v>
       </c>
       <c r="E107" t="n">
         <v>27.1</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>31.1</v>
+        <v>4.1</v>
       </c>
       <c r="D108" t="n">
-        <v>4.1</v>
+        <v>-22.8</v>
       </c>
       <c r="E108" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="D109" t="n">
-        <v>-22.8</v>
+        <v>-19.3</v>
       </c>
       <c r="E109" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>7.8</v>
+        <v>10.9</v>
       </c>
       <c r="D110" t="n">
-        <v>-18.9</v>
+        <v>-15.5</v>
       </c>
       <c r="E110" t="n">
-        <v>26.7</v>
+        <v>26.4</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4870,359 +4870,359 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>7.4</v>
       </c>
       <c r="D111" t="n">
-        <v>-19.3</v>
+        <v>-18.9</v>
       </c>
       <c r="E111" t="n">
-        <v>26.7</v>
+        <v>26.3</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>11</v>
+        <v>6.9</v>
       </c>
       <c r="D112" t="n">
-        <v>-15.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E112" t="n">
-        <v>26.5</v>
+        <v>26.2</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>7.4</v>
+        <v>10.9</v>
       </c>
       <c r="D113" t="n">
-        <v>-18.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E113" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>5.6</v>
+        <v>10.2</v>
       </c>
       <c r="D114" t="n">
-        <v>-20.6</v>
+        <v>-15.5</v>
       </c>
       <c r="E114" t="n">
-        <v>26.2</v>
+        <v>25.7</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>11</v>
+        <v>6.9</v>
       </c>
       <c r="D115" t="n">
-        <v>-15.2</v>
+        <v>-18.9</v>
       </c>
       <c r="E115" t="n">
-        <v>26.2</v>
+        <v>25.7</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>10.2</v>
+        <v>102.4</v>
       </c>
       <c r="D116" t="n">
-        <v>-15.5</v>
+        <v>76.8</v>
       </c>
       <c r="E116" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>31.1</v>
+        <v>10.2</v>
       </c>
       <c r="D117" t="n">
-        <v>5.6</v>
+        <v>-15.2</v>
       </c>
       <c r="E117" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>102.4</v>
+        <v>1.9</v>
       </c>
       <c r="D118" t="n">
-        <v>76.8</v>
+        <v>-22.8</v>
       </c>
       <c r="E118" t="n">
-        <v>25.6</v>
+        <v>24.8</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>10.2</v>
+        <v>1.9</v>
       </c>
       <c r="D119" t="n">
-        <v>-15.2</v>
+        <v>-22.8</v>
       </c>
       <c r="E119" t="n">
-        <v>25.4</v>
+        <v>24.8</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="D120" t="n">
-        <v>-19.3</v>
+        <v>-20.6</v>
       </c>
       <c r="E120" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1.9</v>
+        <v>31.1</v>
       </c>
       <c r="D121" t="n">
-        <v>-22.8</v>
+        <v>6.9</v>
       </c>
       <c r="E121" t="n">
-        <v>24.8</v>
+        <v>24.3</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4.1</v>
+        <v>31.1</v>
       </c>
       <c r="D122" t="n">
-        <v>-20.6</v>
+        <v>7.4</v>
       </c>
       <c r="E122" t="n">
-        <v>24.7</v>
+        <v>23.7</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="D123" t="n">
-        <v>-18.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E123" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>31.1</v>
+        <v>0.2</v>
       </c>
       <c r="D124" t="n">
-        <v>7.4</v>
+        <v>-22.8</v>
       </c>
       <c r="E124" t="n">
-        <v>23.7</v>
+        <v>23</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -5234,28 +5234,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>4.1</v>
       </c>
       <c r="D125" t="n">
-        <v>-19.3</v>
+        <v>-18.9</v>
       </c>
       <c r="E125" t="n">
-        <v>23.4</v>
+        <v>22.9</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5264,69 +5264,69 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D126" t="n">
         <v>-15.5</v>
       </c>
       <c r="E126" t="n">
-        <v>23.3</v>
+        <v>22.9</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>31.1</v>
+        <v>7.4</v>
       </c>
       <c r="D127" t="n">
-        <v>7.8</v>
+        <v>-15.2</v>
       </c>
       <c r="E127" t="n">
-        <v>23.3</v>
+        <v>22.6</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="D128" t="n">
-        <v>-22.8</v>
+        <v>-20.6</v>
       </c>
       <c r="E128" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -5338,99 +5338,99 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>7.8</v>
+        <v>1.9</v>
       </c>
       <c r="D129" t="n">
-        <v>-15.2</v>
+        <v>-20.6</v>
       </c>
       <c r="E129" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
       <c r="D130" t="n">
-        <v>-18.9</v>
+        <v>-15.5</v>
       </c>
       <c r="E130" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="D131" t="n">
-        <v>-15.5</v>
+        <v>-15.2</v>
       </c>
       <c r="E131" t="n">
-        <v>22.9</v>
+        <v>22</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
       <c r="D132" t="n">
-        <v>-15.2</v>
+        <v>-19.3</v>
       </c>
       <c r="E132" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
@@ -5442,106 +5442,106 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C133" t="n">
         <v>1.9</v>
       </c>
       <c r="D133" t="n">
-        <v>-20.6</v>
+        <v>-19.3</v>
       </c>
       <c r="E133" t="n">
-        <v>22.5</v>
+        <v>21.2</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1.9</v>
+        <v>31.1</v>
       </c>
       <c r="D134" t="n">
-        <v>-19.3</v>
+        <v>10.2</v>
       </c>
       <c r="E134" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="D135" t="n">
-        <v>-15.5</v>
+        <v>-18.9</v>
       </c>
       <c r="E135" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>31.1</v>
+        <v>0.2</v>
       </c>
       <c r="D136" t="n">
-        <v>10.2</v>
+        <v>-20.6</v>
       </c>
       <c r="E136" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5560,237 +5560,237 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0.2</v>
+        <v>31.1</v>
       </c>
       <c r="D138" t="n">
-        <v>-20.6</v>
+        <v>10.9</v>
       </c>
       <c r="E138" t="n">
-        <v>20.8</v>
+        <v>20.2</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>20.9</v>
+        <v>4.1</v>
       </c>
       <c r="D139" t="n">
-        <v>0.2</v>
+        <v>-15.5</v>
       </c>
       <c r="E139" t="n">
-        <v>20.8</v>
+        <v>19.5</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>5.6</v>
+        <v>0.2</v>
       </c>
       <c r="D140" t="n">
-        <v>-15.2</v>
+        <v>-19.3</v>
       </c>
       <c r="E140" t="n">
-        <v>20.8</v>
+        <v>19.5</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>31.1</v>
+        <v>4.1</v>
       </c>
       <c r="D141" t="n">
-        <v>11</v>
+        <v>-15.2</v>
       </c>
       <c r="E141" t="n">
-        <v>20.1</v>
+        <v>19.2</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="D142" t="n">
-        <v>-15.5</v>
+        <v>-18.9</v>
       </c>
       <c r="E142" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="D143" t="n">
-        <v>-19.3</v>
+        <v>-15.5</v>
       </c>
       <c r="E143" t="n">
-        <v>19.5</v>
+        <v>17.4</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="D144" t="n">
-        <v>-15.2</v>
+        <v>-15.5</v>
       </c>
       <c r="E144" t="n">
-        <v>19.2</v>
+        <v>17.4</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="D145" t="n">
-        <v>-18.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E145" t="n">
-        <v>19</v>
+        <v>17.1</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>20.9</v>
+        <v>1.9</v>
       </c>
       <c r="D146" t="n">
-        <v>1.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E146" t="n">
-        <v>19</v>
+        <v>17.1</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -5801,156 +5801,156 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1.9</v>
+        <v>17.1</v>
       </c>
       <c r="D147" t="n">
-        <v>-15.5</v>
+        <v>0.2</v>
       </c>
       <c r="E147" t="n">
-        <v>17.4</v>
+        <v>16.9</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1.9</v>
+        <v>16.9</v>
       </c>
       <c r="D148" t="n">
-        <v>-15.2</v>
+        <v>0.2</v>
       </c>
       <c r="E148" t="n">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>17.1</v>
+        <v>0.2</v>
       </c>
       <c r="D149" t="n">
-        <v>0.2</v>
+        <v>-15.5</v>
       </c>
       <c r="E149" t="n">
-        <v>16.9</v>
+        <v>15.7</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>20.9</v>
+        <v>0.2</v>
       </c>
       <c r="D150" t="n">
-        <v>4.1</v>
+        <v>-15.2</v>
       </c>
       <c r="E150" t="n">
-        <v>16.9</v>
+        <v>15.4</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.2</v>
+        <v>17.1</v>
       </c>
       <c r="D151" t="n">
-        <v>-15.5</v>
+        <v>1.9</v>
       </c>
       <c r="E151" t="n">
-        <v>15.7</v>
+        <v>15.2</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0.2</v>
+        <v>17.1</v>
       </c>
       <c r="D152" t="n">
-        <v>-15.2</v>
+        <v>1.9</v>
       </c>
       <c r="E152" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -5962,47 +5962,47 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>20.9</v>
+        <v>16.9</v>
       </c>
       <c r="D153" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="E153" t="n">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="D154" t="n">
         <v>1.9</v>
       </c>
       <c r="E154" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -6014,80 +6014,80 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C155" t="n">
         <v>31.1</v>
       </c>
       <c r="D155" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="E155" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>20.9</v>
+        <v>31.1</v>
       </c>
       <c r="D156" t="n">
-        <v>7.4</v>
+        <v>17.1</v>
       </c>
       <c r="E156" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>20.9</v>
+        <v>17.1</v>
       </c>
       <c r="D157" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="E157" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6096,69 +6096,69 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="D158" t="n">
         <v>4.1</v>
       </c>
       <c r="E158" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>17.1</v>
+        <v>10.9</v>
       </c>
       <c r="D159" t="n">
-        <v>5.6</v>
+        <v>0.2</v>
       </c>
       <c r="E159" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>11</v>
+        <v>17.1</v>
       </c>
       <c r="D160" t="n">
-        <v>0.2</v>
+        <v>6.9</v>
       </c>
       <c r="E160" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -6170,73 +6170,73 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>20.9</v>
+        <v>16.9</v>
       </c>
       <c r="D161" t="n">
-        <v>10.2</v>
+        <v>6.9</v>
       </c>
       <c r="E161" t="n">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>31.1</v>
+        <v>10.2</v>
       </c>
       <c r="D162" t="n">
-        <v>20.9</v>
+        <v>0.2</v>
       </c>
       <c r="E162" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>10.2</v>
+        <v>17.1</v>
       </c>
       <c r="D163" t="n">
-        <v>0.2</v>
+        <v>7.4</v>
       </c>
       <c r="E163" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
@@ -6248,54 +6248,54 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>20.9</v>
+        <v>16.9</v>
       </c>
       <c r="D164" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="E164" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>17.1</v>
+        <v>10.9</v>
       </c>
       <c r="D165" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
       <c r="E165" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6304,24 +6304,24 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>17.1</v>
+        <v>10.9</v>
       </c>
       <c r="D166" t="n">
-        <v>7.8</v>
+        <v>1.9</v>
       </c>
       <c r="E166" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6330,17 +6330,17 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>11</v>
+        <v>10.2</v>
       </c>
       <c r="D167" t="n">
         <v>1.9</v>
       </c>
       <c r="E167" t="n">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -6399,78 +6399,78 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>7.8</v>
+        <v>-15.5</v>
       </c>
       <c r="D170" t="n">
-        <v>0.2</v>
+        <v>-22.8</v>
       </c>
       <c r="E170" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>-15.5</v>
+        <v>7.4</v>
       </c>
       <c r="D171" t="n">
-        <v>-22.8</v>
+        <v>0.2</v>
       </c>
       <c r="E171" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>7.4</v>
+        <v>17.1</v>
       </c>
       <c r="D172" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="E172" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="D173" t="n">
         <v>4.1</v>
       </c>
       <c r="E173" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6512,199 +6512,199 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="D174" t="n">
         <v>10.2</v>
       </c>
       <c r="E174" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>10.2</v>
+        <v>6.9</v>
       </c>
       <c r="D175" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="E175" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>17.1</v>
+        <v>10.2</v>
       </c>
       <c r="D176" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="E176" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs lng)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>7.8</v>
+        <v>17.1</v>
       </c>
       <c r="D177" t="n">
-        <v>1.9</v>
+        <v>10.9</v>
       </c>
       <c r="E177" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>7.4</v>
+        <v>16.9</v>
       </c>
       <c r="D178" t="n">
-        <v>1.9</v>
+        <v>10.9</v>
       </c>
       <c r="E178" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="D179" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="E179" t="n">
         <v>5.5</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>-15.2</v>
+        <v>7.4</v>
       </c>
       <c r="D180" t="n">
-        <v>-20.6</v>
+        <v>1.9</v>
       </c>
       <c r="E180" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>5.6</v>
+        <v>-15.2</v>
       </c>
       <c r="D181" t="n">
-        <v>0.2</v>
+        <v>-20.6</v>
       </c>
       <c r="E181" t="n">
         <v>5.4</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -6737,182 +6737,182 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>10.2</v>
+        <v>6.9</v>
       </c>
       <c r="D183" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="E183" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>-15.2</v>
+        <v>6.9</v>
       </c>
       <c r="D184" t="n">
-        <v>-19.3</v>
+        <v>1.9</v>
       </c>
       <c r="E184" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>-18.9</v>
+        <v>-15.2</v>
       </c>
       <c r="D185" t="n">
-        <v>-22.8</v>
+        <v>-19.3</v>
       </c>
       <c r="E185" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>-15.5</v>
+        <v>10.9</v>
       </c>
       <c r="D186" t="n">
-        <v>-19.3</v>
+        <v>6.9</v>
       </c>
       <c r="E186" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>4.1</v>
+        <v>-18.9</v>
       </c>
       <c r="D187" t="n">
-        <v>0.2</v>
+        <v>-22.8</v>
       </c>
       <c r="E187" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>20.9</v>
+        <v>-15.5</v>
       </c>
       <c r="D188" t="n">
-        <v>17.1</v>
+        <v>-19.3</v>
       </c>
       <c r="E188" t="n">
         <v>3.9</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="D189" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="E189" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -6945,26 +6945,26 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>5.6</v>
+        <v>-19.3</v>
       </c>
       <c r="D191" t="n">
-        <v>1.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E191" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -6980,13 +6980,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="D192" t="n">
         <v>7.4</v>
       </c>
       <c r="E192" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -6997,282 +6997,282 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>-19.3</v>
+        <v>-15.5</v>
       </c>
       <c r="D193" t="n">
-        <v>-22.8</v>
+        <v>-18.9</v>
       </c>
       <c r="E193" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>-15.5</v>
+        <v>76.8</v>
       </c>
       <c r="D194" t="n">
-        <v>-18.9</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E194" t="n">
         <v>3.4</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>76.8</v>
+        <v>7.4</v>
       </c>
       <c r="D195" t="n">
-        <v>73.40000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="E195" t="n">
         <v>3.4</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs lng)</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>7.4</v>
+        <v>10.2</v>
       </c>
       <c r="D196" t="n">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
       <c r="E196" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs lng)</t>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>11</v>
+        <v>10.2</v>
       </c>
       <c r="D197" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="E197" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>10.2</v>
+        <v>6.9</v>
       </c>
       <c r="D198" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="E198" t="n">
         <v>2.8</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>10.2</v>
+        <v>-20.6</v>
       </c>
       <c r="D199" t="n">
-        <v>7.8</v>
+        <v>-22.8</v>
       </c>
       <c r="E199" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>-20.6</v>
+        <v>4.1</v>
       </c>
       <c r="D200" t="n">
-        <v>-22.8</v>
+        <v>1.9</v>
       </c>
       <c r="E200" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>SBLK</t>
-        </is>
-      </c>
       <c r="C201" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="D201" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="E201" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>4.1</v>
+        <v>-18.9</v>
       </c>
       <c r="D202" t="n">
-        <v>1.9</v>
+        <v>-20.6</v>
       </c>
       <c r="E202" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>-18.9</v>
+        <v>1.9</v>
       </c>
       <c r="D203" t="n">
-        <v>-20.6</v>
+        <v>0.2</v>
       </c>
       <c r="E203" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -7283,208 +7283,208 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
       <c r="D204" t="n">
-        <v>5.6</v>
+        <v>0.2</v>
       </c>
       <c r="E204" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1.9</v>
+        <v>-19.3</v>
       </c>
       <c r="D205" t="n">
-        <v>0.2</v>
+        <v>-20.6</v>
       </c>
       <c r="E205" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>5.6</v>
+        <v>10.9</v>
       </c>
       <c r="D206" t="n">
-        <v>4.1</v>
+        <v>10.2</v>
       </c>
       <c r="E206" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>-19.3</v>
+        <v>7.4</v>
       </c>
       <c r="D207" t="n">
-        <v>-20.6</v>
+        <v>6.9</v>
       </c>
       <c r="E207" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>11</v>
+        <v>-18.9</v>
       </c>
       <c r="D208" t="n">
-        <v>10.2</v>
+        <v>-19.3</v>
       </c>
       <c r="E208" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>-18.9</v>
+        <v>-15.2</v>
       </c>
       <c r="D209" t="n">
-        <v>-19.3</v>
+        <v>-15.5</v>
       </c>
       <c r="E209" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>7.8</v>
+        <v>17.1</v>
       </c>
       <c r="D210" t="n">
-        <v>7.4</v>
+        <v>16.9</v>
       </c>
       <c r="E210" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>-15.2</v>
+        <v>1.9</v>
       </c>
       <c r="D211" t="n">
-        <v>-15.5</v>
+        <v>1.9</v>
       </c>
       <c r="E211" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -1548,7 +1548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1636,7 +1636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1650,31 +1650,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.47</v>
+        <v>6.39</v>
       </c>
       <c r="E2" t="n">
-        <v>24.44</v>
+        <v>12.14</v>
       </c>
       <c r="F2" t="n">
-        <v>20.76</v>
+        <v>9.65</v>
       </c>
       <c r="G2" t="n">
-        <v>18.93</v>
+        <v>8.65</v>
       </c>
       <c r="H2" t="n">
-        <v>16.69</v>
+        <v>7.16</v>
       </c>
       <c r="I2" t="n">
-        <v>20.43</v>
+        <v>9.52</v>
       </c>
       <c r="J2" t="n">
-        <v>39.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.5</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>16.9</v>
+        <v>49</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1699,31 +1699,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>17.47</v>
       </c>
       <c r="E3" t="n">
-        <v>32.75</v>
+        <v>24.44</v>
       </c>
       <c r="F3" t="n">
-        <v>26.6</v>
+        <v>20.76</v>
       </c>
       <c r="G3" t="n">
-        <v>23.61</v>
+        <v>18.93</v>
       </c>
       <c r="H3" t="n">
-        <v>19.89</v>
+        <v>16.69</v>
       </c>
       <c r="I3" t="n">
-        <v>26.07</v>
+        <v>20.43</v>
       </c>
       <c r="J3" t="n">
-        <v>34.2</v>
+        <v>39.9</v>
       </c>
       <c r="K3" t="n">
-        <v>-18.5</v>
+        <v>-4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1734,47 +1734,96 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dry_bulk</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="H4" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="I4" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>whole-company</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>dry_bulk</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>23.57</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>30.38</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>24.68</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G5" t="n">
         <v>21.25</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H5" t="n">
         <v>18.41</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I5" t="n">
         <v>24.02</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J5" t="n">
         <v>28.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K5" t="n">
         <v>-21.9</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L5" t="n">
         <v>1.9</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>HOLD (fairly valued)</t>
         </is>
@@ -1985,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F211"/>
+  <dimension ref="A1:F232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2291,26 +2340,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>102.4</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>1.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E12" t="n">
-        <v>100.5</v>
+        <v>101.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2371,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2332,141 +2381,141 @@
         <v>1.9</v>
       </c>
       <c r="E13" t="n">
-        <v>100.4</v>
+        <v>100.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>76.8</v>
+        <v>102.4</v>
       </c>
       <c r="D14" t="n">
-        <v>-22.8</v>
+        <v>1.9</v>
       </c>
       <c r="E14" t="n">
-        <v>99.7</v>
+        <v>100.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>102.4</v>
+        <v>76.8</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1</v>
+        <v>-22.8</v>
       </c>
       <c r="E15" t="n">
-        <v>98.3</v>
+        <v>99.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>76.8</v>
+        <v>102.4</v>
       </c>
       <c r="D16" t="n">
-        <v>-20.6</v>
+        <v>4.1</v>
       </c>
       <c r="E16" t="n">
-        <v>97.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>73.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="D17" t="n">
-        <v>-22.8</v>
+        <v>-20.6</v>
       </c>
       <c r="E17" t="n">
-        <v>96.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>-19.3</v>
+        <v>-22.8</v>
       </c>
       <c r="E18" t="n">
-        <v>96.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2478,47 +2527,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>76.8</v>
       </c>
       <c r="D19" t="n">
-        <v>-18.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E19" t="n">
-        <v>95.7</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>102.4</v>
+        <v>76.8</v>
       </c>
       <c r="D20" t="n">
-        <v>6.9</v>
+        <v>-18.9</v>
       </c>
       <c r="E20" t="n">
-        <v>95.5</v>
+        <v>95.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2530,47 +2579,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>102.4</v>
       </c>
       <c r="D21" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="E21" t="n">
-        <v>94.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>73.40000000000001</v>
+        <v>102.4</v>
       </c>
       <c r="D22" t="n">
-        <v>-20.6</v>
+        <v>7.4</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
@@ -2582,177 +2631,177 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>-19.3</v>
+        <v>-20.6</v>
       </c>
       <c r="E23" t="n">
-        <v>92.7</v>
+        <v>94</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E24" t="n">
-        <v>92.3</v>
+        <v>92.7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>73.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="D25" t="n">
-        <v>-18.9</v>
+        <v>-15.5</v>
       </c>
       <c r="E25" t="n">
-        <v>92.2</v>
+        <v>92.3</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>102.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>10.2</v>
+        <v>-18.9</v>
       </c>
       <c r="E26" t="n">
         <v>92.2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>76.8</v>
+        <v>102.4</v>
       </c>
       <c r="D27" t="n">
-        <v>-15.2</v>
+        <v>10.2</v>
       </c>
       <c r="E27" t="n">
-        <v>92</v>
+        <v>92.2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>102.4</v>
+        <v>76.8</v>
       </c>
       <c r="D28" t="n">
-        <v>10.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E28" t="n">
-        <v>91.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>73.40000000000001</v>
+        <v>102.4</v>
       </c>
       <c r="D29" t="n">
-        <v>-15.5</v>
+        <v>10.9</v>
       </c>
       <c r="E29" t="n">
-        <v>88.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2764,47 +2813,47 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-15.2</v>
+        <v>-15.5</v>
       </c>
       <c r="E30" t="n">
-        <v>88.5</v>
+        <v>88.8</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>102.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>16.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E31" t="n">
-        <v>85.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -2816,43 +2865,43 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>102.4</v>
       </c>
       <c r="D32" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="E32" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>31.1</v>
+        <v>102.4</v>
       </c>
       <c r="D33" t="n">
-        <v>-52.5</v>
+        <v>17.1</v>
       </c>
       <c r="E33" t="n">
-        <v>83.59999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2863,26 +2912,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>76.8</v>
+        <v>31.1</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2</v>
+        <v>-52.5</v>
       </c>
       <c r="E34" t="n">
-        <v>76.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2894,17 +2943,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>76.8</v>
       </c>
       <c r="D35" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="E35" t="n">
-        <v>74.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2920,7 +2969,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2934,185 +2983,185 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>73.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="E37" t="n">
-        <v>73.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="E38" t="n">
-        <v>72.8</v>
+        <v>73.2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>73.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="D39" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="E39" t="n">
-        <v>71.5</v>
+        <v>72.8</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>73.40000000000001</v>
+        <v>49</v>
       </c>
       <c r="D40" t="n">
-        <v>1.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E40" t="n">
-        <v>71.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>102.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>31.1</v>
+        <v>1.9</v>
       </c>
       <c r="E41" t="n">
-        <v>71.2</v>
+        <v>71.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="E42" t="n">
-        <v>70</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>17.1</v>
+        <v>102.4</v>
       </c>
       <c r="D43" t="n">
-        <v>-52.5</v>
+        <v>31.1</v>
       </c>
       <c r="E43" t="n">
-        <v>69.5</v>
+        <v>71.2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3128,43 +3177,43 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>76.8</v>
       </c>
       <c r="D44" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="E44" t="n">
-        <v>69.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16.9</v>
+        <v>49</v>
       </c>
       <c r="D45" t="n">
-        <v>-52.5</v>
+        <v>-20.6</v>
       </c>
       <c r="E45" t="n">
-        <v>69.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3175,22 +3224,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>73.40000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="D46" t="n">
-        <v>4.1</v>
+        <v>-52.5</v>
       </c>
       <c r="E46" t="n">
-        <v>69.3</v>
+        <v>69.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3206,47 +3255,47 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>76.8</v>
       </c>
       <c r="D47" t="n">
-        <v>10.2</v>
+        <v>7.4</v>
       </c>
       <c r="E47" t="n">
-        <v>66.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>73.40000000000001</v>
+        <v>16.9</v>
       </c>
       <c r="D48" t="n">
-        <v>6.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E48" t="n">
-        <v>66.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3258,80 +3307,80 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="E49" t="n">
-        <v>65.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>76.8</v>
+        <v>49</v>
       </c>
       <c r="D50" t="n">
-        <v>10.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E50" t="n">
-        <v>65.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10.9</v>
+        <v>49</v>
       </c>
       <c r="D51" t="n">
-        <v>-52.5</v>
+        <v>-18.9</v>
       </c>
       <c r="E51" t="n">
-        <v>63.4</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3340,43 +3389,43 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>73.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="D52" t="n">
         <v>10.2</v>
       </c>
       <c r="E52" t="n">
-        <v>63.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>-52.5</v>
+        <v>6.9</v>
       </c>
       <c r="E53" t="n">
-        <v>62.7</v>
+        <v>66.5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -3388,21 +3437,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>10.9</v>
+        <v>7.4</v>
       </c>
       <c r="E54" t="n">
-        <v>62.4</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
@@ -3414,80 +3463,80 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>76.8</v>
       </c>
       <c r="D55" t="n">
-        <v>16.9</v>
+        <v>10.9</v>
       </c>
       <c r="E55" t="n">
-        <v>59.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7.4</v>
+        <v>49</v>
       </c>
       <c r="D56" t="n">
-        <v>-52.5</v>
+        <v>-15.5</v>
       </c>
       <c r="E56" t="n">
-        <v>59.9</v>
+        <v>64.5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>76.8</v>
+        <v>49</v>
       </c>
       <c r="D57" t="n">
-        <v>17.1</v>
+        <v>-15.2</v>
       </c>
       <c r="E57" t="n">
-        <v>59.8</v>
+        <v>64.2</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3496,69 +3545,69 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6.9</v>
+        <v>10.9</v>
       </c>
       <c r="D58" t="n">
         <v>-52.5</v>
       </c>
       <c r="E58" t="n">
-        <v>59.3</v>
+        <v>63.4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4.1</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>-52.5</v>
+        <v>10.2</v>
       </c>
       <c r="E59" t="n">
-        <v>56.5</v>
+        <v>63.2</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>73.40000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="D60" t="n">
-        <v>16.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E60" t="n">
-        <v>56.4</v>
+        <v>62.7</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -3570,54 +3619,54 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>17.1</v>
+        <v>10.9</v>
       </c>
       <c r="E61" t="n">
-        <v>56.3</v>
+        <v>62.4</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1.9</v>
+        <v>76.8</v>
       </c>
       <c r="D62" t="n">
-        <v>-52.5</v>
+        <v>16.9</v>
       </c>
       <c r="E62" t="n">
-        <v>54.4</v>
+        <v>59.9</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3626,39 +3675,39 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="D63" t="n">
         <v>-52.5</v>
       </c>
       <c r="E63" t="n">
-        <v>54.4</v>
+        <v>59.9</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>31.1</v>
+        <v>76.8</v>
       </c>
       <c r="D64" t="n">
-        <v>-22.8</v>
+        <v>17.1</v>
       </c>
       <c r="E64" t="n">
-        <v>54</v>
+        <v>59.8</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3669,7 +3718,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3678,169 +3727,169 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.2</v>
+        <v>6.9</v>
       </c>
       <c r="D65" t="n">
         <v>-52.5</v>
       </c>
       <c r="E65" t="n">
-        <v>52.6</v>
+        <v>59.3</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>31.1</v>
+        <v>4.1</v>
       </c>
       <c r="D66" t="n">
-        <v>-20.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E66" t="n">
-        <v>51.8</v>
+        <v>56.5</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>31.1</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D67" t="n">
-        <v>-19.3</v>
+        <v>16.9</v>
       </c>
       <c r="E67" t="n">
-        <v>50.5</v>
+        <v>56.4</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>31.1</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D68" t="n">
-        <v>-18.9</v>
+        <v>17.1</v>
       </c>
       <c r="E68" t="n">
-        <v>50</v>
+        <v>56.3</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>31.1</v>
+        <v>1.9</v>
       </c>
       <c r="D69" t="n">
-        <v>-15.5</v>
+        <v>-52.5</v>
       </c>
       <c r="E69" t="n">
-        <v>46.6</v>
+        <v>54.4</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>31.1</v>
+        <v>1.9</v>
       </c>
       <c r="D70" t="n">
-        <v>-15.2</v>
+        <v>-52.5</v>
       </c>
       <c r="E70" t="n">
-        <v>46.3</v>
+        <v>54.4</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>76.8</v>
+        <v>31.1</v>
       </c>
       <c r="D71" t="n">
-        <v>31.1</v>
+        <v>-22.8</v>
       </c>
       <c r="E71" t="n">
-        <v>45.7</v>
+        <v>54</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3851,390 +3900,390 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>73.40000000000001</v>
+        <v>102.4</v>
       </c>
       <c r="D72" t="n">
-        <v>31.1</v>
+        <v>49</v>
       </c>
       <c r="E72" t="n">
-        <v>42.2</v>
+        <v>53.4</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>17.1</v>
+        <v>0.2</v>
       </c>
       <c r="D73" t="n">
-        <v>-22.8</v>
+        <v>-52.5</v>
       </c>
       <c r="E73" t="n">
-        <v>39.9</v>
+        <v>52.6</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>16.9</v>
+        <v>31.1</v>
       </c>
       <c r="D74" t="n">
-        <v>-22.8</v>
+        <v>-20.6</v>
       </c>
       <c r="E74" t="n">
-        <v>39.8</v>
+        <v>51.8</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>17.1</v>
+        <v>31.1</v>
       </c>
       <c r="D75" t="n">
-        <v>-20.6</v>
+        <v>-19.3</v>
       </c>
       <c r="E75" t="n">
-        <v>37.7</v>
+        <v>50.5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>16.9</v>
+        <v>31.1</v>
       </c>
       <c r="D76" t="n">
-        <v>-20.6</v>
+        <v>-18.9</v>
       </c>
       <c r="E76" t="n">
-        <v>37.6</v>
+        <v>50</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-15.2</v>
+        <v>49</v>
       </c>
       <c r="D77" t="n">
-        <v>-52.5</v>
+        <v>0.2</v>
       </c>
       <c r="E77" t="n">
-        <v>37.3</v>
+        <v>48.8</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-15.5</v>
+        <v>49</v>
       </c>
       <c r="D78" t="n">
-        <v>-52.5</v>
+        <v>1.9</v>
       </c>
       <c r="E78" t="n">
-        <v>37</v>
+        <v>47.1</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>17.1</v>
+        <v>49</v>
       </c>
       <c r="D79" t="n">
-        <v>-19.3</v>
+        <v>1.9</v>
       </c>
       <c r="E79" t="n">
-        <v>36.4</v>
+        <v>47.1</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>16.9</v>
+        <v>31.1</v>
       </c>
       <c r="D80" t="n">
-        <v>-19.3</v>
+        <v>-15.5</v>
       </c>
       <c r="E80" t="n">
-        <v>36.3</v>
+        <v>46.6</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>17.1</v>
+        <v>31.1</v>
       </c>
       <c r="D81" t="n">
-        <v>-18.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E81" t="n">
-        <v>35.9</v>
+        <v>46.3</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>16.9</v>
+        <v>76.8</v>
       </c>
       <c r="D82" t="n">
-        <v>-18.9</v>
+        <v>31.1</v>
       </c>
       <c r="E82" t="n">
-        <v>35.8</v>
+        <v>45.7</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10.9</v>
+        <v>49</v>
       </c>
       <c r="D83" t="n">
-        <v>-22.8</v>
+        <v>4.1</v>
       </c>
       <c r="E83" t="n">
-        <v>33.8</v>
+        <v>45</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-18.9</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D84" t="n">
-        <v>-52.5</v>
+        <v>31.1</v>
       </c>
       <c r="E84" t="n">
-        <v>33.6</v>
+        <v>42.2</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10.2</v>
+        <v>49</v>
       </c>
       <c r="D85" t="n">
-        <v>-22.8</v>
+        <v>6.9</v>
       </c>
       <c r="E85" t="n">
-        <v>33.1</v>
+        <v>42.1</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-19.3</v>
+        <v>49</v>
       </c>
       <c r="D86" t="n">
-        <v>-52.5</v>
+        <v>7.4</v>
       </c>
       <c r="E86" t="n">
-        <v>33.1</v>
+        <v>41.6</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
@@ -4246,21 +4295,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>17.1</v>
       </c>
       <c r="D87" t="n">
-        <v>-15.5</v>
+        <v>-22.8</v>
       </c>
       <c r="E87" t="n">
-        <v>32.5</v>
+        <v>39.9</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4272,95 +4321,95 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>16.9</v>
       </c>
       <c r="D88" t="n">
-        <v>-15.5</v>
+        <v>-22.8</v>
       </c>
       <c r="E88" t="n">
-        <v>32.4</v>
+        <v>39.8</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>17.1</v>
+        <v>49</v>
       </c>
       <c r="D89" t="n">
-        <v>-15.2</v>
+        <v>10.2</v>
       </c>
       <c r="E89" t="n">
-        <v>32.2</v>
+        <v>38.8</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>16.9</v>
+        <v>49</v>
       </c>
       <c r="D90" t="n">
-        <v>-15.2</v>
+        <v>10.9</v>
       </c>
       <c r="E90" t="n">
-        <v>32.1</v>
+        <v>38.1</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>ECO</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C91" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D91" t="n">
         <v>-20.6</v>
       </c>
-      <c r="D91" t="n">
-        <v>-52.5</v>
-      </c>
       <c r="E91" t="n">
-        <v>31.8</v>
+        <v>37.7</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4371,7 +4420,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4380,102 +4429,102 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10.9</v>
+        <v>16.9</v>
       </c>
       <c r="D92" t="n">
         <v>-20.6</v>
       </c>
       <c r="E92" t="n">
-        <v>31.6</v>
+        <v>37.6</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>31.1</v>
+        <v>-15.2</v>
       </c>
       <c r="D93" t="n">
-        <v>0.2</v>
+        <v>-52.5</v>
       </c>
       <c r="E93" t="n">
-        <v>31</v>
+        <v>37.3</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>10.2</v>
+        <v>-15.5</v>
       </c>
       <c r="D94" t="n">
-        <v>-20.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E94" t="n">
-        <v>30.8</v>
+        <v>37</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>7.4</v>
+        <v>17.1</v>
       </c>
       <c r="D95" t="n">
-        <v>-22.8</v>
+        <v>-19.3</v>
       </c>
       <c r="E95" t="n">
-        <v>30.3</v>
+        <v>36.4</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4484,24 +4533,24 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>10.9</v>
+        <v>16.9</v>
       </c>
       <c r="D96" t="n">
         <v>-19.3</v>
       </c>
       <c r="E96" t="n">
-        <v>30.3</v>
+        <v>36.3</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4510,325 +4559,325 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>10.9</v>
+        <v>17.1</v>
       </c>
       <c r="D97" t="n">
         <v>-18.9</v>
       </c>
       <c r="E97" t="n">
-        <v>29.8</v>
+        <v>35.9</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="D98" t="n">
-        <v>-22.8</v>
+        <v>-18.9</v>
       </c>
       <c r="E98" t="n">
-        <v>29.7</v>
+        <v>35.8</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>CMBT (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C99" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D99" t="n">
         <v>-22.8</v>
       </c>
-      <c r="D99" t="n">
-        <v>-52.5</v>
-      </c>
       <c r="E99" t="n">
-        <v>29.6</v>
+        <v>33.8</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>10.2</v>
+        <v>-18.9</v>
       </c>
       <c r="D100" t="n">
-        <v>-19.3</v>
+        <v>-52.5</v>
       </c>
       <c r="E100" t="n">
-        <v>29.5</v>
+        <v>33.6</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>31.1</v>
+        <v>10.2</v>
       </c>
       <c r="D101" t="n">
-        <v>1.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E101" t="n">
-        <v>29.2</v>
+        <v>33.1</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>31.1</v>
+        <v>-19.3</v>
       </c>
       <c r="D102" t="n">
-        <v>1.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E102" t="n">
-        <v>29.2</v>
+        <v>33.1</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10.2</v>
+        <v>17.1</v>
       </c>
       <c r="D103" t="n">
-        <v>-18.9</v>
+        <v>-15.5</v>
       </c>
       <c r="E103" t="n">
-        <v>29.1</v>
+        <v>32.5</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>102.4</v>
+        <v>16.9</v>
       </c>
       <c r="D104" t="n">
-        <v>73.40000000000001</v>
+        <v>-15.5</v>
       </c>
       <c r="E104" t="n">
-        <v>29</v>
+        <v>32.4</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>7.4</v>
+        <v>17.1</v>
       </c>
       <c r="D105" t="n">
-        <v>-20.6</v>
+        <v>-15.2</v>
       </c>
       <c r="E105" t="n">
-        <v>28</v>
+        <v>32.2</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="D106" t="n">
-        <v>-20.6</v>
+        <v>-15.2</v>
       </c>
       <c r="E106" t="n">
-        <v>27.5</v>
+        <v>32.1</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>31.1</v>
+        <v>49</v>
       </c>
       <c r="D107" t="n">
-        <v>4.1</v>
+        <v>16.9</v>
       </c>
       <c r="E107" t="n">
-        <v>27.1</v>
+        <v>32.1</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4.1</v>
+        <v>49</v>
       </c>
       <c r="D108" t="n">
-        <v>-22.8</v>
+        <v>17.1</v>
       </c>
       <c r="E108" t="n">
-        <v>26.9</v>
+        <v>31.9</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>7.4</v>
+        <v>-20.6</v>
       </c>
       <c r="D109" t="n">
-        <v>-19.3</v>
+        <v>-52.5</v>
       </c>
       <c r="E109" t="n">
-        <v>26.7</v>
+        <v>31.8</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -4844,17 +4893,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>10.9</v>
       </c>
       <c r="D110" t="n">
-        <v>-15.5</v>
+        <v>-20.6</v>
       </c>
       <c r="E110" t="n">
-        <v>26.4</v>
+        <v>31.6</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4865,111 +4914,111 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>7.4</v>
+        <v>31.1</v>
       </c>
       <c r="D111" t="n">
-        <v>-18.9</v>
+        <v>0.2</v>
       </c>
       <c r="E111" t="n">
-        <v>26.3</v>
+        <v>31</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>6.9</v>
+        <v>10.2</v>
       </c>
       <c r="D112" t="n">
-        <v>-19.3</v>
+        <v>-20.6</v>
       </c>
       <c r="E112" t="n">
-        <v>26.2</v>
+        <v>30.8</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>10.9</v>
+        <v>7.4</v>
       </c>
       <c r="D113" t="n">
-        <v>-15.2</v>
+        <v>-22.8</v>
       </c>
       <c r="E113" t="n">
-        <v>26.1</v>
+        <v>30.3</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="D114" t="n">
-        <v>-15.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E114" t="n">
-        <v>25.7</v>
+        <v>30.3</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4978,407 +5027,407 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>6.9</v>
+        <v>10.9</v>
       </c>
       <c r="D115" t="n">
         <v>-18.9</v>
       </c>
       <c r="E115" t="n">
-        <v>25.7</v>
+        <v>29.8</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>102.4</v>
+        <v>6.9</v>
       </c>
       <c r="D116" t="n">
-        <v>76.8</v>
+        <v>-22.8</v>
       </c>
       <c r="E116" t="n">
-        <v>25.6</v>
+        <v>29.7</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>10.2</v>
+        <v>-22.8</v>
       </c>
       <c r="D117" t="n">
-        <v>-15.2</v>
+        <v>-52.5</v>
       </c>
       <c r="E117" t="n">
-        <v>25.4</v>
+        <v>29.6</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1.9</v>
+        <v>10.2</v>
       </c>
       <c r="D118" t="n">
-        <v>-22.8</v>
+        <v>-19.3</v>
       </c>
       <c r="E118" t="n">
-        <v>24.8</v>
+        <v>29.5</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C119" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="D119" t="n">
         <v>1.9</v>
       </c>
-      <c r="D119" t="n">
-        <v>-22.8</v>
-      </c>
       <c r="E119" t="n">
-        <v>24.8</v>
+        <v>29.2</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>4.1</v>
+        <v>31.1</v>
       </c>
       <c r="D120" t="n">
-        <v>-20.6</v>
+        <v>1.9</v>
       </c>
       <c r="E120" t="n">
-        <v>24.7</v>
+        <v>29.2</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>31.1</v>
+        <v>10.2</v>
       </c>
       <c r="D121" t="n">
-        <v>6.9</v>
+        <v>-18.9</v>
       </c>
       <c r="E121" t="n">
-        <v>24.3</v>
+        <v>29.1</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>31.1</v>
+        <v>102.4</v>
       </c>
       <c r="D122" t="n">
-        <v>7.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E122" t="n">
-        <v>23.7</v>
+        <v>29</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="D123" t="n">
-        <v>-19.3</v>
+        <v>-20.6</v>
       </c>
       <c r="E123" t="n">
-        <v>23.4</v>
+        <v>28</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>0.2</v>
+        <v>76.8</v>
       </c>
       <c r="D124" t="n">
-        <v>-22.8</v>
+        <v>49</v>
       </c>
       <c r="E124" t="n">
-        <v>23</v>
+        <v>27.8</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
       <c r="D125" t="n">
-        <v>-18.9</v>
+        <v>-20.6</v>
       </c>
       <c r="E125" t="n">
-        <v>22.9</v>
+        <v>27.5</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>7.4</v>
+        <v>31.1</v>
       </c>
       <c r="D126" t="n">
-        <v>-15.5</v>
+        <v>4.1</v>
       </c>
       <c r="E126" t="n">
-        <v>22.9</v>
+        <v>27.1</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="D127" t="n">
-        <v>-15.2</v>
+        <v>-22.8</v>
       </c>
       <c r="E127" t="n">
-        <v>22.6</v>
+        <v>26.9</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="D128" t="n">
-        <v>-20.6</v>
+        <v>-19.3</v>
       </c>
       <c r="E128" t="n">
-        <v>22.5</v>
+        <v>26.7</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1.9</v>
+        <v>10.9</v>
       </c>
       <c r="D129" t="n">
-        <v>-20.6</v>
+        <v>-15.5</v>
       </c>
       <c r="E129" t="n">
-        <v>22.5</v>
+        <v>26.4</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="D130" t="n">
-        <v>-15.5</v>
+        <v>-18.9</v>
       </c>
       <c r="E130" t="n">
-        <v>22.3</v>
+        <v>26.3</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
@@ -5390,203 +5439,203 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C131" t="n">
         <v>6.9</v>
       </c>
       <c r="D131" t="n">
-        <v>-15.2</v>
+        <v>-19.3</v>
       </c>
       <c r="E131" t="n">
-        <v>22</v>
+        <v>26.2</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1.9</v>
+        <v>10.9</v>
       </c>
       <c r="D132" t="n">
-        <v>-19.3</v>
+        <v>-15.2</v>
       </c>
       <c r="E132" t="n">
-        <v>21.3</v>
+        <v>26.1</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1.9</v>
+        <v>10.2</v>
       </c>
       <c r="D133" t="n">
-        <v>-19.3</v>
+        <v>-15.5</v>
       </c>
       <c r="E133" t="n">
-        <v>21.2</v>
+        <v>25.7</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>31.1</v>
+        <v>6.9</v>
       </c>
       <c r="D134" t="n">
-        <v>10.2</v>
+        <v>-18.9</v>
       </c>
       <c r="E134" t="n">
-        <v>20.9</v>
+        <v>25.7</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1.9</v>
+        <v>102.4</v>
       </c>
       <c r="D135" t="n">
-        <v>-18.9</v>
+        <v>76.8</v>
       </c>
       <c r="E135" t="n">
-        <v>20.8</v>
+        <v>25.6</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="D136" t="n">
-        <v>-20.6</v>
+        <v>-15.2</v>
       </c>
       <c r="E136" t="n">
-        <v>20.8</v>
+        <v>25.4</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C137" t="n">
         <v>1.9</v>
       </c>
       <c r="D137" t="n">
-        <v>-18.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E137" t="n">
-        <v>20.8</v>
+        <v>24.8</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>31.1</v>
+        <v>1.9</v>
       </c>
       <c r="D138" t="n">
-        <v>10.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E138" t="n">
-        <v>20.2</v>
+        <v>24.8</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -5598,17 +5647,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C139" t="n">
         <v>4.1</v>
       </c>
       <c r="D139" t="n">
-        <v>-15.5</v>
+        <v>-20.6</v>
       </c>
       <c r="E139" t="n">
-        <v>19.5</v>
+        <v>24.7</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -5619,832 +5668,832 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D140" t="n">
-        <v>-19.3</v>
+        <v>49</v>
       </c>
       <c r="E140" t="n">
-        <v>19.5</v>
+        <v>24.4</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4.1</v>
+        <v>31.1</v>
       </c>
       <c r="D141" t="n">
-        <v>-15.2</v>
+        <v>6.9</v>
       </c>
       <c r="E141" t="n">
-        <v>19.2</v>
+        <v>24.3</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.2</v>
+        <v>31.1</v>
       </c>
       <c r="D142" t="n">
-        <v>-18.9</v>
+        <v>7.4</v>
       </c>
       <c r="E142" t="n">
-        <v>19</v>
+        <v>23.7</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="D143" t="n">
-        <v>-15.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E143" t="n">
-        <v>17.4</v>
+        <v>23.4</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="D144" t="n">
-        <v>-15.5</v>
+        <v>-22.8</v>
       </c>
       <c r="E144" t="n">
-        <v>17.4</v>
+        <v>23</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="D145" t="n">
-        <v>-15.2</v>
+        <v>-18.9</v>
       </c>
       <c r="E145" t="n">
-        <v>17.1</v>
+        <v>22.9</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="D146" t="n">
-        <v>-15.2</v>
+        <v>-15.5</v>
       </c>
       <c r="E146" t="n">
-        <v>17.1</v>
+        <v>22.9</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>17.1</v>
+        <v>7.4</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2</v>
+        <v>-15.2</v>
       </c>
       <c r="E147" t="n">
-        <v>16.9</v>
+        <v>22.6</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="D148" t="n">
-        <v>0.2</v>
+        <v>-20.6</v>
       </c>
       <c r="E148" t="n">
-        <v>16.8</v>
+        <v>22.5</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="D149" t="n">
-        <v>-15.5</v>
+        <v>-20.6</v>
       </c>
       <c r="E149" t="n">
-        <v>15.7</v>
+        <v>22.5</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.2</v>
+        <v>6.9</v>
       </c>
       <c r="D150" t="n">
-        <v>-15.2</v>
+        <v>-15.5</v>
       </c>
       <c r="E150" t="n">
-        <v>15.4</v>
+        <v>22.3</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>17.1</v>
+        <v>6.9</v>
       </c>
       <c r="D151" t="n">
-        <v>1.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E151" t="n">
-        <v>15.2</v>
+        <v>22</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>17.1</v>
+        <v>1.9</v>
       </c>
       <c r="D152" t="n">
-        <v>1.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E152" t="n">
-        <v>15.1</v>
+        <v>21.3</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="D153" t="n">
-        <v>1.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E153" t="n">
-        <v>15</v>
+        <v>21.2</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>16.9</v>
+        <v>31.1</v>
       </c>
       <c r="D154" t="n">
-        <v>1.9</v>
+        <v>10.2</v>
       </c>
       <c r="E154" t="n">
-        <v>15</v>
+        <v>20.9</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>31.1</v>
+        <v>1.9</v>
       </c>
       <c r="D155" t="n">
-        <v>16.9</v>
+        <v>-18.9</v>
       </c>
       <c r="E155" t="n">
-        <v>14.2</v>
+        <v>20.8</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>31.1</v>
+        <v>0.2</v>
       </c>
       <c r="D156" t="n">
-        <v>17.1</v>
+        <v>-20.6</v>
       </c>
       <c r="E156" t="n">
-        <v>14.1</v>
+        <v>20.8</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>17.1</v>
+        <v>1.9</v>
       </c>
       <c r="D157" t="n">
-        <v>4.1</v>
+        <v>-18.9</v>
       </c>
       <c r="E157" t="n">
-        <v>13</v>
+        <v>20.8</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>16.9</v>
+        <v>31.1</v>
       </c>
       <c r="D158" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="E158" t="n">
-        <v>12.9</v>
+        <v>20.2</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>10.9</v>
+        <v>4.1</v>
       </c>
       <c r="D159" t="n">
-        <v>0.2</v>
+        <v>-15.5</v>
       </c>
       <c r="E159" t="n">
-        <v>10.8</v>
+        <v>19.5</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>17.1</v>
+        <v>0.2</v>
       </c>
       <c r="D160" t="n">
-        <v>6.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E160" t="n">
-        <v>10.2</v>
+        <v>19.5</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>16.9</v>
+        <v>4.1</v>
       </c>
       <c r="D161" t="n">
-        <v>6.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E161" t="n">
-        <v>10.1</v>
+        <v>19.2</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="D162" t="n">
-        <v>0.2</v>
+        <v>-18.9</v>
       </c>
       <c r="E162" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>17.1</v>
+        <v>49</v>
       </c>
       <c r="D163" t="n">
-        <v>7.4</v>
+        <v>31.1</v>
       </c>
       <c r="E163" t="n">
-        <v>9.6</v>
+        <v>17.9</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="D164" t="n">
-        <v>7.4</v>
+        <v>-15.5</v>
       </c>
       <c r="E164" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>10.9</v>
+        <v>1.9</v>
       </c>
       <c r="D165" t="n">
-        <v>1.9</v>
+        <v>-15.5</v>
       </c>
       <c r="E165" t="n">
-        <v>9</v>
+        <v>17.4</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>10.9</v>
+        <v>1.9</v>
       </c>
       <c r="D166" t="n">
-        <v>1.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E166" t="n">
-        <v>9</v>
+        <v>17.1</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>10.2</v>
+        <v>1.9</v>
       </c>
       <c r="D167" t="n">
-        <v>1.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E167" t="n">
-        <v>8.300000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>10.2</v>
+        <v>17.1</v>
       </c>
       <c r="D168" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="E168" t="n">
-        <v>8.300000000000001</v>
+        <v>16.9</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>-15.2</v>
+        <v>16.9</v>
       </c>
       <c r="D169" t="n">
-        <v>-22.8</v>
+        <v>0.2</v>
       </c>
       <c r="E169" t="n">
-        <v>7.7</v>
+        <v>16.8</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
           <t>DHT</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>INSW (WHOLE-CO)</t>
-        </is>
-      </c>
       <c r="C170" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D170" t="n">
         <v>-15.5</v>
       </c>
-      <c r="D170" t="n">
-        <v>-22.8</v>
-      </c>
       <c r="E170" t="n">
-        <v>7.4</v>
+        <v>15.7</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>7.4</v>
+        <v>0.2</v>
       </c>
       <c r="D171" t="n">
-        <v>0.2</v>
+        <v>-15.2</v>
       </c>
       <c r="E171" t="n">
-        <v>7.2</v>
+        <v>15.4</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -6456,17 +6505,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C172" t="n">
         <v>17.1</v>
       </c>
       <c r="D172" t="n">
-        <v>10.2</v>
+        <v>1.9</v>
       </c>
       <c r="E172" t="n">
-        <v>6.9</v>
+        <v>15.2</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -6477,26 +6526,26 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>10.9</v>
+        <v>17.1</v>
       </c>
       <c r="D173" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="E173" t="n">
-        <v>6.9</v>
+        <v>15.1</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -6508,17 +6557,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C174" t="n">
         <v>16.9</v>
       </c>
       <c r="D174" t="n">
-        <v>10.2</v>
+        <v>1.9</v>
       </c>
       <c r="E174" t="n">
-        <v>6.7</v>
+        <v>15</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -6529,204 +6578,204 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="D175" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="E175" t="n">
-        <v>6.7</v>
+        <v>15</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>10.2</v>
+        <v>31.1</v>
       </c>
       <c r="D176" t="n">
-        <v>4.1</v>
+        <v>16.9</v>
       </c>
       <c r="E176" t="n">
-        <v>6.2</v>
+        <v>14.2</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs lng)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
+          <t>CAPT</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
           <t>TNK</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>CMBT (WHOLE-CO)</t>
-        </is>
-      </c>
       <c r="C177" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="D177" t="n">
         <v>17.1</v>
       </c>
-      <c r="D177" t="n">
-        <v>10.9</v>
-      </c>
       <c r="E177" t="n">
-        <v>6.1</v>
+        <v>14.1</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="D178" t="n">
-        <v>10.9</v>
+        <v>4.1</v>
       </c>
       <c r="E178" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>7.4</v>
+        <v>16.9</v>
       </c>
       <c r="D179" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="E179" t="n">
-        <v>5.5</v>
+        <v>12.9</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>7.4</v>
+        <v>10.9</v>
       </c>
       <c r="D180" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="E180" t="n">
-        <v>5.5</v>
+        <v>10.8</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>-15.2</v>
+        <v>17.1</v>
       </c>
       <c r="D181" t="n">
-        <v>-20.6</v>
+        <v>6.9</v>
       </c>
       <c r="E181" t="n">
-        <v>5.4</v>
+        <v>10.2</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>-15.5</v>
+        <v>16.9</v>
       </c>
       <c r="D182" t="n">
-        <v>-20.6</v>
+        <v>6.9</v>
       </c>
       <c r="E182" t="n">
-        <v>5.1</v>
+        <v>10.1</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -6737,78 +6786,78 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>6.9</v>
+        <v>10.2</v>
       </c>
       <c r="D183" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="E183" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>6.9</v>
+        <v>17.1</v>
       </c>
       <c r="D184" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="E184" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>-15.2</v>
+        <v>16.9</v>
       </c>
       <c r="D185" t="n">
-        <v>-19.3</v>
+        <v>7.4</v>
       </c>
       <c r="E185" t="n">
-        <v>4.2</v>
+        <v>9.5</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
@@ -6820,99 +6869,99 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C186" t="n">
         <v>10.9</v>
       </c>
       <c r="D186" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="E186" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>-18.9</v>
+        <v>10.9</v>
       </c>
       <c r="D187" t="n">
-        <v>-22.8</v>
+        <v>1.9</v>
       </c>
       <c r="E187" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>-15.5</v>
+        <v>10.2</v>
       </c>
       <c r="D188" t="n">
-        <v>-19.3</v>
+        <v>1.9</v>
       </c>
       <c r="E188" t="n">
-        <v>3.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>4.1</v>
+        <v>10.2</v>
       </c>
       <c r="D189" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="E189" t="n">
-        <v>3.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -6924,28 +6973,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C190" t="n">
         <v>-15.2</v>
       </c>
       <c r="D190" t="n">
-        <v>-18.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E190" t="n">
-        <v>3.7</v>
+        <v>7.7</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6954,91 +7003,91 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>-19.3</v>
+        <v>-15.5</v>
       </c>
       <c r="D191" t="n">
         <v>-22.8</v>
       </c>
       <c r="E191" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>10.9</v>
+        <v>7.4</v>
       </c>
       <c r="D192" t="n">
-        <v>7.4</v>
+        <v>0.2</v>
       </c>
       <c r="E192" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>-15.5</v>
+        <v>17.1</v>
       </c>
       <c r="D193" t="n">
-        <v>-18.9</v>
+        <v>10.2</v>
       </c>
       <c r="E193" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>76.8</v>
+        <v>10.9</v>
       </c>
       <c r="D194" t="n">
-        <v>73.40000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="E194" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -7049,52 +7098,52 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>7.4</v>
+        <v>16.9</v>
       </c>
       <c r="D195" t="n">
-        <v>4.1</v>
+        <v>10.2</v>
       </c>
       <c r="E195" t="n">
-        <v>3.4</v>
+        <v>6.7</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>10.2</v>
+        <v>6.9</v>
       </c>
       <c r="D196" t="n">
-        <v>6.9</v>
+        <v>0.2</v>
       </c>
       <c r="E196" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -7106,80 +7155,80 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C197" t="n">
         <v>10.2</v>
       </c>
       <c r="D197" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="E197" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (product vs lng)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>6.9</v>
+        <v>17.1</v>
       </c>
       <c r="D198" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="E198" t="n">
-        <v>2.8</v>
+        <v>6.1</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>-20.6</v>
+        <v>16.9</v>
       </c>
       <c r="D199" t="n">
-        <v>-22.8</v>
+        <v>10.9</v>
       </c>
       <c r="E199" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7188,24 +7237,24 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="D200" t="n">
         <v>1.9</v>
       </c>
       <c r="E200" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7214,24 +7263,24 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="D201" t="n">
         <v>1.9</v>
       </c>
       <c r="E201" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7240,39 +7289,39 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>-18.9</v>
+        <v>-15.2</v>
       </c>
       <c r="D202" t="n">
         <v>-20.6</v>
       </c>
       <c r="E202" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1.9</v>
+        <v>-15.5</v>
       </c>
       <c r="D203" t="n">
-        <v>0.2</v>
+        <v>-20.6</v>
       </c>
       <c r="E203" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -7283,22 +7332,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C204" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D204" t="n">
         <v>1.9</v>
       </c>
-      <c r="D204" t="n">
-        <v>0.2</v>
-      </c>
       <c r="E204" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -7309,59 +7358,59 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>-19.3</v>
+        <v>6.9</v>
       </c>
       <c r="D205" t="n">
-        <v>-20.6</v>
+        <v>1.9</v>
       </c>
       <c r="E205" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>10.9</v>
+        <v>-15.2</v>
       </c>
       <c r="D206" t="n">
-        <v>10.2</v>
+        <v>-19.3</v>
       </c>
       <c r="E206" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7370,17 +7419,17 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>7.4</v>
+        <v>10.9</v>
       </c>
       <c r="D207" t="n">
         <v>6.9</v>
       </c>
       <c r="E207" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -7392,97 +7441,643 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C208" t="n">
         <v>-18.9</v>
       </c>
       <c r="D208" t="n">
-        <v>-19.3</v>
+        <v>-22.8</v>
       </c>
       <c r="E208" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>-15.2</v>
+        <v>-15.5</v>
       </c>
       <c r="D209" t="n">
-        <v>-15.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E209" t="n">
-        <v>0.3</v>
+        <v>3.9</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>17.1</v>
+        <v>4.1</v>
       </c>
       <c r="D210" t="n">
-        <v>16.9</v>
+        <v>0.2</v>
       </c>
       <c r="E210" t="n">
-        <v>0.1</v>
+        <v>3.9</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="D211" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="E211" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="D212" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="E212" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>CMBT (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D213" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E213" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="D214" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="E214" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>TEN (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="D215" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="E215" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D216" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E216" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs lng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D217" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E217" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D218" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E218" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs containerships)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D219" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E219" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>INSW (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="D220" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="E220" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E221" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="C222" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E222" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="D223" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="E223" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
         <is>
           <t>TRMD</t>
         </is>
       </c>
-      <c r="C211" t="n">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
         <v>1.9</v>
       </c>
-      <c r="D211" t="n">
+      <c r="D224" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E224" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
         <v>1.9</v>
       </c>
-      <c r="E211" t="n">
+      <c r="D225" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E225" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="D226" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="E226" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CMBT (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>STNG</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D227" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D228" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="D229" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs containerships)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="D230" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="E230" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (product vs crude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D231" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E232" t="n">
         <v>0</v>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F232" t="inlineStr">
         <is>
           <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -1653,28 +1653,28 @@
         <v>6.39</v>
       </c>
       <c r="E2" t="n">
-        <v>12.14</v>
+        <v>11.66</v>
       </c>
       <c r="F2" t="n">
-        <v>9.65</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>8.65</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>7.16</v>
+        <v>7.34</v>
       </c>
       <c r="I2" t="n">
-        <v>9.52</v>
+        <v>9.35</v>
       </c>
       <c r="J2" t="n">
-        <v>89.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>14.9</v>
       </c>
       <c r="L2" t="n">
-        <v>49</v>
+        <v>46.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -2340,26 +2340,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>102.4</v>
       </c>
       <c r="D12" t="n">
-        <v>-52.5</v>
+        <v>1.9</v>
       </c>
       <c r="E12" t="n">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2381,63 +2381,63 @@
         <v>1.9</v>
       </c>
       <c r="E13" t="n">
-        <v>100.5</v>
+        <v>100.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>102.4</v>
+        <v>76.8</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E14" t="n">
-        <v>100.4</v>
+        <v>99.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>76.8</v>
+        <v>46.3</v>
       </c>
       <c r="D15" t="n">
-        <v>-22.8</v>
+        <v>-52.5</v>
       </c>
       <c r="E15" t="n">
-        <v>99.7</v>
+        <v>98.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3068,26 +3068,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>49</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>-22.8</v>
+        <v>1.9</v>
       </c>
       <c r="E40" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3109,122 +3109,122 @@
         <v>1.9</v>
       </c>
       <c r="E41" t="n">
-        <v>71.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>73.40000000000001</v>
+        <v>102.4</v>
       </c>
       <c r="D42" t="n">
-        <v>1.9</v>
+        <v>31.1</v>
       </c>
       <c r="E42" t="n">
-        <v>71.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>102.4</v>
+        <v>76.8</v>
       </c>
       <c r="D43" t="n">
-        <v>31.1</v>
+        <v>6.9</v>
       </c>
       <c r="E43" t="n">
-        <v>71.2</v>
+        <v>70</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>76.8</v>
+        <v>17.1</v>
       </c>
       <c r="D44" t="n">
-        <v>6.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E44" t="n">
-        <v>70</v>
+        <v>69.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>49</v>
+        <v>76.8</v>
       </c>
       <c r="D45" t="n">
-        <v>-20.6</v>
+        <v>7.4</v>
       </c>
       <c r="E45" t="n">
-        <v>69.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3233,310 +3233,310 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="D46" t="n">
         <v>-52.5</v>
       </c>
       <c r="E46" t="n">
-        <v>69.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="E47" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.9</v>
+        <v>46.3</v>
       </c>
       <c r="D48" t="n">
-        <v>-52.5</v>
+        <v>-22.8</v>
       </c>
       <c r="E48" t="n">
-        <v>69.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>73.40000000000001</v>
+        <v>46.3</v>
       </c>
       <c r="D49" t="n">
-        <v>4.1</v>
+        <v>-20.6</v>
       </c>
       <c r="E49" t="n">
-        <v>69.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>49</v>
+        <v>76.8</v>
       </c>
       <c r="D50" t="n">
-        <v>-19.3</v>
+        <v>10.2</v>
       </c>
       <c r="E50" t="n">
-        <v>68.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>49</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>-18.9</v>
+        <v>6.9</v>
       </c>
       <c r="E51" t="n">
-        <v>67.90000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>10.2</v>
+        <v>7.4</v>
       </c>
       <c r="E52" t="n">
-        <v>66.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>73.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="D53" t="n">
-        <v>6.9</v>
+        <v>10.9</v>
       </c>
       <c r="E53" t="n">
-        <v>66.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>73.40000000000001</v>
+        <v>46.3</v>
       </c>
       <c r="D54" t="n">
-        <v>7.4</v>
+        <v>-19.3</v>
       </c>
       <c r="E54" t="n">
-        <v>65.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>76.8</v>
+        <v>46.3</v>
       </c>
       <c r="D55" t="n">
-        <v>10.9</v>
+        <v>-18.9</v>
       </c>
       <c r="E55" t="n">
-        <v>65.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>49</v>
+        <v>10.9</v>
       </c>
       <c r="D56" t="n">
-        <v>-15.5</v>
+        <v>-52.5</v>
       </c>
       <c r="E56" t="n">
-        <v>64.5</v>
+        <v>63.4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>49</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>-15.2</v>
+        <v>10.2</v>
       </c>
       <c r="E57" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3545,17 +3545,17 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="D58" t="n">
         <v>-52.5</v>
       </c>
       <c r="E58" t="n">
-        <v>63.4</v>
+        <v>62.7</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -3567,73 +3567,73 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="E59" t="n">
-        <v>63.2</v>
+        <v>62.4</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>10.2</v>
+        <v>46.3</v>
       </c>
       <c r="D60" t="n">
-        <v>-52.5</v>
+        <v>-15.5</v>
       </c>
       <c r="E60" t="n">
-        <v>62.7</v>
+        <v>61.8</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>73.40000000000001</v>
+        <v>46.3</v>
       </c>
       <c r="D61" t="n">
-        <v>10.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E61" t="n">
-        <v>62.4</v>
+        <v>61.5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -3822,33 +3822,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.9</v>
+        <v>102.4</v>
       </c>
       <c r="D69" t="n">
-        <v>-52.5</v>
+        <v>46.3</v>
       </c>
       <c r="E69" t="n">
-        <v>54.4</v>
+        <v>56.1</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3867,59 +3867,59 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>31.1</v>
+        <v>1.9</v>
       </c>
       <c r="D71" t="n">
-        <v>-22.8</v>
+        <v>-52.5</v>
       </c>
       <c r="E71" t="n">
-        <v>54</v>
+        <v>54.4</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>102.4</v>
+        <v>31.1</v>
       </c>
       <c r="D72" t="n">
-        <v>49</v>
+        <v>-22.8</v>
       </c>
       <c r="E72" t="n">
-        <v>53.4</v>
+        <v>54</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4030,52 +4030,52 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>49</v>
+        <v>31.1</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2</v>
+        <v>-15.5</v>
       </c>
       <c r="E77" t="n">
-        <v>48.8</v>
+        <v>46.6</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>49</v>
+        <v>31.1</v>
       </c>
       <c r="D78" t="n">
-        <v>1.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E78" t="n">
-        <v>47.1</v>
+        <v>46.3</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -4087,99 +4087,99 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>49</v>
+        <v>46.3</v>
       </c>
       <c r="D79" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="E79" t="n">
-        <v>47.1</v>
+        <v>46.1</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>TEN (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>CAPT</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>DHT</t>
-        </is>
-      </c>
       <c r="C80" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="D80" t="n">
         <v>31.1</v>
       </c>
-      <c r="D80" t="n">
-        <v>-15.5</v>
-      </c>
       <c r="E80" t="n">
-        <v>46.6</v>
+        <v>45.7</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>31.1</v>
+        <v>46.3</v>
       </c>
       <c r="D81" t="n">
-        <v>-15.2</v>
+        <v>1.9</v>
       </c>
       <c r="E81" t="n">
-        <v>46.3</v>
+        <v>44.4</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>76.8</v>
+        <v>46.3</v>
       </c>
       <c r="D82" t="n">
-        <v>31.1</v>
+        <v>1.9</v>
       </c>
       <c r="E82" t="n">
-        <v>45.7</v>
+        <v>44.4</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -4195,13 +4195,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>49</v>
+        <v>46.3</v>
       </c>
       <c r="D83" t="n">
         <v>4.1</v>
       </c>
       <c r="E83" t="n">
-        <v>45</v>
+        <v>42.3</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4238,319 +4238,319 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>49</v>
+        <v>17.1</v>
       </c>
       <c r="D85" t="n">
-        <v>6.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E85" t="n">
-        <v>42.1</v>
+        <v>39.9</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>49</v>
+        <v>16.9</v>
       </c>
       <c r="D86" t="n">
-        <v>7.4</v>
+        <v>-22.8</v>
       </c>
       <c r="E86" t="n">
-        <v>41.6</v>
+        <v>39.8</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>17.1</v>
+        <v>46.3</v>
       </c>
       <c r="D87" t="n">
-        <v>-22.8</v>
+        <v>6.9</v>
       </c>
       <c r="E87" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>16.9</v>
+        <v>46.3</v>
       </c>
       <c r="D88" t="n">
-        <v>-22.8</v>
+        <v>7.4</v>
       </c>
       <c r="E88" t="n">
-        <v>39.8</v>
+        <v>38.9</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>49</v>
+        <v>17.1</v>
       </c>
       <c r="D89" t="n">
-        <v>10.2</v>
+        <v>-20.6</v>
       </c>
       <c r="E89" t="n">
-        <v>38.8</v>
+        <v>37.7</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>49</v>
+        <v>16.9</v>
       </c>
       <c r="D90" t="n">
-        <v>10.9</v>
+        <v>-20.6</v>
       </c>
       <c r="E90" t="n">
-        <v>38.1</v>
+        <v>37.6</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>17.1</v>
+        <v>-15.2</v>
       </c>
       <c r="D91" t="n">
-        <v>-20.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E91" t="n">
-        <v>37.7</v>
+        <v>37.3</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>16.9</v>
+        <v>-15.5</v>
       </c>
       <c r="D92" t="n">
-        <v>-20.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E92" t="n">
-        <v>37.6</v>
+        <v>37</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-15.2</v>
+        <v>17.1</v>
       </c>
       <c r="D93" t="n">
-        <v>-52.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E93" t="n">
-        <v>37.3</v>
+        <v>36.4</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-15.5</v>
+        <v>16.9</v>
       </c>
       <c r="D94" t="n">
-        <v>-52.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E94" t="n">
-        <v>37</v>
+        <v>36.3</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>17.1</v>
+        <v>46.3</v>
       </c>
       <c r="D95" t="n">
-        <v>-19.3</v>
+        <v>10.2</v>
       </c>
       <c r="E95" t="n">
-        <v>36.4</v>
+        <v>36.1</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="D96" t="n">
-        <v>-19.3</v>
+        <v>-18.9</v>
       </c>
       <c r="E96" t="n">
-        <v>36.3</v>
+        <v>35.9</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4559,43 +4559,43 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="D97" t="n">
         <v>-18.9</v>
       </c>
       <c r="E97" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>16.9</v>
+        <v>46.3</v>
       </c>
       <c r="D98" t="n">
-        <v>-18.9</v>
+        <v>10.9</v>
       </c>
       <c r="E98" t="n">
-        <v>35.8</v>
+        <v>35.4</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4810,22 +4810,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>49</v>
+        <v>-20.6</v>
       </c>
       <c r="D107" t="n">
-        <v>16.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E107" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -4836,59 +4836,59 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>49</v>
+        <v>10.9</v>
       </c>
       <c r="D108" t="n">
-        <v>17.1</v>
+        <v>-20.6</v>
       </c>
       <c r="E108" t="n">
-        <v>31.9</v>
+        <v>31.6</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-20.6</v>
+        <v>31.1</v>
       </c>
       <c r="D109" t="n">
-        <v>-52.5</v>
+        <v>0.2</v>
       </c>
       <c r="E109" t="n">
-        <v>31.8</v>
+        <v>31</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4897,95 +4897,95 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="D110" t="n">
         <v>-20.6</v>
       </c>
       <c r="E110" t="n">
-        <v>31.6</v>
+        <v>30.8</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>31.1</v>
+        <v>76.8</v>
       </c>
       <c r="D111" t="n">
-        <v>0.2</v>
+        <v>46.3</v>
       </c>
       <c r="E111" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>10.2</v>
+        <v>7.4</v>
       </c>
       <c r="D112" t="n">
-        <v>-20.6</v>
+        <v>-22.8</v>
       </c>
       <c r="E112" t="n">
-        <v>30.8</v>
+        <v>30.3</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>7.4</v>
+        <v>10.9</v>
       </c>
       <c r="D113" t="n">
-        <v>-22.8</v>
+        <v>-19.3</v>
       </c>
       <c r="E113" t="n">
         <v>30.3</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -4997,125 +4997,125 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C114" t="n">
         <v>10.9</v>
       </c>
       <c r="D114" t="n">
-        <v>-19.3</v>
+        <v>-18.9</v>
       </c>
       <c r="E114" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="D115" t="n">
-        <v>-18.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E115" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6.9</v>
+        <v>-22.8</v>
       </c>
       <c r="D116" t="n">
-        <v>-22.8</v>
+        <v>-52.5</v>
       </c>
       <c r="E116" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-22.8</v>
+        <v>10.2</v>
       </c>
       <c r="D117" t="n">
-        <v>-52.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E117" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>10.2</v>
+        <v>46.3</v>
       </c>
       <c r="D118" t="n">
-        <v>-19.3</v>
+        <v>16.9</v>
       </c>
       <c r="E118" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -5174,104 +5174,104 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>10.2</v>
+        <v>46.3</v>
       </c>
       <c r="D121" t="n">
-        <v>-18.9</v>
+        <v>17.1</v>
       </c>
       <c r="E121" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>102.4</v>
+        <v>10.2</v>
       </c>
       <c r="D122" t="n">
-        <v>73.40000000000001</v>
+        <v>-18.9</v>
       </c>
       <c r="E122" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>7.4</v>
+        <v>102.4</v>
       </c>
       <c r="D123" t="n">
-        <v>-20.6</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E123" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>76.8</v>
+        <v>7.4</v>
       </c>
       <c r="D124" t="n">
-        <v>49</v>
+        <v>-20.6</v>
       </c>
       <c r="E124" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
@@ -5304,319 +5304,319 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>31.1</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D126" t="n">
-        <v>4.1</v>
+        <v>46.3</v>
       </c>
       <c r="E126" t="n">
         <v>27.1</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t>CAPT</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>INSW (WHOLE-CO)</t>
-        </is>
-      </c>
       <c r="C127" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="D127" t="n">
         <v>4.1</v>
       </c>
-      <c r="D127" t="n">
-        <v>-22.8</v>
-      </c>
       <c r="E127" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="D128" t="n">
-        <v>-19.3</v>
+        <v>-22.8</v>
       </c>
       <c r="E128" t="n">
-        <v>26.7</v>
+        <v>26.9</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>10.9</v>
+        <v>7.4</v>
       </c>
       <c r="D129" t="n">
-        <v>-15.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E129" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>7.4</v>
+        <v>10.9</v>
       </c>
       <c r="D130" t="n">
-        <v>-18.9</v>
+        <v>-15.5</v>
       </c>
       <c r="E130" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="D131" t="n">
-        <v>-19.3</v>
+        <v>-18.9</v>
       </c>
       <c r="E131" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="D132" t="n">
-        <v>-15.2</v>
+        <v>-19.3</v>
       </c>
       <c r="E132" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="D133" t="n">
-        <v>-15.5</v>
+        <v>-15.2</v>
       </c>
       <c r="E133" t="n">
-        <v>25.7</v>
+        <v>26.1</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>6.9</v>
+        <v>10.2</v>
       </c>
       <c r="D134" t="n">
-        <v>-18.9</v>
+        <v>-15.5</v>
       </c>
       <c r="E134" t="n">
         <v>25.7</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>102.4</v>
+        <v>6.9</v>
       </c>
       <c r="D135" t="n">
-        <v>76.8</v>
+        <v>-18.9</v>
       </c>
       <c r="E135" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>10.2</v>
+        <v>102.4</v>
       </c>
       <c r="D136" t="n">
-        <v>-15.2</v>
+        <v>76.8</v>
       </c>
       <c r="E136" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1.9</v>
+        <v>10.2</v>
       </c>
       <c r="D137" t="n">
-        <v>-22.8</v>
+        <v>-15.2</v>
       </c>
       <c r="E137" t="n">
-        <v>24.8</v>
+        <v>25.4</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5635,59 +5635,59 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="D139" t="n">
-        <v>-20.6</v>
+        <v>-22.8</v>
       </c>
       <c r="E139" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>73.40000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="D140" t="n">
-        <v>49</v>
+        <v>-20.6</v>
       </c>
       <c r="E140" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -6266,33 +6266,33 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>49</v>
+        <v>1.9</v>
       </c>
       <c r="D163" t="n">
-        <v>31.1</v>
+        <v>-15.5</v>
       </c>
       <c r="E163" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6311,40 +6311,40 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C165" t="n">
         <v>1.9</v>
       </c>
       <c r="D165" t="n">
-        <v>-15.5</v>
+        <v>-15.2</v>
       </c>
       <c r="E165" t="n">
-        <v>17.4</v>
+        <v>17.1</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6363,40 +6363,40 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1.9</v>
+        <v>17.1</v>
       </c>
       <c r="D167" t="n">
-        <v>-15.2</v>
+        <v>0.2</v>
       </c>
       <c r="E167" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6405,43 +6405,43 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="D168" t="n">
         <v>0.2</v>
       </c>
       <c r="E168" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>16.9</v>
+        <v>0.2</v>
       </c>
       <c r="D169" t="n">
-        <v>0.2</v>
+        <v>-15.5</v>
       </c>
       <c r="E169" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -6453,73 +6453,73 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C170" t="n">
         <v>0.2</v>
       </c>
       <c r="D170" t="n">
-        <v>-15.5</v>
+        <v>-15.2</v>
       </c>
       <c r="E170" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0.2</v>
+        <v>17.1</v>
       </c>
       <c r="D171" t="n">
-        <v>-15.2</v>
+        <v>1.9</v>
       </c>
       <c r="E171" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>17.1</v>
+        <v>46.3</v>
       </c>
       <c r="D172" t="n">
-        <v>1.9</v>
+        <v>31.1</v>
       </c>
       <c r="E172" t="n">
         <v>15.2</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -510,12 +510,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -524,31 +524,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.34</v>
+        <v>36.72</v>
       </c>
       <c r="E2" t="n">
-        <v>17.74</v>
+        <v>83.45</v>
       </c>
       <c r="F2" t="n">
-        <v>13.18</v>
+        <v>68.47</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>44.4</v>
       </c>
       <c r="H2" t="n">
-        <v>0.63</v>
+        <v>40.56</v>
       </c>
       <c r="I2" t="n">
-        <v>10.81</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>232.3</v>
+        <v>127.3</v>
       </c>
       <c r="K2" t="n">
-        <v>-88.2</v>
+        <v>10.5</v>
       </c>
       <c r="L2" t="n">
-        <v>102.4</v>
+        <v>75.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -559,12 +559,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -573,31 +573,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>36.72</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>83.95999999999999</v>
+        <v>94.77</v>
       </c>
       <c r="F3" t="n">
-        <v>68.89</v>
+        <v>81.78</v>
       </c>
       <c r="G3" t="n">
-        <v>44.66</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>40.82</v>
+        <v>62.29</v>
       </c>
       <c r="I3" t="n">
-        <v>64.93000000000001</v>
+        <v>79.59</v>
       </c>
       <c r="J3" t="n">
-        <v>128.6</v>
+        <v>39.4</v>
       </c>
       <c r="K3" t="n">
-        <v>11.2</v>
+        <v>-8.4</v>
       </c>
       <c r="L3" t="n">
-        <v>76.8</v>
+        <v>17.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,31 +622,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.79</v>
+        <v>5.34</v>
       </c>
       <c r="E4" t="n">
-        <v>23.95</v>
+        <v>11.9</v>
       </c>
       <c r="F4" t="n">
-        <v>18.9</v>
+        <v>7.99</v>
       </c>
       <c r="G4" t="n">
-        <v>8.039999999999999</v>
+        <v>-1.46</v>
       </c>
       <c r="H4" t="n">
-        <v>6.95</v>
+        <v>-2.63</v>
       </c>
       <c r="I4" t="n">
-        <v>16.77</v>
+        <v>5.99</v>
       </c>
       <c r="J4" t="n">
-        <v>87.2</v>
+        <v>122.9</v>
       </c>
       <c r="K4" t="n">
-        <v>-45.7</v>
+        <v>-149.2</v>
       </c>
       <c r="L4" t="n">
-        <v>31.1</v>
+        <v>12.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -657,12 +657,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -671,31 +671,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>67.98999999999999</v>
+        <v>14.1</v>
       </c>
       <c r="E5" t="n">
-        <v>94.77</v>
+        <v>21.61</v>
       </c>
       <c r="F5" t="n">
-        <v>81.78</v>
+        <v>16.15</v>
       </c>
       <c r="G5" t="n">
-        <v>64.56999999999999</v>
+        <v>10.88</v>
       </c>
       <c r="H5" t="n">
-        <v>62.29</v>
+        <v>8.85</v>
       </c>
       <c r="I5" t="n">
-        <v>79.59</v>
+        <v>15.69</v>
       </c>
       <c r="J5" t="n">
-        <v>39.4</v>
+        <v>53.3</v>
       </c>
       <c r="K5" t="n">
-        <v>-8.4</v>
+        <v>-37.2</v>
       </c>
       <c r="L5" t="n">
-        <v>17.1</v>
+        <v>11.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -706,12 +706,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.1</v>
+        <v>12.79</v>
       </c>
       <c r="E6" t="n">
-        <v>21.51</v>
+        <v>20.11</v>
       </c>
       <c r="F6" t="n">
-        <v>16.13</v>
+        <v>15.49</v>
       </c>
       <c r="G6" t="n">
-        <v>10.82</v>
+        <v>5.75</v>
       </c>
       <c r="H6" t="n">
-        <v>8.81</v>
+        <v>4.85</v>
       </c>
       <c r="I6" t="n">
-        <v>15.64</v>
+        <v>13.62</v>
       </c>
       <c r="J6" t="n">
-        <v>52.6</v>
+        <v>57.3</v>
       </c>
       <c r="K6" t="n">
-        <v>-37.5</v>
+        <v>-62.1</v>
       </c>
       <c r="L6" t="n">
-        <v>10.9</v>
+        <v>6.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -772,28 +772,28 @@
         <v>17.65</v>
       </c>
       <c r="E7" t="n">
-        <v>19.44</v>
+        <v>18.84</v>
       </c>
       <c r="F7" t="n">
-        <v>16.05</v>
+        <v>15.52</v>
       </c>
       <c r="G7" t="n">
-        <v>9.77</v>
+        <v>9.41</v>
       </c>
       <c r="H7" t="n">
-        <v>8.960000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>14.92</v>
+        <v>14.42</v>
       </c>
       <c r="J7" t="n">
-        <v>10.1</v>
+        <v>6.7</v>
       </c>
       <c r="K7" t="n">
-        <v>-49.2</v>
+        <v>-51.1</v>
       </c>
       <c r="L7" t="n">
-        <v>-15.5</v>
+        <v>-18.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -821,28 +821,28 @@
         <v>35.52</v>
       </c>
       <c r="E8" t="n">
-        <v>40.26</v>
+        <v>38.69</v>
       </c>
       <c r="F8" t="n">
-        <v>31.83</v>
+        <v>30.44</v>
       </c>
       <c r="G8" t="n">
-        <v>15.62</v>
+        <v>14.69</v>
       </c>
       <c r="H8" t="n">
-        <v>13.52</v>
+        <v>12.65</v>
       </c>
       <c r="I8" t="n">
-        <v>28.82</v>
+        <v>27.53</v>
       </c>
       <c r="J8" t="n">
-        <v>13.3</v>
+        <v>8.9</v>
       </c>
       <c r="K8" t="n">
-        <v>-61.9</v>
+        <v>-64.40000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-18.9</v>
+        <v>-22.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -853,12 +853,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -867,31 +867,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49.88</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>55.11</v>
+        <v>77.87</v>
       </c>
       <c r="F9" t="n">
-        <v>43.45</v>
+        <v>65.86</v>
       </c>
       <c r="G9" t="n">
-        <v>21.92</v>
+        <v>42.3</v>
       </c>
       <c r="H9" t="n">
-        <v>19.32</v>
+        <v>38.53</v>
       </c>
       <c r="I9" t="n">
-        <v>39.59</v>
+        <v>61.34</v>
       </c>
       <c r="J9" t="n">
-        <v>10.5</v>
+        <v>-2.1</v>
       </c>
       <c r="K9" t="n">
-        <v>-61.3</v>
+        <v>-51.5</v>
       </c>
       <c r="L9" t="n">
-        <v>-20.6</v>
+        <v>-22.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -902,12 +902,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -916,31 +916,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79.51000000000001</v>
+        <v>49.88</v>
       </c>
       <c r="E10" t="n">
-        <v>77.87</v>
+        <v>53.4</v>
       </c>
       <c r="F10" t="n">
-        <v>65.86</v>
+        <v>41.93</v>
       </c>
       <c r="G10" t="n">
-        <v>42.3</v>
+        <v>20.88</v>
       </c>
       <c r="H10" t="n">
-        <v>38.53</v>
+        <v>18.34</v>
       </c>
       <c r="I10" t="n">
-        <v>61.34</v>
+        <v>38.18</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1</v>
+        <v>7.1</v>
       </c>
       <c r="K10" t="n">
-        <v>-51.5</v>
+        <v>-63.2</v>
       </c>
       <c r="L10" t="n">
-        <v>-22.8</v>
+        <v>-23.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1653,28 +1653,28 @@
         <v>6.39</v>
       </c>
       <c r="E2" t="n">
-        <v>11.66</v>
+        <v>12.08</v>
       </c>
       <c r="F2" t="n">
-        <v>9.460000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="G2" t="n">
-        <v>8.529999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="H2" t="n">
-        <v>7.34</v>
+        <v>7.58</v>
       </c>
       <c r="I2" t="n">
-        <v>9.35</v>
+        <v>9.67</v>
       </c>
       <c r="J2" t="n">
-        <v>82.5</v>
+        <v>89</v>
       </c>
       <c r="K2" t="n">
-        <v>14.9</v>
+        <v>18.6</v>
       </c>
       <c r="L2" t="n">
-        <v>46.3</v>
+        <v>51.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1800,28 +1800,28 @@
         <v>23.57</v>
       </c>
       <c r="E5" t="n">
-        <v>30.38</v>
+        <v>30.41</v>
       </c>
       <c r="F5" t="n">
-        <v>24.68</v>
+        <v>24.71</v>
       </c>
       <c r="G5" t="n">
-        <v>21.25</v>
+        <v>21.28</v>
       </c>
       <c r="H5" t="n">
-        <v>18.41</v>
+        <v>18.43</v>
       </c>
       <c r="I5" t="n">
-        <v>24.02</v>
+        <v>24.05</v>
       </c>
       <c r="J5" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="K5" t="n">
-        <v>-21.9</v>
+        <v>-21.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2089,24 +2089,24 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>102.4</v>
+        <v>75.7</v>
       </c>
       <c r="D2" t="n">
         <v>-52.5</v>
       </c>
       <c r="E2" t="n">
-        <v>154.8</v>
+        <v>128.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2115,24 +2115,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D3" t="n">
         <v>-52.5</v>
       </c>
       <c r="E3" t="n">
-        <v>129.3</v>
+        <v>125.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2141,39 +2141,39 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>73.40000000000001</v>
+        <v>51.3</v>
       </c>
       <c r="D4" t="n">
         <v>-52.5</v>
       </c>
       <c r="E4" t="n">
-        <v>125.8</v>
+        <v>103.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>102.4</v>
+        <v>75.7</v>
       </c>
       <c r="D5" t="n">
-        <v>-22.8</v>
+        <v>-23.5</v>
       </c>
       <c r="E5" t="n">
-        <v>125.2</v>
+        <v>99.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2184,22 +2184,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>102.4</v>
+        <v>75.7</v>
       </c>
       <c r="D6" t="n">
-        <v>-20.6</v>
+        <v>-22.8</v>
       </c>
       <c r="E6" t="n">
-        <v>123</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2210,260 +2210,260 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>102.4</v>
+        <v>75.7</v>
       </c>
       <c r="D7" t="n">
-        <v>-19.3</v>
+        <v>-22.5</v>
       </c>
       <c r="E7" t="n">
-        <v>121.7</v>
+        <v>98.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>102.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>-18.9</v>
+        <v>-23.5</v>
       </c>
       <c r="E8" t="n">
-        <v>121.2</v>
+        <v>96.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>102.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>-15.5</v>
+        <v>-22.8</v>
       </c>
       <c r="E9" t="n">
-        <v>117.8</v>
+        <v>96.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>102.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>-15.2</v>
+        <v>-22.5</v>
       </c>
       <c r="E10" t="n">
-        <v>117.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>102.4</v>
+        <v>75.7</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2</v>
+        <v>-19.3</v>
       </c>
       <c r="E11" t="n">
-        <v>102.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>102.4</v>
+        <v>75.7</v>
       </c>
       <c r="D12" t="n">
-        <v>1.9</v>
+        <v>-18.3</v>
       </c>
       <c r="E12" t="n">
-        <v>100.5</v>
+        <v>94</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>102.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E13" t="n">
-        <v>100.4</v>
+        <v>92.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>-22.8</v>
+        <v>-18.3</v>
       </c>
       <c r="E14" t="n">
-        <v>99.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>46.3</v>
+        <v>75.7</v>
       </c>
       <c r="D15" t="n">
-        <v>-52.5</v>
+        <v>-15.2</v>
       </c>
       <c r="E15" t="n">
-        <v>98.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>102.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1</v>
+        <v>-15.2</v>
       </c>
       <c r="E16" t="n">
-        <v>98.3</v>
+        <v>88.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -2475,73 +2475,73 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>76.8</v>
+        <v>75.7</v>
       </c>
       <c r="D17" t="n">
-        <v>-20.6</v>
+        <v>0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>97.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>73.40000000000001</v>
+        <v>51.3</v>
       </c>
       <c r="D18" t="n">
-        <v>-22.8</v>
+        <v>-23.5</v>
       </c>
       <c r="E18" t="n">
-        <v>96.2</v>
+        <v>74.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>76.8</v>
+        <v>51.3</v>
       </c>
       <c r="D19" t="n">
-        <v>-19.3</v>
+        <v>-22.8</v>
       </c>
       <c r="E19" t="n">
-        <v>96.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2553,73 +2553,73 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>76.8</v>
+        <v>75.7</v>
       </c>
       <c r="D20" t="n">
-        <v>-18.9</v>
+        <v>1.9</v>
       </c>
       <c r="E20" t="n">
-        <v>95.7</v>
+        <v>73.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>102.4</v>
+        <v>51.3</v>
       </c>
       <c r="D21" t="n">
-        <v>6.9</v>
+        <v>-22.5</v>
       </c>
       <c r="E21" t="n">
-        <v>95.5</v>
+        <v>73.8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>102.4</v>
+        <v>75.7</v>
       </c>
       <c r="D22" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>94.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -2631,73 +2631,73 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>-20.6</v>
+        <v>0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>73.2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>73.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="D24" t="n">
-        <v>-19.3</v>
+        <v>4.1</v>
       </c>
       <c r="E24" t="n">
-        <v>92.7</v>
+        <v>71.7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.5</v>
+        <v>1.9</v>
       </c>
       <c r="E25" t="n">
-        <v>92.3</v>
+        <v>71.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -2709,125 +2709,125 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.9</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>92.2</v>
+        <v>71.3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>102.4</v>
+        <v>51.3</v>
       </c>
       <c r="D27" t="n">
-        <v>10.2</v>
+        <v>-19.3</v>
       </c>
       <c r="E27" t="n">
-        <v>92.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>76.8</v>
+        <v>51.3</v>
       </c>
       <c r="D28" t="n">
-        <v>-15.2</v>
+        <v>-18.3</v>
       </c>
       <c r="E28" t="n">
-        <v>92</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>102.4</v>
+        <v>17.1</v>
       </c>
       <c r="D29" t="n">
-        <v>10.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E29" t="n">
-        <v>91.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>73.40000000000001</v>
+        <v>16.9</v>
       </c>
       <c r="D30" t="n">
-        <v>-15.5</v>
+        <v>-52.5</v>
       </c>
       <c r="E30" t="n">
-        <v>88.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -2839,177 +2839,177 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>-15.2</v>
+        <v>4.1</v>
       </c>
       <c r="E31" t="n">
-        <v>88.5</v>
+        <v>69.3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>102.4</v>
+        <v>75.7</v>
       </c>
       <c r="D32" t="n">
-        <v>16.9</v>
+        <v>6.5</v>
       </c>
       <c r="E32" t="n">
-        <v>85.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>102.4</v>
+        <v>75.7</v>
       </c>
       <c r="D33" t="n">
-        <v>17.1</v>
+        <v>6.9</v>
       </c>
       <c r="E33" t="n">
-        <v>85.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>31.1</v>
+        <v>75.7</v>
       </c>
       <c r="D34" t="n">
-        <v>-52.5</v>
+        <v>7.4</v>
       </c>
       <c r="E34" t="n">
-        <v>83.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2</v>
+        <v>6.5</v>
       </c>
       <c r="E35" t="n">
-        <v>76.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="E36" t="n">
-        <v>74.90000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>76.8</v>
+        <v>51.3</v>
       </c>
       <c r="D37" t="n">
-        <v>1.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E37" t="n">
-        <v>74.90000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -3021,21 +3021,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2</v>
+        <v>7.4</v>
       </c>
       <c r="E38" t="n">
-        <v>73.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
@@ -3047,99 +3047,99 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>76.8</v>
+        <v>75.7</v>
       </c>
       <c r="D39" t="n">
-        <v>4.1</v>
+        <v>10.2</v>
       </c>
       <c r="E39" t="n">
-        <v>72.8</v>
+        <v>65.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>73.40000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="D40" t="n">
-        <v>1.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E40" t="n">
-        <v>71.5</v>
+        <v>64.7</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>73.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="D41" t="n">
-        <v>1.9</v>
+        <v>11.3</v>
       </c>
       <c r="E41" t="n">
-        <v>71.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>102.4</v>
+        <v>11.3</v>
       </c>
       <c r="D42" t="n">
-        <v>31.1</v>
+        <v>-52.5</v>
       </c>
       <c r="E42" t="n">
-        <v>71.2</v>
+        <v>63.7</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3151,99 +3151,99 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>76.8</v>
+        <v>75.7</v>
       </c>
       <c r="D43" t="n">
-        <v>6.9</v>
+        <v>12.2</v>
       </c>
       <c r="E43" t="n">
-        <v>70</v>
+        <v>63.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>17.1</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>-52.5</v>
+        <v>10.2</v>
       </c>
       <c r="E44" t="n">
-        <v>69.5</v>
+        <v>63.2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>76.8</v>
+        <v>10.2</v>
       </c>
       <c r="D45" t="n">
-        <v>7.4</v>
+        <v>-52.5</v>
       </c>
       <c r="E45" t="n">
-        <v>69.40000000000001</v>
+        <v>62.7</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.9</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>-52.5</v>
+        <v>11.3</v>
       </c>
       <c r="E46" t="n">
-        <v>69.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3255,69 +3255,69 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>4.1</v>
+        <v>12.2</v>
       </c>
       <c r="E47" t="n">
-        <v>69.3</v>
+        <v>61.1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>46.3</v>
+        <v>7.4</v>
       </c>
       <c r="D48" t="n">
-        <v>-22.8</v>
+        <v>-52.5</v>
       </c>
       <c r="E48" t="n">
-        <v>69.2</v>
+        <v>59.9</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>46.3</v>
+        <v>6.9</v>
       </c>
       <c r="D49" t="n">
-        <v>-20.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E49" t="n">
-        <v>66.90000000000001</v>
+        <v>59.3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3328,163 +3328,163 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>76.8</v>
+        <v>6.5</v>
       </c>
       <c r="D50" t="n">
-        <v>10.2</v>
+        <v>-52.5</v>
       </c>
       <c r="E50" t="n">
-        <v>66.59999999999999</v>
+        <v>58.9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>73.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="D51" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="E51" t="n">
-        <v>66.5</v>
+        <v>58.8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>73.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="D52" t="n">
-        <v>7.4</v>
+        <v>17.1</v>
       </c>
       <c r="E52" t="n">
-        <v>65.90000000000001</v>
+        <v>58.7</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>76.8</v>
+        <v>4.1</v>
       </c>
       <c r="D53" t="n">
-        <v>10.9</v>
+        <v>-52.5</v>
       </c>
       <c r="E53" t="n">
-        <v>65.90000000000001</v>
+        <v>56.5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>46.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>-19.3</v>
+        <v>16.9</v>
       </c>
       <c r="E54" t="n">
-        <v>65.59999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>46.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>-18.9</v>
+        <v>17.1</v>
       </c>
       <c r="E55" t="n">
-        <v>65.2</v>
+        <v>56.3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3493,50 +3493,50 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10.9</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
         <v>-52.5</v>
       </c>
       <c r="E56" t="n">
-        <v>63.4</v>
+        <v>54.5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>73.40000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="D57" t="n">
-        <v>10.2</v>
+        <v>-52.5</v>
       </c>
       <c r="E57" t="n">
-        <v>63.2</v>
+        <v>54.4</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3545,13 +3545,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="D58" t="n">
         <v>-52.5</v>
       </c>
       <c r="E58" t="n">
-        <v>62.7</v>
+        <v>52.6</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3562,26 +3562,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>73.40000000000001</v>
+        <v>51.3</v>
       </c>
       <c r="D59" t="n">
-        <v>10.9</v>
+        <v>0.2</v>
       </c>
       <c r="E59" t="n">
-        <v>62.4</v>
+        <v>51.1</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -3593,21 +3593,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>46.3</v>
+        <v>51.3</v>
       </c>
       <c r="D60" t="n">
-        <v>-15.5</v>
+        <v>1.9</v>
       </c>
       <c r="E60" t="n">
-        <v>61.8</v>
+        <v>49.4</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -3619,693 +3619,693 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>46.3</v>
+        <v>51.3</v>
       </c>
       <c r="D61" t="n">
-        <v>-15.2</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>61.5</v>
+        <v>49.3</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>76.8</v>
+        <v>51.3</v>
       </c>
       <c r="D62" t="n">
-        <v>16.9</v>
+        <v>4.1</v>
       </c>
       <c r="E62" t="n">
-        <v>59.9</v>
+        <v>47.3</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7.4</v>
+        <v>51.3</v>
       </c>
       <c r="D63" t="n">
-        <v>-52.5</v>
+        <v>6.5</v>
       </c>
       <c r="E63" t="n">
-        <v>59.9</v>
+        <v>44.8</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>76.8</v>
+        <v>51.3</v>
       </c>
       <c r="D64" t="n">
-        <v>17.1</v>
+        <v>6.9</v>
       </c>
       <c r="E64" t="n">
-        <v>59.8</v>
+        <v>44.4</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6.9</v>
+        <v>51.3</v>
       </c>
       <c r="D65" t="n">
-        <v>-52.5</v>
+        <v>7.4</v>
       </c>
       <c r="E65" t="n">
-        <v>59.3</v>
+        <v>43.9</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4.1</v>
+        <v>51.3</v>
       </c>
       <c r="D66" t="n">
-        <v>-52.5</v>
+        <v>10.2</v>
       </c>
       <c r="E66" t="n">
-        <v>56.5</v>
+        <v>41.1</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>73.40000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="D67" t="n">
-        <v>16.9</v>
+        <v>-23.5</v>
       </c>
       <c r="E67" t="n">
-        <v>56.4</v>
+        <v>40.5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>73.40000000000001</v>
+        <v>16.9</v>
       </c>
       <c r="D68" t="n">
-        <v>17.1</v>
+        <v>-23.5</v>
       </c>
       <c r="E68" t="n">
-        <v>56.3</v>
+        <v>40.4</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>102.4</v>
+        <v>51.3</v>
       </c>
       <c r="D69" t="n">
-        <v>46.3</v>
+        <v>11.3</v>
       </c>
       <c r="E69" t="n">
-        <v>56.1</v>
+        <v>40</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.9</v>
+        <v>17.1</v>
       </c>
       <c r="D70" t="n">
-        <v>-52.5</v>
+        <v>-22.8</v>
       </c>
       <c r="E70" t="n">
-        <v>54.4</v>
+        <v>39.9</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.9</v>
+        <v>16.9</v>
       </c>
       <c r="D71" t="n">
-        <v>-52.5</v>
+        <v>-22.8</v>
       </c>
       <c r="E71" t="n">
-        <v>54.4</v>
+        <v>39.8</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>31.1</v>
+        <v>17.1</v>
       </c>
       <c r="D72" t="n">
-        <v>-22.8</v>
+        <v>-22.5</v>
       </c>
       <c r="E72" t="n">
-        <v>54</v>
+        <v>39.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.2</v>
+        <v>16.9</v>
       </c>
       <c r="D73" t="n">
-        <v>-52.5</v>
+        <v>-22.5</v>
       </c>
       <c r="E73" t="n">
-        <v>52.6</v>
+        <v>39.4</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>31.1</v>
+        <v>51.3</v>
       </c>
       <c r="D74" t="n">
-        <v>-20.6</v>
+        <v>12.2</v>
       </c>
       <c r="E74" t="n">
-        <v>51.8</v>
+        <v>39.1</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>31.1</v>
+        <v>-15.2</v>
       </c>
       <c r="D75" t="n">
-        <v>-19.3</v>
+        <v>-52.5</v>
       </c>
       <c r="E75" t="n">
-        <v>50.5</v>
+        <v>37.3</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>31.1</v>
+        <v>17.1</v>
       </c>
       <c r="D76" t="n">
-        <v>-18.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E76" t="n">
-        <v>50</v>
+        <v>36.4</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>31.1</v>
+        <v>16.9</v>
       </c>
       <c r="D77" t="n">
-        <v>-15.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E77" t="n">
-        <v>46.6</v>
+        <v>36.3</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>31.1</v>
+        <v>12.2</v>
       </c>
       <c r="D78" t="n">
-        <v>-15.2</v>
+        <v>-23.5</v>
       </c>
       <c r="E78" t="n">
-        <v>46.3</v>
+        <v>35.7</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>46.3</v>
+        <v>17.1</v>
       </c>
       <c r="D79" t="n">
-        <v>0.2</v>
+        <v>-18.3</v>
       </c>
       <c r="E79" t="n">
-        <v>46.1</v>
+        <v>35.3</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>76.8</v>
+        <v>16.9</v>
       </c>
       <c r="D80" t="n">
-        <v>31.1</v>
+        <v>-18.3</v>
       </c>
       <c r="E80" t="n">
-        <v>45.7</v>
+        <v>35.2</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>46.3</v>
+        <v>12.2</v>
       </c>
       <c r="D81" t="n">
-        <v>1.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E81" t="n">
-        <v>44.4</v>
+        <v>35.1</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>46.3</v>
+        <v>11.3</v>
       </c>
       <c r="D82" t="n">
-        <v>1.9</v>
+        <v>-23.5</v>
       </c>
       <c r="E82" t="n">
-        <v>44.4</v>
+        <v>34.8</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>46.3</v>
+        <v>12.2</v>
       </c>
       <c r="D83" t="n">
-        <v>4.1</v>
+        <v>-22.5</v>
       </c>
       <c r="E83" t="n">
-        <v>42.3</v>
+        <v>34.7</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>73.40000000000001</v>
+        <v>51.3</v>
       </c>
       <c r="D84" t="n">
-        <v>31.1</v>
+        <v>16.9</v>
       </c>
       <c r="E84" t="n">
-        <v>42.2</v>
+        <v>34.4</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>TNK</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>INSW (WHOLE-CO)</t>
-        </is>
-      </c>
       <c r="C85" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="D85" t="n">
         <v>17.1</v>
       </c>
-      <c r="D85" t="n">
-        <v>-22.8</v>
-      </c>
       <c r="E85" t="n">
-        <v>39.9</v>
+        <v>34.3</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>16.9</v>
+        <v>-18.3</v>
       </c>
       <c r="D86" t="n">
-        <v>-22.8</v>
+        <v>-52.5</v>
       </c>
       <c r="E86" t="n">
-        <v>39.8</v>
+        <v>34.2</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>46.3</v>
+        <v>11.3</v>
       </c>
       <c r="D87" t="n">
-        <v>6.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E87" t="n">
-        <v>39.4</v>
+        <v>34.1</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -4316,33 +4316,33 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>46.3</v>
+        <v>11.3</v>
       </c>
       <c r="D88" t="n">
-        <v>7.4</v>
+        <v>-22.5</v>
       </c>
       <c r="E88" t="n">
-        <v>38.9</v>
+        <v>33.8</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4351,50 +4351,50 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>17.1</v>
+        <v>10.2</v>
       </c>
       <c r="D89" t="n">
-        <v>-20.6</v>
+        <v>-23.5</v>
       </c>
       <c r="E89" t="n">
-        <v>37.7</v>
+        <v>33.7</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>16.9</v>
+        <v>10.2</v>
       </c>
       <c r="D90" t="n">
-        <v>-20.6</v>
+        <v>-22.8</v>
       </c>
       <c r="E90" t="n">
-        <v>37.6</v>
+        <v>33.1</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4403,43 +4403,43 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-15.2</v>
+        <v>-19.3</v>
       </c>
       <c r="D91" t="n">
         <v>-52.5</v>
       </c>
       <c r="E91" t="n">
-        <v>37.3</v>
+        <v>33.1</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-15.5</v>
+        <v>10.2</v>
       </c>
       <c r="D92" t="n">
-        <v>-52.5</v>
+        <v>-22.5</v>
       </c>
       <c r="E92" t="n">
-        <v>37</v>
+        <v>32.7</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -4451,21 +4451,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>17.1</v>
       </c>
       <c r="D93" t="n">
-        <v>-19.3</v>
+        <v>-15.2</v>
       </c>
       <c r="E93" t="n">
-        <v>36.4</v>
+        <v>32.2</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
@@ -4477,385 +4477,385 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>16.9</v>
       </c>
       <c r="D94" t="n">
-        <v>-19.3</v>
+        <v>-15.2</v>
       </c>
       <c r="E94" t="n">
-        <v>36.3</v>
+        <v>32.1</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>46.3</v>
+        <v>12.2</v>
       </c>
       <c r="D95" t="n">
-        <v>10.2</v>
+        <v>-19.3</v>
       </c>
       <c r="E95" t="n">
-        <v>36.1</v>
+        <v>31.6</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>17.1</v>
+        <v>7.4</v>
       </c>
       <c r="D96" t="n">
-        <v>-18.9</v>
+        <v>-23.5</v>
       </c>
       <c r="E96" t="n">
-        <v>35.9</v>
+        <v>30.9</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>16.9</v>
+        <v>11.3</v>
       </c>
       <c r="D97" t="n">
-        <v>-18.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E97" t="n">
-        <v>35.8</v>
+        <v>30.6</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>46.3</v>
+        <v>12.2</v>
       </c>
       <c r="D98" t="n">
-        <v>10.9</v>
+        <v>-18.3</v>
       </c>
       <c r="E98" t="n">
-        <v>35.4</v>
+        <v>30.5</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="D99" t="n">
-        <v>-22.8</v>
+        <v>-23.5</v>
       </c>
       <c r="E99" t="n">
-        <v>33.8</v>
+        <v>30.3</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-18.9</v>
+        <v>7.4</v>
       </c>
       <c r="D100" t="n">
-        <v>-52.5</v>
+        <v>-22.8</v>
       </c>
       <c r="E100" t="n">
-        <v>33.6</v>
+        <v>30.3</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10.2</v>
+        <v>-22.5</v>
       </c>
       <c r="D101" t="n">
-        <v>-22.8</v>
+        <v>-52.5</v>
       </c>
       <c r="E101" t="n">
-        <v>33.1</v>
+        <v>30</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-19.3</v>
+        <v>6.5</v>
       </c>
       <c r="D102" t="n">
-        <v>-52.5</v>
+        <v>-23.5</v>
       </c>
       <c r="E102" t="n">
-        <v>33.1</v>
+        <v>29.9</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>17.1</v>
+        <v>7.4</v>
       </c>
       <c r="D103" t="n">
-        <v>-15.5</v>
+        <v>-22.5</v>
       </c>
       <c r="E103" t="n">
-        <v>32.5</v>
+        <v>29.9</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="D104" t="n">
-        <v>-15.5</v>
+        <v>-22.8</v>
       </c>
       <c r="E104" t="n">
-        <v>32.4</v>
+        <v>29.7</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>17.1</v>
+        <v>-22.8</v>
       </c>
       <c r="D105" t="n">
-        <v>-15.2</v>
+        <v>-52.5</v>
       </c>
       <c r="E105" t="n">
-        <v>32.2</v>
+        <v>29.6</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>16.9</v>
+        <v>11.3</v>
       </c>
       <c r="D106" t="n">
-        <v>-15.2</v>
+        <v>-18.3</v>
       </c>
       <c r="E106" t="n">
-        <v>32.1</v>
+        <v>29.6</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-20.6</v>
+        <v>10.2</v>
       </c>
       <c r="D107" t="n">
-        <v>-52.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E107" t="n">
-        <v>31.8</v>
+        <v>29.5</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="D108" t="n">
-        <v>-20.6</v>
+        <v>-22.5</v>
       </c>
       <c r="E108" t="n">
-        <v>31.6</v>
+        <v>29.3</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -4867,158 +4867,158 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>31.1</v>
+        <v>6.5</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2</v>
+        <v>-22.8</v>
       </c>
       <c r="E109" t="n">
-        <v>31</v>
+        <v>29.3</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>10.2</v>
+        <v>-23.5</v>
       </c>
       <c r="D110" t="n">
-        <v>-20.6</v>
+        <v>-52.5</v>
       </c>
       <c r="E110" t="n">
-        <v>30.8</v>
+        <v>29</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>76.8</v>
+        <v>6.5</v>
       </c>
       <c r="D111" t="n">
-        <v>46.3</v>
+        <v>-22.5</v>
       </c>
       <c r="E111" t="n">
-        <v>30.5</v>
+        <v>29</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>7.4</v>
+        <v>10.2</v>
       </c>
       <c r="D112" t="n">
-        <v>-22.8</v>
+        <v>-18.3</v>
       </c>
       <c r="E112" t="n">
-        <v>30.3</v>
+        <v>28.5</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>10.9</v>
+        <v>4.1</v>
       </c>
       <c r="D113" t="n">
-        <v>-19.3</v>
+        <v>-23.5</v>
       </c>
       <c r="E113" t="n">
-        <v>30.3</v>
+        <v>27.5</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>10.9</v>
+        <v>12.2</v>
       </c>
       <c r="D114" t="n">
-        <v>-18.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E114" t="n">
-        <v>29.8</v>
+        <v>27.4</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5027,121 +5027,121 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>6.9</v>
+        <v>4.1</v>
       </c>
       <c r="D115" t="n">
         <v>-22.8</v>
       </c>
       <c r="E115" t="n">
-        <v>29.7</v>
+        <v>26.9</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-22.8</v>
+        <v>7.4</v>
       </c>
       <c r="D116" t="n">
-        <v>-52.5</v>
+        <v>-19.3</v>
       </c>
       <c r="E116" t="n">
-        <v>29.6</v>
+        <v>26.7</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>10.2</v>
+        <v>4.1</v>
       </c>
       <c r="D117" t="n">
-        <v>-19.3</v>
+        <v>-22.5</v>
       </c>
       <c r="E117" t="n">
-        <v>29.5</v>
+        <v>26.5</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>46.3</v>
+        <v>11.3</v>
       </c>
       <c r="D118" t="n">
-        <v>16.9</v>
+        <v>-15.2</v>
       </c>
       <c r="E118" t="n">
-        <v>29.4</v>
+        <v>26.5</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>31.1</v>
+        <v>6.9</v>
       </c>
       <c r="D119" t="n">
-        <v>1.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E119" t="n">
-        <v>29.2</v>
+        <v>26.2</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
@@ -5153,106 +5153,106 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>31.1</v>
+        <v>6.5</v>
       </c>
       <c r="D120" t="n">
-        <v>1.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E120" t="n">
-        <v>29.2</v>
+        <v>25.8</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>46.3</v>
+        <v>7.4</v>
       </c>
       <c r="D121" t="n">
-        <v>17.1</v>
+        <v>-18.3</v>
       </c>
       <c r="E121" t="n">
-        <v>29.2</v>
+        <v>25.7</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>10.2</v>
+        <v>2</v>
       </c>
       <c r="D122" t="n">
-        <v>-18.9</v>
+        <v>-23.5</v>
       </c>
       <c r="E122" t="n">
-        <v>29.1</v>
+        <v>25.5</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>102.4</v>
+        <v>10.2</v>
       </c>
       <c r="D123" t="n">
-        <v>73.40000000000001</v>
+        <v>-15.2</v>
       </c>
       <c r="E123" t="n">
-        <v>29</v>
+        <v>25.4</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5261,17 +5261,17 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
       <c r="D124" t="n">
-        <v>-20.6</v>
+        <v>-23.5</v>
       </c>
       <c r="E124" t="n">
-        <v>28</v>
+        <v>25.4</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -5283,17 +5283,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>6.9</v>
       </c>
       <c r="D125" t="n">
-        <v>-20.6</v>
+        <v>-18.3</v>
       </c>
       <c r="E125" t="n">
-        <v>27.5</v>
+        <v>25.1</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5304,241 +5304,241 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>73.40000000000001</v>
+        <v>2</v>
       </c>
       <c r="D126" t="n">
-        <v>46.3</v>
+        <v>-22.8</v>
       </c>
       <c r="E126" t="n">
-        <v>27.1</v>
+        <v>24.9</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>31.1</v>
+        <v>1.9</v>
       </c>
       <c r="D127" t="n">
-        <v>4.1</v>
+        <v>-22.8</v>
       </c>
       <c r="E127" t="n">
-        <v>27.1</v>
+        <v>24.8</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="D128" t="n">
-        <v>-22.8</v>
+        <v>-18.3</v>
       </c>
       <c r="E128" t="n">
-        <v>26.9</v>
+        <v>24.7</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="D129" t="n">
-        <v>-19.3</v>
+        <v>-22.5</v>
       </c>
       <c r="E129" t="n">
-        <v>26.7</v>
+        <v>24.5</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>10.9</v>
+        <v>1.9</v>
       </c>
       <c r="D130" t="n">
-        <v>-15.5</v>
+        <v>-22.5</v>
       </c>
       <c r="E130" t="n">
-        <v>26.4</v>
+        <v>24.4</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>7.4</v>
+        <v>75.7</v>
       </c>
       <c r="D131" t="n">
-        <v>-18.9</v>
+        <v>51.3</v>
       </c>
       <c r="E131" t="n">
-        <v>26.3</v>
+        <v>24.4</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>6.9</v>
+        <v>0.2</v>
       </c>
       <c r="D132" t="n">
-        <v>-19.3</v>
+        <v>-23.5</v>
       </c>
       <c r="E132" t="n">
-        <v>26.2</v>
+        <v>23.6</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>10.9</v>
+        <v>4.1</v>
       </c>
       <c r="D133" t="n">
-        <v>-15.2</v>
+        <v>-19.3</v>
       </c>
       <c r="E133" t="n">
-        <v>26.1</v>
+        <v>23.4</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="D134" t="n">
-        <v>-15.5</v>
+        <v>-22.8</v>
       </c>
       <c r="E134" t="n">
-        <v>25.7</v>
+        <v>23</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5547,429 +5547,429 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>6.9</v>
+        <v>0.2</v>
       </c>
       <c r="D135" t="n">
-        <v>-18.9</v>
+        <v>-22.5</v>
       </c>
       <c r="E135" t="n">
-        <v>25.7</v>
+        <v>22.7</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>102.4</v>
+        <v>7.4</v>
       </c>
       <c r="D136" t="n">
-        <v>76.8</v>
+        <v>-15.2</v>
       </c>
       <c r="E136" t="n">
-        <v>25.6</v>
+        <v>22.6</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>10.2</v>
+        <v>4.1</v>
       </c>
       <c r="D137" t="n">
-        <v>-15.2</v>
+        <v>-18.3</v>
       </c>
       <c r="E137" t="n">
-        <v>25.4</v>
+        <v>22.3</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1.9</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D138" t="n">
-        <v>-22.8</v>
+        <v>51.3</v>
       </c>
       <c r="E138" t="n">
-        <v>24.8</v>
+        <v>22.1</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="D139" t="n">
-        <v>-22.8</v>
+        <v>-15.2</v>
       </c>
       <c r="E139" t="n">
-        <v>24.8</v>
+        <v>22</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="D140" t="n">
-        <v>-20.6</v>
+        <v>-15.2</v>
       </c>
       <c r="E140" t="n">
-        <v>24.7</v>
+        <v>21.6</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>31.1</v>
+        <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>6.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E141" t="n">
-        <v>24.3</v>
+        <v>21.4</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>31.1</v>
+        <v>1.9</v>
       </c>
       <c r="D142" t="n">
-        <v>7.4</v>
+        <v>-19.3</v>
       </c>
       <c r="E142" t="n">
-        <v>23.7</v>
+        <v>21.2</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="D143" t="n">
-        <v>-19.3</v>
+        <v>-18.3</v>
       </c>
       <c r="E143" t="n">
-        <v>23.4</v>
+        <v>20.3</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="D144" t="n">
-        <v>-22.8</v>
+        <v>-18.3</v>
       </c>
       <c r="E144" t="n">
-        <v>23</v>
+        <v>20.2</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="D145" t="n">
-        <v>-18.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E145" t="n">
-        <v>22.9</v>
+        <v>19.5</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="D146" t="n">
-        <v>-15.5</v>
+        <v>-15.2</v>
       </c>
       <c r="E146" t="n">
-        <v>22.9</v>
+        <v>19.2</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>7.4</v>
+        <v>0.2</v>
       </c>
       <c r="D147" t="n">
-        <v>-15.2</v>
+        <v>-18.3</v>
       </c>
       <c r="E147" t="n">
-        <v>22.6</v>
+        <v>18.4</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="D148" t="n">
-        <v>-20.6</v>
+        <v>-15.2</v>
       </c>
       <c r="E148" t="n">
-        <v>22.5</v>
+        <v>17.2</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C149" t="n">
         <v>1.9</v>
       </c>
       <c r="D149" t="n">
-        <v>-20.6</v>
+        <v>-15.2</v>
       </c>
       <c r="E149" t="n">
-        <v>22.5</v>
+        <v>17.1</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>6.9</v>
+        <v>17.1</v>
       </c>
       <c r="D150" t="n">
-        <v>-15.5</v>
+        <v>0.2</v>
       </c>
       <c r="E150" t="n">
-        <v>22.3</v>
+        <v>16.9</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="D151" t="n">
-        <v>-15.2</v>
+        <v>0.2</v>
       </c>
       <c r="E151" t="n">
-        <v>22</v>
+        <v>16.8</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -5980,397 +5980,397 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="D152" t="n">
-        <v>-19.3</v>
+        <v>-15.2</v>
       </c>
       <c r="E152" t="n">
-        <v>21.3</v>
+        <v>15.4</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
           <t>TRMD</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>MPCC</t>
-        </is>
-      </c>
       <c r="C153" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D153" t="n">
         <v>1.9</v>
       </c>
-      <c r="D153" t="n">
-        <v>-19.3</v>
-      </c>
       <c r="E153" t="n">
-        <v>21.2</v>
+        <v>15.2</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>31.1</v>
+        <v>17.1</v>
       </c>
       <c r="D154" t="n">
-        <v>10.2</v>
+        <v>2</v>
       </c>
       <c r="E154" t="n">
-        <v>20.9</v>
+        <v>15</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
           <t>TRMD</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>FRO</t>
-        </is>
-      </c>
       <c r="C155" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D155" t="n">
         <v>1.9</v>
       </c>
-      <c r="D155" t="n">
-        <v>-18.9</v>
-      </c>
       <c r="E155" t="n">
-        <v>20.8</v>
+        <v>15</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0.2</v>
+        <v>16.9</v>
       </c>
       <c r="D156" t="n">
-        <v>-20.6</v>
+        <v>2</v>
       </c>
       <c r="E156" t="n">
-        <v>20.8</v>
+        <v>14.9</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1.9</v>
+        <v>17.1</v>
       </c>
       <c r="D157" t="n">
-        <v>-18.9</v>
+        <v>4.1</v>
       </c>
       <c r="E157" t="n">
-        <v>20.8</v>
+        <v>13</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>31.1</v>
+        <v>16.9</v>
       </c>
       <c r="D158" t="n">
-        <v>10.9</v>
+        <v>4.1</v>
       </c>
       <c r="E158" t="n">
-        <v>20.2</v>
+        <v>12.9</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>4.1</v>
+        <v>12.2</v>
       </c>
       <c r="D159" t="n">
-        <v>-15.5</v>
+        <v>0.2</v>
       </c>
       <c r="E159" t="n">
-        <v>19.5</v>
+        <v>12.1</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
+          <t>CMBT (WHOLE-CO)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
           <t>ASC</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>MPCC</t>
-        </is>
-      </c>
       <c r="C160" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="D160" t="n">
         <v>0.2</v>
       </c>
-      <c r="D160" t="n">
-        <v>-19.3</v>
-      </c>
       <c r="E160" t="n">
-        <v>19.5</v>
+        <v>11.1</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>4.1</v>
+        <v>17.1</v>
       </c>
       <c r="D161" t="n">
-        <v>-15.2</v>
+        <v>6.5</v>
       </c>
       <c r="E161" t="n">
-        <v>19.2</v>
+        <v>10.6</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>0.2</v>
+        <v>16.9</v>
       </c>
       <c r="D162" t="n">
-        <v>-18.9</v>
+        <v>6.5</v>
       </c>
       <c r="E162" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
+          <t>BRUT</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
           <t>TRMD</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>DHT</t>
-        </is>
-      </c>
       <c r="C163" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D163" t="n">
         <v>1.9</v>
       </c>
-      <c r="D163" t="n">
-        <v>-15.5</v>
-      </c>
       <c r="E163" t="n">
-        <v>17.4</v>
+        <v>10.3</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1.9</v>
+        <v>17.1</v>
       </c>
       <c r="D164" t="n">
-        <v>-15.5</v>
+        <v>6.9</v>
       </c>
       <c r="E164" t="n">
-        <v>17.4</v>
+        <v>10.2</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1.9</v>
+        <v>12.2</v>
       </c>
       <c r="D165" t="n">
-        <v>-15.2</v>
+        <v>2</v>
       </c>
       <c r="E165" t="n">
-        <v>17.1</v>
+        <v>10.2</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1.9</v>
+        <v>16.9</v>
       </c>
       <c r="D166" t="n">
-        <v>-15.2</v>
+        <v>6.9</v>
       </c>
       <c r="E166" t="n">
-        <v>17.1</v>
+        <v>10.1</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6379,310 +6379,310 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>17.1</v>
+        <v>10.2</v>
       </c>
       <c r="D167" t="n">
         <v>0.2</v>
       </c>
       <c r="E167" t="n">
-        <v>16.9</v>
+        <v>10</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="D168" t="n">
-        <v>0.2</v>
+        <v>7.4</v>
       </c>
       <c r="E168" t="n">
-        <v>16.8</v>
+        <v>9.6</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>0.2</v>
+        <v>16.9</v>
       </c>
       <c r="D169" t="n">
-        <v>-15.5</v>
+        <v>7.4</v>
       </c>
       <c r="E169" t="n">
-        <v>15.7</v>
+        <v>9.5</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0.2</v>
+        <v>11.3</v>
       </c>
       <c r="D170" t="n">
-        <v>-15.2</v>
+        <v>1.9</v>
       </c>
       <c r="E170" t="n">
-        <v>15.4</v>
+        <v>9.4</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>17.1</v>
+        <v>11.3</v>
       </c>
       <c r="D171" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="E171" t="n">
-        <v>15.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>46.3</v>
+        <v>10.2</v>
       </c>
       <c r="D172" t="n">
-        <v>31.1</v>
+        <v>1.9</v>
       </c>
       <c r="E172" t="n">
-        <v>15.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>17.1</v>
+        <v>-15.2</v>
       </c>
       <c r="D173" t="n">
-        <v>1.9</v>
+        <v>-23.5</v>
       </c>
       <c r="E173" t="n">
-        <v>15.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>16.9</v>
+        <v>10.2</v>
       </c>
       <c r="D174" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="E174" t="n">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>16.9</v>
+        <v>12.2</v>
       </c>
       <c r="D175" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="E175" t="n">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>31.1</v>
+        <v>-15.2</v>
       </c>
       <c r="D176" t="n">
-        <v>16.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E176" t="n">
-        <v>14.2</v>
+        <v>7.7</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>31.1</v>
+        <v>-15.2</v>
       </c>
       <c r="D177" t="n">
-        <v>17.1</v>
+        <v>-22.5</v>
       </c>
       <c r="E177" t="n">
-        <v>14.1</v>
+        <v>7.3</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>17.1</v>
+        <v>7.4</v>
       </c>
       <c r="D178" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="E178" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6691,102 +6691,102 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>16.9</v>
+        <v>11.3</v>
       </c>
       <c r="D179" t="n">
         <v>4.1</v>
       </c>
       <c r="E179" t="n">
-        <v>12.9</v>
+        <v>7.2</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>10.9</v>
+        <v>17.1</v>
       </c>
       <c r="D180" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="E180" t="n">
-        <v>10.8</v>
+        <v>6.9</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="D181" t="n">
-        <v>6.9</v>
+        <v>10.2</v>
       </c>
       <c r="E181" t="n">
-        <v>10.2</v>
+        <v>6.7</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="D182" t="n">
-        <v>6.9</v>
+        <v>0.2</v>
       </c>
       <c r="E182" t="n">
-        <v>10.1</v>
+        <v>6.7</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6795,128 +6795,128 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>10.2</v>
+        <v>6.5</v>
       </c>
       <c r="D183" t="n">
         <v>0.2</v>
       </c>
       <c r="E183" t="n">
-        <v>10</v>
+        <v>6.3</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>17.1</v>
+        <v>10.2</v>
       </c>
       <c r="D184" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="E184" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (product vs lng)</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="D185" t="n">
-        <v>7.4</v>
+        <v>11.3</v>
       </c>
       <c r="E185" t="n">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>10.9</v>
+        <v>12.2</v>
       </c>
       <c r="D186" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="E186" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
+          <t>CMDB</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
           <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>GNK</t>
-        </is>
-      </c>
       <c r="C187" t="n">
-        <v>10.9</v>
+        <v>16.9</v>
       </c>
       <c r="D187" t="n">
-        <v>1.9</v>
+        <v>11.3</v>
       </c>
       <c r="E187" t="n">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6925,24 +6925,24 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>10.2</v>
+        <v>7.4</v>
       </c>
       <c r="D188" t="n">
         <v>1.9</v>
       </c>
       <c r="E188" t="n">
-        <v>8.300000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6951,43 +6951,43 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>10.2</v>
+        <v>7.4</v>
       </c>
       <c r="D189" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="E189" t="n">
-        <v>8.300000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>-15.2</v>
+        <v>12.2</v>
       </c>
       <c r="D190" t="n">
-        <v>-22.8</v>
+        <v>6.9</v>
       </c>
       <c r="E190" t="n">
-        <v>7.7</v>
+        <v>5.4</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
@@ -6999,47 +6999,47 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>-15.5</v>
+        <v>-18.3</v>
       </c>
       <c r="D191" t="n">
-        <v>-22.8</v>
+        <v>-23.5</v>
       </c>
       <c r="E191" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="D192" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="E192" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
@@ -7051,147 +7051,147 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="C193" t="n">
         <v>17.1</v>
       </c>
       <c r="D193" t="n">
-        <v>10.2</v>
+        <v>12.2</v>
       </c>
       <c r="E193" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="D194" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="E194" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>16.9</v>
+        <v>12.2</v>
       </c>
       <c r="D195" t="n">
-        <v>10.2</v>
+        <v>7.4</v>
       </c>
       <c r="E195" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>6.9</v>
+        <v>11.3</v>
       </c>
       <c r="D196" t="n">
-        <v>0.2</v>
+        <v>6.5</v>
       </c>
       <c r="E196" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>10.2</v>
+        <v>16.9</v>
       </c>
       <c r="D197" t="n">
-        <v>4.1</v>
+        <v>12.2</v>
       </c>
       <c r="E197" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>17.1</v>
+        <v>-18.3</v>
       </c>
       <c r="D198" t="n">
-        <v>10.9</v>
+        <v>-22.8</v>
       </c>
       <c r="E198" t="n">
-        <v>6.1</v>
+        <v>4.6</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -7202,241 +7202,241 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>16.9</v>
+        <v>6.5</v>
       </c>
       <c r="D199" t="n">
-        <v>10.9</v>
+        <v>1.9</v>
       </c>
       <c r="E199" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="D200" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="E200" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>7.4</v>
+        <v>11.3</v>
       </c>
       <c r="D201" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="E201" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>-15.2</v>
+        <v>-18.3</v>
       </c>
       <c r="D202" t="n">
-        <v>-20.6</v>
+        <v>-22.5</v>
       </c>
       <c r="E202" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>-15.5</v>
+        <v>-15.2</v>
       </c>
       <c r="D203" t="n">
-        <v>-20.6</v>
+        <v>-19.3</v>
       </c>
       <c r="E203" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>6.9</v>
+        <v>-19.3</v>
       </c>
       <c r="D204" t="n">
-        <v>1.9</v>
+        <v>-23.5</v>
       </c>
       <c r="E204" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>6.9</v>
+        <v>4.1</v>
       </c>
       <c r="D205" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="E205" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>-15.2</v>
+        <v>11.3</v>
       </c>
       <c r="D206" t="n">
-        <v>-19.3</v>
+        <v>7.4</v>
       </c>
       <c r="E206" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="D207" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="E207" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7445,76 +7445,76 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>-18.9</v>
+        <v>-19.3</v>
       </c>
       <c r="D208" t="n">
         <v>-22.8</v>
       </c>
       <c r="E208" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>-15.5</v>
+        <v>7.4</v>
       </c>
       <c r="D209" t="n">
-        <v>-19.3</v>
+        <v>4.1</v>
       </c>
       <c r="E209" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (containerships vs lng)</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>4.1</v>
+        <v>10.2</v>
       </c>
       <c r="D210" t="n">
-        <v>0.2</v>
+        <v>6.9</v>
       </c>
       <c r="E210" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7523,50 +7523,50 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>-15.2</v>
+        <v>-19.3</v>
       </c>
       <c r="D211" t="n">
-        <v>-18.9</v>
+        <v>-22.5</v>
       </c>
       <c r="E211" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>-19.3</v>
+        <v>-15.2</v>
       </c>
       <c r="D212" t="n">
-        <v>-22.8</v>
+        <v>-18.3</v>
       </c>
       <c r="E212" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7575,43 +7575,43 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="D213" t="n">
         <v>7.4</v>
       </c>
       <c r="E213" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>-15.5</v>
+        <v>6.9</v>
       </c>
       <c r="D214" t="n">
-        <v>-18.9</v>
+        <v>4.1</v>
       </c>
       <c r="E214" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
@@ -7627,13 +7627,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>76.8</v>
+        <v>75.7</v>
       </c>
       <c r="D215" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="E215" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -7653,221 +7653,221 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="D216" t="n">
         <v>4.1</v>
       </c>
       <c r="E216" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs lng)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>10.2</v>
+        <v>4.1</v>
       </c>
       <c r="D217" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="E217" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>10.2</v>
+        <v>4.1</v>
       </c>
       <c r="D218" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="E218" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>6.9</v>
+        <v>12.2</v>
       </c>
       <c r="D219" t="n">
-        <v>4.1</v>
+        <v>10.2</v>
       </c>
       <c r="E219" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>-20.6</v>
+        <v>2</v>
       </c>
       <c r="D220" t="n">
-        <v>-22.8</v>
+        <v>0.2</v>
       </c>
       <c r="E220" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="D221" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="E221" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>4.1</v>
+        <v>-18.3</v>
       </c>
       <c r="D222" t="n">
-        <v>1.9</v>
+        <v>-19.3</v>
       </c>
       <c r="E222" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>-18.9</v>
+        <v>11.3</v>
       </c>
       <c r="D223" t="n">
-        <v>-20.6</v>
+        <v>10.2</v>
       </c>
       <c r="E223" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1.9</v>
+        <v>-22.5</v>
       </c>
       <c r="D224" t="n">
-        <v>0.2</v>
+        <v>-23.5</v>
       </c>
       <c r="E224" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -7878,78 +7878,78 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="D225" t="n">
-        <v>0.2</v>
+        <v>6.5</v>
       </c>
       <c r="E225" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>-19.3</v>
+        <v>12.2</v>
       </c>
       <c r="D226" t="n">
-        <v>-20.6</v>
+        <v>11.3</v>
       </c>
       <c r="E226" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>10.9</v>
+        <v>-22.8</v>
       </c>
       <c r="D227" t="n">
-        <v>10.2</v>
+        <v>-23.5</v>
       </c>
       <c r="E227" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -7987,47 +7987,47 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>-18.9</v>
+        <v>-22.5</v>
       </c>
       <c r="D229" t="n">
-        <v>-19.3</v>
+        <v>-22.8</v>
       </c>
       <c r="E229" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>-15.2</v>
+        <v>6.9</v>
       </c>
       <c r="D230" t="n">
-        <v>-15.5</v>
+        <v>6.5</v>
       </c>
       <c r="E230" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -8069,13 +8069,13 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="D232" t="n">
         <v>1.9</v>
       </c>
       <c r="E232" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -510,12 +510,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -524,31 +524,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36.72</v>
+        <v>5.21</v>
       </c>
       <c r="E2" t="n">
-        <v>83.45</v>
+        <v>17.74</v>
       </c>
       <c r="F2" t="n">
-        <v>68.47</v>
+        <v>13.18</v>
       </c>
       <c r="G2" t="n">
-        <v>44.4</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>40.56</v>
+        <v>0.63</v>
       </c>
       <c r="I2" t="n">
-        <v>64.54000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="J2" t="n">
-        <v>127.3</v>
+        <v>240.6</v>
       </c>
       <c r="K2" t="n">
-        <v>10.5</v>
+        <v>-87.90000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>75.7</v>
+        <v>107.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -559,12 +559,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -573,31 +573,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>67.98999999999999</v>
+        <v>35.76</v>
       </c>
       <c r="E3" t="n">
-        <v>94.77</v>
+        <v>84.64</v>
       </c>
       <c r="F3" t="n">
-        <v>81.78</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>64.56999999999999</v>
+        <v>45.06</v>
       </c>
       <c r="H3" t="n">
-        <v>62.29</v>
+        <v>41.19</v>
       </c>
       <c r="I3" t="n">
-        <v>79.59</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>39.4</v>
+        <v>136.7</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.4</v>
+        <v>15.2</v>
       </c>
       <c r="L3" t="n">
-        <v>17.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,31 +622,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.34</v>
+        <v>12.73</v>
       </c>
       <c r="E4" t="n">
-        <v>11.9</v>
+        <v>24.54</v>
       </c>
       <c r="F4" t="n">
-        <v>7.99</v>
+        <v>19.43</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.46</v>
+        <v>8.4</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.63</v>
+        <v>7.27</v>
       </c>
       <c r="I4" t="n">
-        <v>5.99</v>
+        <v>17.26</v>
       </c>
       <c r="J4" t="n">
-        <v>122.9</v>
+        <v>92.7</v>
       </c>
       <c r="K4" t="n">
-        <v>-149.2</v>
+        <v>-42.9</v>
       </c>
       <c r="L4" t="n">
-        <v>12.2</v>
+        <v>35.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -657,12 +657,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -671,31 +671,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.1</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>21.61</v>
+        <v>94.77</v>
       </c>
       <c r="F5" t="n">
-        <v>16.15</v>
+        <v>81.78</v>
       </c>
       <c r="G5" t="n">
-        <v>10.88</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>8.85</v>
+        <v>62.29</v>
       </c>
       <c r="I5" t="n">
-        <v>15.69</v>
+        <v>79.59</v>
       </c>
       <c r="J5" t="n">
-        <v>53.3</v>
+        <v>43.6</v>
       </c>
       <c r="K5" t="n">
-        <v>-37.2</v>
+        <v>-5.6</v>
       </c>
       <c r="L5" t="n">
-        <v>11.3</v>
+        <v>20.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -706,12 +706,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.79</v>
+        <v>14.08</v>
       </c>
       <c r="E6" t="n">
-        <v>20.11</v>
+        <v>22.07</v>
       </c>
       <c r="F6" t="n">
-        <v>15.49</v>
+        <v>16.56</v>
       </c>
       <c r="G6" t="n">
-        <v>5.75</v>
+        <v>11.15</v>
       </c>
       <c r="H6" t="n">
-        <v>4.85</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>13.62</v>
+        <v>16.07</v>
       </c>
       <c r="J6" t="n">
-        <v>57.3</v>
+        <v>56.7</v>
       </c>
       <c r="K6" t="n">
-        <v>-62.1</v>
+        <v>-35.3</v>
       </c>
       <c r="L6" t="n">
-        <v>6.5</v>
+        <v>14.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -769,31 +769,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.65</v>
+        <v>17.08</v>
       </c>
       <c r="E7" t="n">
-        <v>18.84</v>
+        <v>19.44</v>
       </c>
       <c r="F7" t="n">
-        <v>15.52</v>
+        <v>16.05</v>
       </c>
       <c r="G7" t="n">
-        <v>9.41</v>
+        <v>9.77</v>
       </c>
       <c r="H7" t="n">
-        <v>8.630000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>14.42</v>
+        <v>14.92</v>
       </c>
       <c r="J7" t="n">
-        <v>6.7</v>
+        <v>13.8</v>
       </c>
       <c r="K7" t="n">
-        <v>-51.1</v>
+        <v>-47.5</v>
       </c>
       <c r="L7" t="n">
-        <v>-18.3</v>
+        <v>-12.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>35.52</v>
+        <v>35.44</v>
       </c>
       <c r="E8" t="n">
-        <v>38.69</v>
+        <v>40.26</v>
       </c>
       <c r="F8" t="n">
-        <v>30.44</v>
+        <v>31.83</v>
       </c>
       <c r="G8" t="n">
-        <v>14.69</v>
+        <v>15.62</v>
       </c>
       <c r="H8" t="n">
-        <v>12.65</v>
+        <v>13.52</v>
       </c>
       <c r="I8" t="n">
-        <v>27.53</v>
+        <v>28.82</v>
       </c>
       <c r="J8" t="n">
-        <v>8.9</v>
+        <v>13.6</v>
       </c>
       <c r="K8" t="n">
-        <v>-64.40000000000001</v>
+        <v>-61.9</v>
       </c>
       <c r="L8" t="n">
-        <v>-22.5</v>
+        <v>-18.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -853,12 +853,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -867,31 +867,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79.51000000000001</v>
+        <v>49.6</v>
       </c>
       <c r="E9" t="n">
-        <v>77.87</v>
+        <v>55.8</v>
       </c>
       <c r="F9" t="n">
-        <v>65.86</v>
+        <v>44.06</v>
       </c>
       <c r="G9" t="n">
-        <v>42.3</v>
+        <v>22.35</v>
       </c>
       <c r="H9" t="n">
-        <v>38.53</v>
+        <v>19.73</v>
       </c>
       <c r="I9" t="n">
-        <v>61.34</v>
+        <v>40.17</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1</v>
+        <v>12.5</v>
       </c>
       <c r="K9" t="n">
-        <v>-51.5</v>
+        <v>-60.2</v>
       </c>
       <c r="L9" t="n">
-        <v>-22.8</v>
+        <v>-19</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -902,12 +902,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -916,31 +916,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>49.88</v>
+        <v>77.81</v>
       </c>
       <c r="E10" t="n">
-        <v>53.4</v>
+        <v>77.87</v>
       </c>
       <c r="F10" t="n">
-        <v>41.93</v>
+        <v>65.86</v>
       </c>
       <c r="G10" t="n">
-        <v>20.88</v>
+        <v>42.3</v>
       </c>
       <c r="H10" t="n">
-        <v>18.34</v>
+        <v>38.53</v>
       </c>
       <c r="I10" t="n">
-        <v>38.18</v>
+        <v>61.34</v>
       </c>
       <c r="J10" t="n">
-        <v>7.1</v>
+        <v>0.1</v>
       </c>
       <c r="K10" t="n">
-        <v>-63.2</v>
+        <v>-50.5</v>
       </c>
       <c r="L10" t="n">
-        <v>-23.5</v>
+        <v>-21.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.85</v>
+        <v>5.78</v>
       </c>
       <c r="E11" t="n">
         <v>4.07</v>
@@ -983,13 +983,13 @@
         <v>2.78</v>
       </c>
       <c r="J11" t="n">
-        <v>-30.4</v>
+        <v>-29.6</v>
       </c>
       <c r="K11" t="n">
-        <v>-80.3</v>
+        <v>-80.09999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-52.5</v>
+        <v>-51.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.71</v>
+        <v>20.87</v>
       </c>
       <c r="E2" t="n">
         <v>49.7</v>
@@ -1149,13 +1149,13 @@
         <v>35.91</v>
       </c>
       <c r="K2" t="n">
-        <v>140</v>
+        <v>138.1</v>
       </c>
       <c r="L2" t="n">
-        <v>-62.3</v>
+        <v>-62.6</v>
       </c>
       <c r="M2" t="n">
-        <v>73.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.48</v>
+        <v>29.29</v>
       </c>
       <c r="E3" t="n">
         <v>39.36</v>
@@ -1207,13 +1207,13 @@
         <v>30.67</v>
       </c>
       <c r="K3" t="n">
-        <v>33.5</v>
+        <v>34.4</v>
       </c>
       <c r="L3" t="n">
-        <v>-45.3</v>
+        <v>-45</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>72.58</v>
+        <v>70.09</v>
       </c>
       <c r="E2" t="n">
         <v>105.66</v>
@@ -1367,13 +1367,13 @@
         <v>79.98999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>45.6</v>
+        <v>50.7</v>
       </c>
       <c r="L2" t="n">
-        <v>-34.2</v>
+        <v>-31.9</v>
       </c>
       <c r="M2" t="n">
-        <v>10.2</v>
+        <v>14.1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26.81</v>
+        <v>26.31</v>
       </c>
       <c r="E3" t="n">
         <v>40.58</v>
@@ -1419,13 +1419,13 @@
         <v>27.32</v>
       </c>
       <c r="K3" t="n">
-        <v>51.4</v>
+        <v>54.3</v>
       </c>
       <c r="L3" t="n">
-        <v>-58.9</v>
+        <v>-58.1</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.12</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
         <v>18.21</v>
@@ -1471,17 +1471,17 @@
         <v>15.15</v>
       </c>
       <c r="K4" t="n">
-        <v>20.4</v>
+        <v>13.8</v>
       </c>
       <c r="L4" t="n">
-        <v>-37.7</v>
+        <v>-41.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2</v>
+        <v>-5.3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.97</v>
+        <v>6.86</v>
       </c>
       <c r="E5" t="n">
         <v>8.58</v>
@@ -1523,13 +1523,13 @@
         <v>5.91</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>-61</v>
+        <v>-60.4</v>
       </c>
       <c r="M5" t="n">
-        <v>-15.2</v>
+        <v>-13.8</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.39</v>
+        <v>6.36</v>
       </c>
       <c r="E2" t="n">
         <v>12.08</v>
@@ -1668,13 +1668,13 @@
         <v>9.67</v>
       </c>
       <c r="J2" t="n">
-        <v>89</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>18.6</v>
+        <v>19.1</v>
       </c>
       <c r="L2" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.47</v>
+        <v>17.99</v>
       </c>
       <c r="E3" t="n">
         <v>24.44</v>
@@ -1717,13 +1717,13 @@
         <v>20.43</v>
       </c>
       <c r="J3" t="n">
-        <v>39.9</v>
+        <v>35.9</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.5</v>
+        <v>-7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>16.9</v>
+        <v>13.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24.4</v>
+        <v>24.64</v>
       </c>
       <c r="E4" t="n">
         <v>32.75</v>
@@ -1766,13 +1766,13 @@
         <v>26.07</v>
       </c>
       <c r="J4" t="n">
-        <v>34.2</v>
+        <v>32.9</v>
       </c>
       <c r="K4" t="n">
-        <v>-18.5</v>
+        <v>-19.3</v>
       </c>
       <c r="L4" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23.57</v>
+        <v>24.39</v>
       </c>
       <c r="E5" t="n">
         <v>30.41</v>
@@ -1815,13 +1815,13 @@
         <v>24.05</v>
       </c>
       <c r="J5" t="n">
-        <v>29</v>
+        <v>24.7</v>
       </c>
       <c r="K5" t="n">
-        <v>-21.8</v>
+        <v>-24.4</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>-1.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>37.79</v>
+        <v>37.74</v>
       </c>
       <c r="E2" t="n">
         <v>44.45</v>
@@ -1960,13 +1960,13 @@
         <v>40.59</v>
       </c>
       <c r="J2" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.3</v>
+        <v>-4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="E3" t="n">
         <v>2.26</v>
@@ -2009,13 +2009,13 @@
         <v>2.11</v>
       </c>
       <c r="J3" t="n">
-        <v>-13.6</v>
+        <v>-13.9</v>
       </c>
       <c r="K3" t="n">
-        <v>-34.2</v>
+        <v>-34.4</v>
       </c>
       <c r="L3" t="n">
-        <v>-19.3</v>
+        <v>-19.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2089,24 +2089,24 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>75.7</v>
+        <v>107.4</v>
       </c>
       <c r="D2" t="n">
-        <v>-52.5</v>
+        <v>-51.9</v>
       </c>
       <c r="E2" t="n">
-        <v>128.2</v>
+        <v>159.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2115,91 +2115,91 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>73.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>-52.5</v>
+        <v>-51.9</v>
       </c>
       <c r="E3" t="n">
-        <v>125.8</v>
+        <v>135</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>51.3</v>
+        <v>107.4</v>
       </c>
       <c r="D4" t="n">
-        <v>-52.5</v>
+        <v>-21.2</v>
       </c>
       <c r="E4" t="n">
-        <v>103.8</v>
+        <v>128.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>75.7</v>
+        <v>107.4</v>
       </c>
       <c r="D5" t="n">
-        <v>-23.5</v>
+        <v>-19.6</v>
       </c>
       <c r="E5" t="n">
-        <v>99.2</v>
+        <v>127.1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>75.7</v>
+        <v>107.4</v>
       </c>
       <c r="D6" t="n">
-        <v>-22.8</v>
+        <v>-19</v>
       </c>
       <c r="E6" t="n">
-        <v>98.59999999999999</v>
+        <v>126.4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2219,17 +2219,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>75.7</v>
+        <v>107.4</v>
       </c>
       <c r="D7" t="n">
-        <v>-22.5</v>
+        <v>-18.7</v>
       </c>
       <c r="E7" t="n">
-        <v>98.2</v>
+        <v>126.1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2241,17 +2241,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>73.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="D8" t="n">
-        <v>-23.5</v>
+        <v>-51.9</v>
       </c>
       <c r="E8" t="n">
-        <v>96.8</v>
+        <v>123.9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2262,241 +2262,241 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>73.40000000000001</v>
+        <v>107.4</v>
       </c>
       <c r="D9" t="n">
-        <v>-22.8</v>
+        <v>-13.8</v>
       </c>
       <c r="E9" t="n">
-        <v>96.2</v>
+        <v>121.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>73.40000000000001</v>
+        <v>107.4</v>
       </c>
       <c r="D10" t="n">
-        <v>-22.5</v>
+        <v>-12.7</v>
       </c>
       <c r="E10" t="n">
-        <v>95.90000000000001</v>
+        <v>120.1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>75.7</v>
+        <v>107.4</v>
       </c>
       <c r="D11" t="n">
-        <v>-19.3</v>
+        <v>-5.3</v>
       </c>
       <c r="E11" t="n">
-        <v>95.09999999999999</v>
+        <v>112.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>75.7</v>
+        <v>107.4</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.3</v>
+        <v>-1.4</v>
       </c>
       <c r="E12" t="n">
-        <v>94</v>
+        <v>108.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>73.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.3</v>
+        <v>-21.2</v>
       </c>
       <c r="E13" t="n">
-        <v>92.7</v>
+        <v>104.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>73.40000000000001</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.3</v>
+        <v>-51.9</v>
       </c>
       <c r="E14" t="n">
-        <v>91.59999999999999</v>
+        <v>103.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>75.7</v>
+        <v>107.4</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.2</v>
+        <v>3.8</v>
       </c>
       <c r="E15" t="n">
-        <v>90.90000000000001</v>
+        <v>103.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>73.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>-15.2</v>
+        <v>-19.6</v>
       </c>
       <c r="E16" t="n">
-        <v>88.5</v>
+        <v>102.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>75.7</v>
+        <v>107.4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="E17" t="n">
-        <v>75.59999999999999</v>
+        <v>102.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2505,95 +2505,95 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>51.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>-23.5</v>
+        <v>-19</v>
       </c>
       <c r="E18" t="n">
-        <v>74.8</v>
+        <v>102.2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>51.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>-22.8</v>
+        <v>-18.7</v>
       </c>
       <c r="E19" t="n">
-        <v>74.2</v>
+        <v>101.8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>75.7</v>
+        <v>107.4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="E20" t="n">
-        <v>73.8</v>
+        <v>101.6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>51.3</v>
+        <v>107.4</v>
       </c>
       <c r="D21" t="n">
-        <v>-22.5</v>
+        <v>7.6</v>
       </c>
       <c r="E21" t="n">
-        <v>73.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
@@ -2605,333 +2605,333 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>75.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>-13.8</v>
       </c>
       <c r="E22" t="n">
-        <v>73.7</v>
+        <v>97</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>73.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2</v>
+        <v>-12.7</v>
       </c>
       <c r="E23" t="n">
-        <v>73.2</v>
+        <v>95.8</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>75.7</v>
+        <v>107.4</v>
       </c>
       <c r="D24" t="n">
-        <v>4.1</v>
+        <v>13.6</v>
       </c>
       <c r="E24" t="n">
-        <v>71.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>73.40000000000001</v>
+        <v>107.4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.9</v>
+        <v>14.1</v>
       </c>
       <c r="E25" t="n">
-        <v>71.5</v>
+        <v>93.3</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>73.40000000000001</v>
+        <v>107.4</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>14.1</v>
       </c>
       <c r="E26" t="n">
-        <v>71.3</v>
+        <v>93.3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>51.3</v>
+        <v>72</v>
       </c>
       <c r="D27" t="n">
-        <v>-19.3</v>
+        <v>-21.2</v>
       </c>
       <c r="E27" t="n">
-        <v>70.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>51.3</v>
+        <v>72</v>
       </c>
       <c r="D28" t="n">
-        <v>-18.3</v>
+        <v>-19.6</v>
       </c>
       <c r="E28" t="n">
-        <v>69.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17.1</v>
+        <v>72</v>
       </c>
       <c r="D29" t="n">
-        <v>-52.5</v>
+        <v>-19</v>
       </c>
       <c r="E29" t="n">
-        <v>69.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.9</v>
+        <v>72</v>
       </c>
       <c r="D30" t="n">
-        <v>-52.5</v>
+        <v>-18.7</v>
       </c>
       <c r="E30" t="n">
-        <v>69.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>73.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>4.1</v>
+        <v>-5.3</v>
       </c>
       <c r="E31" t="n">
-        <v>69.3</v>
+        <v>88.5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>75.7</v>
+        <v>35.6</v>
       </c>
       <c r="D32" t="n">
-        <v>6.5</v>
+        <v>-51.9</v>
       </c>
       <c r="E32" t="n">
-        <v>69.3</v>
+        <v>87.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>75.7</v>
+        <v>107.4</v>
       </c>
       <c r="D33" t="n">
-        <v>6.9</v>
+        <v>20.6</v>
       </c>
       <c r="E33" t="n">
-        <v>68.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>75.7</v>
+        <v>72</v>
       </c>
       <c r="D34" t="n">
-        <v>7.4</v>
+        <v>-13.8</v>
       </c>
       <c r="E34" t="n">
-        <v>68.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
@@ -2943,17 +2943,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>73.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>6.5</v>
+        <v>-12.7</v>
       </c>
       <c r="E35" t="n">
-        <v>66.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2964,130 +2964,130 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>73.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>6.9</v>
+        <v>-1.4</v>
       </c>
       <c r="E36" t="n">
-        <v>66.5</v>
+        <v>84.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>51.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-15.2</v>
+        <v>3.8</v>
       </c>
       <c r="E37" t="n">
-        <v>66.5</v>
+        <v>79.3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>73.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="E38" t="n">
-        <v>65.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>75.7</v>
+        <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>10.2</v>
+        <v>-5.3</v>
       </c>
       <c r="E39" t="n">
-        <v>65.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>-52.5</v>
+        <v>5.8</v>
       </c>
       <c r="E40" t="n">
-        <v>64.7</v>
+        <v>77.3</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3099,255 +3099,255 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>75.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>11.3</v>
+        <v>7.6</v>
       </c>
       <c r="E41" t="n">
-        <v>64.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11.3</v>
+        <v>72</v>
       </c>
       <c r="D42" t="n">
-        <v>-52.5</v>
+        <v>-1.4</v>
       </c>
       <c r="E42" t="n">
-        <v>63.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>75.7</v>
+        <v>52</v>
       </c>
       <c r="D43" t="n">
-        <v>12.2</v>
+        <v>-21.2</v>
       </c>
       <c r="E43" t="n">
-        <v>63.5</v>
+        <v>73.2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>73.40000000000001</v>
+        <v>20.6</v>
       </c>
       <c r="D44" t="n">
-        <v>10.2</v>
+        <v>-51.9</v>
       </c>
       <c r="E44" t="n">
-        <v>63.2</v>
+        <v>72.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10.2</v>
+        <v>107.4</v>
       </c>
       <c r="D45" t="n">
-        <v>-52.5</v>
+        <v>35.6</v>
       </c>
       <c r="E45" t="n">
-        <v>62.7</v>
+        <v>71.8</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>73.40000000000001</v>
+        <v>52</v>
       </c>
       <c r="D46" t="n">
-        <v>11.3</v>
+        <v>-19.6</v>
       </c>
       <c r="E46" t="n">
-        <v>62.1</v>
+        <v>71.7</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>73.40000000000001</v>
+        <v>52</v>
       </c>
       <c r="D47" t="n">
-        <v>12.2</v>
+        <v>-19</v>
       </c>
       <c r="E47" t="n">
-        <v>61.1</v>
+        <v>71</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7.4</v>
+        <v>52</v>
       </c>
       <c r="D48" t="n">
-        <v>-52.5</v>
+        <v>-18.7</v>
       </c>
       <c r="E48" t="n">
-        <v>59.9</v>
+        <v>70.7</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6.9</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>-52.5</v>
+        <v>13.6</v>
       </c>
       <c r="E49" t="n">
-        <v>59.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>-52.5</v>
+        <v>14.1</v>
       </c>
       <c r="E50" t="n">
-        <v>58.9</v>
+        <v>69</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -3359,73 +3359,73 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>75.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>16.9</v>
+        <v>14.1</v>
       </c>
       <c r="E51" t="n">
-        <v>58.8</v>
+        <v>69</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>75.7</v>
+        <v>72</v>
       </c>
       <c r="D52" t="n">
-        <v>17.1</v>
+        <v>3.8</v>
       </c>
       <c r="E52" t="n">
-        <v>58.7</v>
+        <v>68.2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
       <c r="C53" t="n">
-        <v>4.1</v>
+        <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>-52.5</v>
+        <v>4.7</v>
       </c>
       <c r="E53" t="n">
-        <v>56.5</v>
+        <v>67.3</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3437,17 +3437,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>73.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="D54" t="n">
-        <v>16.9</v>
+        <v>5.8</v>
       </c>
       <c r="E54" t="n">
-        <v>56.4</v>
+        <v>66.2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3458,33 +3458,33 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>73.40000000000001</v>
+        <v>14.1</v>
       </c>
       <c r="D55" t="n">
-        <v>17.1</v>
+        <v>-51.9</v>
       </c>
       <c r="E55" t="n">
-        <v>56.3</v>
+        <v>66</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3493,50 +3493,50 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>14.1</v>
       </c>
       <c r="D56" t="n">
-        <v>-52.5</v>
+        <v>-51.9</v>
       </c>
       <c r="E56" t="n">
-        <v>54.5</v>
+        <v>66</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.9</v>
+        <v>52</v>
       </c>
       <c r="D57" t="n">
-        <v>-52.5</v>
+        <v>-13.8</v>
       </c>
       <c r="E57" t="n">
-        <v>54.4</v>
+        <v>65.8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3545,17 +3545,17 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.2</v>
+        <v>13.6</v>
       </c>
       <c r="D58" t="n">
-        <v>-52.5</v>
+        <v>-51.9</v>
       </c>
       <c r="E58" t="n">
-        <v>52.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -3567,522 +3567,522 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2</v>
+        <v>-12.7</v>
       </c>
       <c r="E59" t="n">
-        <v>51.1</v>
+        <v>64.7</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>51.3</v>
+        <v>72</v>
       </c>
       <c r="D60" t="n">
-        <v>1.9</v>
+        <v>7.6</v>
       </c>
       <c r="E60" t="n">
-        <v>49.4</v>
+        <v>64.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>51.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>20.6</v>
       </c>
       <c r="E61" t="n">
-        <v>49.3</v>
+        <v>62.5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>51.3</v>
+        <v>7.6</v>
       </c>
       <c r="D62" t="n">
-        <v>4.1</v>
+        <v>-51.9</v>
       </c>
       <c r="E62" t="n">
-        <v>47.3</v>
+        <v>59.4</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>51.3</v>
+        <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>6.5</v>
+        <v>13.6</v>
       </c>
       <c r="E63" t="n">
-        <v>44.8</v>
+        <v>58.5</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>51.3</v>
+        <v>72</v>
       </c>
       <c r="D64" t="n">
-        <v>6.9</v>
+        <v>14.1</v>
       </c>
       <c r="E64" t="n">
-        <v>44.4</v>
+        <v>57.9</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>51.3</v>
+        <v>72</v>
       </c>
       <c r="D65" t="n">
-        <v>7.4</v>
+        <v>14.1</v>
       </c>
       <c r="E65" t="n">
-        <v>43.9</v>
+        <v>57.9</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>51.3</v>
+        <v>5.8</v>
       </c>
       <c r="D66" t="n">
-        <v>10.2</v>
+        <v>-51.9</v>
       </c>
       <c r="E66" t="n">
-        <v>41.1</v>
+        <v>57.7</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>17.1</v>
+        <v>52</v>
       </c>
       <c r="D67" t="n">
-        <v>-23.5</v>
+        <v>-5.3</v>
       </c>
       <c r="E67" t="n">
-        <v>40.5</v>
+        <v>57.4</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>16.9</v>
+        <v>35.6</v>
       </c>
       <c r="D68" t="n">
-        <v>-23.5</v>
+        <v>-21.2</v>
       </c>
       <c r="E68" t="n">
-        <v>40.4</v>
+        <v>56.7</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>51.3</v>
+        <v>4.7</v>
       </c>
       <c r="D69" t="n">
-        <v>11.3</v>
+        <v>-51.9</v>
       </c>
       <c r="E69" t="n">
-        <v>40</v>
+        <v>56.6</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>17.1</v>
+        <v>3.8</v>
       </c>
       <c r="D70" t="n">
-        <v>-22.8</v>
+        <v>-51.9</v>
       </c>
       <c r="E70" t="n">
-        <v>39.9</v>
+        <v>55.7</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>16.9</v>
+        <v>107.4</v>
       </c>
       <c r="D71" t="n">
-        <v>-22.8</v>
+        <v>52</v>
       </c>
       <c r="E71" t="n">
-        <v>39.8</v>
+        <v>55.4</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>17.1</v>
+        <v>35.6</v>
       </c>
       <c r="D72" t="n">
-        <v>-22.5</v>
+        <v>-19.6</v>
       </c>
       <c r="E72" t="n">
-        <v>39.5</v>
+        <v>55.2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>16.9</v>
+        <v>35.6</v>
       </c>
       <c r="D73" t="n">
-        <v>-22.5</v>
+        <v>-19</v>
       </c>
       <c r="E73" t="n">
-        <v>39.4</v>
+        <v>54.6</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>51.3</v>
+        <v>35.6</v>
       </c>
       <c r="D74" t="n">
-        <v>12.2</v>
+        <v>-18.7</v>
       </c>
       <c r="E74" t="n">
-        <v>39.1</v>
+        <v>54.3</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-15.2</v>
+        <v>52</v>
       </c>
       <c r="D75" t="n">
-        <v>-52.5</v>
+        <v>-1.4</v>
       </c>
       <c r="E75" t="n">
-        <v>37.3</v>
+        <v>53.4</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>CCEC</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>TNK</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>MPCC</t>
-        </is>
-      </c>
       <c r="C76" t="n">
-        <v>17.1</v>
+        <v>72</v>
       </c>
       <c r="D76" t="n">
-        <v>-19.3</v>
+        <v>20.6</v>
       </c>
       <c r="E76" t="n">
-        <v>36.4</v>
+        <v>51.4</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>16.9</v>
+        <v>-1.4</v>
       </c>
       <c r="D77" t="n">
-        <v>-19.3</v>
+        <v>-51.9</v>
       </c>
       <c r="E77" t="n">
-        <v>36.3</v>
+        <v>50.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>12.2</v>
+        <v>35.6</v>
       </c>
       <c r="D78" t="n">
-        <v>-23.5</v>
+        <v>-13.8</v>
       </c>
       <c r="E78" t="n">
-        <v>35.7</v>
+        <v>49.4</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4091,13 +4091,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>17.1</v>
+        <v>35.6</v>
       </c>
       <c r="D79" t="n">
-        <v>-18.3</v>
+        <v>-12.7</v>
       </c>
       <c r="E79" t="n">
-        <v>35.3</v>
+        <v>48.2</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4108,48 +4108,48 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>16.9</v>
+        <v>52</v>
       </c>
       <c r="D80" t="n">
-        <v>-18.3</v>
+        <v>3.8</v>
       </c>
       <c r="E80" t="n">
-        <v>35.2</v>
+        <v>48.2</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>12.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D81" t="n">
-        <v>-22.8</v>
+        <v>35.6</v>
       </c>
       <c r="E81" t="n">
-        <v>35.1</v>
+        <v>47.6</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4160,52 +4160,52 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>11.3</v>
+        <v>52</v>
       </c>
       <c r="D82" t="n">
-        <v>-23.5</v>
+        <v>4.7</v>
       </c>
       <c r="E82" t="n">
-        <v>34.8</v>
+        <v>47.3</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>12.2</v>
+        <v>-5.3</v>
       </c>
       <c r="D83" t="n">
-        <v>-22.5</v>
+        <v>-51.9</v>
       </c>
       <c r="E83" t="n">
-        <v>34.7</v>
+        <v>46.5</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
@@ -4217,17 +4217,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="D84" t="n">
-        <v>16.9</v>
+        <v>5.8</v>
       </c>
       <c r="E84" t="n">
-        <v>34.4</v>
+        <v>46.2</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4243,106 +4243,106 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="D85" t="n">
-        <v>17.1</v>
+        <v>7.6</v>
       </c>
       <c r="E85" t="n">
-        <v>34.3</v>
+        <v>44.5</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-18.3</v>
+        <v>20.6</v>
       </c>
       <c r="D86" t="n">
-        <v>-52.5</v>
+        <v>-21.2</v>
       </c>
       <c r="E86" t="n">
-        <v>34.2</v>
+        <v>41.8</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>11.3</v>
+        <v>35.6</v>
       </c>
       <c r="D87" t="n">
-        <v>-22.8</v>
+        <v>-5.3</v>
       </c>
       <c r="E87" t="n">
-        <v>34.1</v>
+        <v>40.9</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>11.3</v>
+        <v>20.6</v>
       </c>
       <c r="D88" t="n">
-        <v>-22.5</v>
+        <v>-19.6</v>
       </c>
       <c r="E88" t="n">
-        <v>33.8</v>
+        <v>40.2</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4351,50 +4351,50 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10.2</v>
+        <v>20.6</v>
       </c>
       <c r="D89" t="n">
-        <v>-23.5</v>
+        <v>-19</v>
       </c>
       <c r="E89" t="n">
-        <v>33.7</v>
+        <v>39.6</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10.2</v>
+        <v>20.6</v>
       </c>
       <c r="D90" t="n">
-        <v>-22.8</v>
+        <v>-18.7</v>
       </c>
       <c r="E90" t="n">
-        <v>33.1</v>
+        <v>39.3</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4403,91 +4403,91 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-19.3</v>
+        <v>-12.7</v>
       </c>
       <c r="D91" t="n">
-        <v>-52.5</v>
+        <v>-51.9</v>
       </c>
       <c r="E91" t="n">
-        <v>33.1</v>
+        <v>39.2</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10.2</v>
+        <v>52</v>
       </c>
       <c r="D92" t="n">
-        <v>-22.5</v>
+        <v>13.6</v>
       </c>
       <c r="E92" t="n">
-        <v>32.7</v>
+        <v>38.5</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>17.1</v>
+        <v>-13.8</v>
       </c>
       <c r="D93" t="n">
-        <v>-15.2</v>
+        <v>-51.9</v>
       </c>
       <c r="E93" t="n">
-        <v>32.2</v>
+        <v>38.1</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>16.9</v>
+        <v>52</v>
       </c>
       <c r="D94" t="n">
-        <v>-15.2</v>
+        <v>14.1</v>
       </c>
       <c r="E94" t="n">
-        <v>32.1</v>
+        <v>37.9</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -4498,78 +4498,78 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>12.2</v>
+        <v>52</v>
       </c>
       <c r="D95" t="n">
-        <v>-19.3</v>
+        <v>14.1</v>
       </c>
       <c r="E95" t="n">
-        <v>31.6</v>
+        <v>37.9</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>7.4</v>
+        <v>35.6</v>
       </c>
       <c r="D96" t="n">
-        <v>-23.5</v>
+        <v>-1.4</v>
       </c>
       <c r="E96" t="n">
-        <v>30.9</v>
+        <v>37</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>11.3</v>
+        <v>72</v>
       </c>
       <c r="D97" t="n">
-        <v>-19.3</v>
+        <v>35.6</v>
       </c>
       <c r="E97" t="n">
-        <v>30.6</v>
+        <v>36.5</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
@@ -4581,54 +4581,54 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>12.2</v>
+        <v>107.4</v>
       </c>
       <c r="D98" t="n">
-        <v>-18.3</v>
+        <v>72</v>
       </c>
       <c r="E98" t="n">
-        <v>30.5</v>
+        <v>35.4</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6.9</v>
+        <v>14.1</v>
       </c>
       <c r="D99" t="n">
-        <v>-23.5</v>
+        <v>-21.2</v>
       </c>
       <c r="E99" t="n">
-        <v>30.3</v>
+        <v>35.3</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4637,180 +4637,180 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>7.4</v>
+        <v>14.1</v>
       </c>
       <c r="D100" t="n">
-        <v>-22.8</v>
+        <v>-21.2</v>
       </c>
       <c r="E100" t="n">
-        <v>30.3</v>
+        <v>35.3</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-22.5</v>
+        <v>13.6</v>
       </c>
       <c r="D101" t="n">
-        <v>-52.5</v>
+        <v>-21.2</v>
       </c>
       <c r="E101" t="n">
-        <v>30</v>
+        <v>34.7</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>6.5</v>
+        <v>20.6</v>
       </c>
       <c r="D102" t="n">
-        <v>-23.5</v>
+        <v>-13.8</v>
       </c>
       <c r="E102" t="n">
-        <v>29.9</v>
+        <v>34.4</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>7.4</v>
+        <v>14.1</v>
       </c>
       <c r="D103" t="n">
-        <v>-22.5</v>
+        <v>-19.6</v>
       </c>
       <c r="E103" t="n">
-        <v>29.9</v>
+        <v>33.8</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6.9</v>
+        <v>14.1</v>
       </c>
       <c r="D104" t="n">
-        <v>-22.8</v>
+        <v>-19.6</v>
       </c>
       <c r="E104" t="n">
-        <v>29.7</v>
+        <v>33.8</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-22.8</v>
+        <v>20.6</v>
       </c>
       <c r="D105" t="n">
-        <v>-52.5</v>
+        <v>-12.7</v>
       </c>
       <c r="E105" t="n">
-        <v>29.6</v>
+        <v>33.3</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>11.3</v>
+        <v>-18.7</v>
       </c>
       <c r="D106" t="n">
-        <v>-18.3</v>
+        <v>-51.9</v>
       </c>
       <c r="E106" t="n">
-        <v>29.6</v>
+        <v>33.2</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4819,65 +4819,65 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10.2</v>
+        <v>13.6</v>
       </c>
       <c r="D107" t="n">
-        <v>-19.3</v>
+        <v>-19.6</v>
       </c>
       <c r="E107" t="n">
-        <v>29.5</v>
+        <v>33.2</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6.9</v>
+        <v>14.1</v>
       </c>
       <c r="D108" t="n">
-        <v>-22.5</v>
+        <v>-19</v>
       </c>
       <c r="E108" t="n">
-        <v>29.3</v>
+        <v>33.1</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6.5</v>
+        <v>14.1</v>
       </c>
       <c r="D109" t="n">
-        <v>-22.8</v>
+        <v>-19</v>
       </c>
       <c r="E109" t="n">
-        <v>29.3</v>
+        <v>33.1</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -4897,13 +4897,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-23.5</v>
+        <v>-19</v>
       </c>
       <c r="D110" t="n">
-        <v>-52.5</v>
+        <v>-51.9</v>
       </c>
       <c r="E110" t="n">
-        <v>29</v>
+        <v>32.9</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4923,50 +4923,50 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>6.5</v>
+        <v>14.1</v>
       </c>
       <c r="D111" t="n">
-        <v>-22.5</v>
+        <v>-18.7</v>
       </c>
       <c r="E111" t="n">
-        <v>29</v>
+        <v>32.8</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>10.2</v>
+        <v>14.1</v>
       </c>
       <c r="D112" t="n">
-        <v>-18.3</v>
+        <v>-18.7</v>
       </c>
       <c r="E112" t="n">
-        <v>28.5</v>
+        <v>32.8</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4975,667 +4975,667 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4.1</v>
+        <v>13.6</v>
       </c>
       <c r="D113" t="n">
-        <v>-23.5</v>
+        <v>-19</v>
       </c>
       <c r="E113" t="n">
-        <v>27.5</v>
+        <v>32.6</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>12.2</v>
+        <v>13.6</v>
       </c>
       <c r="D114" t="n">
-        <v>-15.2</v>
+        <v>-18.7</v>
       </c>
       <c r="E114" t="n">
-        <v>27.4</v>
+        <v>32.2</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4.1</v>
+        <v>-19.6</v>
       </c>
       <c r="D115" t="n">
-        <v>-22.8</v>
+        <v>-51.9</v>
       </c>
       <c r="E115" t="n">
-        <v>26.9</v>
+        <v>32.2</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>7.4</v>
+        <v>35.6</v>
       </c>
       <c r="D116" t="n">
-        <v>-19.3</v>
+        <v>3.8</v>
       </c>
       <c r="E116" t="n">
-        <v>26.7</v>
+        <v>31.7</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4.1</v>
+        <v>52</v>
       </c>
       <c r="D117" t="n">
-        <v>-22.5</v>
+        <v>20.6</v>
       </c>
       <c r="E117" t="n">
-        <v>26.5</v>
+        <v>31.4</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>11.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D118" t="n">
-        <v>-15.2</v>
+        <v>52</v>
       </c>
       <c r="E118" t="n">
-        <v>26.5</v>
+        <v>31.1</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6.9</v>
+        <v>35.6</v>
       </c>
       <c r="D119" t="n">
-        <v>-19.3</v>
+        <v>4.7</v>
       </c>
       <c r="E119" t="n">
-        <v>26.2</v>
+        <v>30.9</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>6.5</v>
+        <v>-21.2</v>
       </c>
       <c r="D120" t="n">
-        <v>-19.3</v>
+        <v>-51.9</v>
       </c>
       <c r="E120" t="n">
-        <v>25.8</v>
+        <v>30.7</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>7.4</v>
+        <v>35.6</v>
       </c>
       <c r="D121" t="n">
-        <v>-18.3</v>
+        <v>5.8</v>
       </c>
       <c r="E121" t="n">
-        <v>25.7</v>
+        <v>29.8</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="D122" t="n">
-        <v>-23.5</v>
+        <v>-21.2</v>
       </c>
       <c r="E122" t="n">
-        <v>25.5</v>
+        <v>28.7</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>10.2</v>
+        <v>35.6</v>
       </c>
       <c r="D123" t="n">
-        <v>-15.2</v>
+        <v>7.6</v>
       </c>
       <c r="E123" t="n">
-        <v>25.4</v>
+        <v>28</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1.9</v>
+        <v>14.1</v>
       </c>
       <c r="D124" t="n">
-        <v>-23.5</v>
+        <v>-13.8</v>
       </c>
       <c r="E124" t="n">
-        <v>25.4</v>
+        <v>27.9</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>6.9</v>
+        <v>14.1</v>
       </c>
       <c r="D125" t="n">
-        <v>-18.3</v>
+        <v>-13.8</v>
       </c>
       <c r="E125" t="n">
-        <v>25.1</v>
+        <v>27.9</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>13.6</v>
       </c>
       <c r="D126" t="n">
-        <v>-22.8</v>
+        <v>-13.8</v>
       </c>
       <c r="E126" t="n">
-        <v>24.9</v>
+        <v>27.4</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1.9</v>
+        <v>7.6</v>
       </c>
       <c r="D127" t="n">
-        <v>-22.8</v>
+        <v>-19.6</v>
       </c>
       <c r="E127" t="n">
-        <v>24.8</v>
+        <v>27.2</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="D128" t="n">
-        <v>-18.3</v>
+        <v>-21.2</v>
       </c>
       <c r="E128" t="n">
-        <v>24.7</v>
+        <v>27</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>14.1</v>
       </c>
       <c r="D129" t="n">
-        <v>-22.5</v>
+        <v>-12.7</v>
       </c>
       <c r="E129" t="n">
-        <v>24.5</v>
+        <v>26.8</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1.9</v>
+        <v>14.1</v>
       </c>
       <c r="D130" t="n">
-        <v>-22.5</v>
+        <v>-12.7</v>
       </c>
       <c r="E130" t="n">
-        <v>24.4</v>
+        <v>26.8</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>75.7</v>
+        <v>7.6</v>
       </c>
       <c r="D131" t="n">
-        <v>51.3</v>
+        <v>-19</v>
       </c>
       <c r="E131" t="n">
-        <v>24.4</v>
+        <v>26.6</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.2</v>
+        <v>13.6</v>
       </c>
       <c r="D132" t="n">
-        <v>-23.5</v>
+        <v>-12.7</v>
       </c>
       <c r="E132" t="n">
-        <v>23.6</v>
+        <v>26.2</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="D133" t="n">
-        <v>-19.3</v>
+        <v>-18.7</v>
       </c>
       <c r="E133" t="n">
-        <v>23.4</v>
+        <v>26.2</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs containerships)</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>TNK</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
           <t>ASC</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>INSW (WHOLE-CO)</t>
-        </is>
-      </c>
       <c r="C134" t="n">
-        <v>0.2</v>
+        <v>20.6</v>
       </c>
       <c r="D134" t="n">
-        <v>-22.8</v>
+        <v>-5.3</v>
       </c>
       <c r="E134" t="n">
-        <v>23</v>
+        <v>25.9</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="D135" t="n">
-        <v>-22.5</v>
+        <v>-21.2</v>
       </c>
       <c r="E135" t="n">
-        <v>22.7</v>
+        <v>25.9</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="D136" t="n">
-        <v>-15.2</v>
+        <v>-19.6</v>
       </c>
       <c r="E136" t="n">
-        <v>22.6</v>
+        <v>25.5</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="D137" t="n">
-        <v>-18.3</v>
+        <v>-21.2</v>
       </c>
       <c r="E137" t="n">
-        <v>22.3</v>
+        <v>25</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs crude)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>73.40000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="D138" t="n">
-        <v>51.3</v>
+        <v>-19</v>
       </c>
       <c r="E138" t="n">
-        <v>22.1</v>
+        <v>24.8</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
@@ -5647,433 +5647,433 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="D139" t="n">
-        <v>-15.2</v>
+        <v>-18.7</v>
       </c>
       <c r="E139" t="n">
-        <v>22</v>
+        <v>24.5</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="D140" t="n">
-        <v>-15.2</v>
+        <v>-19.6</v>
       </c>
       <c r="E140" t="n">
-        <v>21.6</v>
+        <v>24.4</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>107.4</v>
       </c>
       <c r="D141" t="n">
-        <v>-19.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="E141" t="n">
-        <v>21.4</v>
+        <v>24.3</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="D142" t="n">
-        <v>-19.3</v>
+        <v>-19</v>
       </c>
       <c r="E142" t="n">
-        <v>21.2</v>
+        <v>23.7</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="D143" t="n">
-        <v>-18.3</v>
+        <v>-19.6</v>
       </c>
       <c r="E143" t="n">
-        <v>20.3</v>
+        <v>23.5</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="D144" t="n">
-        <v>-18.3</v>
+        <v>-18.7</v>
       </c>
       <c r="E144" t="n">
-        <v>20.2</v>
+        <v>23.4</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="D145" t="n">
-        <v>-19.3</v>
+        <v>-19</v>
       </c>
       <c r="E145" t="n">
-        <v>19.5</v>
+        <v>22.9</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="D146" t="n">
-        <v>-15.2</v>
+        <v>-18.7</v>
       </c>
       <c r="E146" t="n">
-        <v>19.2</v>
+        <v>22.5</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.2</v>
+        <v>20.6</v>
       </c>
       <c r="D147" t="n">
-        <v>-18.3</v>
+        <v>-1.4</v>
       </c>
       <c r="E147" t="n">
-        <v>18.4</v>
+        <v>22</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>35.6</v>
       </c>
       <c r="D148" t="n">
-        <v>-15.2</v>
+        <v>13.6</v>
       </c>
       <c r="E148" t="n">
-        <v>17.2</v>
+        <v>22</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1.9</v>
+        <v>35.6</v>
       </c>
       <c r="D149" t="n">
-        <v>-15.2</v>
+        <v>14.1</v>
       </c>
       <c r="E149" t="n">
-        <v>17.1</v>
+        <v>21.5</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>17.1</v>
+        <v>35.6</v>
       </c>
       <c r="D150" t="n">
-        <v>0.2</v>
+        <v>14.1</v>
       </c>
       <c r="E150" t="n">
-        <v>16.9</v>
+        <v>21.5</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>16.9</v>
+        <v>7.6</v>
       </c>
       <c r="D151" t="n">
-        <v>0.2</v>
+        <v>-13.8</v>
       </c>
       <c r="E151" t="n">
-        <v>16.8</v>
+        <v>21.4</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0.2</v>
+        <v>7.6</v>
       </c>
       <c r="D152" t="n">
-        <v>-15.2</v>
+        <v>-12.7</v>
       </c>
       <c r="E152" t="n">
-        <v>15.4</v>
+        <v>20.2</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (containerships vs crude)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>17.1</v>
+        <v>72</v>
       </c>
       <c r="D153" t="n">
-        <v>1.9</v>
+        <v>52</v>
       </c>
       <c r="E153" t="n">
-        <v>15.2</v>
+        <v>20</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>17.1</v>
+        <v>-1.4</v>
       </c>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>-21.2</v>
       </c>
       <c r="E154" t="n">
-        <v>15</v>
+        <v>19.8</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>16.9</v>
+        <v>5.8</v>
       </c>
       <c r="D155" t="n">
-        <v>1.9</v>
+        <v>-13.8</v>
       </c>
       <c r="E155" t="n">
-        <v>15</v>
+        <v>19.6</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -6084,22 +6084,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>16.9</v>
+        <v>14.1</v>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>-5.3</v>
       </c>
       <c r="E156" t="n">
-        <v>14.9</v>
+        <v>19.5</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -6110,26 +6110,26 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>17.1</v>
+        <v>14.1</v>
       </c>
       <c r="D157" t="n">
-        <v>4.1</v>
+        <v>-5.3</v>
       </c>
       <c r="E157" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
@@ -6141,340 +6141,340 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>16.9</v>
+        <v>13.6</v>
       </c>
       <c r="D158" t="n">
-        <v>4.1</v>
+        <v>-5.3</v>
       </c>
       <c r="E158" t="n">
-        <v>12.9</v>
+        <v>18.9</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>12.2</v>
+        <v>4.7</v>
       </c>
       <c r="D159" t="n">
-        <v>0.2</v>
+        <v>-13.8</v>
       </c>
       <c r="E159" t="n">
-        <v>12.1</v>
+        <v>18.5</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>11.3</v>
+        <v>5.8</v>
       </c>
       <c r="D160" t="n">
-        <v>0.2</v>
+        <v>-12.7</v>
       </c>
       <c r="E160" t="n">
-        <v>11.1</v>
+        <v>18.5</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>17.1</v>
+        <v>-1.4</v>
       </c>
       <c r="D161" t="n">
-        <v>6.5</v>
+        <v>-19.6</v>
       </c>
       <c r="E161" t="n">
-        <v>10.6</v>
+        <v>18.3</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>16.9</v>
+        <v>3.8</v>
       </c>
       <c r="D162" t="n">
-        <v>6.5</v>
+        <v>-13.8</v>
       </c>
       <c r="E162" t="n">
-        <v>10.5</v>
+        <v>17.7</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>12.2</v>
+        <v>-1.4</v>
       </c>
       <c r="D163" t="n">
-        <v>1.9</v>
+        <v>-19</v>
       </c>
       <c r="E163" t="n">
-        <v>10.3</v>
+        <v>17.6</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>17.1</v>
+        <v>4.7</v>
       </c>
       <c r="D164" t="n">
-        <v>6.9</v>
+        <v>-12.7</v>
       </c>
       <c r="E164" t="n">
-        <v>10.2</v>
+        <v>17.4</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (lng vs crude)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>12.2</v>
+        <v>-1.4</v>
       </c>
       <c r="D165" t="n">
-        <v>2</v>
+        <v>-18.7</v>
       </c>
       <c r="E165" t="n">
-        <v>10.2</v>
+        <v>17.3</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>16.9</v>
+        <v>20.6</v>
       </c>
       <c r="D166" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="E166" t="n">
-        <v>10.1</v>
+        <v>16.8</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>10.2</v>
+        <v>3.8</v>
       </c>
       <c r="D167" t="n">
-        <v>0.2</v>
+        <v>-12.7</v>
       </c>
       <c r="E167" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>17.1</v>
+        <v>52</v>
       </c>
       <c r="D168" t="n">
-        <v>7.4</v>
+        <v>35.6</v>
       </c>
       <c r="E168" t="n">
-        <v>9.6</v>
+        <v>16.4</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>16.9</v>
+        <v>20.6</v>
       </c>
       <c r="D169" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="E169" t="n">
-        <v>9.5</v>
+        <v>15.9</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
+          <t>MIXED SECTOR (crude vs lng)</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>11.3</v>
+        <v>-5.3</v>
       </c>
       <c r="D170" t="n">
-        <v>1.9</v>
+        <v>-21.2</v>
       </c>
       <c r="E170" t="n">
-        <v>9.4</v>
+        <v>15.8</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6483,76 +6483,76 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>11.3</v>
+        <v>14.1</v>
       </c>
       <c r="D171" t="n">
-        <v>2</v>
+        <v>-1.4</v>
       </c>
       <c r="E171" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>10.2</v>
+        <v>14.1</v>
       </c>
       <c r="D172" t="n">
-        <v>1.9</v>
+        <v>-1.4</v>
       </c>
       <c r="E172" t="n">
-        <v>8.300000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>-15.2</v>
+        <v>35.6</v>
       </c>
       <c r="D173" t="n">
-        <v>-23.5</v>
+        <v>20.6</v>
       </c>
       <c r="E173" t="n">
-        <v>8.300000000000001</v>
+        <v>15</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6561,91 +6561,91 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>10.2</v>
+        <v>13.6</v>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>-1.4</v>
       </c>
       <c r="E174" t="n">
-        <v>8.199999999999999</v>
+        <v>14.9</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>12.2</v>
+        <v>20.6</v>
       </c>
       <c r="D175" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="E175" t="n">
-        <v>8.199999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>-15.2</v>
+        <v>-5.3</v>
       </c>
       <c r="D176" t="n">
-        <v>-22.8</v>
+        <v>-19.6</v>
       </c>
       <c r="E176" t="n">
-        <v>7.7</v>
+        <v>14.3</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>-15.2</v>
+        <v>-5.3</v>
       </c>
       <c r="D177" t="n">
-        <v>-22.5</v>
+        <v>-19</v>
       </c>
       <c r="E177" t="n">
-        <v>7.3</v>
+        <v>13.7</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -6656,100 +6656,100 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>7.4</v>
+        <v>-5.3</v>
       </c>
       <c r="D178" t="n">
-        <v>0.2</v>
+        <v>-18.7</v>
       </c>
       <c r="E178" t="n">
-        <v>7.2</v>
+        <v>13.3</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>11.3</v>
+        <v>20.6</v>
       </c>
       <c r="D179" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="E179" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>17.1</v>
+        <v>7.6</v>
       </c>
       <c r="D180" t="n">
-        <v>10.2</v>
+        <v>-5.3</v>
       </c>
       <c r="E180" t="n">
-        <v>6.9</v>
+        <v>12.9</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>16.9</v>
+        <v>-1.4</v>
       </c>
       <c r="D181" t="n">
-        <v>10.2</v>
+        <v>-13.8</v>
       </c>
       <c r="E181" t="n">
-        <v>6.7</v>
+        <v>12.4</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -6760,33 +6760,33 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>6.9</v>
+        <v>-1.4</v>
       </c>
       <c r="D182" t="n">
-        <v>0.2</v>
+        <v>-12.7</v>
       </c>
       <c r="E182" t="n">
-        <v>6.7</v>
+        <v>11.3</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs crude)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6795,128 +6795,128 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="D183" t="n">
-        <v>0.2</v>
+        <v>-5.3</v>
       </c>
       <c r="E183" t="n">
-        <v>6.3</v>
+        <v>11.2</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TEN (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>10.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D184" t="n">
-        <v>4.1</v>
+        <v>72</v>
       </c>
       <c r="E184" t="n">
-        <v>6.2</v>
+        <v>11.1</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs lng)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>17.1</v>
+        <v>14.1</v>
       </c>
       <c r="D185" t="n">
-        <v>11.3</v>
+        <v>3.8</v>
       </c>
       <c r="E185" t="n">
-        <v>5.8</v>
+        <v>10.3</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>12.2</v>
+        <v>14.1</v>
       </c>
       <c r="D186" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="E186" t="n">
-        <v>5.8</v>
+        <v>10.3</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs product); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>16.9</v>
+        <v>4.7</v>
       </c>
       <c r="D187" t="n">
-        <v>11.3</v>
+        <v>-5.3</v>
       </c>
       <c r="E187" t="n">
-        <v>5.7</v>
+        <v>10.1</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (lng vs product)</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6925,91 +6925,91 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>7.4</v>
+        <v>13.6</v>
       </c>
       <c r="D188" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="E188" t="n">
-        <v>5.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs product)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>7.4</v>
+        <v>14.1</v>
       </c>
       <c r="D189" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="E189" t="n">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs lng)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>12.2</v>
+        <v>14.1</v>
       </c>
       <c r="D190" t="n">
-        <v>6.9</v>
+        <v>4.7</v>
       </c>
       <c r="E190" t="n">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>-18.3</v>
+        <v>3.8</v>
       </c>
       <c r="D191" t="n">
-        <v>-23.5</v>
+        <v>-5.3</v>
       </c>
       <c r="E191" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -7020,260 +7020,260 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="D192" t="n">
-        <v>1.9</v>
+        <v>-1.4</v>
       </c>
       <c r="E192" t="n">
-        <v>5</v>
+        <v>8.9</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>17.1</v>
+        <v>13.6</v>
       </c>
       <c r="D193" t="n">
-        <v>12.2</v>
+        <v>4.7</v>
       </c>
       <c r="E193" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs lng)</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>6.9</v>
+        <v>-12.7</v>
       </c>
       <c r="D194" t="n">
-        <v>2</v>
+        <v>-21.2</v>
       </c>
       <c r="E194" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>12.2</v>
+        <v>-5.3</v>
       </c>
       <c r="D195" t="n">
-        <v>7.4</v>
+        <v>-13.8</v>
       </c>
       <c r="E195" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>11.3</v>
+        <v>14.1</v>
       </c>
       <c r="D196" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="E196" t="n">
-        <v>4.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>16.9</v>
+        <v>14.1</v>
       </c>
       <c r="D197" t="n">
-        <v>12.2</v>
+        <v>5.8</v>
       </c>
       <c r="E197" t="n">
-        <v>4.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs crude)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>-18.3</v>
+        <v>13.6</v>
       </c>
       <c r="D198" t="n">
-        <v>-22.8</v>
+        <v>5.8</v>
       </c>
       <c r="E198" t="n">
-        <v>4.6</v>
+        <v>7.7</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>6.5</v>
+        <v>-13.8</v>
       </c>
       <c r="D199" t="n">
-        <v>1.9</v>
+        <v>-21.2</v>
       </c>
       <c r="E199" t="n">
-        <v>4.6</v>
+        <v>7.3</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED SECTOR (product vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>6.5</v>
+        <v>-5.3</v>
       </c>
       <c r="D200" t="n">
-        <v>2</v>
+        <v>-12.7</v>
       </c>
       <c r="E200" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>11.3</v>
+        <v>5.8</v>
       </c>
       <c r="D201" t="n">
-        <v>6.9</v>
+        <v>-1.4</v>
       </c>
       <c r="E201" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs dry_bulk); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -7285,255 +7285,255 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>-18.3</v>
+        <v>-12.7</v>
       </c>
       <c r="D202" t="n">
-        <v>-22.5</v>
+        <v>-19.6</v>
       </c>
       <c r="E202" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (crude vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>-15.2</v>
+        <v>20.6</v>
       </c>
       <c r="D203" t="n">
-        <v>-19.3</v>
+        <v>13.6</v>
       </c>
       <c r="E203" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (crude vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>-19.3</v>
+        <v>14.1</v>
       </c>
       <c r="D204" t="n">
-        <v>-23.5</v>
+        <v>7.6</v>
       </c>
       <c r="E204" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>4.1</v>
+        <v>14.1</v>
       </c>
       <c r="D205" t="n">
-        <v>0.2</v>
+        <v>7.6</v>
       </c>
       <c r="E205" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>11.3</v>
+        <v>20.6</v>
       </c>
       <c r="D206" t="n">
-        <v>7.4</v>
+        <v>14.1</v>
       </c>
       <c r="E206" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (crude vs product)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMBT (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>10.2</v>
+        <v>20.6</v>
       </c>
       <c r="D207" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="E207" t="n">
         <v>6.5</v>
       </c>
-      <c r="E207" t="n">
-        <v>3.7</v>
-      </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>INSW (WHOLE-CO)</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>-19.3</v>
+        <v>-12.7</v>
       </c>
       <c r="D208" t="n">
-        <v>-22.8</v>
+        <v>-19</v>
       </c>
       <c r="E208" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="D209" t="n">
-        <v>4.1</v>
+        <v>-1.4</v>
       </c>
       <c r="E209" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs lng)</t>
+          <t>MIXED SECTOR (lng vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>10.2</v>
+        <v>-12.7</v>
       </c>
       <c r="D210" t="n">
-        <v>6.9</v>
+        <v>-18.7</v>
       </c>
       <c r="E210" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs dry_bulk)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>-19.3</v>
+        <v>13.6</v>
       </c>
       <c r="D211" t="n">
-        <v>-22.5</v>
+        <v>7.6</v>
       </c>
       <c r="E211" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (containerships vs crude)</t>
+          <t>MIXED SECTOR (dry_bulk vs containerships)</t>
         </is>
       </c>
     </row>
@@ -7545,132 +7545,132 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>-15.2</v>
+        <v>-13.8</v>
       </c>
       <c r="D212" t="n">
-        <v>-18.3</v>
+        <v>-19.6</v>
       </c>
       <c r="E212" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs crude)</t>
+          <t>MIXED SECTOR (product vs containerships)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>10.2</v>
+        <v>-13.8</v>
       </c>
       <c r="D213" t="n">
-        <v>7.4</v>
+        <v>-19</v>
       </c>
       <c r="E213" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (product vs containerships)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="D214" t="n">
-        <v>4.1</v>
+        <v>-1.4</v>
       </c>
       <c r="E214" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs lng)</t>
+          <t>MIXED SECTOR (product vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TEN (WHOLE-CO)</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>75.7</v>
+        <v>-13.8</v>
       </c>
       <c r="D215" t="n">
-        <v>73.40000000000001</v>
+        <v>-18.7</v>
       </c>
       <c r="E215" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng); MIXED BASIS (crude sleeve vs whole-co)</t>
+          <t>MIXED SECTOR (product vs crude)</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>6.5</v>
+        <v>-1.4</v>
       </c>
       <c r="D216" t="n">
-        <v>4.1</v>
+        <v>-5.3</v>
       </c>
       <c r="E216" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs lng)</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -7679,407 +7679,407 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="D217" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="E217" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs product)</t>
+          <t>MIXED SECTOR (containerships vs product)</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>GNK</t>
-        </is>
-      </c>
       <c r="C218" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="D218" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="E218" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (lng vs dry_bulk)</t>
+          <t>MIXED SECTOR (containerships vs lng)</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>12.2</v>
+        <v>-18.7</v>
       </c>
       <c r="D219" t="n">
-        <v>10.2</v>
+        <v>-21.2</v>
       </c>
       <c r="E219" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2</v>
+        <v>-19</v>
       </c>
       <c r="D220" t="n">
-        <v>0.2</v>
+        <v>-21.2</v>
       </c>
       <c r="E220" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (dry_bulk vs product)</t>
+          <t>MIXED BASIS (crude sleeve vs whole-co)</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
           <t>TRMD</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>ASC</t>
-        </is>
-      </c>
       <c r="C221" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="D221" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="E221" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>MIXED SECTOR (dry_bulk vs product)</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>-18.3</v>
+        <v>7.6</v>
       </c>
       <c r="D222" t="n">
-        <v>-19.3</v>
+        <v>5.8</v>
       </c>
       <c r="E222" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>MIXED SECTOR (crude vs containerships)</t>
+          <t>MIXED SECTOR (containerships vs dry_bulk)</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CMBT (WHOLE-CO)</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>INSW (WHOLE-CO)</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>11.3</v>
+        <v>-19.6</v>
       </c>
       <c r="D223" t="n">